--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B1169E-D279-C448-A7E3-C467514A3824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91B26103-B86D-D644-808C-5144649A0435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13240" yWindow="760" windowWidth="16160" windowHeight="16500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -3305,9 +3305,6 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3363,6 +3360,9 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3764,7 +3764,7 @@
         <v>854</v>
       </c>
       <c r="B5" s="10"/>
-      <c r="C5" s="60" t="s">
+      <c r="C5" s="59" t="s">
         <v>855</v>
       </c>
       <c r="D5" s="10"/>
@@ -4210,7 +4210,7 @@
         <v>856</v>
       </c>
       <c r="B18" s="10"/>
-      <c r="C18" s="60" t="s">
+      <c r="C18" s="59" t="s">
         <v>857</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -4342,38 +4342,38 @@
       <c r="Z21" s="5"/>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="60" t="s">
         <v>859</v>
       </c>
-      <c r="B22" s="61"/>
-      <c r="C22" s="62" t="s">
+      <c r="B22" s="60"/>
+      <c r="C22" s="61" t="s">
         <v>860</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="D22" s="60" t="s">
         <v>859</v>
       </c>
-      <c r="E22" s="61"/>
-      <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="63"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="63"/>
-      <c r="L22" s="63"/>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="63"/>
-      <c r="Q22" s="63"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="63"/>
-      <c r="U22" s="63"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="63"/>
-      <c r="X22" s="63"/>
-      <c r="Y22" s="63"/>
-      <c r="Z22" s="63"/>
+      <c r="E22" s="60"/>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="62"/>
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
     </row>
     <row r="23" spans="1:26">
       <c r="A23" s="16" t="s">
@@ -4732,7 +4732,7 @@
       <c r="B33" s="10" t="s">
         <v>862</v>
       </c>
-      <c r="C33" s="64" t="s">
+      <c r="C33" s="63" t="s">
         <v>863</v>
       </c>
       <c r="D33" s="10" t="s">
@@ -5142,16 +5142,16 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" spans="1:26" ht="16">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="64" t="s">
         <v>865</v>
       </c>
-      <c r="B45" s="65" t="s">
+      <c r="B45" s="64" t="s">
         <v>865</v>
       </c>
-      <c r="C45" s="66" t="s">
+      <c r="C45" s="65" t="s">
         <v>866</v>
       </c>
-      <c r="D45" s="65" t="s">
+      <c r="D45" s="64" t="s">
         <v>867</v>
       </c>
       <c r="E45" s="6"/>
@@ -5318,40 +5318,40 @@
       <c r="Z49" s="5"/>
     </row>
     <row r="50" spans="1:26" ht="16">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="66" t="s">
         <v>868</v>
       </c>
-      <c r="B50" s="68" t="s">
+      <c r="B50" s="67" t="s">
         <v>868</v>
       </c>
-      <c r="C50" s="69" t="s">
+      <c r="C50" s="68" t="s">
         <v>869</v>
       </c>
-      <c r="D50" s="67" t="s">
+      <c r="D50" s="66" t="s">
         <v>868</v>
       </c>
-      <c r="E50" s="67"/>
-      <c r="F50" s="70"/>
-      <c r="G50" s="70"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="70"/>
-      <c r="J50" s="70"/>
-      <c r="K50" s="70"/>
-      <c r="L50" s="70"/>
-      <c r="M50" s="70"/>
-      <c r="N50" s="70"/>
-      <c r="O50" s="70"/>
-      <c r="P50" s="70"/>
-      <c r="Q50" s="70"/>
-      <c r="R50" s="70"/>
-      <c r="S50" s="70"/>
-      <c r="T50" s="70"/>
-      <c r="U50" s="70"/>
-      <c r="V50" s="70"/>
-      <c r="W50" s="70"/>
-      <c r="X50" s="70"/>
-      <c r="Y50" s="70"/>
-      <c r="Z50" s="70"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="69"/>
+      <c r="G50" s="69"/>
+      <c r="H50" s="69"/>
+      <c r="I50" s="69"/>
+      <c r="J50" s="69"/>
+      <c r="K50" s="69"/>
+      <c r="L50" s="69"/>
+      <c r="M50" s="69"/>
+      <c r="N50" s="69"/>
+      <c r="O50" s="69"/>
+      <c r="P50" s="69"/>
+      <c r="Q50" s="69"/>
+      <c r="R50" s="69"/>
+      <c r="S50" s="69"/>
+      <c r="T50" s="69"/>
+      <c r="U50" s="69"/>
+      <c r="V50" s="69"/>
+      <c r="W50" s="69"/>
+      <c r="X50" s="69"/>
+      <c r="Y50" s="69"/>
+      <c r="Z50" s="69"/>
     </row>
     <row r="51" spans="1:26">
       <c r="A51" s="12" t="s">
@@ -5634,40 +5634,40 @@
       <c r="Z58" s="2"/>
     </row>
     <row r="59" spans="1:26" ht="16">
-      <c r="A59" s="71" t="s">
+      <c r="A59" s="70" t="s">
         <v>870</v>
       </c>
-      <c r="B59" s="71" t="s">
+      <c r="B59" s="70" t="s">
         <v>871</v>
       </c>
-      <c r="C59" s="72" t="s">
+      <c r="C59" s="71" t="s">
         <v>872</v>
       </c>
-      <c r="D59" s="71" t="s">
+      <c r="D59" s="70" t="s">
         <v>870</v>
       </c>
-      <c r="E59" s="71"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
-      <c r="J59" s="73"/>
-      <c r="K59" s="73"/>
-      <c r="L59" s="73"/>
-      <c r="M59" s="73"/>
-      <c r="N59" s="73"/>
-      <c r="O59" s="73"/>
-      <c r="P59" s="73"/>
-      <c r="Q59" s="73"/>
-      <c r="R59" s="73"/>
-      <c r="S59" s="73"/>
-      <c r="T59" s="73"/>
-      <c r="U59" s="73"/>
-      <c r="V59" s="73"/>
-      <c r="W59" s="73"/>
-      <c r="X59" s="73"/>
-      <c r="Y59" s="73"/>
-      <c r="Z59" s="73"/>
+      <c r="E59" s="70"/>
+      <c r="F59" s="72"/>
+      <c r="G59" s="72"/>
+      <c r="H59" s="72"/>
+      <c r="I59" s="72"/>
+      <c r="J59" s="72"/>
+      <c r="K59" s="72"/>
+      <c r="L59" s="72"/>
+      <c r="M59" s="72"/>
+      <c r="N59" s="72"/>
+      <c r="O59" s="72"/>
+      <c r="P59" s="72"/>
+      <c r="Q59" s="72"/>
+      <c r="R59" s="72"/>
+      <c r="S59" s="72"/>
+      <c r="T59" s="72"/>
+      <c r="U59" s="72"/>
+      <c r="V59" s="72"/>
+      <c r="W59" s="72"/>
+      <c r="X59" s="72"/>
+      <c r="Y59" s="72"/>
+      <c r="Z59" s="72"/>
     </row>
     <row r="60" spans="1:26" ht="16">
       <c r="A60" s="10" t="s">
@@ -5676,7 +5676,7 @@
       <c r="B60" s="10" t="s">
         <v>874</v>
       </c>
-      <c r="C60" s="60" t="s">
+      <c r="C60" s="59" t="s">
         <v>875</v>
       </c>
       <c r="D60" s="10" t="s">
@@ -7420,7 +7420,7 @@
         <v>876</v>
       </c>
       <c r="B110" s="10"/>
-      <c r="C110" s="60" t="s">
+      <c r="C110" s="59" t="s">
         <v>877</v>
       </c>
       <c r="D110" s="10" t="s">
@@ -7698,7 +7698,7 @@
       <c r="B118" s="10" t="s">
         <v>880</v>
       </c>
-      <c r="C118" s="60" t="s">
+      <c r="C118" s="59" t="s">
         <v>881</v>
       </c>
       <c r="D118" s="10" t="s">
@@ -7908,7 +7908,7 @@
       <c r="B124" s="10" t="s">
         <v>883</v>
       </c>
-      <c r="C124" s="74" t="s">
+      <c r="C124" s="73" t="s">
         <v>884</v>
       </c>
       <c r="D124" s="10" t="s">
@@ -8014,7 +8014,7 @@
       <c r="B127" s="10" t="s">
         <v>887</v>
       </c>
-      <c r="C127" s="74" t="s">
+      <c r="C127" s="73" t="s">
         <v>888</v>
       </c>
       <c r="D127" s="10" t="s">
@@ -8224,7 +8224,7 @@
       <c r="B133" s="10" t="s">
         <v>890</v>
       </c>
-      <c r="C133" s="60" t="s">
+      <c r="C133" s="59" t="s">
         <v>891</v>
       </c>
       <c r="D133" s="10" t="s">
@@ -8578,7 +8578,7 @@
         <v>337</v>
       </c>
       <c r="B143" s="30"/>
-      <c r="C143" s="57" t="s">
+      <c r="C143" s="80" t="s">
         <v>841</v>
       </c>
       <c r="D143" s="6" t="s">
@@ -9102,7 +9102,7 @@
         <v>839</v>
       </c>
       <c r="B158" s="6"/>
-      <c r="C158" s="6" t="s">
+      <c r="C158" s="56" t="s">
         <v>840</v>
       </c>
       <c r="D158" s="6" t="s">
@@ -9240,76 +9240,76 @@
       <c r="Z161" s="2"/>
     </row>
     <row r="162" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A162" s="75" t="s">
+      <c r="A162" s="74" t="s">
         <v>893</v>
       </c>
-      <c r="B162" s="75" t="s">
+      <c r="B162" s="74" t="s">
         <v>893</v>
       </c>
-      <c r="C162" s="76" t="s">
+      <c r="C162" s="75" t="s">
         <v>730</v>
       </c>
-      <c r="D162" s="75" t="s">
+      <c r="D162" s="74" t="s">
         <v>893</v>
       </c>
-      <c r="E162" s="75"/>
-      <c r="F162" s="77"/>
-      <c r="G162" s="77"/>
-      <c r="H162" s="77"/>
-      <c r="I162" s="77"/>
-      <c r="J162" s="77"/>
-      <c r="K162" s="77"/>
-      <c r="L162" s="77"/>
-      <c r="M162" s="77"/>
-      <c r="N162" s="77"/>
-      <c r="O162" s="77"/>
-      <c r="P162" s="77"/>
-      <c r="Q162" s="77"/>
-      <c r="R162" s="77"/>
-      <c r="S162" s="77"/>
-      <c r="T162" s="77"/>
-      <c r="U162" s="77"/>
-      <c r="V162" s="77"/>
-      <c r="W162" s="77"/>
-      <c r="X162" s="77"/>
-      <c r="Y162" s="77"/>
-      <c r="Z162" s="77"/>
+      <c r="E162" s="74"/>
+      <c r="F162" s="76"/>
+      <c r="G162" s="76"/>
+      <c r="H162" s="76"/>
+      <c r="I162" s="76"/>
+      <c r="J162" s="76"/>
+      <c r="K162" s="76"/>
+      <c r="L162" s="76"/>
+      <c r="M162" s="76"/>
+      <c r="N162" s="76"/>
+      <c r="O162" s="76"/>
+      <c r="P162" s="76"/>
+      <c r="Q162" s="76"/>
+      <c r="R162" s="76"/>
+      <c r="S162" s="76"/>
+      <c r="T162" s="76"/>
+      <c r="U162" s="76"/>
+      <c r="V162" s="76"/>
+      <c r="W162" s="76"/>
+      <c r="X162" s="76"/>
+      <c r="Y162" s="76"/>
+      <c r="Z162" s="76"/>
     </row>
     <row r="163" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A163" s="75" t="s">
+      <c r="A163" s="74" t="s">
         <v>894</v>
       </c>
-      <c r="B163" s="75" t="s">
+      <c r="B163" s="74" t="s">
         <v>894</v>
       </c>
-      <c r="C163" s="76" t="s">
+      <c r="C163" s="75" t="s">
         <v>895</v>
       </c>
-      <c r="D163" s="75" t="s">
+      <c r="D163" s="74" t="s">
         <v>894</v>
       </c>
-      <c r="E163" s="75"/>
-      <c r="F163" s="77"/>
-      <c r="G163" s="77"/>
-      <c r="H163" s="77"/>
-      <c r="I163" s="77"/>
-      <c r="J163" s="77"/>
-      <c r="K163" s="77"/>
-      <c r="L163" s="77"/>
-      <c r="M163" s="77"/>
-      <c r="N163" s="77"/>
-      <c r="O163" s="77"/>
-      <c r="P163" s="77"/>
-      <c r="Q163" s="77"/>
-      <c r="R163" s="77"/>
-      <c r="S163" s="77"/>
-      <c r="T163" s="77"/>
-      <c r="U163" s="77"/>
-      <c r="V163" s="77"/>
-      <c r="W163" s="77"/>
-      <c r="X163" s="77"/>
-      <c r="Y163" s="77"/>
-      <c r="Z163" s="77"/>
+      <c r="E163" s="74"/>
+      <c r="F163" s="76"/>
+      <c r="G163" s="76"/>
+      <c r="H163" s="76"/>
+      <c r="I163" s="76"/>
+      <c r="J163" s="76"/>
+      <c r="K163" s="76"/>
+      <c r="L163" s="76"/>
+      <c r="M163" s="76"/>
+      <c r="N163" s="76"/>
+      <c r="O163" s="76"/>
+      <c r="P163" s="76"/>
+      <c r="Q163" s="76"/>
+      <c r="R163" s="76"/>
+      <c r="S163" s="76"/>
+      <c r="T163" s="76"/>
+      <c r="U163" s="76"/>
+      <c r="V163" s="76"/>
+      <c r="W163" s="76"/>
+      <c r="X163" s="76"/>
+      <c r="Y163" s="76"/>
+      <c r="Z163" s="76"/>
     </row>
     <row r="164" spans="1:26" ht="15.75" customHeight="1">
       <c r="A164" s="8" t="s">
@@ -9380,16 +9380,16 @@
       <c r="Z165" s="2"/>
     </row>
     <row r="166" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A166" s="75" t="s">
+      <c r="A166" s="74" t="s">
         <v>896</v>
       </c>
-      <c r="B166" s="75" t="s">
+      <c r="B166" s="74" t="s">
         <v>897</v>
       </c>
-      <c r="C166" s="76" t="s">
+      <c r="C166" s="75" t="s">
         <v>898</v>
       </c>
-      <c r="D166" s="75" t="s">
+      <c r="D166" s="74" t="s">
         <v>896</v>
       </c>
       <c r="E166" s="6"/>
@@ -9556,14 +9556,14 @@
       <c r="Z170" s="2"/>
     </row>
     <row r="171" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A171" s="75" t="s">
+      <c r="A171" s="74" t="s">
         <v>899</v>
       </c>
-      <c r="B171" s="75"/>
-      <c r="C171" s="76" t="s">
+      <c r="B171" s="74"/>
+      <c r="C171" s="75" t="s">
         <v>900</v>
       </c>
-      <c r="D171" s="75" t="s">
+      <c r="D171" s="74" t="s">
         <v>899</v>
       </c>
       <c r="E171" s="6"/>
@@ -9632,7 +9632,7 @@
       <c r="B173" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="C173" s="58" t="s">
+      <c r="C173" s="57" t="s">
         <v>408</v>
       </c>
       <c r="D173" s="6" t="s">
@@ -10188,7 +10188,7 @@
       <c r="B189" s="10" t="s">
         <v>902</v>
       </c>
-      <c r="C189" s="60" t="s">
+      <c r="C189" s="59" t="s">
         <v>903</v>
       </c>
       <c r="D189" s="10" t="s">
@@ -10224,7 +10224,7 @@
       <c r="B190" s="10" t="s">
         <v>905</v>
       </c>
-      <c r="C190" s="60" t="s">
+      <c r="C190" s="59" t="s">
         <v>906</v>
       </c>
       <c r="D190" s="10" t="s">
@@ -11374,7 +11374,7 @@
       <c r="B223" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="C223" s="59" t="s">
+      <c r="C223" s="58" t="s">
         <v>849</v>
       </c>
       <c r="D223" s="12" t="s">
@@ -11938,7 +11938,7 @@
       <c r="B239" s="10" t="s">
         <v>909</v>
       </c>
-      <c r="C239" s="60" t="s">
+      <c r="C239" s="59" t="s">
         <v>910</v>
       </c>
       <c r="D239" s="10" t="s">
@@ -12114,7 +12114,7 @@
         <v>911</v>
       </c>
       <c r="B244" s="10"/>
-      <c r="C244" s="60" t="s">
+      <c r="C244" s="59" t="s">
         <v>912</v>
       </c>
       <c r="D244" s="10" t="s">
@@ -12848,7 +12848,7 @@
       <c r="B265" s="16" t="s">
         <v>916</v>
       </c>
-      <c r="C265" s="78" t="s">
+      <c r="C265" s="77" t="s">
         <v>917</v>
       </c>
       <c r="D265" s="16" t="s">
@@ -12954,7 +12954,7 @@
       <c r="B268" s="16" t="s">
         <v>920</v>
       </c>
-      <c r="C268" s="78" t="s">
+      <c r="C268" s="77" t="s">
         <v>921</v>
       </c>
       <c r="D268" s="16" t="s">
@@ -13232,7 +13232,7 @@
       <c r="B276" s="16" t="s">
         <v>923</v>
       </c>
-      <c r="C276" s="78" t="s">
+      <c r="C276" s="77" t="s">
         <v>924</v>
       </c>
       <c r="D276" s="16" t="s">
@@ -15302,7 +15302,7 @@
       <c r="B335" s="10" t="s">
         <v>926</v>
       </c>
-      <c r="C335" s="60" t="s">
+      <c r="C335" s="59" t="s">
         <v>927</v>
       </c>
       <c r="D335" s="10" t="s">
@@ -15527,10 +15527,10 @@
       <c r="B342" s="10" t="s">
         <v>929</v>
       </c>
-      <c r="C342" s="79" t="s">
+      <c r="C342" s="78" t="s">
         <v>930</v>
       </c>
-      <c r="D342" s="80" t="s">
+      <c r="D342" s="79" t="s">
         <v>928</v>
       </c>
       <c r="E342" s="55"/>
@@ -21257,11 +21257,12 @@
     <hyperlink ref="C276" r:id="rId258" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
     <hyperlink ref="C335" r:id="rId259" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
     <hyperlink ref="C342" r:id="rId260" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C158" r:id="rId261" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId261"/>
+    <tablePart r:id="rId262"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA85A27-CA38-744C-B0AA-973ED790E3F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719103A6-69FF-9142-944B-F01A040CFF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3515,7 +3515,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3708,20 +3708,18 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3999,16 +3997,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="74" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1"/>
@@ -4034,26 +4032,26 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="16">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="78" t="s">
         <v>930</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80" t="s">
+      <c r="B3" s="78"/>
+      <c r="C3" s="78" t="s">
         <v>931</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>932</v>
       </c>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="78" t="s">
+      <c r="A4" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="78"/>
-      <c r="C4" s="79" t="s">
+      <c r="B4" s="76"/>
+      <c r="C4" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="78" t="s">
+      <c r="D4" s="76" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="2"/>
@@ -4721,7 +4719,7 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
     </row>
-    <row r="24" spans="1:25" s="75" customFormat="1" ht="16">
+    <row r="24" spans="1:25" ht="16">
       <c r="A24" s="7" t="s">
         <v>855</v>
       </c>
@@ -4732,27 +4730,27 @@
       <c r="D24" s="7" t="s">
         <v>857</v>
       </c>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
-      <c r="J24" s="74"/>
-      <c r="K24" s="74"/>
-      <c r="L24" s="74"/>
-      <c r="M24" s="74"/>
-      <c r="N24" s="74"/>
-      <c r="O24" s="74"/>
-      <c r="P24" s="74"/>
-      <c r="Q24" s="74"/>
-      <c r="R24" s="74"/>
-      <c r="S24" s="74"/>
-      <c r="T24" s="74"/>
-      <c r="U24" s="74"/>
-      <c r="V24" s="74"/>
-      <c r="W24" s="74"/>
-      <c r="X24" s="74"/>
-      <c r="Y24" s="74"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
     </row>
     <row r="25" spans="1:25" ht="16">
       <c r="A25" s="3" t="s">

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719103A6-69FF-9142-944B-F01A040CFF89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68763133-CCE0-5F45-83FA-B3E2633CBFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="1052">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1049">
   <si>
     <t>Name</t>
   </si>
@@ -2874,12 +2874,6 @@
     <t>https://www.geonames.org/11922367/duba.html</t>
   </si>
   <si>
-    <t>Havlíčkův Brod</t>
-  </si>
-  <si>
-    <t>https://www.geonames.org/11926135/havlickuv-brod.html</t>
-  </si>
-  <si>
     <t>Gablonz</t>
   </si>
   <si>
@@ -3021,15 +3015,6 @@
     <t>https://www.geonames.org/11922042/kdyne.html</t>
   </si>
   <si>
-    <t>Neuhaus</t>
-  </si>
-  <si>
-    <t>Jindřichův Hradec</t>
-  </si>
-  <si>
-    <t>https://www.geonames.org/11922066/jindrichuv-hradec.html</t>
-  </si>
-  <si>
     <t>Neustadt an der Mettau</t>
   </si>
   <si>
@@ -3184,6 +3169,12 @@
   </si>
   <si>
     <t>Schoenbrunn</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/276780/beyrouth.html</t>
+  </si>
+  <si>
+    <t>Beirut</t>
   </si>
 </sst>
 </file>
@@ -3515,7 +3506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3724,6 +3715,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -3774,9 +3768,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D390" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D390">
-    <sortCondition ref="D390"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D389" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D389">
+    <sortCondition ref="D389"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -3986,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Y1254"/>
+  <dimension ref="A2:Y1253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -4216,14 +4210,14 @@
     </row>
     <row r="9" spans="1:25" ht="16">
       <c r="A9" s="3" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -4249,16 +4243,16 @@
     </row>
     <row r="10" spans="1:25" ht="16">
       <c r="A10" s="3" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -4383,16 +4377,16 @@
     </row>
     <row r="14" spans="1:25" ht="16">
       <c r="A14" s="3" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -4952,82 +4946,82 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="1:25" ht="16">
-      <c r="A31" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
+    <row r="31" spans="1:25">
+      <c r="A31" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="11" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
     </row>
     <row r="32" spans="1:25" ht="16">
       <c r="A32" s="3" t="s">
-        <v>1043</v>
+        <v>56</v>
       </c>
       <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
-      <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="2"/>
-      <c r="X32" s="2"/>
-      <c r="Y32" s="2"/>
+      <c r="C32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+      <c r="Y32" s="1"/>
     </row>
     <row r="33" spans="1:25" ht="16">
-      <c r="A33" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B33" s="7"/>
-      <c r="C33" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>58</v>
+      <c r="A33" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>1038</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -5052,48 +5046,48 @@
       <c r="Y33" s="2"/>
     </row>
     <row r="34" spans="1:25" ht="16">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" s="7"/>
+      <c r="C34" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+    </row>
+    <row r="35" spans="1:25" ht="16">
+      <c r="A35" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="12" t="s">
+      <c r="B35" s="3"/>
+      <c r="C35" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-      <c r="Y34" s="1"/>
-    </row>
-    <row r="35" spans="1:25">
-      <c r="A35" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="9"/>
-      <c r="C35" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -5117,18 +5111,16 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:25" ht="16">
-      <c r="A36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>67</v>
+    <row r="36" spans="1:25">
+      <c r="A36" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>62</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
@@ -5152,18 +5144,18 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" spans="1:25">
-      <c r="A37" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="9" t="s">
+    <row r="37" spans="1:25" ht="16">
+      <c r="A37" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>68</v>
+      <c r="D37" s="3" t="s">
+        <v>67</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
@@ -5189,16 +5181,16 @@
     </row>
     <row r="38" spans="1:25">
       <c r="A38" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
@@ -5222,18 +5214,18 @@
       <c r="X38" s="1"/>
       <c r="Y38" s="1"/>
     </row>
-    <row r="39" spans="1:25" ht="16">
-      <c r="A39" s="3" t="s">
-        <v>933</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>933</v>
+    <row r="39" spans="1:25">
+      <c r="A39" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>69</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
@@ -5259,14 +5251,16 @@
     </row>
     <row r="40" spans="1:25" ht="16">
       <c r="A40" s="3" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B40" s="3"/>
+        <v>933</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>934</v>
+      </c>
       <c r="C40" s="3" t="s">
-        <v>1046</v>
+        <v>935</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>1045</v>
+        <v>933</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -5292,49 +5286,49 @@
     </row>
     <row r="41" spans="1:25" ht="16">
       <c r="A41" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" s="2"/>
-      <c r="Q41" s="2"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="2"/>
-      <c r="T41" s="2"/>
-      <c r="U41" s="2"/>
-      <c r="V41" s="2"/>
-      <c r="W41" s="2"/>
-      <c r="X41" s="2"/>
-      <c r="Y41" s="2"/>
+        <v>1040</v>
+      </c>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="1"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+      <c r="Y41" s="1"/>
     </row>
     <row r="42" spans="1:25" ht="16">
       <c r="A42" s="3" t="s">
-        <v>936</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3" t="s">
-        <v>937</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>938</v>
+        <v>72</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>75</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
@@ -5359,17 +5353,15 @@
       <c r="Y42" s="2"/>
     </row>
     <row r="43" spans="1:25" ht="16">
-      <c r="A43" s="7" t="s">
-        <v>860</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>861</v>
-      </c>
-      <c r="C43" s="54" t="s">
-        <v>862</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>863</v>
+      <c r="A43" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>938</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -5395,47 +5387,49 @@
     </row>
     <row r="44" spans="1:25" ht="16">
       <c r="A44" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="8" t="s">
-        <v>77</v>
+        <v>860</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="C44" s="54" t="s">
+        <v>862</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
-      <c r="W44" s="1"/>
-      <c r="X44" s="1"/>
-      <c r="Y44" s="1"/>
+        <v>863</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
     </row>
     <row r="45" spans="1:25" ht="16">
       <c r="A45" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B45" s="7"/>
       <c r="C45" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -5460,15 +5454,15 @@
       <c r="Y45" s="1"/>
     </row>
     <row r="46" spans="1:25" ht="16">
-      <c r="A46" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>87</v>
+      <c r="A46" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
@@ -5493,15 +5487,15 @@
       <c r="Y46" s="1"/>
     </row>
     <row r="47" spans="1:25" ht="16">
-      <c r="A47" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="7"/>
-      <c r="C47" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>80</v>
+      <c r="A47" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
@@ -5526,17 +5520,15 @@
       <c r="Y47" s="1"/>
     </row>
     <row r="48" spans="1:25" ht="16">
-      <c r="A48" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>82</v>
+      <c r="A48" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" s="7"/>
+      <c r="C48" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
@@ -5560,16 +5552,18 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25">
-      <c r="A49" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="B49" s="9"/>
-      <c r="C49" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>88</v>
+    <row r="49" spans="1:25" ht="16">
+      <c r="A49" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -5594,15 +5588,15 @@
       <c r="Y49" s="1"/>
     </row>
     <row r="50" spans="1:25">
-      <c r="A50" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>90</v>
+      <c r="A50" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="9"/>
+      <c r="C50" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>88</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -5627,118 +5621,116 @@
       <c r="Y50" s="1"/>
     </row>
     <row r="51" spans="1:25">
-      <c r="A51" s="9" t="s">
+      <c r="A51" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B51" s="13"/>
+      <c r="C51" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+    </row>
+    <row r="52" spans="1:25">
+      <c r="A52" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B51" s="9"/>
-      <c r="C51" s="16" t="s">
+      <c r="B52" s="9"/>
+      <c r="C52" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D52" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
-      <c r="P51" s="2"/>
-      <c r="Q51" s="2"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="2"/>
-      <c r="T51" s="2"/>
-      <c r="U51" s="2"/>
-      <c r="V51" s="2"/>
-      <c r="W51" s="2"/>
-      <c r="X51" s="2"/>
-      <c r="Y51" s="2"/>
-    </row>
-    <row r="52" spans="1:25" ht="16">
-      <c r="A52" s="7" t="s">
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+    </row>
+    <row r="53" spans="1:25" ht="16">
+      <c r="A53" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B52" s="7"/>
-      <c r="C52" s="15" t="s">
+      <c r="B53" s="7"/>
+      <c r="C53" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="D52" s="7" t="s">
+      <c r="D53" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E52" s="60"/>
-      <c r="F52" s="60"/>
-      <c r="G52" s="60"/>
-      <c r="H52" s="60"/>
-      <c r="I52" s="60"/>
-      <c r="J52" s="60"/>
-      <c r="K52" s="60"/>
-      <c r="L52" s="60"/>
-      <c r="M52" s="60"/>
-      <c r="N52" s="60"/>
-      <c r="O52" s="60"/>
-      <c r="P52" s="60"/>
-      <c r="Q52" s="60"/>
-      <c r="R52" s="60"/>
-      <c r="S52" s="60"/>
-      <c r="T52" s="60"/>
-      <c r="U52" s="60"/>
-      <c r="V52" s="60"/>
-      <c r="W52" s="60"/>
-      <c r="X52" s="60"/>
-      <c r="Y52" s="60"/>
-    </row>
-    <row r="53" spans="1:25" ht="16">
-      <c r="A53" s="5" t="s">
+      <c r="E53" s="60"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="60"/>
+      <c r="I53" s="60"/>
+      <c r="J53" s="60"/>
+      <c r="K53" s="60"/>
+      <c r="L53" s="60"/>
+      <c r="M53" s="60"/>
+      <c r="N53" s="60"/>
+      <c r="O53" s="60"/>
+      <c r="P53" s="60"/>
+      <c r="Q53" s="60"/>
+      <c r="R53" s="60"/>
+      <c r="S53" s="60"/>
+      <c r="T53" s="60"/>
+      <c r="U53" s="60"/>
+      <c r="V53" s="60"/>
+      <c r="W53" s="60"/>
+      <c r="X53" s="60"/>
+      <c r="Y53" s="60"/>
+    </row>
+    <row r="54" spans="1:25" ht="16">
+      <c r="A54" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B54" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D54" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" s="2"/>
-      <c r="Q53" s="2"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="2"/>
-      <c r="T53" s="2"/>
-      <c r="U53" s="2"/>
-      <c r="V53" s="2"/>
-      <c r="W53" s="2"/>
-      <c r="X53" s="2"/>
-      <c r="Y53" s="2"/>
-    </row>
-    <row r="54" spans="1:25" ht="16">
-      <c r="A54" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
@@ -5763,17 +5755,17 @@
       <c r="Y54" s="2"/>
     </row>
     <row r="55" spans="1:25" ht="16">
-      <c r="A55" s="55" t="s">
-        <v>864</v>
-      </c>
-      <c r="B55" s="55" t="s">
-        <v>864</v>
-      </c>
-      <c r="C55" s="56" t="s">
-        <v>865</v>
-      </c>
-      <c r="D55" s="55" t="s">
-        <v>866</v>
+      <c r="A55" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -5798,50 +5790,52 @@
       <c r="Y55" s="2"/>
     </row>
     <row r="56" spans="1:25" ht="16">
-      <c r="A56" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-      <c r="V56" s="1"/>
-      <c r="W56" s="1"/>
-      <c r="X56" s="1"/>
-      <c r="Y56" s="1"/>
+      <c r="A56" s="55" t="s">
+        <v>864</v>
+      </c>
+      <c r="B56" s="55" t="s">
+        <v>864</v>
+      </c>
+      <c r="C56" s="56" t="s">
+        <v>865</v>
+      </c>
+      <c r="D56" s="55" t="s">
+        <v>866</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="2"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
     </row>
     <row r="57" spans="1:25" ht="16">
       <c r="A57" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="12" t="s">
-        <v>105</v>
+        <v>428</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>430</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>104</v>
+        <v>429</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -5867,51 +5861,49 @@
     </row>
     <row r="58" spans="1:25" ht="16">
       <c r="A58" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>107</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B58" s="3"/>
       <c r="C58" s="12" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" s="2"/>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="2"/>
-      <c r="X58" s="2"/>
-      <c r="Y58" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="Q58" s="1"/>
+      <c r="R58" s="1"/>
+      <c r="S58" s="1"/>
+      <c r="T58" s="1"/>
+      <c r="U58" s="1"/>
+      <c r="V58" s="1"/>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
     </row>
     <row r="59" spans="1:25" ht="16">
       <c r="A59" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
@@ -5937,116 +5929,118 @@
     </row>
     <row r="60" spans="1:25" ht="16">
       <c r="A60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
+      <c r="W60" s="2"/>
+      <c r="X60" s="2"/>
+      <c r="Y60" s="2"/>
+    </row>
+    <row r="61" spans="1:25" ht="16">
+      <c r="A61" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>941</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D61" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-      <c r="S60" s="1"/>
-      <c r="T60" s="1"/>
-      <c r="U60" s="1"/>
-      <c r="V60" s="1"/>
-      <c r="W60" s="1"/>
-      <c r="X60" s="1"/>
-      <c r="Y60" s="1"/>
-    </row>
-    <row r="61" spans="1:25">
-      <c r="A61" s="9" t="s">
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="M61" s="1"/>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
+      <c r="P61" s="1"/>
+      <c r="Q61" s="1"/>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+      <c r="T61" s="1"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+    </row>
+    <row r="62" spans="1:25">
+      <c r="A62" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="B61" s="17"/>
-      <c r="C61" s="11" t="s">
+      <c r="B62" s="17"/>
+      <c r="C62" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D61" s="9" t="s">
+      <c r="D62" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E61" s="63"/>
-      <c r="F61" s="63"/>
-      <c r="G61" s="63"/>
-      <c r="H61" s="63"/>
-      <c r="I61" s="63"/>
-      <c r="J61" s="63"/>
-      <c r="K61" s="63"/>
-      <c r="L61" s="63"/>
-      <c r="M61" s="63"/>
-      <c r="N61" s="63"/>
-      <c r="O61" s="63"/>
-      <c r="P61" s="63"/>
-      <c r="Q61" s="63"/>
-      <c r="R61" s="63"/>
-      <c r="S61" s="63"/>
-      <c r="T61" s="63"/>
-      <c r="U61" s="63"/>
-      <c r="V61" s="63"/>
-      <c r="W61" s="63"/>
-      <c r="X61" s="63"/>
-      <c r="Y61" s="63"/>
-    </row>
-    <row r="62" spans="1:25" ht="16">
-      <c r="A62" s="57" t="s">
+      <c r="E62" s="63"/>
+      <c r="F62" s="63"/>
+      <c r="G62" s="63"/>
+      <c r="H62" s="63"/>
+      <c r="I62" s="63"/>
+      <c r="J62" s="63"/>
+      <c r="K62" s="63"/>
+      <c r="L62" s="63"/>
+      <c r="M62" s="63"/>
+      <c r="N62" s="63"/>
+      <c r="O62" s="63"/>
+      <c r="P62" s="63"/>
+      <c r="Q62" s="63"/>
+      <c r="R62" s="63"/>
+      <c r="S62" s="63"/>
+      <c r="T62" s="63"/>
+      <c r="U62" s="63"/>
+      <c r="V62" s="63"/>
+      <c r="W62" s="63"/>
+      <c r="X62" s="63"/>
+      <c r="Y62" s="63"/>
+    </row>
+    <row r="63" spans="1:25" ht="16">
+      <c r="A63" s="57" t="s">
         <v>867</v>
       </c>
-      <c r="B62" s="58" t="s">
+      <c r="B63" s="58" t="s">
         <v>867</v>
       </c>
-      <c r="C62" s="59" t="s">
+      <c r="C63" s="59" t="s">
         <v>868</v>
       </c>
-      <c r="D62" s="57" t="s">
-        <v>867</v>
-      </c>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-      <c r="S62" s="1"/>
-      <c r="T62" s="1"/>
-      <c r="U62" s="1"/>
-      <c r="V62" s="1"/>
-      <c r="W62" s="1"/>
-      <c r="X62" s="1"/>
-      <c r="Y62" s="1"/>
-    </row>
-    <row r="63" spans="1:25" ht="16">
-      <c r="A63" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3" t="s">
-        <v>868</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="57" t="s">
         <v>867</v>
       </c>
       <c r="E63" s="1"/>
@@ -6071,16 +6065,16 @@
       <c r="X63" s="1"/>
       <c r="Y63" s="1"/>
     </row>
-    <row r="64" spans="1:25">
-      <c r="A64" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="B64" s="17"/>
-      <c r="C64" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>113</v>
+    <row r="64" spans="1:25" ht="16">
+      <c r="A64" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>867</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -6104,18 +6098,16 @@
       <c r="X64" s="1"/>
       <c r="Y64" s="1"/>
     </row>
-    <row r="65" spans="1:25" ht="16">
+    <row r="65" spans="1:25">
       <c r="A65" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
+      </c>
+      <c r="B65" s="17"/>
+      <c r="C65" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -6139,16 +6131,18 @@
       <c r="X65" s="1"/>
       <c r="Y65" s="1"/>
     </row>
-    <row r="66" spans="1:25">
+    <row r="66" spans="1:25" ht="16">
       <c r="A66" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="B66" s="17"/>
-      <c r="C66" s="11" t="s">
-        <v>119</v>
+        <v>115</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>117</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -6172,18 +6166,16 @@
       <c r="X66" s="1"/>
       <c r="Y66" s="1"/>
     </row>
-    <row r="67" spans="1:25" ht="16">
-      <c r="A67" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>120</v>
+    <row r="67" spans="1:25">
+      <c r="A67" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B67" s="17"/>
+      <c r="C67" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -6208,15 +6200,17 @@
       <c r="Y67" s="1"/>
     </row>
     <row r="68" spans="1:25" ht="16">
-      <c r="A68" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="B68" s="7"/>
-      <c r="C68" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>123</v>
+      <c r="A68" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
@@ -6240,16 +6234,16 @@
       <c r="X68" s="1"/>
       <c r="Y68" s="1"/>
     </row>
-    <row r="69" spans="1:25">
-      <c r="A69" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B69" s="9"/>
-      <c r="C69" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>125</v>
+    <row r="69" spans="1:25" ht="16">
+      <c r="A69" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B69" s="7"/>
+      <c r="C69" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>123</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
@@ -6273,18 +6267,16 @@
       <c r="X69" s="1"/>
       <c r="Y69" s="1"/>
     </row>
-    <row r="70" spans="1:25" ht="16">
-      <c r="A70" s="3" t="s">
-        <v>942</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>943</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>944</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>942</v>
+    <row r="70" spans="1:25">
+      <c r="A70" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B70" s="9"/>
+      <c r="C70" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>125</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
@@ -6308,18 +6300,18 @@
       <c r="X70" s="1"/>
       <c r="Y70" s="1"/>
     </row>
-    <row r="71" spans="1:25">
-      <c r="A71" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>127</v>
+    <row r="71" spans="1:25" ht="16">
+      <c r="A71" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>942</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -6343,18 +6335,18 @@
       <c r="X71" s="1"/>
       <c r="Y71" s="1"/>
     </row>
-    <row r="72" spans="1:25" ht="16">
-      <c r="A72" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C72" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>130</v>
+    <row r="72" spans="1:25">
+      <c r="A72" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
@@ -6379,17 +6371,17 @@
       <c r="Y72" s="1"/>
     </row>
     <row r="73" spans="1:25" ht="16">
-      <c r="A73" s="61" t="s">
-        <v>869</v>
-      </c>
-      <c r="B73" s="61" t="s">
-        <v>870</v>
-      </c>
-      <c r="C73" s="62" t="s">
-        <v>871</v>
-      </c>
-      <c r="D73" s="61" t="s">
-        <v>869</v>
+      <c r="A73" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C73" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -6414,17 +6406,17 @@
       <c r="Y73" s="1"/>
     </row>
     <row r="74" spans="1:25" ht="16">
-      <c r="A74" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>946</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>947</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>945</v>
+      <c r="A74" s="61" t="s">
+        <v>869</v>
+      </c>
+      <c r="B74" s="61" t="s">
+        <v>870</v>
+      </c>
+      <c r="C74" s="62" t="s">
+        <v>871</v>
+      </c>
+      <c r="D74" s="61" t="s">
+        <v>869</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -6449,17 +6441,17 @@
       <c r="Y74" s="1"/>
     </row>
     <row r="75" spans="1:25" ht="16">
-      <c r="A75" s="7" t="s">
-        <v>872</v>
-      </c>
-      <c r="B75" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="C75" s="53" t="s">
-        <v>874</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>872</v>
+      <c r="A75" s="3" t="s">
+        <v>945</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>946</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>945</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -6484,16 +6476,16 @@
       <c r="Y75" s="1"/>
     </row>
     <row r="76" spans="1:25" ht="16">
-      <c r="A76" s="3" t="s">
+      <c r="A76" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="B76" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>949</v>
-      </c>
-      <c r="D76" s="1" t="s">
+      <c r="B76" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="C76" s="80" t="s">
+        <v>874</v>
+      </c>
+      <c r="D76" s="7" t="s">
         <v>872</v>
       </c>
       <c r="E76" s="1"/>
@@ -7505,16 +7497,16 @@
     </row>
     <row r="106" spans="1:25" ht="15.75" customHeight="1">
       <c r="A106" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="C106" s="3" t="s">
         <v>950</v>
       </c>
-      <c r="B106" s="3" t="s">
-        <v>951</v>
-      </c>
-      <c r="C106" s="3" t="s">
-        <v>952</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
@@ -7676,16 +7668,16 @@
     </row>
     <row r="111" spans="1:25" ht="18.75" customHeight="1">
       <c r="A111" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="C111" s="3" t="s">
         <v>953</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="D111" s="1" t="s">
         <v>954</v>
-      </c>
-      <c r="C111" s="3" t="s">
-        <v>955</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>956</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -8282,16 +8274,16 @@
     </row>
     <row r="129" spans="1:25" ht="15.75" customHeight="1">
       <c r="A129" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="C129" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="B129" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="C129" s="3" t="s">
-        <v>959</v>
-      </c>
       <c r="D129" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -8622,14 +8614,14 @@
     </row>
     <row r="139" spans="1:25" ht="15.75" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -8655,16 +8647,16 @@
     </row>
     <row r="140" spans="1:25" ht="15.75" customHeight="1">
       <c r="A140" s="3" t="s">
+        <v>960</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="C140" s="3" t="s">
         <v>962</v>
       </c>
-      <c r="B140" s="3" t="s">
-        <v>963</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>964</v>
-      </c>
       <c r="D140" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
@@ -8690,14 +8682,14 @@
     </row>
     <row r="141" spans="1:25" ht="15.75" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -9267,16 +9259,16 @@
     </row>
     <row r="159" spans="1:25" ht="15.75" customHeight="1">
       <c r="A159" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="C159" s="3" t="s">
         <v>965</v>
       </c>
-      <c r="B159" s="3" t="s">
-        <v>966</v>
-      </c>
-      <c r="C159" s="3" t="s">
-        <v>967</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -9302,16 +9294,16 @@
     </row>
     <row r="160" spans="1:25" ht="15.75" customHeight="1">
       <c r="A160" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="C160" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="B160" s="3" t="s">
-        <v>969</v>
-      </c>
-      <c r="C160" s="3" t="s">
-        <v>970</v>
-      </c>
       <c r="D160" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -9681,16 +9673,16 @@
     </row>
     <row r="171" spans="1:25" ht="15.75" customHeight="1">
       <c r="A171" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="C171" s="3" t="s">
         <v>971</v>
       </c>
-      <c r="B171" s="3" t="s">
-        <v>972</v>
-      </c>
-      <c r="C171" s="3" t="s">
-        <v>973</v>
-      </c>
       <c r="D171" s="1" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -9716,16 +9708,16 @@
     </row>
     <row r="172" spans="1:25" ht="15.75" customHeight="1">
       <c r="A172" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="C172" s="3" t="s">
         <v>974</v>
       </c>
-      <c r="B172" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="C172" s="3" t="s">
-        <v>976</v>
-      </c>
       <c r="D172" s="1" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -10097,7 +10089,7 @@
         <v>367</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>366</v>
@@ -10159,16 +10151,16 @@
     </row>
     <row r="185" spans="1:25" ht="15.75" customHeight="1">
       <c r="A185" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="C185" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="B185" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="C185" s="3" t="s">
-        <v>980</v>
-      </c>
       <c r="D185" s="1" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -10194,16 +10186,16 @@
     </row>
     <row r="186" spans="1:25" ht="15.75" customHeight="1">
       <c r="A186" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="C186" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="B186" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="C186" s="3" t="s">
-        <v>983</v>
-      </c>
       <c r="D186" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -10437,16 +10429,16 @@
     </row>
     <row r="193" spans="1:25" ht="15.75" customHeight="1">
       <c r="A193" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="C193" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B193" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="C193" s="3" t="s">
-        <v>986</v>
-      </c>
       <c r="D193" s="1" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -10812,14 +10804,14 @@
     </row>
     <row r="204" spans="1:25" ht="15.75" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -10979,14 +10971,14 @@
     </row>
     <row r="209" spans="1:25" ht="15.75" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -11180,7 +11172,7 @@
         <v>435</v>
       </c>
       <c r="B215" s="3"/>
-      <c r="C215" s="12" t="s">
+      <c r="C215" s="50" t="s">
         <v>846</v>
       </c>
       <c r="D215" s="3" t="s">
@@ -11280,14 +11272,14 @@
     </row>
     <row r="218" spans="1:25" ht="15.75" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B218" s="3"/>
       <c r="C218" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
@@ -11386,8 +11378,8 @@
       <c r="B221" s="3" t="s">
         <v>901</v>
       </c>
-      <c r="C221" s="3" t="s">
-        <v>996</v>
+      <c r="C221" s="50" t="s">
+        <v>994</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>900</v>
@@ -11415,17 +11407,17 @@
       <c r="Y221" s="1"/>
     </row>
     <row r="222" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A222" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="C222" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>997</v>
+      <c r="A222" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B222" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="D222" s="9" t="s">
+        <v>442</v>
       </c>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -11451,16 +11443,16 @@
     </row>
     <row r="223" spans="1:25" ht="15.75" customHeight="1">
       <c r="A223" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B223" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C223" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>447</v>
       </c>
       <c r="D223" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E223" s="1"/>
       <c r="F223" s="1"/>
@@ -11485,52 +11477,52 @@
       <c r="Y223" s="1"/>
     </row>
     <row r="224" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A224" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="B224" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C224" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="D224" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="E224" s="1"/>
-      <c r="F224" s="1"/>
-      <c r="G224" s="1"/>
-      <c r="H224" s="1"/>
-      <c r="I224" s="1"/>
-      <c r="J224" s="1"/>
-      <c r="K224" s="1"/>
-      <c r="L224" s="1"/>
-      <c r="M224" s="1"/>
-      <c r="N224" s="1"/>
-      <c r="O224" s="1"/>
-      <c r="P224" s="1"/>
-      <c r="Q224" s="1"/>
-      <c r="R224" s="1"/>
-      <c r="S224" s="1"/>
-      <c r="T224" s="1"/>
-      <c r="U224" s="1"/>
-      <c r="V224" s="1"/>
-      <c r="W224" s="1"/>
-      <c r="X224" s="1"/>
-      <c r="Y224" s="1"/>
+      <c r="A224" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="C224" s="53" t="s">
+        <v>905</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="E224" s="2"/>
+      <c r="F224" s="2"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
+      <c r="R224" s="2"/>
+      <c r="S224" s="2"/>
+      <c r="T224" s="2"/>
+      <c r="U224" s="2"/>
+      <c r="V224" s="2"/>
+      <c r="W224" s="2"/>
+      <c r="X224" s="2"/>
+      <c r="Y224" s="2"/>
     </row>
     <row r="225" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A225" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="B225" s="7" t="s">
-        <v>904</v>
-      </c>
-      <c r="C225" s="53" t="s">
-        <v>905</v>
-      </c>
-      <c r="D225" s="7" t="s">
-        <v>903</v>
+      <c r="A225" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C225" s="50" t="s">
+        <v>841</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
@@ -11556,51 +11548,49 @@
     </row>
     <row r="226" spans="1:25" ht="15.75" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>448</v>
+        <v>995</v>
       </c>
       <c r="B226" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C226" s="50" t="s">
-        <v>841</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="2"/>
-      <c r="H226" s="2"/>
-      <c r="I226" s="2"/>
-      <c r="J226" s="2"/>
-      <c r="K226" s="2"/>
-      <c r="L226" s="2"/>
-      <c r="M226" s="2"/>
-      <c r="N226" s="2"/>
-      <c r="O226" s="2"/>
-      <c r="P226" s="2"/>
-      <c r="Q226" s="2"/>
-      <c r="R226" s="2"/>
-      <c r="S226" s="2"/>
-      <c r="T226" s="2"/>
-      <c r="U226" s="2"/>
-      <c r="V226" s="2"/>
-      <c r="W226" s="2"/>
-      <c r="X226" s="2"/>
-      <c r="Y226" s="2"/>
+        <v>996</v>
+      </c>
+      <c r="C226" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="E226" s="1"/>
+      <c r="F226" s="1"/>
+      <c r="G226" s="1"/>
+      <c r="H226" s="1"/>
+      <c r="I226" s="1"/>
+      <c r="J226" s="1"/>
+      <c r="K226" s="1"/>
+      <c r="L226" s="1"/>
+      <c r="M226" s="1"/>
+      <c r="N226" s="1"/>
+      <c r="O226" s="1"/>
+      <c r="P226" s="1"/>
+      <c r="Q226" s="1"/>
+      <c r="R226" s="1"/>
+      <c r="S226" s="1"/>
+      <c r="T226" s="1"/>
+      <c r="U226" s="1"/>
+      <c r="V226" s="1"/>
+      <c r="W226" s="1"/>
+      <c r="X226" s="1"/>
+      <c r="Y226" s="1"/>
     </row>
     <row r="227" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A227" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C227" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D227" s="1" t="s">
-        <v>1003</v>
+      <c r="A227" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B227" s="9"/>
+      <c r="C227" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="D227" s="34" t="s">
+        <v>453</v>
       </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -11625,15 +11615,15 @@
       <c r="Y227" s="1"/>
     </row>
     <row r="228" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A228" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B228" s="9"/>
-      <c r="C228" s="33" t="s">
-        <v>452</v>
-      </c>
-      <c r="D228" s="34" t="s">
-        <v>453</v>
+      <c r="A228" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="E228" s="1"/>
       <c r="F228" s="1"/>
@@ -11658,118 +11648,120 @@
       <c r="Y228" s="1"/>
     </row>
     <row r="229" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A229" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="B229" s="3"/>
-      <c r="C229" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
-      <c r="J229" s="1"/>
-      <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
-      <c r="M229" s="1"/>
-      <c r="N229" s="1"/>
-      <c r="O229" s="1"/>
-      <c r="P229" s="1"/>
-      <c r="Q229" s="1"/>
-      <c r="R229" s="1"/>
-      <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
-      <c r="U229" s="1"/>
-      <c r="V229" s="1"/>
-      <c r="W229" s="1"/>
-      <c r="X229" s="1"/>
-      <c r="Y229" s="1"/>
+      <c r="A229" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B229" s="9"/>
+      <c r="C229" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+      <c r="J229" s="2"/>
+      <c r="K229" s="2"/>
+      <c r="L229" s="2"/>
+      <c r="M229" s="2"/>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
+      <c r="P229" s="2"/>
+      <c r="Q229" s="2"/>
+      <c r="R229" s="2"/>
+      <c r="S229" s="2"/>
+      <c r="T229" s="2"/>
+      <c r="U229" s="2"/>
+      <c r="V229" s="2"/>
+      <c r="W229" s="2"/>
+      <c r="X229" s="2"/>
+      <c r="Y229" s="2"/>
     </row>
     <row r="230" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A230" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="B230" s="9"/>
-      <c r="C230" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="D230" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-      <c r="J230" s="2"/>
-      <c r="K230" s="2"/>
-      <c r="L230" s="2"/>
-      <c r="M230" s="2"/>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" s="2"/>
-      <c r="Q230" s="2"/>
-      <c r="R230" s="2"/>
-      <c r="S230" s="2"/>
-      <c r="T230" s="2"/>
-      <c r="U230" s="2"/>
-      <c r="V230" s="2"/>
-      <c r="W230" s="2"/>
-      <c r="X230" s="2"/>
-      <c r="Y230" s="2"/>
+      <c r="A230" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C230" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+      <c r="J230" s="1"/>
+      <c r="K230" s="1"/>
+      <c r="L230" s="1"/>
+      <c r="M230" s="1"/>
+      <c r="N230" s="1"/>
+      <c r="O230" s="1"/>
+      <c r="P230" s="1"/>
+      <c r="Q230" s="1"/>
+      <c r="R230" s="1"/>
+      <c r="S230" s="1"/>
+      <c r="T230" s="1"/>
+      <c r="U230" s="1"/>
+      <c r="V230" s="1"/>
+      <c r="W230" s="1"/>
+      <c r="X230" s="1"/>
+      <c r="Y230" s="1"/>
     </row>
     <row r="231" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A231" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="C231" s="29" t="s">
-        <v>462</v>
-      </c>
-      <c r="D231" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="E231" s="1"/>
-      <c r="F231" s="1"/>
-      <c r="G231" s="1"/>
-      <c r="H231" s="1"/>
-      <c r="I231" s="1"/>
-      <c r="J231" s="1"/>
-      <c r="K231" s="1"/>
-      <c r="L231" s="1"/>
-      <c r="M231" s="1"/>
-      <c r="N231" s="1"/>
-      <c r="O231" s="1"/>
-      <c r="P231" s="1"/>
-      <c r="Q231" s="1"/>
-      <c r="R231" s="1"/>
-      <c r="S231" s="1"/>
-      <c r="T231" s="1"/>
-      <c r="U231" s="1"/>
-      <c r="V231" s="1"/>
-      <c r="W231" s="1"/>
-      <c r="X231" s="1"/>
-      <c r="Y231" s="1"/>
+      <c r="A231" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D231" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="2"/>
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2"/>
+      <c r="M231" s="2"/>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2"/>
+      <c r="P231" s="2"/>
+      <c r="Q231" s="2"/>
+      <c r="R231" s="2"/>
+      <c r="S231" s="2"/>
+      <c r="T231" s="2"/>
+      <c r="U231" s="2"/>
+      <c r="V231" s="2"/>
+      <c r="W231" s="2"/>
+      <c r="X231" s="2"/>
+      <c r="Y231" s="2"/>
     </row>
     <row r="232" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A232" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="B232" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>463</v>
+      <c r="A232" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C232" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
@@ -11794,17 +11786,15 @@
       <c r="Y232" s="2"/>
     </row>
     <row r="233" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A233" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="B233" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C233" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="D233" s="7" t="s">
-        <v>466</v>
+      <c r="A233" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
@@ -11829,15 +11819,15 @@
       <c r="Y233" s="2"/>
     </row>
     <row r="234" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A234" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B234" s="3"/>
-      <c r="C234" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>468</v>
+      <c r="A234" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B234" s="7"/>
+      <c r="C234" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
@@ -11862,81 +11852,81 @@
       <c r="Y234" s="2"/>
     </row>
     <row r="235" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A235" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="B235" s="7"/>
-      <c r="C235" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="D235" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
-      <c r="J235" s="2"/>
-      <c r="K235" s="2"/>
-      <c r="L235" s="2"/>
-      <c r="M235" s="2"/>
-      <c r="N235" s="2"/>
-      <c r="O235" s="2"/>
-      <c r="P235" s="2"/>
-      <c r="Q235" s="2"/>
-      <c r="R235" s="2"/>
-      <c r="S235" s="2"/>
-      <c r="T235" s="2"/>
-      <c r="U235" s="2"/>
-      <c r="V235" s="2"/>
-      <c r="W235" s="2"/>
-      <c r="X235" s="2"/>
-      <c r="Y235" s="2"/>
+      <c r="A235" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B235" s="3"/>
+      <c r="C235" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+      <c r="N235" s="1"/>
+      <c r="O235" s="1"/>
+      <c r="P235" s="1"/>
+      <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
+      <c r="T235" s="1"/>
+      <c r="U235" s="1"/>
+      <c r="V235" s="1"/>
+      <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
     </row>
     <row r="236" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A236" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B236" s="3"/>
-      <c r="C236" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="E236" s="1"/>
-      <c r="F236" s="1"/>
-      <c r="G236" s="1"/>
-      <c r="H236" s="1"/>
-      <c r="I236" s="1"/>
-      <c r="J236" s="1"/>
-      <c r="K236" s="1"/>
-      <c r="L236" s="1"/>
-      <c r="M236" s="1"/>
-      <c r="N236" s="1"/>
-      <c r="O236" s="1"/>
-      <c r="P236" s="1"/>
-      <c r="Q236" s="1"/>
-      <c r="R236" s="1"/>
-      <c r="S236" s="1"/>
-      <c r="T236" s="1"/>
-      <c r="U236" s="1"/>
-      <c r="V236" s="1"/>
-      <c r="W236" s="1"/>
-      <c r="X236" s="1"/>
-      <c r="Y236" s="1"/>
+      <c r="A236" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B236" s="7"/>
+      <c r="C236" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="2"/>
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+      <c r="J236" s="2"/>
+      <c r="K236" s="2"/>
+      <c r="L236" s="2"/>
+      <c r="M236" s="2"/>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
+      <c r="P236" s="2"/>
+      <c r="Q236" s="2"/>
+      <c r="R236" s="2"/>
+      <c r="S236" s="2"/>
+      <c r="T236" s="2"/>
+      <c r="U236" s="2"/>
+      <c r="V236" s="2"/>
+      <c r="W236" s="2"/>
+      <c r="X236" s="2"/>
+      <c r="Y236" s="2"/>
     </row>
     <row r="237" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A237" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="B237" s="7"/>
-      <c r="C237" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="D237" s="7" t="s">
-        <v>477</v>
+      <c r="A237" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>478</v>
       </c>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
@@ -11961,118 +11951,120 @@
       <c r="Y237" s="2"/>
     </row>
     <row r="238" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A238" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B238" s="3"/>
-      <c r="C238" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
-      <c r="K238" s="2"/>
-      <c r="L238" s="2"/>
-      <c r="M238" s="2"/>
-      <c r="N238" s="2"/>
-      <c r="O238" s="2"/>
-      <c r="P238" s="2"/>
-      <c r="Q238" s="2"/>
-      <c r="R238" s="2"/>
-      <c r="S238" s="2"/>
-      <c r="T238" s="2"/>
-      <c r="U238" s="2"/>
-      <c r="V238" s="2"/>
-      <c r="W238" s="2"/>
-      <c r="X238" s="2"/>
-      <c r="Y238" s="2"/>
+      <c r="A238" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="B238" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="C238" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="D238" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+      <c r="N238" s="1"/>
+      <c r="O238" s="1"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
+      <c r="V238" s="1"/>
+      <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
     </row>
     <row r="239" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A239" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="B239" s="35" t="s">
-        <v>484</v>
-      </c>
-      <c r="C239" s="36" t="s">
-        <v>485</v>
-      </c>
-      <c r="D239" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="E239" s="1"/>
-      <c r="F239" s="1"/>
-      <c r="G239" s="1"/>
-      <c r="H239" s="1"/>
-      <c r="I239" s="1"/>
-      <c r="J239" s="1"/>
-      <c r="K239" s="1"/>
-      <c r="L239" s="1"/>
-      <c r="M239" s="1"/>
-      <c r="N239" s="1"/>
-      <c r="O239" s="1"/>
-      <c r="P239" s="1"/>
-      <c r="Q239" s="1"/>
-      <c r="R239" s="1"/>
-      <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
-      <c r="U239" s="1"/>
-      <c r="V239" s="1"/>
-      <c r="W239" s="1"/>
-      <c r="X239" s="1"/>
-      <c r="Y239" s="1"/>
+      <c r="A239" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B239" s="7"/>
+      <c r="C239" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+      <c r="P239" s="2"/>
+      <c r="Q239" s="2"/>
+      <c r="R239" s="2"/>
+      <c r="S239" s="2"/>
+      <c r="T239" s="2"/>
+      <c r="U239" s="2"/>
+      <c r="V239" s="2"/>
+      <c r="W239" s="2"/>
+      <c r="X239" s="2"/>
+      <c r="Y239" s="2"/>
     </row>
     <row r="240" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A240" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="B240" s="7"/>
-      <c r="C240" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="D240" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
-      <c r="G240" s="2"/>
-      <c r="H240" s="2"/>
-      <c r="I240" s="2"/>
-      <c r="J240" s="2"/>
-      <c r="K240" s="2"/>
-      <c r="L240" s="2"/>
-      <c r="M240" s="2"/>
-      <c r="N240" s="2"/>
-      <c r="O240" s="2"/>
-      <c r="P240" s="2"/>
-      <c r="Q240" s="2"/>
-      <c r="R240" s="2"/>
-      <c r="S240" s="2"/>
-      <c r="T240" s="2"/>
-      <c r="U240" s="2"/>
-      <c r="V240" s="2"/>
-      <c r="W240" s="2"/>
-      <c r="X240" s="2"/>
-      <c r="Y240" s="2"/>
+      <c r="A240" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="B240" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="C240" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="D240" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="E240" s="1"/>
+      <c r="F240" s="1"/>
+      <c r="G240" s="1"/>
+      <c r="H240" s="1"/>
+      <c r="I240" s="1"/>
+      <c r="J240" s="1"/>
+      <c r="K240" s="1"/>
+      <c r="L240" s="1"/>
+      <c r="M240" s="1"/>
+      <c r="N240" s="1"/>
+      <c r="O240" s="1"/>
+      <c r="P240" s="1"/>
+      <c r="Q240" s="1"/>
+      <c r="R240" s="1"/>
+      <c r="S240" s="1"/>
+      <c r="T240" s="1"/>
+      <c r="U240" s="1"/>
+      <c r="V240" s="1"/>
+      <c r="W240" s="1"/>
+      <c r="X240" s="1"/>
+      <c r="Y240" s="1"/>
     </row>
     <row r="241" spans="1:25" ht="15.75" customHeight="1">
       <c r="A241" s="35" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B241" s="35" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C241" s="37" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D241" s="35" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -12097,17 +12089,15 @@
       <c r="Y241" s="1"/>
     </row>
     <row r="242" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A242" s="35" t="s">
-        <v>490</v>
-      </c>
-      <c r="B242" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="C242" s="37" t="s">
-        <v>492</v>
-      </c>
-      <c r="D242" s="35" t="s">
-        <v>490</v>
+      <c r="A242" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B242" s="3"/>
+      <c r="C242" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>509</v>
       </c>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -12133,14 +12123,16 @@
     </row>
     <row r="243" spans="1:25" ht="15.75" customHeight="1">
       <c r="A243" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B243" s="3"/>
-      <c r="C243" s="3" t="s">
-        <v>508</v>
+        <v>493</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>495</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -12165,17 +12157,15 @@
       <c r="Y243" s="1"/>
     </row>
     <row r="244" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A244" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C244" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>493</v>
+      <c r="A244" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B244" s="7"/>
+      <c r="C244" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>496</v>
       </c>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -12200,15 +12190,17 @@
       <c r="Y244" s="1"/>
     </row>
     <row r="245" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A245" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="B245" s="7"/>
-      <c r="C245" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="D245" s="7" t="s">
-        <v>496</v>
+      <c r="A245" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -12233,17 +12225,17 @@
       <c r="Y245" s="1"/>
     </row>
     <row r="246" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A246" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="B246" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C246" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="D246" s="5" t="s">
-        <v>501</v>
+      <c r="A246" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C246" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>504</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -12268,17 +12260,15 @@
       <c r="Y246" s="1"/>
     </row>
     <row r="247" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A247" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C247" s="50" t="s">
-        <v>847</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>504</v>
+      <c r="A247" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B247" s="5"/>
+      <c r="C247" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>505</v>
       </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -12303,15 +12293,17 @@
       <c r="Y247" s="1"/>
     </row>
     <row r="248" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A248" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B248" s="5"/>
-      <c r="C248" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="D248" s="5" t="s">
-        <v>505</v>
+      <c r="A248" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C248" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>560</v>
       </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -12337,16 +12329,14 @@
     </row>
     <row r="249" spans="1:25" ht="15.75" customHeight="1">
       <c r="A249" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B249" s="3" t="s">
-        <v>560</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B249" s="3"/>
       <c r="C249" s="4" t="s">
-        <v>561</v>
+        <v>511</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -12371,15 +12361,15 @@
       <c r="Y249" s="1"/>
     </row>
     <row r="250" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A250" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B250" s="3"/>
-      <c r="C250" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>510</v>
+      <c r="A250" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B250" s="38"/>
+      <c r="C250" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D250" s="34" t="s">
+        <v>512</v>
       </c>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -12404,15 +12394,15 @@
       <c r="Y250" s="1"/>
     </row>
     <row r="251" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A251" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="B251" s="38"/>
-      <c r="C251" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="D251" s="34" t="s">
-        <v>512</v>
+      <c r="A251" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B251" s="5"/>
+      <c r="C251" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>514</v>
       </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -12437,15 +12427,15 @@
       <c r="Y251" s="1"/>
     </row>
     <row r="252" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A252" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="B252" s="5"/>
-      <c r="C252" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D252" s="5" t="s">
-        <v>514</v>
+      <c r="A252" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B252" s="3"/>
+      <c r="C252" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -12470,15 +12460,15 @@
       <c r="Y252" s="1"/>
     </row>
     <row r="253" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A253" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B253" s="3"/>
-      <c r="C253" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>516</v>
+      <c r="A253" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="B253" s="7"/>
+      <c r="C253" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="E253" s="1"/>
       <c r="F253" s="1"/>
@@ -12504,47 +12494,49 @@
     </row>
     <row r="254" spans="1:25" ht="15.75" customHeight="1">
       <c r="A254" s="7" t="s">
-        <v>518</v>
+        <v>849</v>
       </c>
       <c r="B254" s="7"/>
       <c r="C254" s="29" t="s">
-        <v>519</v>
+        <v>850</v>
       </c>
       <c r="D254" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="E254" s="1"/>
-      <c r="F254" s="1"/>
-      <c r="G254" s="1"/>
-      <c r="H254" s="1"/>
-      <c r="I254" s="1"/>
-      <c r="J254" s="1"/>
-      <c r="K254" s="1"/>
-      <c r="L254" s="1"/>
-      <c r="M254" s="1"/>
-      <c r="N254" s="1"/>
-      <c r="O254" s="1"/>
-      <c r="P254" s="1"/>
-      <c r="Q254" s="1"/>
-      <c r="R254" s="1"/>
-      <c r="S254" s="1"/>
-      <c r="T254" s="1"/>
-      <c r="U254" s="1"/>
-      <c r="V254" s="1"/>
-      <c r="W254" s="1"/>
-      <c r="X254" s="1"/>
-      <c r="Y254" s="1"/>
+        <v>849</v>
+      </c>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="2"/>
+      <c r="H254" s="2"/>
+      <c r="I254" s="2"/>
+      <c r="J254" s="2"/>
+      <c r="K254" s="2"/>
+      <c r="L254" s="2"/>
+      <c r="M254" s="2"/>
+      <c r="N254" s="2"/>
+      <c r="O254" s="2"/>
+      <c r="P254" s="2"/>
+      <c r="Q254" s="2"/>
+      <c r="R254" s="2"/>
+      <c r="S254" s="2"/>
+      <c r="T254" s="2"/>
+      <c r="U254" s="2"/>
+      <c r="V254" s="2"/>
+      <c r="W254" s="2"/>
+      <c r="X254" s="2"/>
+      <c r="Y254" s="2"/>
     </row>
     <row r="255" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A255" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="B255" s="7"/>
-      <c r="C255" s="29" t="s">
-        <v>850</v>
-      </c>
-      <c r="D255" s="7" t="s">
-        <v>849</v>
+      <c r="A255" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
@@ -12569,17 +12561,15 @@
       <c r="Y255" s="2"/>
     </row>
     <row r="256" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A256" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B256" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C256" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>520</v>
+      <c r="A256" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B256" s="7"/>
+      <c r="C256" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
@@ -12604,50 +12594,52 @@
       <c r="Y256" s="2"/>
     </row>
     <row r="257" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A257" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B257" s="7"/>
-      <c r="C257" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D257" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E257" s="2"/>
-      <c r="F257" s="2"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
-      <c r="J257" s="2"/>
-      <c r="K257" s="2"/>
-      <c r="L257" s="2"/>
-      <c r="M257" s="2"/>
-      <c r="N257" s="2"/>
-      <c r="O257" s="2"/>
-      <c r="P257" s="2"/>
-      <c r="Q257" s="2"/>
-      <c r="R257" s="2"/>
-      <c r="S257" s="2"/>
-      <c r="T257" s="2"/>
-      <c r="U257" s="2"/>
-      <c r="V257" s="2"/>
-      <c r="W257" s="2"/>
-      <c r="X257" s="2"/>
-      <c r="Y257" s="2"/>
+      <c r="A257" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D257" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E257" s="1"/>
+      <c r="F257" s="1"/>
+      <c r="G257" s="1"/>
+      <c r="H257" s="1"/>
+      <c r="I257" s="1"/>
+      <c r="J257" s="1"/>
+      <c r="K257" s="1"/>
+      <c r="L257" s="1"/>
+      <c r="M257" s="1"/>
+      <c r="N257" s="1"/>
+      <c r="O257" s="1"/>
+      <c r="P257" s="1"/>
+      <c r="Q257" s="1"/>
+      <c r="R257" s="1"/>
+      <c r="S257" s="1"/>
+      <c r="T257" s="1"/>
+      <c r="U257" s="1"/>
+      <c r="V257" s="1"/>
+      <c r="W257" s="1"/>
+      <c r="X257" s="1"/>
+      <c r="Y257" s="1"/>
     </row>
     <row r="258" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A258" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="B258" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D258" s="5" t="s">
-        <v>525</v>
+      <c r="A258" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -12672,52 +12664,50 @@
       <c r="Y258" s="1"/>
     </row>
     <row r="259" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A259" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="B259" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C259" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="E259" s="1"/>
-      <c r="F259" s="1"/>
-      <c r="G259" s="1"/>
-      <c r="H259" s="1"/>
-      <c r="I259" s="1"/>
-      <c r="J259" s="1"/>
-      <c r="K259" s="1"/>
-      <c r="L259" s="1"/>
-      <c r="M259" s="1"/>
-      <c r="N259" s="1"/>
-      <c r="O259" s="1"/>
-      <c r="P259" s="1"/>
-      <c r="Q259" s="1"/>
-      <c r="R259" s="1"/>
-      <c r="S259" s="1"/>
-      <c r="T259" s="1"/>
-      <c r="U259" s="1"/>
-      <c r="V259" s="1"/>
-      <c r="W259" s="1"/>
-      <c r="X259" s="1"/>
-      <c r="Y259" s="1"/>
+      <c r="A259" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C259" s="52" t="s">
+        <v>848</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="2"/>
+      <c r="H259" s="2"/>
+      <c r="I259" s="2"/>
+      <c r="J259" s="2"/>
+      <c r="K259" s="2"/>
+      <c r="L259" s="2"/>
+      <c r="M259" s="2"/>
+      <c r="N259" s="2"/>
+      <c r="O259" s="2"/>
+      <c r="P259" s="2"/>
+      <c r="Q259" s="2"/>
+      <c r="R259" s="2"/>
+      <c r="S259" s="2"/>
+      <c r="T259" s="2"/>
+      <c r="U259" s="2"/>
+      <c r="V259" s="2"/>
+      <c r="W259" s="2"/>
+      <c r="X259" s="2"/>
+      <c r="Y259" s="2"/>
     </row>
     <row r="260" spans="1:25" ht="15.75" customHeight="1">
       <c r="A260" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B260" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="C260" s="52" t="s">
-        <v>848</v>
+        <v>533</v>
+      </c>
+      <c r="B260" s="9"/>
+      <c r="C260" s="10" t="s">
+        <v>534</v>
       </c>
       <c r="D260" s="9" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
@@ -12742,15 +12732,17 @@
       <c r="Y260" s="2"/>
     </row>
     <row r="261" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A261" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B261" s="9"/>
-      <c r="C261" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="D261" s="9" t="s">
-        <v>533</v>
+      <c r="A261" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
@@ -12775,17 +12767,15 @@
       <c r="Y261" s="2"/>
     </row>
     <row r="262" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A262" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B262" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C262" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>535</v>
+      <c r="A262" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>538</v>
       </c>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
@@ -12810,50 +12800,52 @@
       <c r="Y262" s="2"/>
     </row>
     <row r="263" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A263" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="B263" s="5"/>
-      <c r="C263" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="D263" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
-      <c r="G263" s="2"/>
-      <c r="H263" s="2"/>
-      <c r="I263" s="2"/>
-      <c r="J263" s="2"/>
-      <c r="K263" s="2"/>
-      <c r="L263" s="2"/>
-      <c r="M263" s="2"/>
-      <c r="N263" s="2"/>
-      <c r="O263" s="2"/>
-      <c r="P263" s="2"/>
-      <c r="Q263" s="2"/>
-      <c r="R263" s="2"/>
-      <c r="S263" s="2"/>
-      <c r="T263" s="2"/>
-      <c r="U263" s="2"/>
-      <c r="V263" s="2"/>
-      <c r="W263" s="2"/>
-      <c r="X263" s="2"/>
-      <c r="Y263" s="2"/>
+      <c r="A263" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B263" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C263" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="E263" s="1"/>
+      <c r="F263" s="1"/>
+      <c r="G263" s="1"/>
+      <c r="H263" s="1"/>
+      <c r="I263" s="1"/>
+      <c r="J263" s="1"/>
+      <c r="K263" s="1"/>
+      <c r="L263" s="1"/>
+      <c r="M263" s="1"/>
+      <c r="N263" s="1"/>
+      <c r="O263" s="1"/>
+      <c r="P263" s="1"/>
+      <c r="Q263" s="1"/>
+      <c r="R263" s="1"/>
+      <c r="S263" s="1"/>
+      <c r="T263" s="1"/>
+      <c r="U263" s="1"/>
+      <c r="V263" s="1"/>
+      <c r="W263" s="1"/>
+      <c r="X263" s="1"/>
+      <c r="Y263" s="1"/>
     </row>
     <row r="264" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A264" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B264" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="C264" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D264" s="7" t="s">
-        <v>540</v>
+      <c r="A264" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="E264" s="1"/>
       <c r="F264" s="1"/>
@@ -12878,52 +12870,52 @@
       <c r="Y264" s="1"/>
     </row>
     <row r="265" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A265" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="B265" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="C265" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="D265" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="E265" s="1"/>
-      <c r="F265" s="1"/>
-      <c r="G265" s="1"/>
-      <c r="H265" s="1"/>
-      <c r="I265" s="1"/>
-      <c r="J265" s="1"/>
-      <c r="K265" s="1"/>
-      <c r="L265" s="1"/>
-      <c r="M265" s="1"/>
-      <c r="N265" s="1"/>
-      <c r="O265" s="1"/>
-      <c r="P265" s="1"/>
-      <c r="Q265" s="1"/>
-      <c r="R265" s="1"/>
-      <c r="S265" s="1"/>
-      <c r="T265" s="1"/>
-      <c r="U265" s="1"/>
-      <c r="V265" s="1"/>
-      <c r="W265" s="1"/>
-      <c r="X265" s="1"/>
-      <c r="Y265" s="1"/>
+      <c r="A265" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="B265" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="2"/>
+      <c r="I265" s="2"/>
+      <c r="J265" s="2"/>
+      <c r="K265" s="2"/>
+      <c r="L265" s="2"/>
+      <c r="M265" s="2"/>
+      <c r="N265" s="2"/>
+      <c r="O265" s="2"/>
+      <c r="P265" s="2"/>
+      <c r="Q265" s="2"/>
+      <c r="R265" s="2"/>
+      <c r="S265" s="2"/>
+      <c r="T265" s="2"/>
+      <c r="U265" s="2"/>
+      <c r="V265" s="2"/>
+      <c r="W265" s="2"/>
+      <c r="X265" s="2"/>
+      <c r="Y265" s="2"/>
     </row>
     <row r="266" spans="1:25" ht="15.75" customHeight="1">
       <c r="A266" s="3" t="s">
-        <v>1004</v>
+        <v>547</v>
       </c>
       <c r="B266" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C266" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>1004</v>
+        <v>548</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
@@ -12948,17 +12940,17 @@
       <c r="Y266" s="2"/>
     </row>
     <row r="267" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A267" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B267" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C267" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>547</v>
+      <c r="A267" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C267" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="D267" s="34" t="s">
+        <v>550</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
@@ -12984,16 +12976,12 @@
     </row>
     <row r="268" spans="1:25" ht="15.75" customHeight="1">
       <c r="A268" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B268" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C268" s="33" t="s">
-        <v>552</v>
-      </c>
+        <v>906</v>
+      </c>
+      <c r="B268" s="9"/>
+      <c r="C268" s="33"/>
       <c r="D268" s="34" t="s">
-        <v>550</v>
+        <v>906</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
@@ -13018,13 +13006,15 @@
       <c r="Y268" s="2"/>
     </row>
     <row r="269" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A269" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="B269" s="9"/>
-      <c r="C269" s="33"/>
-      <c r="D269" s="34" t="s">
-        <v>906</v>
+      <c r="A269" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B269" s="13"/>
+      <c r="C269" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="D269" s="41" t="s">
+        <v>555</v>
       </c>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
@@ -13049,15 +13039,17 @@
       <c r="Y269" s="2"/>
     </row>
     <row r="270" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A270" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="B270" s="13"/>
-      <c r="C270" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="D270" s="41" t="s">
-        <v>555</v>
+      <c r="A270" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C270" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="D270" s="34" t="s">
+        <v>556</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
@@ -13083,16 +13075,14 @@
     </row>
     <row r="271" spans="1:25" ht="15.75" customHeight="1">
       <c r="A271" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="C271" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="D271" s="34" t="s">
-        <v>556</v>
+        <v>562</v>
+      </c>
+      <c r="B271" s="9"/>
+      <c r="C271" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
@@ -13118,14 +13108,16 @@
     </row>
     <row r="272" spans="1:25" ht="15.75" customHeight="1">
       <c r="A272" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="B272" s="9"/>
+        <v>565</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>566</v>
+      </c>
       <c r="C272" s="34" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D272" s="9" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
@@ -13150,17 +13142,17 @@
       <c r="Y272" s="2"/>
     </row>
     <row r="273" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A273" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B273" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="C273" s="34" t="s">
-        <v>567</v>
-      </c>
-      <c r="D273" s="9" t="s">
-        <v>568</v>
+      <c r="A273" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="B273" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="C273" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D273" s="43" t="s">
+        <v>569</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
@@ -13185,17 +13177,15 @@
       <c r="Y273" s="2"/>
     </row>
     <row r="274" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A274" s="43" t="s">
-        <v>569</v>
-      </c>
-      <c r="B274" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="C274" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="D274" s="43" t="s">
-        <v>569</v>
+      <c r="A274" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B274" s="3"/>
+      <c r="C274" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>1002</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
@@ -13220,15 +13210,17 @@
       <c r="Y274" s="2"/>
     </row>
     <row r="275" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A275" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B275" s="3"/>
-      <c r="C275" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>1007</v>
+      <c r="A275" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C275" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
@@ -13253,17 +13245,17 @@
       <c r="Y275" s="2"/>
     </row>
     <row r="276" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A276" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="B276" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C276" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="D276" s="9" t="s">
-        <v>570</v>
+      <c r="A276" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C276" s="53" t="s">
+        <v>909</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>907</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
@@ -13288,16 +13280,16 @@
       <c r="Y276" s="2"/>
     </row>
     <row r="277" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A277" s="7" t="s">
+      <c r="A277" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="B277" s="7" t="s">
+      <c r="B277" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="C277" s="53" t="s">
-        <v>909</v>
-      </c>
-      <c r="D277" s="7" t="s">
+      <c r="C277" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D277" s="1" t="s">
         <v>907</v>
       </c>
       <c r="E277" s="2"/>
@@ -13324,16 +13316,16 @@
     </row>
     <row r="278" spans="1:25" ht="15.75" customHeight="1">
       <c r="A278" s="3" t="s">
-        <v>907</v>
+        <v>573</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C278" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>907</v>
+        <v>842</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
@@ -13358,50 +13350,50 @@
       <c r="Y278" s="2"/>
     </row>
     <row r="279" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A279" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="B279" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="C279" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E279" s="2"/>
-      <c r="F279" s="2"/>
-      <c r="G279" s="2"/>
-      <c r="H279" s="2"/>
-      <c r="I279" s="2"/>
-      <c r="J279" s="2"/>
-      <c r="K279" s="2"/>
-      <c r="L279" s="2"/>
-      <c r="M279" s="2"/>
-      <c r="N279" s="2"/>
-      <c r="O279" s="2"/>
-      <c r="P279" s="2"/>
-      <c r="Q279" s="2"/>
-      <c r="R279" s="2"/>
-      <c r="S279" s="2"/>
-      <c r="T279" s="2"/>
-      <c r="U279" s="2"/>
-      <c r="V279" s="2"/>
-      <c r="W279" s="2"/>
-      <c r="X279" s="2"/>
-      <c r="Y279" s="2"/>
+      <c r="A279" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B279" s="7"/>
+      <c r="C279" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E279" s="1"/>
+      <c r="F279" s="1"/>
+      <c r="G279" s="1"/>
+      <c r="H279" s="1"/>
+      <c r="I279" s="1"/>
+      <c r="J279" s="1"/>
+      <c r="K279" s="1"/>
+      <c r="L279" s="1"/>
+      <c r="M279" s="1"/>
+      <c r="N279" s="1"/>
+      <c r="O279" s="1"/>
+      <c r="P279" s="1"/>
+      <c r="Q279" s="1"/>
+      <c r="R279" s="1"/>
+      <c r="S279" s="1"/>
+      <c r="T279" s="1"/>
+      <c r="U279" s="1"/>
+      <c r="V279" s="1"/>
+      <c r="W279" s="1"/>
+      <c r="X279" s="1"/>
+      <c r="Y279" s="1"/>
     </row>
     <row r="280" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A280" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B280" s="7"/>
-      <c r="C280" s="8" t="s">
-        <v>576</v>
-      </c>
-      <c r="D280" s="7" t="s">
-        <v>577</v>
+      <c r="A280" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>578</v>
       </c>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
@@ -13426,17 +13418,17 @@
       <c r="Y280" s="1"/>
     </row>
     <row r="281" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A281" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="B281" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C281" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="D281" s="5" t="s">
-        <v>578</v>
+      <c r="A281" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
@@ -13461,17 +13453,15 @@
       <c r="Y281" s="1"/>
     </row>
     <row r="282" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A282" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="B282" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C282" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>581</v>
+      <c r="A282" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="B282" s="7"/>
+      <c r="C282" s="53" t="s">
+        <v>911</v>
+      </c>
+      <c r="D282" s="7" t="s">
+        <v>910</v>
       </c>
       <c r="E282" s="1"/>
       <c r="F282" s="1"/>
@@ -13497,47 +13487,49 @@
     </row>
     <row r="283" spans="1:25" ht="15.75" customHeight="1">
       <c r="A283" s="7" t="s">
-        <v>910</v>
+        <v>584</v>
       </c>
       <c r="B283" s="7"/>
-      <c r="C283" s="53" t="s">
-        <v>911</v>
+      <c r="C283" s="29" t="s">
+        <v>585</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="E283" s="1"/>
-      <c r="F283" s="1"/>
-      <c r="G283" s="1"/>
-      <c r="H283" s="1"/>
-      <c r="I283" s="1"/>
-      <c r="J283" s="1"/>
-      <c r="K283" s="1"/>
-      <c r="L283" s="1"/>
-      <c r="M283" s="1"/>
-      <c r="N283" s="1"/>
-      <c r="O283" s="1"/>
-      <c r="P283" s="1"/>
-      <c r="Q283" s="1"/>
-      <c r="R283" s="1"/>
-      <c r="S283" s="1"/>
-      <c r="T283" s="1"/>
-      <c r="U283" s="1"/>
-      <c r="V283" s="1"/>
-      <c r="W283" s="1"/>
-      <c r="X283" s="1"/>
-      <c r="Y283" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="2"/>
+      <c r="H283" s="2"/>
+      <c r="I283" s="2"/>
+      <c r="J283" s="2"/>
+      <c r="K283" s="2"/>
+      <c r="L283" s="2"/>
+      <c r="M283" s="2"/>
+      <c r="N283" s="2"/>
+      <c r="O283" s="2"/>
+      <c r="P283" s="2"/>
+      <c r="Q283" s="2"/>
+      <c r="R283" s="2"/>
+      <c r="S283" s="2"/>
+      <c r="T283" s="2"/>
+      <c r="U283" s="2"/>
+      <c r="V283" s="2"/>
+      <c r="W283" s="2"/>
+      <c r="X283" s="2"/>
+      <c r="Y283" s="2"/>
     </row>
     <row r="284" spans="1:25" ht="15.75" customHeight="1">
       <c r="A284" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="B284" s="7"/>
+        <v>589</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>590</v>
+      </c>
       <c r="C284" s="29" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
@@ -13562,17 +13554,17 @@
       <c r="Y284" s="2"/>
     </row>
     <row r="285" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A285" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B285" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="C285" s="29" t="s">
-        <v>591</v>
-      </c>
-      <c r="D285" s="7" t="s">
-        <v>592</v>
+      <c r="A285" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>1005</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
@@ -13597,17 +13589,17 @@
       <c r="Y285" s="2"/>
     </row>
     <row r="286" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A286" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B286" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C286" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>1010</v>
+      <c r="A286" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D286" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
@@ -13633,16 +13625,14 @@
     </row>
     <row r="287" spans="1:25" ht="15.75" customHeight="1">
       <c r="A287" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B287" s="5" t="s">
-        <v>587</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="B287" s="5"/>
       <c r="C287" s="6" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
@@ -13667,15 +13657,15 @@
       <c r="Y287" s="2"/>
     </row>
     <row r="288" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A288" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="D288" s="5" t="s">
-        <v>593</v>
+      <c r="A288" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B288" s="3"/>
+      <c r="C288" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
@@ -13700,15 +13690,17 @@
       <c r="Y288" s="2"/>
     </row>
     <row r="289" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A289" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="B289" s="3"/>
-      <c r="C289" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>595</v>
+      <c r="A289" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C289" s="30" t="s">
+        <v>599</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>600</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -13733,17 +13725,15 @@
       <c r="Y289" s="2"/>
     </row>
     <row r="290" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A290" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="B290" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="C290" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="D290" s="5" t="s">
-        <v>600</v>
+      <c r="A290" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B290" s="3"/>
+      <c r="C290" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
@@ -13769,14 +13759,16 @@
     </row>
     <row r="291" spans="1:25" ht="15.75" customHeight="1">
       <c r="A291" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B291" s="3"/>
+        <v>603</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="C291" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
@@ -13801,17 +13793,17 @@
       <c r="Y291" s="2"/>
     </row>
     <row r="292" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A292" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B292" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C292" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>606</v>
+      <c r="A292" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="B292" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C292" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="D292" s="9" t="s">
+        <v>607</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
@@ -13837,16 +13829,14 @@
     </row>
     <row r="293" spans="1:25" ht="15.75" customHeight="1">
       <c r="A293" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="B293" s="9" t="s">
-        <v>608</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="B293" s="9"/>
       <c r="C293" s="10" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D293" s="9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
@@ -13872,14 +13862,14 @@
     </row>
     <row r="294" spans="1:25" ht="15.75" customHeight="1">
       <c r="A294" s="9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B294" s="9"/>
-      <c r="C294" s="10" t="s">
-        <v>611</v>
+      <c r="C294" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="D294" s="9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E294" s="2"/>
       <c r="F294" s="2"/>
@@ -13904,50 +13894,52 @@
       <c r="Y294" s="2"/>
     </row>
     <row r="295" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A295" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="B295" s="9"/>
-      <c r="C295" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="D295" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="E295" s="2"/>
-      <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
-      <c r="H295" s="2"/>
-      <c r="I295" s="2"/>
-      <c r="J295" s="2"/>
-      <c r="K295" s="2"/>
-      <c r="L295" s="2"/>
-      <c r="M295" s="2"/>
-      <c r="N295" s="2"/>
-      <c r="O295" s="2"/>
-      <c r="P295" s="2"/>
-      <c r="Q295" s="2"/>
-      <c r="R295" s="2"/>
-      <c r="S295" s="2"/>
-      <c r="T295" s="2"/>
-      <c r="U295" s="2"/>
-      <c r="V295" s="2"/>
-      <c r="W295" s="2"/>
-      <c r="X295" s="2"/>
-      <c r="Y295" s="2"/>
+      <c r="A295" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C295" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1"/>
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+      <c r="J295" s="1"/>
+      <c r="K295" s="1"/>
+      <c r="L295" s="1"/>
+      <c r="M295" s="1"/>
+      <c r="N295" s="1"/>
+      <c r="O295" s="1"/>
+      <c r="P295" s="1"/>
+      <c r="Q295" s="1"/>
+      <c r="R295" s="1"/>
+      <c r="S295" s="1"/>
+      <c r="T295" s="1"/>
+      <c r="U295" s="1"/>
+      <c r="V295" s="1"/>
+      <c r="W295" s="1"/>
+      <c r="X295" s="1"/>
+      <c r="Y295" s="1"/>
     </row>
     <row r="296" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A296" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="B296" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="C296" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>614</v>
+      <c r="A296" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C296" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>620</v>
       </c>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
@@ -13972,17 +13964,17 @@
       <c r="Y296" s="1"/>
     </row>
     <row r="297" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A297" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B297" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="C297" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="D297" s="7" t="s">
-        <v>620</v>
+      <c r="A297" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B297" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C297" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="D297" s="34" t="s">
+        <v>624</v>
       </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
@@ -14007,17 +13999,17 @@
       <c r="Y297" s="1"/>
     </row>
     <row r="298" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A298" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="B298" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C298" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="D298" s="34" t="s">
-        <v>624</v>
+      <c r="A298" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="C298" s="41" t="s">
+        <v>626</v>
+      </c>
+      <c r="D298" s="13" t="s">
+        <v>625</v>
       </c>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
@@ -14043,16 +14035,14 @@
     </row>
     <row r="299" spans="1:25" ht="15.75" customHeight="1">
       <c r="A299" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="B299" s="13" t="s">
-        <v>625</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="B299" s="13"/>
       <c r="C299" s="41" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D299" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1"/>
       <c r="F299" s="1"/>
@@ -14077,83 +14067,83 @@
       <c r="Y299" s="1"/>
     </row>
     <row r="300" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A300" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B300" s="13"/>
-      <c r="C300" s="41" t="s">
-        <v>628</v>
-      </c>
-      <c r="D300" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="E300" s="1"/>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
-      <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
-      <c r="L300" s="1"/>
-      <c r="M300" s="1"/>
-      <c r="N300" s="1"/>
-      <c r="O300" s="1"/>
-      <c r="P300" s="1"/>
-      <c r="Q300" s="1"/>
-      <c r="R300" s="1"/>
-      <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
-      <c r="U300" s="1"/>
-      <c r="V300" s="1"/>
-      <c r="W300" s="1"/>
-      <c r="X300" s="1"/>
-      <c r="Y300" s="1"/>
+      <c r="A300" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="B300" s="9"/>
+      <c r="C300" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="D300" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="2"/>
+      <c r="I300" s="2"/>
+      <c r="J300" s="2"/>
+      <c r="K300" s="2"/>
+      <c r="L300" s="2"/>
+      <c r="M300" s="2"/>
+      <c r="N300" s="2"/>
+      <c r="O300" s="2"/>
+      <c r="P300" s="2"/>
+      <c r="Q300" s="2"/>
+      <c r="R300" s="2"/>
+      <c r="S300" s="2"/>
+      <c r="T300" s="2"/>
+      <c r="U300" s="2"/>
+      <c r="V300" s="2"/>
+      <c r="W300" s="2"/>
+      <c r="X300" s="2"/>
+      <c r="Y300" s="2"/>
     </row>
     <row r="301" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A301" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="B301" s="9"/>
-      <c r="C301" s="34" t="s">
-        <v>630</v>
-      </c>
-      <c r="D301" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="E301" s="2"/>
-      <c r="F301" s="2"/>
-      <c r="G301" s="2"/>
-      <c r="H301" s="2"/>
-      <c r="I301" s="2"/>
-      <c r="J301" s="2"/>
-      <c r="K301" s="2"/>
-      <c r="L301" s="2"/>
-      <c r="M301" s="2"/>
-      <c r="N301" s="2"/>
-      <c r="O301" s="2"/>
-      <c r="P301" s="2"/>
-      <c r="Q301" s="2"/>
-      <c r="R301" s="2"/>
-      <c r="S301" s="2"/>
-      <c r="T301" s="2"/>
-      <c r="U301" s="2"/>
-      <c r="V301" s="2"/>
-      <c r="W301" s="2"/>
-      <c r="X301" s="2"/>
-      <c r="Y301" s="2"/>
+      <c r="A301" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E301" s="1"/>
+      <c r="F301" s="1"/>
+      <c r="G301" s="1"/>
+      <c r="H301" s="1"/>
+      <c r="I301" s="1"/>
+      <c r="J301" s="1"/>
+      <c r="K301" s="1"/>
+      <c r="L301" s="1"/>
+      <c r="M301" s="1"/>
+      <c r="N301" s="1"/>
+      <c r="O301" s="1"/>
+      <c r="P301" s="1"/>
+      <c r="Q301" s="1"/>
+      <c r="R301" s="1"/>
+      <c r="S301" s="1"/>
+      <c r="T301" s="1"/>
+      <c r="U301" s="1"/>
+      <c r="V301" s="1"/>
+      <c r="W301" s="1"/>
+      <c r="X301" s="1"/>
+      <c r="Y301" s="1"/>
     </row>
     <row r="302" spans="1:25" ht="15.75" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B302" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C302" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
+      </c>
+      <c r="B302" s="3"/>
+      <c r="C302" s="18" t="s">
+        <v>635</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
@@ -14179,14 +14169,14 @@
     </row>
     <row r="303" spans="1:25" ht="15.75" customHeight="1">
       <c r="A303" s="3" t="s">
-        <v>634</v>
+        <v>1044</v>
       </c>
       <c r="B303" s="3"/>
-      <c r="C303" s="18" t="s">
-        <v>635</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>636</v>
+      <c r="C303" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>1046</v>
       </c>
       <c r="E303" s="1"/>
       <c r="F303" s="1"/>
@@ -14211,46 +14201,48 @@
       <c r="Y303" s="1"/>
     </row>
     <row r="304" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A304" s="3" t="s">
-        <v>1049</v>
-      </c>
-      <c r="B304" s="3"/>
-      <c r="C304" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="E304" s="1"/>
-      <c r="F304" s="1"/>
-      <c r="G304" s="1"/>
-      <c r="H304" s="1"/>
-      <c r="I304" s="1"/>
-      <c r="J304" s="1"/>
-      <c r="K304" s="1"/>
-      <c r="L304" s="1"/>
-      <c r="M304" s="1"/>
-      <c r="N304" s="1"/>
-      <c r="O304" s="1"/>
-      <c r="P304" s="1"/>
-      <c r="Q304" s="1"/>
-      <c r="R304" s="1"/>
-      <c r="S304" s="1"/>
-      <c r="T304" s="1"/>
-      <c r="U304" s="1"/>
-      <c r="V304" s="1"/>
-      <c r="W304" s="1"/>
-      <c r="X304" s="1"/>
-      <c r="Y304" s="1"/>
+      <c r="A304" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="B304" s="9"/>
+      <c r="C304" s="10"/>
+      <c r="D304" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="E304" s="2"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
+      <c r="H304" s="2"/>
+      <c r="I304" s="2"/>
+      <c r="J304" s="2"/>
+      <c r="K304" s="2"/>
+      <c r="L304" s="2"/>
+      <c r="M304" s="2"/>
+      <c r="N304" s="2"/>
+      <c r="O304" s="2"/>
+      <c r="P304" s="2"/>
+      <c r="Q304" s="2"/>
+      <c r="R304" s="2"/>
+      <c r="S304" s="2"/>
+      <c r="T304" s="2"/>
+      <c r="U304" s="2"/>
+      <c r="V304" s="2"/>
+      <c r="W304" s="2"/>
+      <c r="X304" s="2"/>
+      <c r="Y304" s="2"/>
     </row>
     <row r="305" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A305" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="B305" s="9"/>
-      <c r="C305" s="10"/>
-      <c r="D305" s="9" t="s">
-        <v>913</v>
+      <c r="A305" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="B305" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="C305" s="68" t="s">
+        <v>916</v>
+      </c>
+      <c r="D305" s="13" t="s">
+        <v>917</v>
       </c>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
@@ -14275,52 +14267,50 @@
       <c r="Y305" s="2"/>
     </row>
     <row r="306" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A306" s="13" t="s">
-        <v>914</v>
-      </c>
-      <c r="B306" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C306" s="68" t="s">
-        <v>916</v>
-      </c>
-      <c r="D306" s="13" t="s">
-        <v>917</v>
-      </c>
-      <c r="E306" s="2"/>
-      <c r="F306" s="2"/>
-      <c r="G306" s="2"/>
-      <c r="H306" s="2"/>
-      <c r="I306" s="2"/>
-      <c r="J306" s="2"/>
-      <c r="K306" s="2"/>
-      <c r="L306" s="2"/>
-      <c r="M306" s="2"/>
-      <c r="N306" s="2"/>
-      <c r="O306" s="2"/>
-      <c r="P306" s="2"/>
-      <c r="Q306" s="2"/>
-      <c r="R306" s="2"/>
-      <c r="S306" s="2"/>
-      <c r="T306" s="2"/>
-      <c r="U306" s="2"/>
-      <c r="V306" s="2"/>
-      <c r="W306" s="2"/>
-      <c r="X306" s="2"/>
-      <c r="Y306" s="2"/>
+      <c r="A306" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="B306" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C306" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D306" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="E306" s="1"/>
+      <c r="F306" s="1"/>
+      <c r="G306" s="1"/>
+      <c r="H306" s="1"/>
+      <c r="I306" s="1"/>
+      <c r="J306" s="1"/>
+      <c r="K306" s="1"/>
+      <c r="L306" s="1"/>
+      <c r="M306" s="1"/>
+      <c r="N306" s="1"/>
+      <c r="O306" s="1"/>
+      <c r="P306" s="1"/>
+      <c r="Q306" s="1"/>
+      <c r="R306" s="1"/>
+      <c r="S306" s="1"/>
+      <c r="T306" s="1"/>
+      <c r="U306" s="1"/>
+      <c r="V306" s="1"/>
+      <c r="W306" s="1"/>
+      <c r="X306" s="1"/>
+      <c r="Y306" s="1"/>
     </row>
     <row r="307" spans="1:25" ht="15.75" customHeight="1">
       <c r="A307" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="B307" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C307" s="11" t="s">
-        <v>639</v>
+        <v>641</v>
+      </c>
+      <c r="B307" s="9"/>
+      <c r="C307" s="10" t="s">
+        <v>642</v>
       </c>
       <c r="D307" s="9" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
@@ -14345,15 +14335,17 @@
       <c r="Y307" s="1"/>
     </row>
     <row r="308" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A308" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="B308" s="9"/>
-      <c r="C308" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="D308" s="9" t="s">
-        <v>643</v>
+      <c r="A308" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="B308" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="C308" s="68" t="s">
+        <v>920</v>
+      </c>
+      <c r="D308" s="13" t="s">
+        <v>918</v>
       </c>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
@@ -14379,16 +14371,16 @@
     </row>
     <row r="309" spans="1:25" ht="15.75" customHeight="1">
       <c r="A309" s="13" t="s">
-        <v>918</v>
+        <v>644</v>
       </c>
       <c r="B309" s="13" t="s">
-        <v>919</v>
-      </c>
-      <c r="C309" s="68" t="s">
-        <v>920</v>
+        <v>645</v>
+      </c>
+      <c r="C309" s="14" t="s">
+        <v>646</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>918</v>
+        <v>644</v>
       </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
@@ -14413,17 +14405,15 @@
       <c r="Y309" s="1"/>
     </row>
     <row r="310" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A310" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="B310" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="C310" s="14" t="s">
-        <v>646</v>
-      </c>
-      <c r="D310" s="13" t="s">
-        <v>644</v>
+      <c r="A310" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="B310" s="9"/>
+      <c r="C310" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="D310" s="9" t="s">
+        <v>647</v>
       </c>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
@@ -14449,14 +14439,14 @@
     </row>
     <row r="311" spans="1:25" ht="15.75" customHeight="1">
       <c r="A311" s="9" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B311" s="9"/>
-      <c r="C311" s="10" t="s">
-        <v>648</v>
+      <c r="C311" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="D311" s="9" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
@@ -14482,14 +14472,14 @@
     </row>
     <row r="312" spans="1:25" ht="15.75" customHeight="1">
       <c r="A312" s="9" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B312" s="9"/>
-      <c r="C312" s="11" t="s">
-        <v>650</v>
+      <c r="C312" s="10" t="s">
+        <v>652</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
@@ -14515,14 +14505,14 @@
     </row>
     <row r="313" spans="1:25" ht="15.75" customHeight="1">
       <c r="A313" s="9" t="s">
-        <v>651</v>
+        <v>851</v>
       </c>
       <c r="B313" s="9"/>
       <c r="C313" s="10" t="s">
-        <v>652</v>
+        <v>852</v>
       </c>
       <c r="D313" s="9" t="s">
-        <v>651</v>
+        <v>851</v>
       </c>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
@@ -14548,14 +14538,16 @@
     </row>
     <row r="314" spans="1:25" ht="15.75" customHeight="1">
       <c r="A314" s="9" t="s">
-        <v>851</v>
-      </c>
-      <c r="B314" s="9"/>
-      <c r="C314" s="10" t="s">
-        <v>852</v>
+        <v>653</v>
+      </c>
+      <c r="B314" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C314" s="11" t="s">
+        <v>655</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>851</v>
+        <v>653</v>
       </c>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
@@ -14581,16 +14573,14 @@
     </row>
     <row r="315" spans="1:25" ht="15.75" customHeight="1">
       <c r="A315" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="B315" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="C315" s="11" t="s">
-        <v>655</v>
+        <v>656</v>
+      </c>
+      <c r="B315" s="9"/>
+      <c r="C315" s="16" t="s">
+        <v>657</v>
       </c>
       <c r="D315" s="9" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
@@ -14615,15 +14605,17 @@
       <c r="Y315" s="1"/>
     </row>
     <row r="316" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A316" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="B316" s="9"/>
-      <c r="C316" s="16" t="s">
-        <v>657</v>
-      </c>
-      <c r="D316" s="9" t="s">
-        <v>656</v>
+      <c r="A316" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="B316" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="C316" s="68" t="s">
+        <v>923</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>921</v>
       </c>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
@@ -14648,17 +14640,17 @@
       <c r="Y316" s="1"/>
     </row>
     <row r="317" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A317" s="13" t="s">
-        <v>921</v>
-      </c>
-      <c r="B317" s="13" t="s">
-        <v>922</v>
-      </c>
-      <c r="C317" s="68" t="s">
-        <v>923</v>
-      </c>
-      <c r="D317" s="13" t="s">
-        <v>921</v>
+      <c r="A317" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C317" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
@@ -14683,50 +14675,50 @@
       <c r="Y317" s="1"/>
     </row>
     <row r="318" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A318" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="B318" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="C318" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="D318" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="E318" s="1"/>
-      <c r="F318" s="1"/>
-      <c r="G318" s="1"/>
-      <c r="H318" s="1"/>
-      <c r="I318" s="1"/>
-      <c r="J318" s="1"/>
-      <c r="K318" s="1"/>
-      <c r="L318" s="1"/>
-      <c r="M318" s="1"/>
-      <c r="N318" s="1"/>
-      <c r="O318" s="1"/>
-      <c r="P318" s="1"/>
-      <c r="Q318" s="1"/>
-      <c r="R318" s="1"/>
-      <c r="S318" s="1"/>
-      <c r="T318" s="1"/>
-      <c r="U318" s="1"/>
-      <c r="V318" s="1"/>
-      <c r="W318" s="1"/>
-      <c r="X318" s="1"/>
-      <c r="Y318" s="1"/>
+      <c r="A318" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="B318" s="9"/>
+      <c r="C318" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="D318" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E318" s="2"/>
+      <c r="F318" s="2"/>
+      <c r="G318" s="2"/>
+      <c r="H318" s="2"/>
+      <c r="I318" s="2"/>
+      <c r="J318" s="2"/>
+      <c r="K318" s="2"/>
+      <c r="L318" s="2"/>
+      <c r="M318" s="2"/>
+      <c r="N318" s="2"/>
+      <c r="O318" s="2"/>
+      <c r="P318" s="2"/>
+      <c r="Q318" s="2"/>
+      <c r="R318" s="2"/>
+      <c r="S318" s="2"/>
+      <c r="T318" s="2"/>
+      <c r="U318" s="2"/>
+      <c r="V318" s="2"/>
+      <c r="W318" s="2"/>
+      <c r="X318" s="2"/>
+      <c r="Y318" s="2"/>
     </row>
     <row r="319" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A319" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="B319" s="9"/>
-      <c r="C319" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="D319" s="9" t="s">
-        <v>658</v>
+      <c r="A319" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C319" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>985</v>
       </c>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
@@ -14752,16 +14744,14 @@
     </row>
     <row r="320" spans="1:25" ht="15.75" customHeight="1">
       <c r="A320" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>988</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="B320" s="3"/>
       <c r="C320" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>987</v>
+        <v>664</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
@@ -14787,49 +14777,49 @@
     </row>
     <row r="321" spans="1:25" ht="15.75" customHeight="1">
       <c r="A321" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B321" s="3"/>
+        <v>1008</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1009</v>
+      </c>
       <c r="C321" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="E321" s="2"/>
-      <c r="F321" s="2"/>
-      <c r="G321" s="2"/>
-      <c r="H321" s="2"/>
-      <c r="I321" s="2"/>
-      <c r="J321" s="2"/>
-      <c r="K321" s="2"/>
-      <c r="L321" s="2"/>
-      <c r="M321" s="2"/>
-      <c r="N321" s="2"/>
-      <c r="O321" s="2"/>
-      <c r="P321" s="2"/>
-      <c r="Q321" s="2"/>
-      <c r="R321" s="2"/>
-      <c r="S321" s="2"/>
-      <c r="T321" s="2"/>
-      <c r="U321" s="2"/>
-      <c r="V321" s="2"/>
-      <c r="W321" s="2"/>
-      <c r="X321" s="2"/>
-      <c r="Y321" s="2"/>
+        <v>1010</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E321" s="1"/>
+      <c r="F321" s="1"/>
+      <c r="G321" s="1"/>
+      <c r="H321" s="1"/>
+      <c r="I321" s="1"/>
+      <c r="J321" s="1"/>
+      <c r="K321" s="1"/>
+      <c r="L321" s="1"/>
+      <c r="M321" s="1"/>
+      <c r="N321" s="1"/>
+      <c r="O321" s="1"/>
+      <c r="P321" s="1"/>
+      <c r="Q321" s="1"/>
+      <c r="R321" s="1"/>
+      <c r="S321" s="1"/>
+      <c r="T321" s="1"/>
+      <c r="U321" s="1"/>
+      <c r="V321" s="1"/>
+      <c r="W321" s="1"/>
+      <c r="X321" s="1"/>
+      <c r="Y321" s="1"/>
     </row>
     <row r="322" spans="1:25" ht="15.75" customHeight="1">
       <c r="A322" s="3" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B322" s="3" t="s">
-        <v>1014</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="B322" s="3"/>
       <c r="C322" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>1013</v>
+        <v>667</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
@@ -14854,15 +14844,17 @@
       <c r="Y322" s="1"/>
     </row>
     <row r="323" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A323" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B323" s="3"/>
-      <c r="C323" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>666</v>
+      <c r="A323" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="C323" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="D323" s="9" t="s">
+        <v>676</v>
       </c>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
@@ -14887,17 +14879,17 @@
       <c r="Y323" s="1"/>
     </row>
     <row r="324" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A324" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B324" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="C324" s="45" t="s">
-        <v>675</v>
-      </c>
-      <c r="D324" s="9" t="s">
-        <v>676</v>
+      <c r="A324" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B324" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="C324" s="46" t="s">
+        <v>679</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>680</v>
       </c>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
@@ -14922,17 +14914,17 @@
       <c r="Y324" s="1"/>
     </row>
     <row r="325" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A325" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="B325" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="C325" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="D325" s="13" t="s">
-        <v>680</v>
+      <c r="A325" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="C325" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D325" s="9" t="s">
+        <v>684</v>
       </c>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
@@ -14957,17 +14949,15 @@
       <c r="Y325" s="1"/>
     </row>
     <row r="326" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A326" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="B326" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="C326" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="D326" s="9" t="s">
-        <v>684</v>
+      <c r="A326" s="13" t="s">
+        <v>685</v>
+      </c>
+      <c r="B326" s="13"/>
+      <c r="C326" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>687</v>
       </c>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
@@ -14992,15 +14982,17 @@
       <c r="Y326" s="1"/>
     </row>
     <row r="327" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A327" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B327" s="13"/>
-      <c r="C327" s="14" t="s">
-        <v>686</v>
-      </c>
-      <c r="D327" s="13" t="s">
-        <v>687</v>
+      <c r="A327" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>668</v>
       </c>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
@@ -15025,17 +15017,15 @@
       <c r="Y327" s="1"/>
     </row>
     <row r="328" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A328" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B328" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C328" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D328" s="7" t="s">
-        <v>668</v>
+      <c r="A328" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B328" s="9"/>
+      <c r="C328" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="D328" s="9" t="s">
+        <v>671</v>
       </c>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
@@ -15061,14 +15051,14 @@
     </row>
     <row r="329" spans="1:25" ht="15.75" customHeight="1">
       <c r="A329" s="9" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B329" s="9"/>
-      <c r="C329" s="11" t="s">
-        <v>672</v>
+      <c r="C329" s="10" t="s">
+        <v>689</v>
       </c>
       <c r="D329" s="9" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
@@ -15094,14 +15084,16 @@
     </row>
     <row r="330" spans="1:25" ht="15.75" customHeight="1">
       <c r="A330" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B330" s="9"/>
-      <c r="C330" s="10" t="s">
-        <v>689</v>
+        <v>690</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>692</v>
       </c>
       <c r="D330" s="9" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
@@ -15127,16 +15119,14 @@
     </row>
     <row r="331" spans="1:25" ht="15.75" customHeight="1">
       <c r="A331" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B331" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C331" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
+      </c>
+      <c r="B331" s="9"/>
+      <c r="C331" s="10" t="s">
+        <v>844</v>
       </c>
       <c r="D331" s="9" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
@@ -15161,15 +15151,17 @@
       <c r="Y331" s="1"/>
     </row>
     <row r="332" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A332" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B332" s="9"/>
-      <c r="C332" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="D332" s="9" t="s">
-        <v>695</v>
+      <c r="A332" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>1011</v>
       </c>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
@@ -15194,17 +15186,15 @@
       <c r="Y332" s="1"/>
     </row>
     <row r="333" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A333" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B333" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C333" s="3" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>1016</v>
+      <c r="A333" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="B333" s="13"/>
+      <c r="C333" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D333" s="13" t="s">
+        <v>696</v>
       </c>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
@@ -15230,49 +15220,51 @@
     </row>
     <row r="334" spans="1:25" ht="15.75" customHeight="1">
       <c r="A334" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B334" s="13"/>
-      <c r="C334" s="22" t="s">
-        <v>697</v>
+        <v>698</v>
+      </c>
+      <c r="B334" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="C334" s="14" t="s">
+        <v>700</v>
       </c>
       <c r="D334" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="E334" s="1"/>
-      <c r="F334" s="1"/>
-      <c r="G334" s="1"/>
-      <c r="H334" s="1"/>
-      <c r="I334" s="1"/>
-      <c r="J334" s="1"/>
-      <c r="K334" s="1"/>
-      <c r="L334" s="1"/>
-      <c r="M334" s="1"/>
-      <c r="N334" s="1"/>
-      <c r="O334" s="1"/>
-      <c r="P334" s="1"/>
-      <c r="Q334" s="1"/>
-      <c r="R334" s="1"/>
-      <c r="S334" s="1"/>
-      <c r="T334" s="1"/>
-      <c r="U334" s="1"/>
-      <c r="V334" s="1"/>
-      <c r="W334" s="1"/>
-      <c r="X334" s="1"/>
-      <c r="Y334" s="1"/>
+        <v>698</v>
+      </c>
+      <c r="E334" s="2"/>
+      <c r="F334" s="2"/>
+      <c r="G334" s="2"/>
+      <c r="H334" s="2"/>
+      <c r="I334" s="2"/>
+      <c r="J334" s="2"/>
+      <c r="K334" s="2"/>
+      <c r="L334" s="2"/>
+      <c r="M334" s="2"/>
+      <c r="N334" s="2"/>
+      <c r="O334" s="2"/>
+      <c r="P334" s="2"/>
+      <c r="Q334" s="2"/>
+      <c r="R334" s="2"/>
+      <c r="S334" s="2"/>
+      <c r="T334" s="2"/>
+      <c r="U334" s="2"/>
+      <c r="V334" s="2"/>
+      <c r="W334" s="2"/>
+      <c r="X334" s="2"/>
+      <c r="Y334" s="2"/>
     </row>
     <row r="335" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A335" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="B335" s="13" t="s">
-        <v>699</v>
-      </c>
-      <c r="C335" s="14" t="s">
-        <v>700</v>
-      </c>
-      <c r="D335" s="13" t="s">
-        <v>698</v>
+      <c r="A335" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B335" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C335" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D335" s="9" t="s">
+        <v>701</v>
       </c>
       <c r="E335" s="2"/>
       <c r="F335" s="2"/>
@@ -15297,52 +15289,52 @@
       <c r="Y335" s="2"/>
     </row>
     <row r="336" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A336" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B336" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="C336" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D336" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="E336" s="2"/>
-      <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
-      <c r="H336" s="2"/>
-      <c r="I336" s="2"/>
-      <c r="J336" s="2"/>
-      <c r="K336" s="2"/>
-      <c r="L336" s="2"/>
-      <c r="M336" s="2"/>
-      <c r="N336" s="2"/>
-      <c r="O336" s="2"/>
-      <c r="P336" s="2"/>
-      <c r="Q336" s="2"/>
-      <c r="R336" s="2"/>
-      <c r="S336" s="2"/>
-      <c r="T336" s="2"/>
-      <c r="U336" s="2"/>
-      <c r="V336" s="2"/>
-      <c r="W336" s="2"/>
-      <c r="X336" s="2"/>
-      <c r="Y336" s="2"/>
+      <c r="A336" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C336" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E336" s="1"/>
+      <c r="F336" s="1"/>
+      <c r="G336" s="1"/>
+      <c r="H336" s="1"/>
+      <c r="I336" s="1"/>
+      <c r="J336" s="1"/>
+      <c r="K336" s="1"/>
+      <c r="L336" s="1"/>
+      <c r="M336" s="1"/>
+      <c r="N336" s="1"/>
+      <c r="O336" s="1"/>
+      <c r="P336" s="1"/>
+      <c r="Q336" s="1"/>
+      <c r="R336" s="1"/>
+      <c r="S336" s="1"/>
+      <c r="T336" s="1"/>
+      <c r="U336" s="1"/>
+      <c r="V336" s="1"/>
+      <c r="W336" s="1"/>
+      <c r="X336" s="1"/>
+      <c r="Y336" s="1"/>
     </row>
     <row r="337" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A337" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C337" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="D337" s="1" t="s">
-        <v>1019</v>
+      <c r="A337" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B337" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="C337" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="D337" s="9" t="s">
+        <v>704</v>
       </c>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
@@ -15367,87 +15359,87 @@
       <c r="Y337" s="1"/>
     </row>
     <row r="338" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A338" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="B338" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="C338" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D338" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="E338" s="1"/>
-      <c r="F338" s="1"/>
-      <c r="G338" s="1"/>
-      <c r="H338" s="1"/>
-      <c r="I338" s="1"/>
-      <c r="J338" s="1"/>
-      <c r="K338" s="1"/>
-      <c r="L338" s="1"/>
-      <c r="M338" s="1"/>
-      <c r="N338" s="1"/>
-      <c r="O338" s="1"/>
-      <c r="P338" s="1"/>
-      <c r="Q338" s="1"/>
-      <c r="R338" s="1"/>
-      <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
-      <c r="U338" s="1"/>
-      <c r="V338" s="1"/>
-      <c r="W338" s="1"/>
-      <c r="X338" s="1"/>
-      <c r="Y338" s="1"/>
+      <c r="A338" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="E338" s="2"/>
+      <c r="F338" s="2"/>
+      <c r="G338" s="2"/>
+      <c r="H338" s="2"/>
+      <c r="I338" s="2"/>
+      <c r="J338" s="2"/>
+      <c r="K338" s="2"/>
+      <c r="L338" s="2"/>
+      <c r="M338" s="2"/>
+      <c r="N338" s="2"/>
+      <c r="O338" s="2"/>
+      <c r="P338" s="2"/>
+      <c r="Q338" s="2"/>
+      <c r="R338" s="2"/>
+      <c r="S338" s="2"/>
+      <c r="T338" s="2"/>
+      <c r="U338" s="2"/>
+      <c r="V338" s="2"/>
+      <c r="W338" s="2"/>
+      <c r="X338" s="2"/>
+      <c r="Y338" s="2"/>
     </row>
     <row r="339" spans="1:25" ht="15.75" customHeight="1">
       <c r="A339" s="3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C339" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E339" s="2"/>
-      <c r="F339" s="2"/>
-      <c r="G339" s="2"/>
-      <c r="H339" s="2"/>
-      <c r="I339" s="2"/>
-      <c r="J339" s="2"/>
-      <c r="K339" s="2"/>
-      <c r="L339" s="2"/>
-      <c r="M339" s="2"/>
-      <c r="N339" s="2"/>
-      <c r="O339" s="2"/>
-      <c r="P339" s="2"/>
-      <c r="Q339" s="2"/>
-      <c r="R339" s="2"/>
-      <c r="S339" s="2"/>
-      <c r="T339" s="2"/>
-      <c r="U339" s="2"/>
-      <c r="V339" s="2"/>
-      <c r="W339" s="2"/>
-      <c r="X339" s="2"/>
-      <c r="Y339" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="E339" s="1"/>
+      <c r="F339" s="1"/>
+      <c r="G339" s="1"/>
+      <c r="H339" s="1"/>
+      <c r="I339" s="1"/>
+      <c r="J339" s="1"/>
+      <c r="K339" s="1"/>
+      <c r="L339" s="1"/>
+      <c r="M339" s="1"/>
+      <c r="N339" s="1"/>
+      <c r="O339" s="1"/>
+      <c r="P339" s="1"/>
+      <c r="Q339" s="1"/>
+      <c r="R339" s="1"/>
+      <c r="S339" s="1"/>
+      <c r="T339" s="1"/>
+      <c r="U339" s="1"/>
+      <c r="V339" s="1"/>
+      <c r="W339" s="1"/>
+      <c r="X339" s="1"/>
+      <c r="Y339" s="1"/>
     </row>
     <row r="340" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A340" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B340" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="C340" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="D340" s="3" t="s">
-        <v>710</v>
+      <c r="A340" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C340" s="47" t="s">
+        <v>715</v>
+      </c>
+      <c r="D340" s="5" t="s">
+        <v>716</v>
       </c>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
@@ -15473,16 +15465,14 @@
     </row>
     <row r="341" spans="1:25" ht="15.75" customHeight="1">
       <c r="A341" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="B341" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="C341" s="47" t="s">
-        <v>715</v>
+        <v>717</v>
+      </c>
+      <c r="B341" s="5"/>
+      <c r="C341" s="6" t="s">
+        <v>718</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
@@ -15507,669 +15497,642 @@
       <c r="Y341" s="1"/>
     </row>
     <row r="342" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A342" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="B342" s="5"/>
-      <c r="C342" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="D342" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="E342" s="1"/>
-      <c r="F342" s="1"/>
-      <c r="G342" s="1"/>
-      <c r="H342" s="1"/>
-      <c r="I342" s="1"/>
-      <c r="J342" s="1"/>
-      <c r="K342" s="1"/>
-      <c r="L342" s="1"/>
-      <c r="M342" s="1"/>
-      <c r="N342" s="1"/>
-      <c r="O342" s="1"/>
-      <c r="P342" s="1"/>
-      <c r="Q342" s="1"/>
-      <c r="R342" s="1"/>
-      <c r="S342" s="1"/>
-      <c r="T342" s="1"/>
-      <c r="U342" s="1"/>
-      <c r="V342" s="1"/>
-      <c r="W342" s="1"/>
-      <c r="X342" s="1"/>
-      <c r="Y342" s="1"/>
+      <c r="A342" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C342" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D342" s="3" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="343" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A343" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="B343" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="C343" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="D343" s="3" t="s">
-        <v>719</v>
+      <c r="A343" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="B343" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="C343" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="D343" s="9" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="344" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A344" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="B344" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="C344" s="11" t="s">
-        <v>724</v>
-      </c>
-      <c r="D344" s="9" t="s">
-        <v>722</v>
+      <c r="A344" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D344" s="3" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="345" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A345" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="B345" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="C345" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="D345" s="3" t="s">
-        <v>727</v>
+      <c r="A345" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="B345" s="5"/>
+      <c r="C345" s="47" t="s">
+        <v>729</v>
+      </c>
+      <c r="D345" s="5" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="346" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A346" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="B346" s="5"/>
-      <c r="C346" s="47" t="s">
-        <v>729</v>
-      </c>
-      <c r="D346" s="5" t="s">
-        <v>728</v>
+      <c r="A346" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B346" s="3"/>
+      <c r="C346" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="347" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A347" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B347" s="3"/>
-      <c r="C347" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="D347" s="3" t="s">
-        <v>730</v>
+      <c r="A347" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B347" s="9"/>
+      <c r="C347" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="D347" s="9" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="348" spans="1:25" ht="15.75" customHeight="1">
       <c r="A348" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="B348" s="9"/>
+        <v>734</v>
+      </c>
+      <c r="B348" s="9" t="s">
+        <v>735</v>
+      </c>
       <c r="C348" s="10" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D348" s="9" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="349" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A349" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="B349" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="C349" s="10" t="s">
-        <v>736</v>
-      </c>
-      <c r="D349" s="9" t="s">
-        <v>734</v>
+      <c r="A349" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C349" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="D349" s="5" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="350" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A350" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="B350" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="C350" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="D350" s="5" t="s">
-        <v>737</v>
+      <c r="A350" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="351" spans="1:25" ht="15.75" customHeight="1">
       <c r="A351" s="3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="352" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A352" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="B352" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="C352" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="D352" s="3" t="s">
-        <v>743</v>
+      <c r="A352" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B352" s="5"/>
+      <c r="C352" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1">
       <c r="A353" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="B353" s="5"/>
-      <c r="C353" s="6" t="s">
-        <v>746</v>
+        <v>748</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C353" s="30" t="s">
+        <v>750</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A354" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="B354" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="C354" s="30" t="s">
-        <v>750</v>
-      </c>
-      <c r="D354" s="5" t="s">
-        <v>748</v>
+      <c r="A354" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1">
       <c r="A355" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A356" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="B356" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="C356" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D356" s="3" t="s">
-        <v>754</v>
+      <c r="A356" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A357" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="B357" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="C357" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="D357" s="5" t="s">
-        <v>757</v>
+      <c r="A357" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B357" s="7"/>
+      <c r="C357" s="31" t="s">
+        <v>761</v>
+      </c>
+      <c r="D357" s="7" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A358" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="B358" s="7"/>
-      <c r="C358" s="31" t="s">
-        <v>761</v>
-      </c>
-      <c r="D358" s="7" t="s">
-        <v>762</v>
+      <c r="A358" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1">
       <c r="A359" s="3" t="s">
-        <v>1022</v>
+        <v>763</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>1023</v>
+        <v>764</v>
       </c>
       <c r="C359" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>1022</v>
+        <v>765</v>
+      </c>
+      <c r="D359" s="3" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A360" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="B360" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C360" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>763</v>
+      <c r="A360" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="D360" s="5" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A361" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="B361" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="C361" s="6" t="s">
-        <v>768</v>
-      </c>
-      <c r="D361" s="5" t="s">
-        <v>769</v>
+      <c r="A361" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C361" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D361" s="3" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A362" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="C362" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="D362" s="3" t="s">
-        <v>770</v>
+      <c r="A362" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B362" s="9"/>
+      <c r="C362" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="D362" s="9" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1">
       <c r="A363" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="B363" s="9"/>
-      <c r="C363" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
+      </c>
+      <c r="B363" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="C363" s="10" t="s">
+        <v>777</v>
       </c>
       <c r="D363" s="9" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1">
       <c r="A364" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="B364" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="C364" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
+      </c>
+      <c r="B364" s="9"/>
+      <c r="C364" s="11" t="s">
+        <v>779</v>
       </c>
       <c r="D364" s="9" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A365" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="B365" s="9"/>
-      <c r="C365" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="D365" s="9" t="s">
-        <v>780</v>
+      <c r="A365" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C365" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1">
       <c r="A366" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="B366" s="7" t="s">
-        <v>784</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="B366" s="7"/>
       <c r="C366" s="8" t="s">
-        <v>170</v>
+        <v>782</v>
       </c>
       <c r="D366" s="7" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A367" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="B367" s="7"/>
-      <c r="C367" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="D367" s="7" t="s">
-        <v>781</v>
+      <c r="A367" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="B367" s="5"/>
+      <c r="C367" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="D367" s="5" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1">
       <c r="A368" s="5" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B368" s="5"/>
       <c r="C368" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1">
       <c r="A369" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B369" s="5"/>
       <c r="C369" s="6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1">
       <c r="A370" s="5" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B370" s="5"/>
       <c r="C370" s="6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1">
       <c r="A371" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="B371" s="5"/>
+        <v>800</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>801</v>
+      </c>
       <c r="C371" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1">
       <c r="A372" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B372" s="5" t="s">
-        <v>801</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="B372" s="5"/>
       <c r="C372" s="6" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D372" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A373" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="B373" s="5"/>
-      <c r="C373" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="D373" s="5" t="s">
-        <v>806</v>
+      <c r="A373" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="B373" s="7"/>
+      <c r="C373" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A374" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="B374" s="7"/>
-      <c r="C374" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="D374" s="7" t="s">
-        <v>807</v>
+      <c r="A374" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B374" s="5"/>
+      <c r="C374" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="D374" s="5" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A375" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="B375" s="5"/>
-      <c r="C375" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="D375" s="5" t="s">
-        <v>809</v>
+      <c r="A375" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C375" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A376" s="3" t="s">
+      <c r="A376" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D376" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A377" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B377" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="B376" s="3" t="s">
+      <c r="C377" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="C376" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A377" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="B377" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="C377" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="D377" s="5" t="s">
-        <v>811</v>
+      <c r="D377" s="1" t="s">
+        <v>1024</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1">
       <c r="A378" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B378" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C378" s="3" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>1029</v>
+        <v>814</v>
+      </c>
+      <c r="B378" s="3"/>
+      <c r="C378" s="50" t="s">
+        <v>815</v>
+      </c>
+      <c r="D378" s="3" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A379" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B379" s="3"/>
-      <c r="C379" s="12" t="s">
-        <v>815</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>814</v>
+      <c r="A379" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="B379" s="9"/>
+      <c r="C379" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="D379" s="9" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1">
       <c r="A380" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="B380" s="9"/>
-      <c r="C380" s="10" t="s">
-        <v>817</v>
+        <v>819</v>
+      </c>
+      <c r="B380" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="C380" s="11" t="s">
+        <v>821</v>
       </c>
       <c r="D380" s="9" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A381" s="9" t="s">
-        <v>819</v>
-      </c>
-      <c r="B381" s="9" t="s">
-        <v>820</v>
-      </c>
-      <c r="C381" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="D381" s="9" t="s">
-        <v>819</v>
+      <c r="A381" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="B381" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="C381" s="53" t="s">
+        <v>926</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A382" s="7" t="s">
-        <v>924</v>
-      </c>
-      <c r="B382" s="7" t="s">
-        <v>925</v>
-      </c>
-      <c r="C382" s="53" t="s">
-        <v>926</v>
-      </c>
-      <c r="D382" s="7" t="s">
-        <v>924</v>
+      <c r="A382" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C382" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A383" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B383" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C383" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>822</v>
+      <c r="A383" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="D383" s="9" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A384" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="B384" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="C384" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="D384" s="9" t="s">
-        <v>825</v>
+      <c r="A384" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="B384" s="3"/>
+      <c r="C384" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A385" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="B385" s="3"/>
-      <c r="C385" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="D385" s="3" t="s">
-        <v>828</v>
+      <c r="A385" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="D385" s="48" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A386" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="D386" s="48" t="s">
-        <v>830</v>
+      <c r="A386" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C386" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A387" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="B387" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="C387" s="12" t="s">
-        <v>834</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>832</v>
+      <c r="A387" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="B387" s="5"/>
+      <c r="C387" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="D387" s="49" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A388" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="B388" s="5"/>
-      <c r="C388" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="D388" s="49" t="s">
-        <v>837</v>
+      <c r="A388" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A389" s="3" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B389" s="3" t="s">
-        <v>1033</v>
-      </c>
-      <c r="C389" s="3" t="s">
-        <v>1034</v>
-      </c>
-      <c r="D389" s="1" t="s">
-        <v>1032</v>
+      <c r="A389" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="B389" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="C389" s="69" t="s">
+        <v>929</v>
+      </c>
+      <c r="D389" s="70" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A390" s="7" t="s">
-        <v>927</v>
-      </c>
-      <c r="B390" s="7" t="s">
-        <v>928</v>
-      </c>
-      <c r="C390" s="69" t="s">
-        <v>929</v>
-      </c>
-      <c r="D390" s="70" t="s">
-        <v>927</v>
-      </c>
+      <c r="A390" s="3"/>
+      <c r="B390" s="3"/>
+      <c r="C390" s="3"/>
+      <c r="D390" s="1"/>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1">
       <c r="A391" s="3"/>
@@ -21348,12 +21311,6 @@
       <c r="B1253" s="3"/>
       <c r="C1253" s="3"/>
       <c r="D1253" s="1"/>
-    </row>
-    <row r="1254" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1254" s="3"/>
-      <c r="B1254" s="3"/>
-      <c r="C1254" s="3"/>
-      <c r="D1254" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21373,33 +21330,33 @@
     <hyperlink ref="C27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
     <hyperlink ref="C29" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="C30" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="C31" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="C33" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="C34" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="C36" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="C37" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="C38" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="C41" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="C44" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="C45" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="C47" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="C48" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="C46" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="C50" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="C51" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
-    <hyperlink ref="C52" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
-    <hyperlink ref="C53" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
-    <hyperlink ref="C54" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
-    <hyperlink ref="C57" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
-    <hyperlink ref="C58" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
-    <hyperlink ref="C59" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
-    <hyperlink ref="C61" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
-    <hyperlink ref="C64" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
-    <hyperlink ref="C66" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
-    <hyperlink ref="C67" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
-    <hyperlink ref="C68" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
-    <hyperlink ref="C69" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
-    <hyperlink ref="C72" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
+    <hyperlink ref="C32" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C34" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C35" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C37" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C38" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C39" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C42" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C45" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C46" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C48" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C49" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C47" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="C51" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="C52" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
+    <hyperlink ref="C53" r:id="rId31" xr:uid="{00000000-0004-0000-0000-00001E000000}"/>
+    <hyperlink ref="C54" r:id="rId32" xr:uid="{00000000-0004-0000-0000-00001F000000}"/>
+    <hyperlink ref="C55" r:id="rId33" xr:uid="{00000000-0004-0000-0000-000020000000}"/>
+    <hyperlink ref="C58" r:id="rId34" xr:uid="{00000000-0004-0000-0000-000021000000}"/>
+    <hyperlink ref="C59" r:id="rId35" xr:uid="{00000000-0004-0000-0000-000022000000}"/>
+    <hyperlink ref="C60" r:id="rId36" xr:uid="{00000000-0004-0000-0000-000023000000}"/>
+    <hyperlink ref="C62" r:id="rId37" xr:uid="{00000000-0004-0000-0000-000024000000}"/>
+    <hyperlink ref="C65" r:id="rId38" xr:uid="{00000000-0004-0000-0000-000025000000}"/>
+    <hyperlink ref="C67" r:id="rId39" xr:uid="{00000000-0004-0000-0000-000026000000}"/>
+    <hyperlink ref="C68" r:id="rId40" xr:uid="{00000000-0004-0000-0000-000027000000}"/>
+    <hyperlink ref="C69" r:id="rId41" xr:uid="{00000000-0004-0000-0000-000028000000}"/>
+    <hyperlink ref="C70" r:id="rId42" xr:uid="{00000000-0004-0000-0000-000029000000}"/>
+    <hyperlink ref="C73" r:id="rId43" xr:uid="{00000000-0004-0000-0000-00002A000000}"/>
     <hyperlink ref="C77" r:id="rId44" xr:uid="{00000000-0004-0000-0000-00002B000000}"/>
     <hyperlink ref="C78" r:id="rId45" xr:uid="{00000000-0004-0000-0000-00002D000000}"/>
     <hyperlink ref="C79" r:id="rId46" xr:uid="{00000000-0004-0000-0000-00002E000000}"/>
@@ -21487,117 +21444,117 @@
     <hyperlink ref="C211" r:id="rId128" xr:uid="{00000000-0004-0000-0000-000081000000}"/>
     <hyperlink ref="C212" r:id="rId129" xr:uid="{00000000-0004-0000-0000-000082000000}"/>
     <hyperlink ref="C213" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
-    <hyperlink ref="C56" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
+    <hyperlink ref="C57" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C216" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C223" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C228" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C231" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C232" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C233" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C235" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C236" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C237" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C240" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C241" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C242" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C244" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C245" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C246" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C248" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C250" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C251" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C252" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C254" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C257" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C258" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C259" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C263" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C264" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C267" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C268" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C270" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C271" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C249" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C273" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C274" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C280" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C281" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C284" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C287" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C285" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C288" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C290" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C293" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C294" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C295" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C297" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C298" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C299" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C300" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C303" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C307" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C308" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C310" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C311" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C312" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C315" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C316" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C318" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C328" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C329" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C324" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C325" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C327" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C330" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C331" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C334" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C335" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C340" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C341" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C342" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C344" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C346" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C348" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C350" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C353" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C354" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C357" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C358" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C361" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C362" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C363" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C365" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C367" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C366" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C222" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C227" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C230" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C231" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C232" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C234" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C235" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C236" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C239" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C240" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C241" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C243" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C244" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C245" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C247" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C249" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C250" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C251" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C253" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C256" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C257" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C258" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C262" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C263" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C266" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C267" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C269" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C270" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C248" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C272" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C273" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C279" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C280" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C283" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C286" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C284" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C287" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C289" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C292" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C293" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C294" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C296" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C297" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C298" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C299" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C302" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C306" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C307" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C309" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C310" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C311" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C314" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C315" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C317" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C327" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C328" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C323" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C324" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C326" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C329" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C330" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C333" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C334" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C339" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C340" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C341" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C343" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C345" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C347" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C349" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C352" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C353" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C356" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C357" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C360" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C361" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C362" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C364" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C366" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C365" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C8" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C368" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C369" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C370" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C371" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C372" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C373" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C374" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C375" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C377" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C379" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C381" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C383" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C385" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C386" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C387" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C388" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C367" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C368" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C369" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C370" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C371" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C372" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C373" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C374" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C376" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C378" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C380" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C382" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C384" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C385" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C386" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C387" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="C167" r:id="rId230" xr:uid="{98DDE684-CC21-7C49-B22B-C4F92C88FD93}"/>
-    <hyperlink ref="C226" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
-    <hyperlink ref="C260" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
+    <hyperlink ref="C225" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
+    <hyperlink ref="C259" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
     <hyperlink ref="C133" r:id="rId233" xr:uid="{6B2056CE-BB4C-D74B-A597-EA3A8C5C2030}"/>
     <hyperlink ref="C6" r:id="rId234" xr:uid="{D36410A9-1671-0F4D-A4CE-1789BA83AD03}"/>
     <hyperlink ref="C24" r:id="rId235" xr:uid="{8BADE627-88AB-8344-8C39-BDD2E908CD68}"/>
     <hyperlink ref="C28" r:id="rId236" xr:uid="{9A78F6E5-FAD9-D44F-86D5-32F682810C25}"/>
-    <hyperlink ref="C43" r:id="rId237" xr:uid="{96F374B9-F9B0-DF49-9B55-E293F8DA5DCD}"/>
-    <hyperlink ref="C55" r:id="rId238" xr:uid="{2F24235C-0F55-7242-B0DB-D39FA769533F}"/>
-    <hyperlink ref="C62" r:id="rId239" xr:uid="{5A1146AA-9805-A347-B730-5B0808F11B3B}"/>
-    <hyperlink ref="C73" r:id="rId240" xr:uid="{58F3AE7F-1DA3-6240-91A1-A13FDF65C789}"/>
-    <hyperlink ref="C75" r:id="rId241" xr:uid="{1D033436-520E-E44F-B67A-E62812550F02}"/>
+    <hyperlink ref="C44" r:id="rId237" xr:uid="{96F374B9-F9B0-DF49-9B55-E293F8DA5DCD}"/>
+    <hyperlink ref="C56" r:id="rId238" xr:uid="{2F24235C-0F55-7242-B0DB-D39FA769533F}"/>
+    <hyperlink ref="C63" r:id="rId239" xr:uid="{5A1146AA-9805-A347-B730-5B0808F11B3B}"/>
+    <hyperlink ref="C74" r:id="rId240" xr:uid="{58F3AE7F-1DA3-6240-91A1-A13FDF65C789}"/>
+    <hyperlink ref="C76" r:id="rId241" xr:uid="{1D033436-520E-E44F-B67A-E62812550F02}"/>
     <hyperlink ref="C128" r:id="rId242" xr:uid="{72A990A2-096D-474A-A3C3-4EEBBA8E1841}"/>
     <hyperlink ref="C137" r:id="rId243" xr:uid="{3B616239-7266-2E41-9399-7FA527C68832}"/>
     <hyperlink ref="C147" r:id="rId244" xr:uid="{A0B7F6C6-0B8F-8D4B-B4BC-AE7AECCC68C7}"/>
@@ -21608,20 +21565,22 @@
     <hyperlink ref="C196" r:id="rId249" xr:uid="{B4AAB667-FFFA-F64C-BC79-708CC2119E9B}"/>
     <hyperlink ref="C202" r:id="rId250" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
     <hyperlink ref="C220" r:id="rId251" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
-    <hyperlink ref="C225" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
-    <hyperlink ref="C277" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
-    <hyperlink ref="C283" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
-    <hyperlink ref="C306" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
-    <hyperlink ref="C309" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
-    <hyperlink ref="C317" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C382" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C390" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C224" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
+    <hyperlink ref="C276" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
+    <hyperlink ref="C282" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
+    <hyperlink ref="C305" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
+    <hyperlink ref="C308" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
+    <hyperlink ref="C316" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
+    <hyperlink ref="C381" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C389" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C188" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
+    <hyperlink ref="C215" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
+    <hyperlink ref="C221" r:id="rId262" xr:uid="{8D2B8DC1-9F59-E049-A731-DAB4A3C99261}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId261"/>
+    <tablePart r:id="rId263"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68763133-CCE0-5F45-83FA-B3E2633CBFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97960E61-00F9-3D48-943D-507125F71680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1049">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="1048">
   <si>
     <t>Name</t>
   </si>
@@ -3010,9 +3010,6 @@
   </si>
   <si>
     <t>Nauheim</t>
-  </si>
-  <si>
-    <t>https://www.geonames.org/11922042/kdyne.html</t>
   </si>
   <si>
     <t>Neustadt an der Mettau</t>
@@ -3768,9 +3765,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D389" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D389">
-    <sortCondition ref="D389"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D388" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D388">
+    <sortCondition ref="D388"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -3980,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Y1253"/>
+  <dimension ref="A2:Y1252"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -4210,14 +4207,14 @@
     </row>
     <row r="9" spans="1:25" ht="16">
       <c r="A9" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -4243,16 +4240,16 @@
     </row>
     <row r="10" spans="1:25" ht="16">
       <c r="A10" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>1033</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>1034</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -4377,16 +4374,16 @@
     </row>
     <row r="14" spans="1:25" ht="16">
       <c r="A14" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>1036</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>1037</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -4948,14 +4945,14 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="9" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="11" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>1047</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>1048</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -5014,14 +5011,14 @@
     </row>
     <row r="33" spans="1:25" ht="16">
       <c r="A33" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -5286,14 +5283,14 @@
     </row>
     <row r="41" spans="1:25" ht="16">
       <c r="A41" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -8682,14 +8679,14 @@
     </row>
     <row r="141" spans="1:25" ht="15.75" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -11372,17 +11369,17 @@
       <c r="Y220" s="1"/>
     </row>
     <row r="221" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A221" s="3" t="s">
-        <v>900</v>
-      </c>
-      <c r="B221" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="C221" s="50" t="s">
-        <v>994</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>900</v>
+      <c r="A221" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="C221" s="11" t="s">
+        <v>444</v>
+      </c>
+      <c r="D221" s="9" t="s">
+        <v>442</v>
       </c>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
@@ -11408,16 +11405,16 @@
     </row>
     <row r="222" spans="1:25" ht="15.75" customHeight="1">
       <c r="A222" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C222" s="11" t="s">
-        <v>444</v>
+        <v>446</v>
+      </c>
+      <c r="C222" s="10" t="s">
+        <v>447</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -11442,52 +11439,52 @@
       <c r="Y222" s="1"/>
     </row>
     <row r="223" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A223" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="B223" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C223" s="10" t="s">
-        <v>447</v>
-      </c>
-      <c r="D223" s="9" t="s">
-        <v>445</v>
-      </c>
-      <c r="E223" s="1"/>
-      <c r="F223" s="1"/>
-      <c r="G223" s="1"/>
-      <c r="H223" s="1"/>
-      <c r="I223" s="1"/>
-      <c r="J223" s="1"/>
-      <c r="K223" s="1"/>
-      <c r="L223" s="1"/>
-      <c r="M223" s="1"/>
-      <c r="N223" s="1"/>
-      <c r="O223" s="1"/>
-      <c r="P223" s="1"/>
-      <c r="Q223" s="1"/>
-      <c r="R223" s="1"/>
-      <c r="S223" s="1"/>
-      <c r="T223" s="1"/>
-      <c r="U223" s="1"/>
-      <c r="V223" s="1"/>
-      <c r="W223" s="1"/>
-      <c r="X223" s="1"/>
-      <c r="Y223" s="1"/>
+      <c r="A223" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="C223" s="53" t="s">
+        <v>905</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>903</v>
+      </c>
+      <c r="E223" s="2"/>
+      <c r="F223" s="2"/>
+      <c r="G223" s="2"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="2"/>
+      <c r="U223" s="2"/>
+      <c r="V223" s="2"/>
+      <c r="W223" s="2"/>
+      <c r="X223" s="2"/>
+      <c r="Y223" s="2"/>
     </row>
     <row r="224" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A224" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="B224" s="7" t="s">
-        <v>904</v>
-      </c>
-      <c r="C224" s="53" t="s">
-        <v>905</v>
-      </c>
-      <c r="D224" s="7" t="s">
-        <v>903</v>
+      <c r="A224" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C224" s="50" t="s">
+        <v>841</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>450</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
@@ -11513,51 +11510,49 @@
     </row>
     <row r="225" spans="1:25" ht="15.75" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>448</v>
+        <v>994</v>
       </c>
       <c r="B225" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C225" s="50" t="s">
-        <v>841</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E225" s="2"/>
-      <c r="F225" s="2"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-      <c r="J225" s="2"/>
-      <c r="K225" s="2"/>
-      <c r="L225" s="2"/>
-      <c r="M225" s="2"/>
-      <c r="N225" s="2"/>
-      <c r="O225" s="2"/>
-      <c r="P225" s="2"/>
-      <c r="Q225" s="2"/>
-      <c r="R225" s="2"/>
-      <c r="S225" s="2"/>
-      <c r="T225" s="2"/>
-      <c r="U225" s="2"/>
-      <c r="V225" s="2"/>
-      <c r="W225" s="2"/>
-      <c r="X225" s="2"/>
-      <c r="Y225" s="2"/>
+        <v>995</v>
+      </c>
+      <c r="C225" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="E225" s="1"/>
+      <c r="F225" s="1"/>
+      <c r="G225" s="1"/>
+      <c r="H225" s="1"/>
+      <c r="I225" s="1"/>
+      <c r="J225" s="1"/>
+      <c r="K225" s="1"/>
+      <c r="L225" s="1"/>
+      <c r="M225" s="1"/>
+      <c r="N225" s="1"/>
+      <c r="O225" s="1"/>
+      <c r="P225" s="1"/>
+      <c r="Q225" s="1"/>
+      <c r="R225" s="1"/>
+      <c r="S225" s="1"/>
+      <c r="T225" s="1"/>
+      <c r="U225" s="1"/>
+      <c r="V225" s="1"/>
+      <c r="W225" s="1"/>
+      <c r="X225" s="1"/>
+      <c r="Y225" s="1"/>
     </row>
     <row r="226" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A226" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>996</v>
-      </c>
-      <c r="C226" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>998</v>
+      <c r="A226" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B226" s="9"/>
+      <c r="C226" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="D226" s="34" t="s">
+        <v>453</v>
       </c>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -11582,15 +11577,15 @@
       <c r="Y226" s="1"/>
     </row>
     <row r="227" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A227" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B227" s="9"/>
-      <c r="C227" s="33" t="s">
-        <v>452</v>
-      </c>
-      <c r="D227" s="34" t="s">
-        <v>453</v>
+      <c r="A227" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B227" s="3"/>
+      <c r="C227" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -11615,118 +11610,120 @@
       <c r="Y227" s="1"/>
     </row>
     <row r="228" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A228" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="B228" s="3"/>
-      <c r="C228" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="E228" s="1"/>
-      <c r="F228" s="1"/>
-      <c r="G228" s="1"/>
-      <c r="H228" s="1"/>
-      <c r="I228" s="1"/>
-      <c r="J228" s="1"/>
-      <c r="K228" s="1"/>
-      <c r="L228" s="1"/>
-      <c r="M228" s="1"/>
-      <c r="N228" s="1"/>
-      <c r="O228" s="1"/>
-      <c r="P228" s="1"/>
-      <c r="Q228" s="1"/>
-      <c r="R228" s="1"/>
-      <c r="S228" s="1"/>
-      <c r="T228" s="1"/>
-      <c r="U228" s="1"/>
-      <c r="V228" s="1"/>
-      <c r="W228" s="1"/>
-      <c r="X228" s="1"/>
-      <c r="Y228" s="1"/>
+      <c r="A228" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B228" s="9"/>
+      <c r="C228" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="D228" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="E228" s="2"/>
+      <c r="F228" s="2"/>
+      <c r="G228" s="2"/>
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
+      <c r="J228" s="2"/>
+      <c r="K228" s="2"/>
+      <c r="L228" s="2"/>
+      <c r="M228" s="2"/>
+      <c r="N228" s="2"/>
+      <c r="O228" s="2"/>
+      <c r="P228" s="2"/>
+      <c r="Q228" s="2"/>
+      <c r="R228" s="2"/>
+      <c r="S228" s="2"/>
+      <c r="T228" s="2"/>
+      <c r="U228" s="2"/>
+      <c r="V228" s="2"/>
+      <c r="W228" s="2"/>
+      <c r="X228" s="2"/>
+      <c r="Y228" s="2"/>
     </row>
     <row r="229" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A229" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="B229" s="9"/>
-      <c r="C229" s="10" t="s">
-        <v>458</v>
-      </c>
-      <c r="D229" s="9" t="s">
-        <v>459</v>
-      </c>
-      <c r="E229" s="2"/>
-      <c r="F229" s="2"/>
-      <c r="G229" s="2"/>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
-      <c r="J229" s="2"/>
-      <c r="K229" s="2"/>
-      <c r="L229" s="2"/>
-      <c r="M229" s="2"/>
-      <c r="N229" s="2"/>
-      <c r="O229" s="2"/>
-      <c r="P229" s="2"/>
-      <c r="Q229" s="2"/>
-      <c r="R229" s="2"/>
-      <c r="S229" s="2"/>
-      <c r="T229" s="2"/>
-      <c r="U229" s="2"/>
-      <c r="V229" s="2"/>
-      <c r="W229" s="2"/>
-      <c r="X229" s="2"/>
-      <c r="Y229" s="2"/>
+      <c r="A229" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C229" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="E229" s="1"/>
+      <c r="F229" s="1"/>
+      <c r="G229" s="1"/>
+      <c r="H229" s="1"/>
+      <c r="I229" s="1"/>
+      <c r="J229" s="1"/>
+      <c r="K229" s="1"/>
+      <c r="L229" s="1"/>
+      <c r="M229" s="1"/>
+      <c r="N229" s="1"/>
+      <c r="O229" s="1"/>
+      <c r="P229" s="1"/>
+      <c r="Q229" s="1"/>
+      <c r="R229" s="1"/>
+      <c r="S229" s="1"/>
+      <c r="T229" s="1"/>
+      <c r="U229" s="1"/>
+      <c r="V229" s="1"/>
+      <c r="W229" s="1"/>
+      <c r="X229" s="1"/>
+      <c r="Y229" s="1"/>
     </row>
     <row r="230" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A230" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="B230" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="C230" s="29" t="s">
-        <v>462</v>
-      </c>
-      <c r="D230" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="E230" s="1"/>
-      <c r="F230" s="1"/>
-      <c r="G230" s="1"/>
-      <c r="H230" s="1"/>
-      <c r="I230" s="1"/>
-      <c r="J230" s="1"/>
-      <c r="K230" s="1"/>
-      <c r="L230" s="1"/>
-      <c r="M230" s="1"/>
-      <c r="N230" s="1"/>
-      <c r="O230" s="1"/>
-      <c r="P230" s="1"/>
-      <c r="Q230" s="1"/>
-      <c r="R230" s="1"/>
-      <c r="S230" s="1"/>
-      <c r="T230" s="1"/>
-      <c r="U230" s="1"/>
-      <c r="V230" s="1"/>
-      <c r="W230" s="1"/>
-      <c r="X230" s="1"/>
-      <c r="Y230" s="1"/>
+      <c r="A230" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="E230" s="2"/>
+      <c r="F230" s="2"/>
+      <c r="G230" s="2"/>
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
+      <c r="J230" s="2"/>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2"/>
+      <c r="M230" s="2"/>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
+      <c r="P230" s="2"/>
+      <c r="Q230" s="2"/>
+      <c r="R230" s="2"/>
+      <c r="S230" s="2"/>
+      <c r="T230" s="2"/>
+      <c r="U230" s="2"/>
+      <c r="V230" s="2"/>
+      <c r="W230" s="2"/>
+      <c r="X230" s="2"/>
+      <c r="Y230" s="2"/>
     </row>
     <row r="231" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A231" s="5" t="s">
-        <v>463</v>
-      </c>
-      <c r="B231" s="5" t="s">
-        <v>464</v>
-      </c>
-      <c r="C231" s="6" t="s">
-        <v>465</v>
-      </c>
-      <c r="D231" s="5" t="s">
-        <v>463</v>
+      <c r="A231" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C231" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
@@ -11751,17 +11748,15 @@
       <c r="Y231" s="2"/>
     </row>
     <row r="232" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A232" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="B232" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C232" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="D232" s="7" t="s">
-        <v>466</v>
+      <c r="A232" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
@@ -11786,15 +11781,15 @@
       <c r="Y232" s="2"/>
     </row>
     <row r="233" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A233" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B233" s="3"/>
-      <c r="C233" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>468</v>
+      <c r="A233" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B233" s="7"/>
+      <c r="C233" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>470</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
@@ -11819,81 +11814,81 @@
       <c r="Y233" s="2"/>
     </row>
     <row r="234" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A234" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="B234" s="7"/>
-      <c r="C234" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="D234" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
-      <c r="J234" s="2"/>
-      <c r="K234" s="2"/>
-      <c r="L234" s="2"/>
-      <c r="M234" s="2"/>
-      <c r="N234" s="2"/>
-      <c r="O234" s="2"/>
-      <c r="P234" s="2"/>
-      <c r="Q234" s="2"/>
-      <c r="R234" s="2"/>
-      <c r="S234" s="2"/>
-      <c r="T234" s="2"/>
-      <c r="U234" s="2"/>
-      <c r="V234" s="2"/>
-      <c r="W234" s="2"/>
-      <c r="X234" s="2"/>
-      <c r="Y234" s="2"/>
+      <c r="A234" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B234" s="3"/>
+      <c r="C234" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E234" s="1"/>
+      <c r="F234" s="1"/>
+      <c r="G234" s="1"/>
+      <c r="H234" s="1"/>
+      <c r="I234" s="1"/>
+      <c r="J234" s="1"/>
+      <c r="K234" s="1"/>
+      <c r="L234" s="1"/>
+      <c r="M234" s="1"/>
+      <c r="N234" s="1"/>
+      <c r="O234" s="1"/>
+      <c r="P234" s="1"/>
+      <c r="Q234" s="1"/>
+      <c r="R234" s="1"/>
+      <c r="S234" s="1"/>
+      <c r="T234" s="1"/>
+      <c r="U234" s="1"/>
+      <c r="V234" s="1"/>
+      <c r="W234" s="1"/>
+      <c r="X234" s="1"/>
+      <c r="Y234" s="1"/>
     </row>
     <row r="235" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A235" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="B235" s="3"/>
-      <c r="C235" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="E235" s="1"/>
-      <c r="F235" s="1"/>
-      <c r="G235" s="1"/>
-      <c r="H235" s="1"/>
-      <c r="I235" s="1"/>
-      <c r="J235" s="1"/>
-      <c r="K235" s="1"/>
-      <c r="L235" s="1"/>
-      <c r="M235" s="1"/>
-      <c r="N235" s="1"/>
-      <c r="O235" s="1"/>
-      <c r="P235" s="1"/>
-      <c r="Q235" s="1"/>
-      <c r="R235" s="1"/>
-      <c r="S235" s="1"/>
-      <c r="T235" s="1"/>
-      <c r="U235" s="1"/>
-      <c r="V235" s="1"/>
-      <c r="W235" s="1"/>
-      <c r="X235" s="1"/>
-      <c r="Y235" s="1"/>
+      <c r="A235" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B235" s="7"/>
+      <c r="C235" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="2"/>
+      <c r="H235" s="2"/>
+      <c r="I235" s="2"/>
+      <c r="J235" s="2"/>
+      <c r="K235" s="2"/>
+      <c r="L235" s="2"/>
+      <c r="M235" s="2"/>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2"/>
+      <c r="P235" s="2"/>
+      <c r="Q235" s="2"/>
+      <c r="R235" s="2"/>
+      <c r="S235" s="2"/>
+      <c r="T235" s="2"/>
+      <c r="U235" s="2"/>
+      <c r="V235" s="2"/>
+      <c r="W235" s="2"/>
+      <c r="X235" s="2"/>
+      <c r="Y235" s="2"/>
     </row>
     <row r="236" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A236" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="B236" s="7"/>
-      <c r="C236" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="D236" s="7" t="s">
-        <v>477</v>
+      <c r="A236" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>478</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
@@ -11918,118 +11913,120 @@
       <c r="Y236" s="2"/>
     </row>
     <row r="237" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A237" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B237" s="3"/>
-      <c r="C237" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
-      <c r="G237" s="2"/>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
-      <c r="J237" s="2"/>
-      <c r="K237" s="2"/>
-      <c r="L237" s="2"/>
-      <c r="M237" s="2"/>
-      <c r="N237" s="2"/>
-      <c r="O237" s="2"/>
-      <c r="P237" s="2"/>
-      <c r="Q237" s="2"/>
-      <c r="R237" s="2"/>
-      <c r="S237" s="2"/>
-      <c r="T237" s="2"/>
-      <c r="U237" s="2"/>
-      <c r="V237" s="2"/>
-      <c r="W237" s="2"/>
-      <c r="X237" s="2"/>
-      <c r="Y237" s="2"/>
+      <c r="A237" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="B237" s="35" t="s">
+        <v>484</v>
+      </c>
+      <c r="C237" s="36" t="s">
+        <v>485</v>
+      </c>
+      <c r="D237" s="35" t="s">
+        <v>483</v>
+      </c>
+      <c r="E237" s="1"/>
+      <c r="F237" s="1"/>
+      <c r="G237" s="1"/>
+      <c r="H237" s="1"/>
+      <c r="I237" s="1"/>
+      <c r="J237" s="1"/>
+      <c r="K237" s="1"/>
+      <c r="L237" s="1"/>
+      <c r="M237" s="1"/>
+      <c r="N237" s="1"/>
+      <c r="O237" s="1"/>
+      <c r="P237" s="1"/>
+      <c r="Q237" s="1"/>
+      <c r="R237" s="1"/>
+      <c r="S237" s="1"/>
+      <c r="T237" s="1"/>
+      <c r="U237" s="1"/>
+      <c r="V237" s="1"/>
+      <c r="W237" s="1"/>
+      <c r="X237" s="1"/>
+      <c r="Y237" s="1"/>
     </row>
     <row r="238" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A238" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="B238" s="35" t="s">
-        <v>484</v>
-      </c>
-      <c r="C238" s="36" t="s">
-        <v>485</v>
-      </c>
-      <c r="D238" s="35" t="s">
-        <v>483</v>
-      </c>
-      <c r="E238" s="1"/>
-      <c r="F238" s="1"/>
-      <c r="G238" s="1"/>
-      <c r="H238" s="1"/>
-      <c r="I238" s="1"/>
-      <c r="J238" s="1"/>
-      <c r="K238" s="1"/>
-      <c r="L238" s="1"/>
-      <c r="M238" s="1"/>
-      <c r="N238" s="1"/>
-      <c r="O238" s="1"/>
-      <c r="P238" s="1"/>
-      <c r="Q238" s="1"/>
-      <c r="R238" s="1"/>
-      <c r="S238" s="1"/>
-      <c r="T238" s="1"/>
-      <c r="U238" s="1"/>
-      <c r="V238" s="1"/>
-      <c r="W238" s="1"/>
-      <c r="X238" s="1"/>
-      <c r="Y238" s="1"/>
+      <c r="A238" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B238" s="7"/>
+      <c r="C238" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="2"/>
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+      <c r="J238" s="2"/>
+      <c r="K238" s="2"/>
+      <c r="L238" s="2"/>
+      <c r="M238" s="2"/>
+      <c r="N238" s="2"/>
+      <c r="O238" s="2"/>
+      <c r="P238" s="2"/>
+      <c r="Q238" s="2"/>
+      <c r="R238" s="2"/>
+      <c r="S238" s="2"/>
+      <c r="T238" s="2"/>
+      <c r="U238" s="2"/>
+      <c r="V238" s="2"/>
+      <c r="W238" s="2"/>
+      <c r="X238" s="2"/>
+      <c r="Y238" s="2"/>
     </row>
     <row r="239" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A239" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="B239" s="7"/>
-      <c r="C239" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="D239" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
-      <c r="G239" s="2"/>
-      <c r="H239" s="2"/>
-      <c r="I239" s="2"/>
-      <c r="J239" s="2"/>
-      <c r="K239" s="2"/>
-      <c r="L239" s="2"/>
-      <c r="M239" s="2"/>
-      <c r="N239" s="2"/>
-      <c r="O239" s="2"/>
-      <c r="P239" s="2"/>
-      <c r="Q239" s="2"/>
-      <c r="R239" s="2"/>
-      <c r="S239" s="2"/>
-      <c r="T239" s="2"/>
-      <c r="U239" s="2"/>
-      <c r="V239" s="2"/>
-      <c r="W239" s="2"/>
-      <c r="X239" s="2"/>
-      <c r="Y239" s="2"/>
+      <c r="A239" s="35" t="s">
+        <v>486</v>
+      </c>
+      <c r="B239" s="35" t="s">
+        <v>487</v>
+      </c>
+      <c r="C239" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="D239" s="35" t="s">
+        <v>489</v>
+      </c>
+      <c r="E239" s="1"/>
+      <c r="F239" s="1"/>
+      <c r="G239" s="1"/>
+      <c r="H239" s="1"/>
+      <c r="I239" s="1"/>
+      <c r="J239" s="1"/>
+      <c r="K239" s="1"/>
+      <c r="L239" s="1"/>
+      <c r="M239" s="1"/>
+      <c r="N239" s="1"/>
+      <c r="O239" s="1"/>
+      <c r="P239" s="1"/>
+      <c r="Q239" s="1"/>
+      <c r="R239" s="1"/>
+      <c r="S239" s="1"/>
+      <c r="T239" s="1"/>
+      <c r="U239" s="1"/>
+      <c r="V239" s="1"/>
+      <c r="W239" s="1"/>
+      <c r="X239" s="1"/>
+      <c r="Y239" s="1"/>
     </row>
     <row r="240" spans="1:25" ht="15.75" customHeight="1">
       <c r="A240" s="35" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B240" s="35" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C240" s="37" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D240" s="35" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -12054,17 +12051,15 @@
       <c r="Y240" s="1"/>
     </row>
     <row r="241" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A241" s="35" t="s">
-        <v>490</v>
-      </c>
-      <c r="B241" s="35" t="s">
-        <v>491</v>
-      </c>
-      <c r="C241" s="37" t="s">
-        <v>492</v>
-      </c>
-      <c r="D241" s="35" t="s">
-        <v>490</v>
+      <c r="A241" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>509</v>
       </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -12090,14 +12085,16 @@
     </row>
     <row r="242" spans="1:25" ht="15.75" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B242" s="3"/>
-      <c r="C242" s="3" t="s">
-        <v>508</v>
+        <v>493</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>495</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -12122,17 +12119,15 @@
       <c r="Y242" s="1"/>
     </row>
     <row r="243" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A243" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C243" s="12" t="s">
-        <v>495</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>493</v>
+      <c r="A243" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B243" s="7"/>
+      <c r="C243" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>496</v>
       </c>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -12157,15 +12152,17 @@
       <c r="Y243" s="1"/>
     </row>
     <row r="244" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A244" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="B244" s="7"/>
-      <c r="C244" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="D244" s="7" t="s">
-        <v>496</v>
+      <c r="A244" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -12190,17 +12187,17 @@
       <c r="Y244" s="1"/>
     </row>
     <row r="245" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A245" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="B245" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C245" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="D245" s="5" t="s">
-        <v>501</v>
+      <c r="A245" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C245" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>504</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -12225,17 +12222,15 @@
       <c r="Y245" s="1"/>
     </row>
     <row r="246" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A246" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C246" s="50" t="s">
-        <v>847</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>504</v>
+      <c r="A246" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B246" s="5"/>
+      <c r="C246" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>505</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -12260,15 +12255,17 @@
       <c r="Y246" s="1"/>
     </row>
     <row r="247" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A247" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B247" s="5"/>
-      <c r="C247" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="D247" s="5" t="s">
-        <v>505</v>
+      <c r="A247" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="B247" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="C247" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>560</v>
       </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -12294,16 +12291,14 @@
     </row>
     <row r="248" spans="1:25" ht="15.75" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B248" s="3" t="s">
-        <v>560</v>
-      </c>
+        <v>510</v>
+      </c>
+      <c r="B248" s="3"/>
       <c r="C248" s="4" t="s">
-        <v>561</v>
+        <v>511</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>560</v>
+        <v>510</v>
       </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -12328,15 +12323,15 @@
       <c r="Y248" s="1"/>
     </row>
     <row r="249" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A249" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B249" s="3"/>
-      <c r="C249" s="4" t="s">
-        <v>511</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>510</v>
+      <c r="A249" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B249" s="38"/>
+      <c r="C249" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D249" s="34" t="s">
+        <v>512</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -12361,15 +12356,15 @@
       <c r="Y249" s="1"/>
     </row>
     <row r="250" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A250" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="B250" s="38"/>
-      <c r="C250" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="D250" s="34" t="s">
-        <v>512</v>
+      <c r="A250" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B250" s="5"/>
+      <c r="C250" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>514</v>
       </c>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -12394,15 +12389,15 @@
       <c r="Y250" s="1"/>
     </row>
     <row r="251" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A251" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="B251" s="5"/>
-      <c r="C251" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>514</v>
+      <c r="A251" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B251" s="3"/>
+      <c r="C251" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -12427,15 +12422,15 @@
       <c r="Y251" s="1"/>
     </row>
     <row r="252" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A252" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B252" s="3"/>
-      <c r="C252" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>516</v>
+      <c r="A252" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="B252" s="7"/>
+      <c r="C252" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>518</v>
       </c>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -12461,47 +12456,49 @@
     </row>
     <row r="253" spans="1:25" ht="15.75" customHeight="1">
       <c r="A253" s="7" t="s">
-        <v>518</v>
+        <v>849</v>
       </c>
       <c r="B253" s="7"/>
       <c r="C253" s="29" t="s">
-        <v>519</v>
+        <v>850</v>
       </c>
       <c r="D253" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="E253" s="1"/>
-      <c r="F253" s="1"/>
-      <c r="G253" s="1"/>
-      <c r="H253" s="1"/>
-      <c r="I253" s="1"/>
-      <c r="J253" s="1"/>
-      <c r="K253" s="1"/>
-      <c r="L253" s="1"/>
-      <c r="M253" s="1"/>
-      <c r="N253" s="1"/>
-      <c r="O253" s="1"/>
-      <c r="P253" s="1"/>
-      <c r="Q253" s="1"/>
-      <c r="R253" s="1"/>
-      <c r="S253" s="1"/>
-      <c r="T253" s="1"/>
-      <c r="U253" s="1"/>
-      <c r="V253" s="1"/>
-      <c r="W253" s="1"/>
-      <c r="X253" s="1"/>
-      <c r="Y253" s="1"/>
+        <v>849</v>
+      </c>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="2"/>
+      <c r="I253" s="2"/>
+      <c r="J253" s="2"/>
+      <c r="K253" s="2"/>
+      <c r="L253" s="2"/>
+      <c r="M253" s="2"/>
+      <c r="N253" s="2"/>
+      <c r="O253" s="2"/>
+      <c r="P253" s="2"/>
+      <c r="Q253" s="2"/>
+      <c r="R253" s="2"/>
+      <c r="S253" s="2"/>
+      <c r="T253" s="2"/>
+      <c r="U253" s="2"/>
+      <c r="V253" s="2"/>
+      <c r="W253" s="2"/>
+      <c r="X253" s="2"/>
+      <c r="Y253" s="2"/>
     </row>
     <row r="254" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A254" s="7" t="s">
-        <v>849</v>
-      </c>
-      <c r="B254" s="7"/>
-      <c r="C254" s="29" t="s">
-        <v>850</v>
-      </c>
-      <c r="D254" s="7" t="s">
-        <v>849</v>
+      <c r="A254" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B254" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C254" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
@@ -12526,17 +12523,15 @@
       <c r="Y254" s="2"/>
     </row>
     <row r="255" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A255" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B255" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C255" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>520</v>
+      <c r="A255" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B255" s="7"/>
+      <c r="C255" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="D255" s="7" t="s">
+        <v>523</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
@@ -12561,50 +12556,52 @@
       <c r="Y255" s="2"/>
     </row>
     <row r="256" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A256" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B256" s="7"/>
-      <c r="C256" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D256" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E256" s="2"/>
-      <c r="F256" s="2"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="2"/>
-      <c r="K256" s="2"/>
-      <c r="L256" s="2"/>
-      <c r="M256" s="2"/>
-      <c r="N256" s="2"/>
-      <c r="O256" s="2"/>
-      <c r="P256" s="2"/>
-      <c r="Q256" s="2"/>
-      <c r="R256" s="2"/>
-      <c r="S256" s="2"/>
-      <c r="T256" s="2"/>
-      <c r="U256" s="2"/>
-      <c r="V256" s="2"/>
-      <c r="W256" s="2"/>
-      <c r="X256" s="2"/>
-      <c r="Y256" s="2"/>
+      <c r="A256" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E256" s="1"/>
+      <c r="F256" s="1"/>
+      <c r="G256" s="1"/>
+      <c r="H256" s="1"/>
+      <c r="I256" s="1"/>
+      <c r="J256" s="1"/>
+      <c r="K256" s="1"/>
+      <c r="L256" s="1"/>
+      <c r="M256" s="1"/>
+      <c r="N256" s="1"/>
+      <c r="O256" s="1"/>
+      <c r="P256" s="1"/>
+      <c r="Q256" s="1"/>
+      <c r="R256" s="1"/>
+      <c r="S256" s="1"/>
+      <c r="T256" s="1"/>
+      <c r="U256" s="1"/>
+      <c r="V256" s="1"/>
+      <c r="W256" s="1"/>
+      <c r="X256" s="1"/>
+      <c r="Y256" s="1"/>
     </row>
     <row r="257" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A257" s="5" t="s">
-        <v>525</v>
-      </c>
-      <c r="B257" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>527</v>
-      </c>
-      <c r="D257" s="5" t="s">
-        <v>525</v>
+      <c r="A257" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B257" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>528</v>
       </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -12629,52 +12626,50 @@
       <c r="Y257" s="1"/>
     </row>
     <row r="258" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A258" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="B258" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C258" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="E258" s="1"/>
-      <c r="F258" s="1"/>
-      <c r="G258" s="1"/>
-      <c r="H258" s="1"/>
-      <c r="I258" s="1"/>
-      <c r="J258" s="1"/>
-      <c r="K258" s="1"/>
-      <c r="L258" s="1"/>
-      <c r="M258" s="1"/>
-      <c r="N258" s="1"/>
-      <c r="O258" s="1"/>
-      <c r="P258" s="1"/>
-      <c r="Q258" s="1"/>
-      <c r="R258" s="1"/>
-      <c r="S258" s="1"/>
-      <c r="T258" s="1"/>
-      <c r="U258" s="1"/>
-      <c r="V258" s="1"/>
-      <c r="W258" s="1"/>
-      <c r="X258" s="1"/>
-      <c r="Y258" s="1"/>
+      <c r="A258" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="B258" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C258" s="52" t="s">
+        <v>848</v>
+      </c>
+      <c r="D258" s="9" t="s">
+        <v>531</v>
+      </c>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="2"/>
+      <c r="H258" s="2"/>
+      <c r="I258" s="2"/>
+      <c r="J258" s="2"/>
+      <c r="K258" s="2"/>
+      <c r="L258" s="2"/>
+      <c r="M258" s="2"/>
+      <c r="N258" s="2"/>
+      <c r="O258" s="2"/>
+      <c r="P258" s="2"/>
+      <c r="Q258" s="2"/>
+      <c r="R258" s="2"/>
+      <c r="S258" s="2"/>
+      <c r="T258" s="2"/>
+      <c r="U258" s="2"/>
+      <c r="V258" s="2"/>
+      <c r="W258" s="2"/>
+      <c r="X258" s="2"/>
+      <c r="Y258" s="2"/>
     </row>
     <row r="259" spans="1:25" ht="15.75" customHeight="1">
       <c r="A259" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B259" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="C259" s="52" t="s">
-        <v>848</v>
+        <v>533</v>
+      </c>
+      <c r="B259" s="9"/>
+      <c r="C259" s="10" t="s">
+        <v>534</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
@@ -12699,15 +12694,17 @@
       <c r="Y259" s="2"/>
     </row>
     <row r="260" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A260" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B260" s="9"/>
-      <c r="C260" s="10" t="s">
-        <v>534</v>
-      </c>
-      <c r="D260" s="9" t="s">
-        <v>533</v>
+      <c r="A260" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B260" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C260" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
@@ -12732,17 +12729,15 @@
       <c r="Y260" s="2"/>
     </row>
     <row r="261" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A261" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B261" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C261" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>535</v>
+      <c r="A261" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B261" s="5"/>
+      <c r="C261" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D261" s="5" t="s">
+        <v>538</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
@@ -12767,50 +12762,52 @@
       <c r="Y261" s="2"/>
     </row>
     <row r="262" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A262" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="B262" s="5"/>
-      <c r="C262" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="D262" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
-      <c r="G262" s="2"/>
-      <c r="H262" s="2"/>
-      <c r="I262" s="2"/>
-      <c r="J262" s="2"/>
-      <c r="K262" s="2"/>
-      <c r="L262" s="2"/>
-      <c r="M262" s="2"/>
-      <c r="N262" s="2"/>
-      <c r="O262" s="2"/>
-      <c r="P262" s="2"/>
-      <c r="Q262" s="2"/>
-      <c r="R262" s="2"/>
-      <c r="S262" s="2"/>
-      <c r="T262" s="2"/>
-      <c r="U262" s="2"/>
-      <c r="V262" s="2"/>
-      <c r="W262" s="2"/>
-      <c r="X262" s="2"/>
-      <c r="Y262" s="2"/>
+      <c r="A262" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C262" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="E262" s="1"/>
+      <c r="F262" s="1"/>
+      <c r="G262" s="1"/>
+      <c r="H262" s="1"/>
+      <c r="I262" s="1"/>
+      <c r="J262" s="1"/>
+      <c r="K262" s="1"/>
+      <c r="L262" s="1"/>
+      <c r="M262" s="1"/>
+      <c r="N262" s="1"/>
+      <c r="O262" s="1"/>
+      <c r="P262" s="1"/>
+      <c r="Q262" s="1"/>
+      <c r="R262" s="1"/>
+      <c r="S262" s="1"/>
+      <c r="T262" s="1"/>
+      <c r="U262" s="1"/>
+      <c r="V262" s="1"/>
+      <c r="W262" s="1"/>
+      <c r="X262" s="1"/>
+      <c r="Y262" s="1"/>
     </row>
     <row r="263" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A263" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="B263" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="C263" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="D263" s="7" t="s">
-        <v>540</v>
+      <c r="A263" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C263" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>546</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -12835,52 +12832,52 @@
       <c r="Y263" s="1"/>
     </row>
     <row r="264" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A264" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="B264" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="C264" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="D264" s="9" t="s">
-        <v>546</v>
-      </c>
-      <c r="E264" s="1"/>
-      <c r="F264" s="1"/>
-      <c r="G264" s="1"/>
-      <c r="H264" s="1"/>
-      <c r="I264" s="1"/>
-      <c r="J264" s="1"/>
-      <c r="K264" s="1"/>
-      <c r="L264" s="1"/>
-      <c r="M264" s="1"/>
-      <c r="N264" s="1"/>
-      <c r="O264" s="1"/>
-      <c r="P264" s="1"/>
-      <c r="Q264" s="1"/>
-      <c r="R264" s="1"/>
-      <c r="S264" s="1"/>
-      <c r="T264" s="1"/>
-      <c r="U264" s="1"/>
-      <c r="V264" s="1"/>
-      <c r="W264" s="1"/>
-      <c r="X264" s="1"/>
-      <c r="Y264" s="1"/>
+      <c r="A264" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B264" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="C264" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="E264" s="2"/>
+      <c r="F264" s="2"/>
+      <c r="G264" s="2"/>
+      <c r="H264" s="2"/>
+      <c r="I264" s="2"/>
+      <c r="J264" s="2"/>
+      <c r="K264" s="2"/>
+      <c r="L264" s="2"/>
+      <c r="M264" s="2"/>
+      <c r="N264" s="2"/>
+      <c r="O264" s="2"/>
+      <c r="P264" s="2"/>
+      <c r="Q264" s="2"/>
+      <c r="R264" s="2"/>
+      <c r="S264" s="2"/>
+      <c r="T264" s="2"/>
+      <c r="U264" s="2"/>
+      <c r="V264" s="2"/>
+      <c r="W264" s="2"/>
+      <c r="X264" s="2"/>
+      <c r="Y264" s="2"/>
     </row>
     <row r="265" spans="1:25" ht="15.75" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>999</v>
+        <v>547</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C265" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D265" s="1" t="s">
-        <v>999</v>
+        <v>548</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
@@ -12905,17 +12902,17 @@
       <c r="Y265" s="2"/>
     </row>
     <row r="266" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A266" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B266" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C266" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>547</v>
+      <c r="A266" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="B266" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C266" s="33" t="s">
+        <v>552</v>
+      </c>
+      <c r="D266" s="34" t="s">
+        <v>550</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
@@ -12941,16 +12938,12 @@
     </row>
     <row r="267" spans="1:25" ht="15.75" customHeight="1">
       <c r="A267" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B267" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C267" s="33" t="s">
-        <v>552</v>
-      </c>
+        <v>906</v>
+      </c>
+      <c r="B267" s="9"/>
+      <c r="C267" s="33"/>
       <c r="D267" s="34" t="s">
-        <v>550</v>
+        <v>906</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
@@ -12975,13 +12968,15 @@
       <c r="Y267" s="2"/>
     </row>
     <row r="268" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A268" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="B268" s="9"/>
-      <c r="C268" s="33"/>
-      <c r="D268" s="34" t="s">
-        <v>906</v>
+      <c r="A268" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B268" s="13"/>
+      <c r="C268" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="D268" s="41" t="s">
+        <v>555</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
@@ -13006,15 +13001,17 @@
       <c r="Y268" s="2"/>
     </row>
     <row r="269" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A269" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="B269" s="13"/>
-      <c r="C269" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="D269" s="41" t="s">
-        <v>555</v>
+      <c r="A269" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C269" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="D269" s="34" t="s">
+        <v>556</v>
       </c>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
@@ -13040,16 +13037,14 @@
     </row>
     <row r="270" spans="1:25" ht="15.75" customHeight="1">
       <c r="A270" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="B270" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="C270" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="D270" s="34" t="s">
-        <v>556</v>
+        <v>562</v>
+      </c>
+      <c r="B270" s="9"/>
+      <c r="C270" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="D270" s="9" t="s">
+        <v>564</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
@@ -13075,14 +13070,16 @@
     </row>
     <row r="271" spans="1:25" ht="15.75" customHeight="1">
       <c r="A271" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="B271" s="9"/>
+        <v>565</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>566</v>
+      </c>
       <c r="C271" s="34" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
@@ -13107,17 +13104,17 @@
       <c r="Y271" s="2"/>
     </row>
     <row r="272" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A272" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B272" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="C272" s="34" t="s">
-        <v>567</v>
-      </c>
-      <c r="D272" s="9" t="s">
-        <v>568</v>
+      <c r="A272" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="B272" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="C272" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D272" s="43" t="s">
+        <v>569</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
@@ -13142,17 +13139,15 @@
       <c r="Y272" s="2"/>
     </row>
     <row r="273" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A273" s="43" t="s">
-        <v>569</v>
-      </c>
-      <c r="B273" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="C273" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="D273" s="43" t="s">
-        <v>569</v>
+      <c r="A273" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B273" s="3"/>
+      <c r="C273" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>1001</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
@@ -13177,15 +13172,17 @@
       <c r="Y273" s="2"/>
     </row>
     <row r="274" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A274" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B274" s="3"/>
-      <c r="C274" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>1002</v>
+      <c r="A274" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="B274" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C274" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="D274" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
@@ -13210,17 +13207,17 @@
       <c r="Y274" s="2"/>
     </row>
     <row r="275" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A275" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="B275" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C275" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="D275" s="9" t="s">
-        <v>570</v>
+      <c r="A275" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="C275" s="53" t="s">
+        <v>909</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>907</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
@@ -13245,16 +13242,16 @@
       <c r="Y275" s="2"/>
     </row>
     <row r="276" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A276" s="7" t="s">
+      <c r="A276" s="3" t="s">
         <v>907</v>
       </c>
-      <c r="B276" s="7" t="s">
+      <c r="B276" s="3" t="s">
         <v>908</v>
       </c>
-      <c r="C276" s="53" t="s">
-        <v>909</v>
-      </c>
-      <c r="D276" s="7" t="s">
+      <c r="C276" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>907</v>
       </c>
       <c r="E276" s="2"/>
@@ -13281,16 +13278,16 @@
     </row>
     <row r="277" spans="1:25" ht="15.75" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>907</v>
+        <v>573</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C277" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>907</v>
+        <v>842</v>
+      </c>
+      <c r="C277" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>574</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
@@ -13315,50 +13312,50 @@
       <c r="Y277" s="2"/>
     </row>
     <row r="278" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A278" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="B278" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="C278" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="E278" s="2"/>
-      <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="2"/>
-      <c r="I278" s="2"/>
-      <c r="J278" s="2"/>
-      <c r="K278" s="2"/>
-      <c r="L278" s="2"/>
-      <c r="M278" s="2"/>
-      <c r="N278" s="2"/>
-      <c r="O278" s="2"/>
-      <c r="P278" s="2"/>
-      <c r="Q278" s="2"/>
-      <c r="R278" s="2"/>
-      <c r="S278" s="2"/>
-      <c r="T278" s="2"/>
-      <c r="U278" s="2"/>
-      <c r="V278" s="2"/>
-      <c r="W278" s="2"/>
-      <c r="X278" s="2"/>
-      <c r="Y278" s="2"/>
+      <c r="A278" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="B278" s="7"/>
+      <c r="C278" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="E278" s="1"/>
+      <c r="F278" s="1"/>
+      <c r="G278" s="1"/>
+      <c r="H278" s="1"/>
+      <c r="I278" s="1"/>
+      <c r="J278" s="1"/>
+      <c r="K278" s="1"/>
+      <c r="L278" s="1"/>
+      <c r="M278" s="1"/>
+      <c r="N278" s="1"/>
+      <c r="O278" s="1"/>
+      <c r="P278" s="1"/>
+      <c r="Q278" s="1"/>
+      <c r="R278" s="1"/>
+      <c r="S278" s="1"/>
+      <c r="T278" s="1"/>
+      <c r="U278" s="1"/>
+      <c r="V278" s="1"/>
+      <c r="W278" s="1"/>
+      <c r="X278" s="1"/>
+      <c r="Y278" s="1"/>
     </row>
     <row r="279" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A279" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="B279" s="7"/>
-      <c r="C279" s="8" t="s">
-        <v>576</v>
-      </c>
-      <c r="D279" s="7" t="s">
-        <v>577</v>
+      <c r="A279" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D279" s="5" t="s">
+        <v>578</v>
       </c>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
@@ -13383,17 +13380,17 @@
       <c r="Y279" s="1"/>
     </row>
     <row r="280" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A280" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="B280" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C280" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="D280" s="5" t="s">
-        <v>578</v>
+      <c r="A280" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B280" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C280" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
@@ -13418,17 +13415,15 @@
       <c r="Y280" s="1"/>
     </row>
     <row r="281" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A281" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="B281" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C281" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>581</v>
+      <c r="A281" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="B281" s="7"/>
+      <c r="C281" s="53" t="s">
+        <v>911</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>910</v>
       </c>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
@@ -13454,47 +13449,49 @@
     </row>
     <row r="282" spans="1:25" ht="15.75" customHeight="1">
       <c r="A282" s="7" t="s">
-        <v>910</v>
+        <v>584</v>
       </c>
       <c r="B282" s="7"/>
-      <c r="C282" s="53" t="s">
-        <v>911</v>
+      <c r="C282" s="29" t="s">
+        <v>585</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="E282" s="1"/>
-      <c r="F282" s="1"/>
-      <c r="G282" s="1"/>
-      <c r="H282" s="1"/>
-      <c r="I282" s="1"/>
-      <c r="J282" s="1"/>
-      <c r="K282" s="1"/>
-      <c r="L282" s="1"/>
-      <c r="M282" s="1"/>
-      <c r="N282" s="1"/>
-      <c r="O282" s="1"/>
-      <c r="P282" s="1"/>
-      <c r="Q282" s="1"/>
-      <c r="R282" s="1"/>
-      <c r="S282" s="1"/>
-      <c r="T282" s="1"/>
-      <c r="U282" s="1"/>
-      <c r="V282" s="1"/>
-      <c r="W282" s="1"/>
-      <c r="X282" s="1"/>
-      <c r="Y282" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="2"/>
+      <c r="H282" s="2"/>
+      <c r="I282" s="2"/>
+      <c r="J282" s="2"/>
+      <c r="K282" s="2"/>
+      <c r="L282" s="2"/>
+      <c r="M282" s="2"/>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
+      <c r="P282" s="2"/>
+      <c r="Q282" s="2"/>
+      <c r="R282" s="2"/>
+      <c r="S282" s="2"/>
+      <c r="T282" s="2"/>
+      <c r="U282" s="2"/>
+      <c r="V282" s="2"/>
+      <c r="W282" s="2"/>
+      <c r="X282" s="2"/>
+      <c r="Y282" s="2"/>
     </row>
     <row r="283" spans="1:25" ht="15.75" customHeight="1">
       <c r="A283" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="B283" s="7"/>
+        <v>589</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>590</v>
+      </c>
       <c r="C283" s="29" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
@@ -13519,17 +13516,17 @@
       <c r="Y283" s="2"/>
     </row>
     <row r="284" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A284" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B284" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="C284" s="29" t="s">
-        <v>591</v>
-      </c>
-      <c r="D284" s="7" t="s">
-        <v>592</v>
+      <c r="A284" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B284" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C284" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>1004</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
@@ -13554,17 +13551,17 @@
       <c r="Y284" s="2"/>
     </row>
     <row r="285" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A285" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="B285" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C285" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>1005</v>
+      <c r="A285" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="D285" s="5" t="s">
+        <v>586</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
@@ -13590,16 +13587,14 @@
     </row>
     <row r="286" spans="1:25" ht="15.75" customHeight="1">
       <c r="A286" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B286" s="5" t="s">
-        <v>587</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="B286" s="5"/>
       <c r="C286" s="6" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>586</v>
+        <v>593</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
@@ -13624,15 +13619,15 @@
       <c r="Y286" s="2"/>
     </row>
     <row r="287" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A287" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B287" s="5"/>
-      <c r="C287" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="D287" s="5" t="s">
-        <v>593</v>
+      <c r="A287" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B287" s="3"/>
+      <c r="C287" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
@@ -13657,15 +13652,17 @@
       <c r="Y287" s="2"/>
     </row>
     <row r="288" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A288" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="B288" s="3"/>
-      <c r="C288" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>595</v>
+      <c r="A288" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C288" s="30" t="s">
+        <v>599</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>600</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
@@ -13690,17 +13687,15 @@
       <c r="Y288" s="2"/>
     </row>
     <row r="289" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A289" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="B289" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="C289" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="D289" s="5" t="s">
-        <v>600</v>
+      <c r="A289" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B289" s="3"/>
+      <c r="C289" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>601</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -13726,14 +13721,16 @@
     </row>
     <row r="290" spans="1:25" ht="15.75" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B290" s="3"/>
+        <v>603</v>
+      </c>
+      <c r="B290" s="3" t="s">
+        <v>604</v>
+      </c>
       <c r="C290" s="3" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>601</v>
+        <v>606</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
@@ -13758,17 +13755,17 @@
       <c r="Y290" s="2"/>
     </row>
     <row r="291" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A291" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B291" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="C291" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>606</v>
+      <c r="A291" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C291" s="10" t="s">
+        <v>609</v>
+      </c>
+      <c r="D291" s="9" t="s">
+        <v>607</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
@@ -13794,16 +13791,14 @@
     </row>
     <row r="292" spans="1:25" ht="15.75" customHeight="1">
       <c r="A292" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="B292" s="9" t="s">
-        <v>608</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="B292" s="9"/>
       <c r="C292" s="10" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
@@ -13829,14 +13824,14 @@
     </row>
     <row r="293" spans="1:25" ht="15.75" customHeight="1">
       <c r="A293" s="9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B293" s="9"/>
-      <c r="C293" s="10" t="s">
-        <v>611</v>
+      <c r="C293" s="11" t="s">
+        <v>613</v>
       </c>
       <c r="D293" s="9" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
@@ -13861,50 +13856,52 @@
       <c r="Y293" s="2"/>
     </row>
     <row r="294" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A294" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="B294" s="9"/>
-      <c r="C294" s="11" t="s">
-        <v>613</v>
-      </c>
-      <c r="D294" s="9" t="s">
-        <v>612</v>
-      </c>
-      <c r="E294" s="2"/>
-      <c r="F294" s="2"/>
-      <c r="G294" s="2"/>
-      <c r="H294" s="2"/>
-      <c r="I294" s="2"/>
-      <c r="J294" s="2"/>
-      <c r="K294" s="2"/>
-      <c r="L294" s="2"/>
-      <c r="M294" s="2"/>
-      <c r="N294" s="2"/>
-      <c r="O294" s="2"/>
-      <c r="P294" s="2"/>
-      <c r="Q294" s="2"/>
-      <c r="R294" s="2"/>
-      <c r="S294" s="2"/>
-      <c r="T294" s="2"/>
-      <c r="U294" s="2"/>
-      <c r="V294" s="2"/>
-      <c r="W294" s="2"/>
-      <c r="X294" s="2"/>
-      <c r="Y294" s="2"/>
+      <c r="A294" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="C294" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E294" s="1"/>
+      <c r="F294" s="1"/>
+      <c r="G294" s="1"/>
+      <c r="H294" s="1"/>
+      <c r="I294" s="1"/>
+      <c r="J294" s="1"/>
+      <c r="K294" s="1"/>
+      <c r="L294" s="1"/>
+      <c r="M294" s="1"/>
+      <c r="N294" s="1"/>
+      <c r="O294" s="1"/>
+      <c r="P294" s="1"/>
+      <c r="Q294" s="1"/>
+      <c r="R294" s="1"/>
+      <c r="S294" s="1"/>
+      <c r="T294" s="1"/>
+      <c r="U294" s="1"/>
+      <c r="V294" s="1"/>
+      <c r="W294" s="1"/>
+      <c r="X294" s="1"/>
+      <c r="Y294" s="1"/>
     </row>
     <row r="295" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A295" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="B295" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="C295" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>614</v>
+      <c r="A295" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C295" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>620</v>
       </c>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
@@ -13929,17 +13926,17 @@
       <c r="Y295" s="1"/>
     </row>
     <row r="296" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A296" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B296" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="C296" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="D296" s="7" t="s">
-        <v>620</v>
+      <c r="A296" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B296" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C296" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="D296" s="34" t="s">
+        <v>624</v>
       </c>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
@@ -13964,17 +13961,17 @@
       <c r="Y296" s="1"/>
     </row>
     <row r="297" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A297" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="B297" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C297" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="D297" s="34" t="s">
-        <v>624</v>
+      <c r="A297" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>625</v>
+      </c>
+      <c r="C297" s="41" t="s">
+        <v>626</v>
+      </c>
+      <c r="D297" s="13" t="s">
+        <v>625</v>
       </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
@@ -14000,16 +13997,14 @@
     </row>
     <row r="298" spans="1:25" ht="15.75" customHeight="1">
       <c r="A298" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="B298" s="13" t="s">
-        <v>625</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="B298" s="13"/>
       <c r="C298" s="41" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D298" s="13" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
@@ -14034,83 +14029,83 @@
       <c r="Y298" s="1"/>
     </row>
     <row r="299" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A299" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B299" s="13"/>
-      <c r="C299" s="41" t="s">
-        <v>628</v>
-      </c>
-      <c r="D299" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="E299" s="1"/>
-      <c r="F299" s="1"/>
-      <c r="G299" s="1"/>
-      <c r="H299" s="1"/>
-      <c r="I299" s="1"/>
-      <c r="J299" s="1"/>
-      <c r="K299" s="1"/>
-      <c r="L299" s="1"/>
-      <c r="M299" s="1"/>
-      <c r="N299" s="1"/>
-      <c r="O299" s="1"/>
-      <c r="P299" s="1"/>
-      <c r="Q299" s="1"/>
-      <c r="R299" s="1"/>
-      <c r="S299" s="1"/>
-      <c r="T299" s="1"/>
-      <c r="U299" s="1"/>
-      <c r="V299" s="1"/>
-      <c r="W299" s="1"/>
-      <c r="X299" s="1"/>
-      <c r="Y299" s="1"/>
+      <c r="A299" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="B299" s="9"/>
+      <c r="C299" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="D299" s="9" t="s">
+        <v>629</v>
+      </c>
+      <c r="E299" s="2"/>
+      <c r="F299" s="2"/>
+      <c r="G299" s="2"/>
+      <c r="H299" s="2"/>
+      <c r="I299" s="2"/>
+      <c r="J299" s="2"/>
+      <c r="K299" s="2"/>
+      <c r="L299" s="2"/>
+      <c r="M299" s="2"/>
+      <c r="N299" s="2"/>
+      <c r="O299" s="2"/>
+      <c r="P299" s="2"/>
+      <c r="Q299" s="2"/>
+      <c r="R299" s="2"/>
+      <c r="S299" s="2"/>
+      <c r="T299" s="2"/>
+      <c r="U299" s="2"/>
+      <c r="V299" s="2"/>
+      <c r="W299" s="2"/>
+      <c r="X299" s="2"/>
+      <c r="Y299" s="2"/>
     </row>
     <row r="300" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A300" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="B300" s="9"/>
-      <c r="C300" s="34" t="s">
-        <v>630</v>
-      </c>
-      <c r="D300" s="9" t="s">
-        <v>629</v>
-      </c>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
-      <c r="G300" s="2"/>
-      <c r="H300" s="2"/>
-      <c r="I300" s="2"/>
-      <c r="J300" s="2"/>
-      <c r="K300" s="2"/>
-      <c r="L300" s="2"/>
-      <c r="M300" s="2"/>
-      <c r="N300" s="2"/>
-      <c r="O300" s="2"/>
-      <c r="P300" s="2"/>
-      <c r="Q300" s="2"/>
-      <c r="R300" s="2"/>
-      <c r="S300" s="2"/>
-      <c r="T300" s="2"/>
-      <c r="U300" s="2"/>
-      <c r="V300" s="2"/>
-      <c r="W300" s="2"/>
-      <c r="X300" s="2"/>
-      <c r="Y300" s="2"/>
+      <c r="A300" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C300" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E300" s="1"/>
+      <c r="F300" s="1"/>
+      <c r="G300" s="1"/>
+      <c r="H300" s="1"/>
+      <c r="I300" s="1"/>
+      <c r="J300" s="1"/>
+      <c r="K300" s="1"/>
+      <c r="L300" s="1"/>
+      <c r="M300" s="1"/>
+      <c r="N300" s="1"/>
+      <c r="O300" s="1"/>
+      <c r="P300" s="1"/>
+      <c r="Q300" s="1"/>
+      <c r="R300" s="1"/>
+      <c r="S300" s="1"/>
+      <c r="T300" s="1"/>
+      <c r="U300" s="1"/>
+      <c r="V300" s="1"/>
+      <c r="W300" s="1"/>
+      <c r="X300" s="1"/>
+      <c r="Y300" s="1"/>
     </row>
     <row r="301" spans="1:25" ht="15.75" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B301" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C301" s="3" t="s">
-        <v>633</v>
+        <v>634</v>
+      </c>
+      <c r="B301" s="3"/>
+      <c r="C301" s="18" t="s">
+        <v>635</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>631</v>
+        <v>636</v>
       </c>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
@@ -14136,14 +14131,14 @@
     </row>
     <row r="302" spans="1:25" ht="15.75" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>634</v>
+        <v>1043</v>
       </c>
       <c r="B302" s="3"/>
-      <c r="C302" s="18" t="s">
-        <v>635</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>636</v>
+      <c r="C302" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D302" s="1" t="s">
+        <v>1045</v>
       </c>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
@@ -14168,46 +14163,48 @@
       <c r="Y302" s="1"/>
     </row>
     <row r="303" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A303" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B303" s="3"/>
-      <c r="C303" s="3" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>1046</v>
-      </c>
-      <c r="E303" s="1"/>
-      <c r="F303" s="1"/>
-      <c r="G303" s="1"/>
-      <c r="H303" s="1"/>
-      <c r="I303" s="1"/>
-      <c r="J303" s="1"/>
-      <c r="K303" s="1"/>
-      <c r="L303" s="1"/>
-      <c r="M303" s="1"/>
-      <c r="N303" s="1"/>
-      <c r="O303" s="1"/>
-      <c r="P303" s="1"/>
-      <c r="Q303" s="1"/>
-      <c r="R303" s="1"/>
-      <c r="S303" s="1"/>
-      <c r="T303" s="1"/>
-      <c r="U303" s="1"/>
-      <c r="V303" s="1"/>
-      <c r="W303" s="1"/>
-      <c r="X303" s="1"/>
-      <c r="Y303" s="1"/>
+      <c r="A303" s="9" t="s">
+        <v>912</v>
+      </c>
+      <c r="B303" s="9"/>
+      <c r="C303" s="10"/>
+      <c r="D303" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="E303" s="2"/>
+      <c r="F303" s="2"/>
+      <c r="G303" s="2"/>
+      <c r="H303" s="2"/>
+      <c r="I303" s="2"/>
+      <c r="J303" s="2"/>
+      <c r="K303" s="2"/>
+      <c r="L303" s="2"/>
+      <c r="M303" s="2"/>
+      <c r="N303" s="2"/>
+      <c r="O303" s="2"/>
+      <c r="P303" s="2"/>
+      <c r="Q303" s="2"/>
+      <c r="R303" s="2"/>
+      <c r="S303" s="2"/>
+      <c r="T303" s="2"/>
+      <c r="U303" s="2"/>
+      <c r="V303" s="2"/>
+      <c r="W303" s="2"/>
+      <c r="X303" s="2"/>
+      <c r="Y303" s="2"/>
     </row>
     <row r="304" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A304" s="9" t="s">
-        <v>912</v>
-      </c>
-      <c r="B304" s="9"/>
-      <c r="C304" s="10"/>
-      <c r="D304" s="9" t="s">
-        <v>913</v>
+      <c r="A304" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="B304" s="13" t="s">
+        <v>915</v>
+      </c>
+      <c r="C304" s="68" t="s">
+        <v>916</v>
+      </c>
+      <c r="D304" s="13" t="s">
+        <v>917</v>
       </c>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
@@ -14232,52 +14229,50 @@
       <c r="Y304" s="2"/>
     </row>
     <row r="305" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A305" s="13" t="s">
-        <v>914</v>
-      </c>
-      <c r="B305" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C305" s="68" t="s">
-        <v>916</v>
-      </c>
-      <c r="D305" s="13" t="s">
-        <v>917</v>
-      </c>
-      <c r="E305" s="2"/>
-      <c r="F305" s="2"/>
-      <c r="G305" s="2"/>
-      <c r="H305" s="2"/>
-      <c r="I305" s="2"/>
-      <c r="J305" s="2"/>
-      <c r="K305" s="2"/>
-      <c r="L305" s="2"/>
-      <c r="M305" s="2"/>
-      <c r="N305" s="2"/>
-      <c r="O305" s="2"/>
-      <c r="P305" s="2"/>
-      <c r="Q305" s="2"/>
-      <c r="R305" s="2"/>
-      <c r="S305" s="2"/>
-      <c r="T305" s="2"/>
-      <c r="U305" s="2"/>
-      <c r="V305" s="2"/>
-      <c r="W305" s="2"/>
-      <c r="X305" s="2"/>
-      <c r="Y305" s="2"/>
+      <c r="A305" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C305" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D305" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="E305" s="1"/>
+      <c r="F305" s="1"/>
+      <c r="G305" s="1"/>
+      <c r="H305" s="1"/>
+      <c r="I305" s="1"/>
+      <c r="J305" s="1"/>
+      <c r="K305" s="1"/>
+      <c r="L305" s="1"/>
+      <c r="M305" s="1"/>
+      <c r="N305" s="1"/>
+      <c r="O305" s="1"/>
+      <c r="P305" s="1"/>
+      <c r="Q305" s="1"/>
+      <c r="R305" s="1"/>
+      <c r="S305" s="1"/>
+      <c r="T305" s="1"/>
+      <c r="U305" s="1"/>
+      <c r="V305" s="1"/>
+      <c r="W305" s="1"/>
+      <c r="X305" s="1"/>
+      <c r="Y305" s="1"/>
     </row>
     <row r="306" spans="1:25" ht="15.75" customHeight="1">
       <c r="A306" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="B306" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C306" s="11" t="s">
-        <v>639</v>
+        <v>641</v>
+      </c>
+      <c r="B306" s="9"/>
+      <c r="C306" s="10" t="s">
+        <v>642</v>
       </c>
       <c r="D306" s="9" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
@@ -14302,15 +14297,17 @@
       <c r="Y306" s="1"/>
     </row>
     <row r="307" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A307" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="B307" s="9"/>
-      <c r="C307" s="10" t="s">
-        <v>642</v>
-      </c>
-      <c r="D307" s="9" t="s">
-        <v>643</v>
+      <c r="A307" s="13" t="s">
+        <v>918</v>
+      </c>
+      <c r="B307" s="13" t="s">
+        <v>919</v>
+      </c>
+      <c r="C307" s="68" t="s">
+        <v>920</v>
+      </c>
+      <c r="D307" s="13" t="s">
+        <v>918</v>
       </c>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
@@ -14336,16 +14333,16 @@
     </row>
     <row r="308" spans="1:25" ht="15.75" customHeight="1">
       <c r="A308" s="13" t="s">
-        <v>918</v>
+        <v>644</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>919</v>
-      </c>
-      <c r="C308" s="68" t="s">
-        <v>920</v>
+        <v>645</v>
+      </c>
+      <c r="C308" s="14" t="s">
+        <v>646</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>918</v>
+        <v>644</v>
       </c>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
@@ -14370,17 +14367,15 @@
       <c r="Y308" s="1"/>
     </row>
     <row r="309" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A309" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="B309" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="C309" s="14" t="s">
-        <v>646</v>
-      </c>
-      <c r="D309" s="13" t="s">
-        <v>644</v>
+      <c r="A309" s="9" t="s">
+        <v>647</v>
+      </c>
+      <c r="B309" s="9"/>
+      <c r="C309" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="D309" s="9" t="s">
+        <v>647</v>
       </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
@@ -14406,14 +14401,14 @@
     </row>
     <row r="310" spans="1:25" ht="15.75" customHeight="1">
       <c r="A310" s="9" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B310" s="9"/>
-      <c r="C310" s="10" t="s">
-        <v>648</v>
+      <c r="C310" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="D310" s="9" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
@@ -14439,14 +14434,14 @@
     </row>
     <row r="311" spans="1:25" ht="15.75" customHeight="1">
       <c r="A311" s="9" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B311" s="9"/>
-      <c r="C311" s="11" t="s">
-        <v>650</v>
+      <c r="C311" s="10" t="s">
+        <v>652</v>
       </c>
       <c r="D311" s="9" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
@@ -14472,14 +14467,14 @@
     </row>
     <row r="312" spans="1:25" ht="15.75" customHeight="1">
       <c r="A312" s="9" t="s">
-        <v>651</v>
+        <v>851</v>
       </c>
       <c r="B312" s="9"/>
       <c r="C312" s="10" t="s">
-        <v>652</v>
+        <v>852</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>651</v>
+        <v>851</v>
       </c>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
@@ -14505,14 +14500,16 @@
     </row>
     <row r="313" spans="1:25" ht="15.75" customHeight="1">
       <c r="A313" s="9" t="s">
-        <v>851</v>
-      </c>
-      <c r="B313" s="9"/>
-      <c r="C313" s="10" t="s">
-        <v>852</v>
+        <v>653</v>
+      </c>
+      <c r="B313" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C313" s="11" t="s">
+        <v>655</v>
       </c>
       <c r="D313" s="9" t="s">
-        <v>851</v>
+        <v>653</v>
       </c>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
@@ -14538,16 +14535,14 @@
     </row>
     <row r="314" spans="1:25" ht="15.75" customHeight="1">
       <c r="A314" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="B314" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="C314" s="11" t="s">
-        <v>655</v>
+        <v>656</v>
+      </c>
+      <c r="B314" s="9"/>
+      <c r="C314" s="16" t="s">
+        <v>657</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
@@ -14572,15 +14567,17 @@
       <c r="Y314" s="1"/>
     </row>
     <row r="315" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A315" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="B315" s="9"/>
-      <c r="C315" s="16" t="s">
-        <v>657</v>
-      </c>
-      <c r="D315" s="9" t="s">
-        <v>656</v>
+      <c r="A315" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="B315" s="13" t="s">
+        <v>922</v>
+      </c>
+      <c r="C315" s="68" t="s">
+        <v>923</v>
+      </c>
+      <c r="D315" s="13" t="s">
+        <v>921</v>
       </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
@@ -14605,17 +14602,17 @@
       <c r="Y315" s="1"/>
     </row>
     <row r="316" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A316" s="13" t="s">
-        <v>921</v>
-      </c>
-      <c r="B316" s="13" t="s">
-        <v>922</v>
-      </c>
-      <c r="C316" s="68" t="s">
-        <v>923</v>
-      </c>
-      <c r="D316" s="13" t="s">
-        <v>921</v>
+      <c r="A316" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C316" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>660</v>
       </c>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
@@ -14640,50 +14637,50 @@
       <c r="Y316" s="1"/>
     </row>
     <row r="317" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A317" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="B317" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="C317" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="D317" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="E317" s="1"/>
-      <c r="F317" s="1"/>
-      <c r="G317" s="1"/>
-      <c r="H317" s="1"/>
-      <c r="I317" s="1"/>
-      <c r="J317" s="1"/>
-      <c r="K317" s="1"/>
-      <c r="L317" s="1"/>
-      <c r="M317" s="1"/>
-      <c r="N317" s="1"/>
-      <c r="O317" s="1"/>
-      <c r="P317" s="1"/>
-      <c r="Q317" s="1"/>
-      <c r="R317" s="1"/>
-      <c r="S317" s="1"/>
-      <c r="T317" s="1"/>
-      <c r="U317" s="1"/>
-      <c r="V317" s="1"/>
-      <c r="W317" s="1"/>
-      <c r="X317" s="1"/>
-      <c r="Y317" s="1"/>
+      <c r="A317" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="B317" s="9"/>
+      <c r="C317" s="10" t="s">
+        <v>659</v>
+      </c>
+      <c r="D317" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="E317" s="2"/>
+      <c r="F317" s="2"/>
+      <c r="G317" s="2"/>
+      <c r="H317" s="2"/>
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+      <c r="K317" s="2"/>
+      <c r="L317" s="2"/>
+      <c r="M317" s="2"/>
+      <c r="N317" s="2"/>
+      <c r="O317" s="2"/>
+      <c r="P317" s="2"/>
+      <c r="Q317" s="2"/>
+      <c r="R317" s="2"/>
+      <c r="S317" s="2"/>
+      <c r="T317" s="2"/>
+      <c r="U317" s="2"/>
+      <c r="V317" s="2"/>
+      <c r="W317" s="2"/>
+      <c r="X317" s="2"/>
+      <c r="Y317" s="2"/>
     </row>
     <row r="318" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A318" s="9" t="s">
-        <v>658</v>
-      </c>
-      <c r="B318" s="9"/>
-      <c r="C318" s="10" t="s">
-        <v>659</v>
-      </c>
-      <c r="D318" s="9" t="s">
-        <v>658</v>
+      <c r="A318" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="C318" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="D318" s="1" t="s">
+        <v>985</v>
       </c>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
@@ -14709,16 +14706,14 @@
     </row>
     <row r="319" spans="1:25" ht="15.75" customHeight="1">
       <c r="A319" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="B319" s="3" t="s">
-        <v>986</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="B319" s="3"/>
       <c r="C319" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>985</v>
+        <v>664</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>665</v>
       </c>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
@@ -14744,49 +14739,49 @@
     </row>
     <row r="320" spans="1:25" ht="15.75" customHeight="1">
       <c r="A320" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B320" s="3"/>
+        <v>1007</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>1008</v>
+      </c>
       <c r="C320" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="E320" s="2"/>
-      <c r="F320" s="2"/>
-      <c r="G320" s="2"/>
-      <c r="H320" s="2"/>
-      <c r="I320" s="2"/>
-      <c r="J320" s="2"/>
-      <c r="K320" s="2"/>
-      <c r="L320" s="2"/>
-      <c r="M320" s="2"/>
-      <c r="N320" s="2"/>
-      <c r="O320" s="2"/>
-      <c r="P320" s="2"/>
-      <c r="Q320" s="2"/>
-      <c r="R320" s="2"/>
-      <c r="S320" s="2"/>
-      <c r="T320" s="2"/>
-      <c r="U320" s="2"/>
-      <c r="V320" s="2"/>
-      <c r="W320" s="2"/>
-      <c r="X320" s="2"/>
-      <c r="Y320" s="2"/>
+        <v>1009</v>
+      </c>
+      <c r="D320" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E320" s="1"/>
+      <c r="F320" s="1"/>
+      <c r="G320" s="1"/>
+      <c r="H320" s="1"/>
+      <c r="I320" s="1"/>
+      <c r="J320" s="1"/>
+      <c r="K320" s="1"/>
+      <c r="L320" s="1"/>
+      <c r="M320" s="1"/>
+      <c r="N320" s="1"/>
+      <c r="O320" s="1"/>
+      <c r="P320" s="1"/>
+      <c r="Q320" s="1"/>
+      <c r="R320" s="1"/>
+      <c r="S320" s="1"/>
+      <c r="T320" s="1"/>
+      <c r="U320" s="1"/>
+      <c r="V320" s="1"/>
+      <c r="W320" s="1"/>
+      <c r="X320" s="1"/>
+      <c r="Y320" s="1"/>
     </row>
     <row r="321" spans="1:25" ht="15.75" customHeight="1">
       <c r="A321" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B321" s="3" t="s">
-        <v>1009</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="B321" s="3"/>
       <c r="C321" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>1008</v>
+        <v>667</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
@@ -14811,15 +14806,17 @@
       <c r="Y321" s="1"/>
     </row>
     <row r="322" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A322" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B322" s="3"/>
-      <c r="C322" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>666</v>
+      <c r="A322" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B322" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="C322" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="D322" s="9" t="s">
+        <v>676</v>
       </c>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
@@ -14844,17 +14841,17 @@
       <c r="Y322" s="1"/>
     </row>
     <row r="323" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A323" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B323" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="C323" s="45" t="s">
-        <v>675</v>
-      </c>
-      <c r="D323" s="9" t="s">
-        <v>676</v>
+      <c r="A323" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B323" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="C323" s="46" t="s">
+        <v>679</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>680</v>
       </c>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
@@ -14879,17 +14876,17 @@
       <c r="Y323" s="1"/>
     </row>
     <row r="324" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A324" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="B324" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="C324" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="D324" s="13" t="s">
-        <v>680</v>
+      <c r="A324" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B324" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="C324" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D324" s="9" t="s">
+        <v>684</v>
       </c>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
@@ -14914,17 +14911,15 @@
       <c r="Y324" s="1"/>
     </row>
     <row r="325" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A325" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="B325" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="C325" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="D325" s="9" t="s">
-        <v>684</v>
+      <c r="A325" s="13" t="s">
+        <v>685</v>
+      </c>
+      <c r="B325" s="13"/>
+      <c r="C325" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>687</v>
       </c>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
@@ -14949,15 +14944,17 @@
       <c r="Y325" s="1"/>
     </row>
     <row r="326" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A326" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B326" s="13"/>
-      <c r="C326" s="14" t="s">
-        <v>686</v>
-      </c>
-      <c r="D326" s="13" t="s">
-        <v>687</v>
+      <c r="A326" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B326" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C326" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>668</v>
       </c>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
@@ -14982,17 +14979,15 @@
       <c r="Y326" s="1"/>
     </row>
     <row r="327" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A327" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B327" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C327" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D327" s="7" t="s">
-        <v>668</v>
+      <c r="A327" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="B327" s="9"/>
+      <c r="C327" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="D327" s="9" t="s">
+        <v>671</v>
       </c>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
@@ -15018,14 +15013,14 @@
     </row>
     <row r="328" spans="1:25" ht="15.75" customHeight="1">
       <c r="A328" s="9" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="B328" s="9"/>
-      <c r="C328" s="11" t="s">
-        <v>672</v>
+      <c r="C328" s="10" t="s">
+        <v>689</v>
       </c>
       <c r="D328" s="9" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
@@ -15051,14 +15046,16 @@
     </row>
     <row r="329" spans="1:25" ht="15.75" customHeight="1">
       <c r="A329" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="B329" s="9"/>
-      <c r="C329" s="10" t="s">
-        <v>689</v>
+        <v>690</v>
+      </c>
+      <c r="B329" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C329" s="11" t="s">
+        <v>692</v>
       </c>
       <c r="D329" s="9" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
@@ -15084,16 +15081,14 @@
     </row>
     <row r="330" spans="1:25" ht="15.75" customHeight="1">
       <c r="A330" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B330" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C330" s="11" t="s">
-        <v>692</v>
+        <v>694</v>
+      </c>
+      <c r="B330" s="9"/>
+      <c r="C330" s="10" t="s">
+        <v>844</v>
       </c>
       <c r="D330" s="9" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
@@ -15118,15 +15113,17 @@
       <c r="Y330" s="1"/>
     </row>
     <row r="331" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A331" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B331" s="9"/>
-      <c r="C331" s="10" t="s">
-        <v>844</v>
-      </c>
-      <c r="D331" s="9" t="s">
-        <v>695</v>
+      <c r="A331" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C331" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>1010</v>
       </c>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
@@ -15151,17 +15148,15 @@
       <c r="Y331" s="1"/>
     </row>
     <row r="332" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A332" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="B332" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C332" s="3" t="s">
-        <v>1013</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>1011</v>
+      <c r="A332" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="B332" s="13"/>
+      <c r="C332" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D332" s="13" t="s">
+        <v>696</v>
       </c>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
@@ -15187,49 +15182,51 @@
     </row>
     <row r="333" spans="1:25" ht="15.75" customHeight="1">
       <c r="A333" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B333" s="13"/>
-      <c r="C333" s="22" t="s">
-        <v>697</v>
+        <v>698</v>
+      </c>
+      <c r="B333" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="C333" s="14" t="s">
+        <v>700</v>
       </c>
       <c r="D333" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="E333" s="1"/>
-      <c r="F333" s="1"/>
-      <c r="G333" s="1"/>
-      <c r="H333" s="1"/>
-      <c r="I333" s="1"/>
-      <c r="J333" s="1"/>
-      <c r="K333" s="1"/>
-      <c r="L333" s="1"/>
-      <c r="M333" s="1"/>
-      <c r="N333" s="1"/>
-      <c r="O333" s="1"/>
-      <c r="P333" s="1"/>
-      <c r="Q333" s="1"/>
-      <c r="R333" s="1"/>
-      <c r="S333" s="1"/>
-      <c r="T333" s="1"/>
-      <c r="U333" s="1"/>
-      <c r="V333" s="1"/>
-      <c r="W333" s="1"/>
-      <c r="X333" s="1"/>
-      <c r="Y333" s="1"/>
+        <v>698</v>
+      </c>
+      <c r="E333" s="2"/>
+      <c r="F333" s="2"/>
+      <c r="G333" s="2"/>
+      <c r="H333" s="2"/>
+      <c r="I333" s="2"/>
+      <c r="J333" s="2"/>
+      <c r="K333" s="2"/>
+      <c r="L333" s="2"/>
+      <c r="M333" s="2"/>
+      <c r="N333" s="2"/>
+      <c r="O333" s="2"/>
+      <c r="P333" s="2"/>
+      <c r="Q333" s="2"/>
+      <c r="R333" s="2"/>
+      <c r="S333" s="2"/>
+      <c r="T333" s="2"/>
+      <c r="U333" s="2"/>
+      <c r="V333" s="2"/>
+      <c r="W333" s="2"/>
+      <c r="X333" s="2"/>
+      <c r="Y333" s="2"/>
     </row>
     <row r="334" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A334" s="13" t="s">
-        <v>698</v>
-      </c>
-      <c r="B334" s="13" t="s">
-        <v>699</v>
-      </c>
-      <c r="C334" s="14" t="s">
-        <v>700</v>
-      </c>
-      <c r="D334" s="13" t="s">
-        <v>698</v>
+      <c r="A334" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B334" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C334" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D334" s="9" t="s">
+        <v>701</v>
       </c>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
@@ -15254,52 +15251,52 @@
       <c r="Y334" s="2"/>
     </row>
     <row r="335" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A335" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B335" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="C335" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D335" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="E335" s="2"/>
-      <c r="F335" s="2"/>
-      <c r="G335" s="2"/>
-      <c r="H335" s="2"/>
-      <c r="I335" s="2"/>
-      <c r="J335" s="2"/>
-      <c r="K335" s="2"/>
-      <c r="L335" s="2"/>
-      <c r="M335" s="2"/>
-      <c r="N335" s="2"/>
-      <c r="O335" s="2"/>
-      <c r="P335" s="2"/>
-      <c r="Q335" s="2"/>
-      <c r="R335" s="2"/>
-      <c r="S335" s="2"/>
-      <c r="T335" s="2"/>
-      <c r="U335" s="2"/>
-      <c r="V335" s="2"/>
-      <c r="W335" s="2"/>
-      <c r="X335" s="2"/>
-      <c r="Y335" s="2"/>
+      <c r="A335" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C335" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E335" s="1"/>
+      <c r="F335" s="1"/>
+      <c r="G335" s="1"/>
+      <c r="H335" s="1"/>
+      <c r="I335" s="1"/>
+      <c r="J335" s="1"/>
+      <c r="K335" s="1"/>
+      <c r="L335" s="1"/>
+      <c r="M335" s="1"/>
+      <c r="N335" s="1"/>
+      <c r="O335" s="1"/>
+      <c r="P335" s="1"/>
+      <c r="Q335" s="1"/>
+      <c r="R335" s="1"/>
+      <c r="S335" s="1"/>
+      <c r="T335" s="1"/>
+      <c r="U335" s="1"/>
+      <c r="V335" s="1"/>
+      <c r="W335" s="1"/>
+      <c r="X335" s="1"/>
+      <c r="Y335" s="1"/>
     </row>
     <row r="336" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A336" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="B336" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C336" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D336" s="1" t="s">
-        <v>1014</v>
+      <c r="A336" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B336" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="C336" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="D336" s="9" t="s">
+        <v>704</v>
       </c>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
@@ -15324,87 +15321,87 @@
       <c r="Y336" s="1"/>
     </row>
     <row r="337" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A337" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="B337" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="C337" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D337" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="E337" s="1"/>
-      <c r="F337" s="1"/>
-      <c r="G337" s="1"/>
-      <c r="H337" s="1"/>
-      <c r="I337" s="1"/>
-      <c r="J337" s="1"/>
-      <c r="K337" s="1"/>
-      <c r="L337" s="1"/>
-      <c r="M337" s="1"/>
-      <c r="N337" s="1"/>
-      <c r="O337" s="1"/>
-      <c r="P337" s="1"/>
-      <c r="Q337" s="1"/>
-      <c r="R337" s="1"/>
-      <c r="S337" s="1"/>
-      <c r="T337" s="1"/>
-      <c r="U337" s="1"/>
-      <c r="V337" s="1"/>
-      <c r="W337" s="1"/>
-      <c r="X337" s="1"/>
-      <c r="Y337" s="1"/>
+      <c r="A337" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C337" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D337" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="E337" s="2"/>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+      <c r="H337" s="2"/>
+      <c r="I337" s="2"/>
+      <c r="J337" s="2"/>
+      <c r="K337" s="2"/>
+      <c r="L337" s="2"/>
+      <c r="M337" s="2"/>
+      <c r="N337" s="2"/>
+      <c r="O337" s="2"/>
+      <c r="P337" s="2"/>
+      <c r="Q337" s="2"/>
+      <c r="R337" s="2"/>
+      <c r="S337" s="2"/>
+      <c r="T337" s="2"/>
+      <c r="U337" s="2"/>
+      <c r="V337" s="2"/>
+      <c r="W337" s="2"/>
+      <c r="X337" s="2"/>
+      <c r="Y337" s="2"/>
     </row>
     <row r="338" spans="1:25" ht="15.75" customHeight="1">
       <c r="A338" s="3" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C338" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>712</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E338" s="2"/>
-      <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-      <c r="H338" s="2"/>
-      <c r="I338" s="2"/>
-      <c r="J338" s="2"/>
-      <c r="K338" s="2"/>
-      <c r="L338" s="2"/>
-      <c r="M338" s="2"/>
-      <c r="N338" s="2"/>
-      <c r="O338" s="2"/>
-      <c r="P338" s="2"/>
-      <c r="Q338" s="2"/>
-      <c r="R338" s="2"/>
-      <c r="S338" s="2"/>
-      <c r="T338" s="2"/>
-      <c r="U338" s="2"/>
-      <c r="V338" s="2"/>
-      <c r="W338" s="2"/>
-      <c r="X338" s="2"/>
-      <c r="Y338" s="2"/>
+        <v>710</v>
+      </c>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+      <c r="K338" s="1"/>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+      <c r="N338" s="1"/>
+      <c r="O338" s="1"/>
+      <c r="P338" s="1"/>
+      <c r="Q338" s="1"/>
+      <c r="R338" s="1"/>
+      <c r="S338" s="1"/>
+      <c r="T338" s="1"/>
+      <c r="U338" s="1"/>
+      <c r="V338" s="1"/>
+      <c r="W338" s="1"/>
+      <c r="X338" s="1"/>
+      <c r="Y338" s="1"/>
     </row>
     <row r="339" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A339" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="C339" s="4" t="s">
-        <v>712</v>
-      </c>
-      <c r="D339" s="3" t="s">
-        <v>710</v>
+      <c r="A339" s="5" t="s">
+        <v>713</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C339" s="47" t="s">
+        <v>715</v>
+      </c>
+      <c r="D339" s="5" t="s">
+        <v>716</v>
       </c>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
@@ -15430,16 +15427,14 @@
     </row>
     <row r="340" spans="1:25" ht="15.75" customHeight="1">
       <c r="A340" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="B340" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="C340" s="47" t="s">
-        <v>715</v>
+        <v>717</v>
+      </c>
+      <c r="B340" s="5"/>
+      <c r="C340" s="6" t="s">
+        <v>718</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
@@ -15464,669 +15459,642 @@
       <c r="Y340" s="1"/>
     </row>
     <row r="341" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A341" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="B341" s="5"/>
-      <c r="C341" s="6" t="s">
-        <v>718</v>
-      </c>
-      <c r="D341" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="E341" s="1"/>
-      <c r="F341" s="1"/>
-      <c r="G341" s="1"/>
-      <c r="H341" s="1"/>
-      <c r="I341" s="1"/>
-      <c r="J341" s="1"/>
-      <c r="K341" s="1"/>
-      <c r="L341" s="1"/>
-      <c r="M341" s="1"/>
-      <c r="N341" s="1"/>
-      <c r="O341" s="1"/>
-      <c r="P341" s="1"/>
-      <c r="Q341" s="1"/>
-      <c r="R341" s="1"/>
-      <c r="S341" s="1"/>
-      <c r="T341" s="1"/>
-      <c r="U341" s="1"/>
-      <c r="V341" s="1"/>
-      <c r="W341" s="1"/>
-      <c r="X341" s="1"/>
-      <c r="Y341" s="1"/>
+      <c r="A341" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>719</v>
+      </c>
     </row>
     <row r="342" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A342" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="B342" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="C342" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="D342" s="3" t="s">
-        <v>719</v>
+      <c r="A342" s="9" t="s">
+        <v>722</v>
+      </c>
+      <c r="B342" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="C342" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="D342" s="9" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="343" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A343" s="9" t="s">
-        <v>722</v>
-      </c>
-      <c r="B343" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="C343" s="11" t="s">
-        <v>724</v>
-      </c>
-      <c r="D343" s="9" t="s">
-        <v>722</v>
+      <c r="A343" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D343" s="3" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="344" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A344" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="B344" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="C344" s="4" t="s">
-        <v>845</v>
-      </c>
-      <c r="D344" s="3" t="s">
-        <v>727</v>
+      <c r="A344" s="5" t="s">
+        <v>728</v>
+      </c>
+      <c r="B344" s="5"/>
+      <c r="C344" s="47" t="s">
+        <v>729</v>
+      </c>
+      <c r="D344" s="5" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="345" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A345" s="5" t="s">
-        <v>728</v>
-      </c>
-      <c r="B345" s="5"/>
-      <c r="C345" s="47" t="s">
-        <v>729</v>
-      </c>
-      <c r="D345" s="5" t="s">
-        <v>728</v>
+      <c r="A345" s="3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B345" s="3"/>
+      <c r="C345" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="D345" s="3" t="s">
+        <v>730</v>
       </c>
     </row>
     <row r="346" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A346" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B346" s="3"/>
-      <c r="C346" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="D346" s="3" t="s">
-        <v>730</v>
+      <c r="A346" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B346" s="9"/>
+      <c r="C346" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="D346" s="9" t="s">
+        <v>732</v>
       </c>
     </row>
     <row r="347" spans="1:25" ht="15.75" customHeight="1">
       <c r="A347" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="B347" s="9"/>
+        <v>734</v>
+      </c>
+      <c r="B347" s="9" t="s">
+        <v>735</v>
+      </c>
       <c r="C347" s="10" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="D347" s="9" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="348" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A348" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="B348" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="C348" s="10" t="s">
-        <v>736</v>
-      </c>
-      <c r="D348" s="9" t="s">
-        <v>734</v>
+      <c r="A348" s="5" t="s">
+        <v>737</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>738</v>
+      </c>
+      <c r="C348" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="D348" s="5" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="349" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A349" s="5" t="s">
-        <v>737</v>
-      </c>
-      <c r="B349" s="5" t="s">
-        <v>738</v>
-      </c>
-      <c r="C349" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="D349" s="5" t="s">
-        <v>737</v>
+      <c r="A349" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C349" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D349" s="3" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="350" spans="1:25" ht="15.75" customHeight="1">
       <c r="A350" s="3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
     </row>
     <row r="351" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A351" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="B351" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="C351" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="D351" s="3" t="s">
-        <v>743</v>
+      <c r="A351" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B351" s="5"/>
+      <c r="C351" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>747</v>
       </c>
     </row>
     <row r="352" spans="1:25" ht="15.75" customHeight="1">
       <c r="A352" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="B352" s="5"/>
-      <c r="C352" s="6" t="s">
-        <v>746</v>
+        <v>748</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="C352" s="30" t="s">
+        <v>750</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A353" s="5" t="s">
-        <v>748</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>749</v>
-      </c>
-      <c r="C353" s="30" t="s">
-        <v>750</v>
-      </c>
-      <c r="D353" s="5" t="s">
-        <v>748</v>
+      <c r="A353" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C353" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D353" s="3" t="s">
+        <v>751</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1">
       <c r="A354" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A355" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="B355" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="C355" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="D355" s="3" t="s">
-        <v>754</v>
+      <c r="A355" s="5" t="s">
+        <v>757</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>758</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>757</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A356" s="5" t="s">
-        <v>757</v>
-      </c>
-      <c r="B356" s="5" t="s">
-        <v>758</v>
-      </c>
-      <c r="C356" s="6" t="s">
-        <v>759</v>
-      </c>
-      <c r="D356" s="5" t="s">
-        <v>757</v>
+      <c r="A356" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B356" s="7"/>
+      <c r="C356" s="31" t="s">
+        <v>761</v>
+      </c>
+      <c r="D356" s="7" t="s">
+        <v>762</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A357" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="B357" s="7"/>
-      <c r="C357" s="31" t="s">
-        <v>761</v>
-      </c>
-      <c r="D357" s="7" t="s">
-        <v>762</v>
+      <c r="A357" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>1016</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1">
       <c r="A358" s="3" t="s">
-        <v>1017</v>
+        <v>763</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>1018</v>
+        <v>764</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>1019</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>1017</v>
+        <v>765</v>
+      </c>
+      <c r="D358" s="3" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A359" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="B359" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="C359" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="D359" s="3" t="s">
-        <v>763</v>
+      <c r="A359" s="5" t="s">
+        <v>766</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>767</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="D359" s="5" t="s">
+        <v>769</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A360" s="5" t="s">
-        <v>766</v>
-      </c>
-      <c r="B360" s="5" t="s">
-        <v>767</v>
-      </c>
-      <c r="C360" s="6" t="s">
-        <v>768</v>
-      </c>
-      <c r="D360" s="5" t="s">
-        <v>769</v>
+      <c r="A360" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>771</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="D360" s="3" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A361" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B361" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="C361" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="D361" s="3" t="s">
-        <v>770</v>
+      <c r="A361" s="9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B361" s="9"/>
+      <c r="C361" s="11" t="s">
+        <v>774</v>
+      </c>
+      <c r="D361" s="9" t="s">
+        <v>773</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1">
       <c r="A362" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="B362" s="9"/>
-      <c r="C362" s="11" t="s">
-        <v>774</v>
+        <v>775</v>
+      </c>
+      <c r="B362" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="C362" s="10" t="s">
+        <v>777</v>
       </c>
       <c r="D362" s="9" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1">
       <c r="A363" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="B363" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="C363" s="10" t="s">
-        <v>777</v>
+        <v>778</v>
+      </c>
+      <c r="B363" s="9"/>
+      <c r="C363" s="11" t="s">
+        <v>779</v>
       </c>
       <c r="D363" s="9" t="s">
-        <v>775</v>
+        <v>780</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A364" s="9" t="s">
-        <v>778</v>
-      </c>
-      <c r="B364" s="9"/>
-      <c r="C364" s="11" t="s">
-        <v>779</v>
-      </c>
-      <c r="D364" s="9" t="s">
-        <v>780</v>
+      <c r="A364" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B364" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C364" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D364" s="7" t="s">
+        <v>785</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1">
       <c r="A365" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="B365" s="7" t="s">
-        <v>784</v>
-      </c>
+        <v>781</v>
+      </c>
+      <c r="B365" s="7"/>
       <c r="C365" s="8" t="s">
-        <v>170</v>
+        <v>782</v>
       </c>
       <c r="D365" s="7" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A366" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="B366" s="7"/>
-      <c r="C366" s="8" t="s">
-        <v>782</v>
-      </c>
-      <c r="D366" s="7" t="s">
-        <v>781</v>
+      <c r="A366" s="5" t="s">
+        <v>790</v>
+      </c>
+      <c r="B366" s="5"/>
+      <c r="C366" s="6" t="s">
+        <v>791</v>
+      </c>
+      <c r="D366" s="5" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1">
       <c r="A367" s="5" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B367" s="5"/>
       <c r="C367" s="6" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1">
       <c r="A368" s="5" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B368" s="5"/>
       <c r="C368" s="6" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1">
       <c r="A369" s="5" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B369" s="5"/>
       <c r="C369" s="6" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1">
       <c r="A370" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="B370" s="5"/>
+        <v>800</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>801</v>
+      </c>
       <c r="C370" s="6" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1">
       <c r="A371" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B371" s="5" t="s">
-        <v>801</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="B371" s="5"/>
       <c r="C371" s="6" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A372" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="B372" s="5"/>
-      <c r="C372" s="6" t="s">
-        <v>805</v>
-      </c>
-      <c r="D372" s="5" t="s">
-        <v>806</v>
+      <c r="A372" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="B372" s="7"/>
+      <c r="C372" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="D372" s="7" t="s">
+        <v>807</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A373" s="7" t="s">
-        <v>807</v>
-      </c>
-      <c r="B373" s="7"/>
-      <c r="C373" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="D373" s="7" t="s">
-        <v>807</v>
+      <c r="A373" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="B373" s="5"/>
+      <c r="C373" s="6" t="s">
+        <v>810</v>
+      </c>
+      <c r="D373" s="5" t="s">
+        <v>809</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A374" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="B374" s="5"/>
-      <c r="C374" s="6" t="s">
-        <v>810</v>
-      </c>
-      <c r="D374" s="5" t="s">
-        <v>809</v>
+      <c r="A374" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>1022</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A375" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="B375" s="3" t="s">
-        <v>1021</v>
-      </c>
-      <c r="C375" s="3" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D375" s="1" t="s">
+      <c r="A375" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>813</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A376" s="3" t="s">
         <v>1023</v>
       </c>
-    </row>
-    <row r="376" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A376" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="B376" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="C376" s="6" t="s">
-        <v>813</v>
-      </c>
-      <c r="D376" s="5" t="s">
-        <v>811</v>
+      <c r="B376" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C376" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1">
       <c r="A377" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="B377" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C377" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>1024</v>
+        <v>814</v>
+      </c>
+      <c r="B377" s="3"/>
+      <c r="C377" s="50" t="s">
+        <v>815</v>
+      </c>
+      <c r="D377" s="3" t="s">
+        <v>814</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A378" s="3" t="s">
-        <v>814</v>
-      </c>
-      <c r="B378" s="3"/>
-      <c r="C378" s="50" t="s">
-        <v>815</v>
-      </c>
-      <c r="D378" s="3" t="s">
-        <v>814</v>
+      <c r="A378" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="B378" s="9"/>
+      <c r="C378" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="D378" s="9" t="s">
+        <v>818</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1">
       <c r="A379" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="B379" s="9"/>
-      <c r="C379" s="10" t="s">
-        <v>817</v>
+        <v>819</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="C379" s="11" t="s">
+        <v>821</v>
       </c>
       <c r="D379" s="9" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A380" s="9" t="s">
-        <v>819</v>
-      </c>
-      <c r="B380" s="9" t="s">
-        <v>820</v>
-      </c>
-      <c r="C380" s="11" t="s">
-        <v>821</v>
-      </c>
-      <c r="D380" s="9" t="s">
-        <v>819</v>
+      <c r="A380" s="7" t="s">
+        <v>924</v>
+      </c>
+      <c r="B380" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="C380" s="53" t="s">
+        <v>926</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>924</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A381" s="7" t="s">
-        <v>924</v>
-      </c>
-      <c r="B381" s="7" t="s">
-        <v>925</v>
-      </c>
-      <c r="C381" s="53" t="s">
-        <v>926</v>
-      </c>
-      <c r="D381" s="7" t="s">
-        <v>924</v>
+      <c r="A381" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C381" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="D381" s="3" t="s">
+        <v>822</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A382" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B382" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C382" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="D382" s="3" t="s">
-        <v>822</v>
+      <c r="A382" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B382" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="C382" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="D382" s="9" t="s">
+        <v>825</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A383" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="B383" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="C383" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="D383" s="9" t="s">
-        <v>825</v>
+      <c r="A383" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="B383" s="3"/>
+      <c r="C383" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="D383" s="3" t="s">
+        <v>828</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A384" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="B384" s="3"/>
-      <c r="C384" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="D384" s="3" t="s">
-        <v>828</v>
+      <c r="A384" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B384" s="5"/>
+      <c r="C384" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="D384" s="48" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A385" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="B385" s="5"/>
-      <c r="C385" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="D385" s="48" t="s">
-        <v>830</v>
+      <c r="A385" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C385" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="D385" s="1" t="s">
+        <v>832</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A386" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="B386" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="C386" s="12" t="s">
-        <v>834</v>
-      </c>
-      <c r="D386" s="1" t="s">
-        <v>832</v>
+      <c r="A386" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="B386" s="5"/>
+      <c r="C386" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="D386" s="49" t="s">
+        <v>837</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A387" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="B387" s="5"/>
-      <c r="C387" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="D387" s="49" t="s">
-        <v>837</v>
+      <c r="A387" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D387" s="1" t="s">
+        <v>1026</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A388" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B388" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="C388" s="3" t="s">
-        <v>1029</v>
-      </c>
-      <c r="D388" s="1" t="s">
-        <v>1027</v>
+      <c r="A388" s="7" t="s">
+        <v>927</v>
+      </c>
+      <c r="B388" s="7" t="s">
+        <v>928</v>
+      </c>
+      <c r="C388" s="69" t="s">
+        <v>929</v>
+      </c>
+      <c r="D388" s="70" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A389" s="7" t="s">
-        <v>927</v>
-      </c>
-      <c r="B389" s="7" t="s">
-        <v>928</v>
-      </c>
-      <c r="C389" s="69" t="s">
-        <v>929</v>
-      </c>
-      <c r="D389" s="70" t="s">
-        <v>927</v>
-      </c>
+      <c r="A389" s="3"/>
+      <c r="B389" s="3"/>
+      <c r="C389" s="3"/>
+      <c r="D389" s="1"/>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1">
       <c r="A390" s="3"/>
@@ -21305,12 +21273,6 @@
       <c r="B1252" s="3"/>
       <c r="C1252" s="3"/>
       <c r="D1252" s="1"/>
-    </row>
-    <row r="1253" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A1253" s="3"/>
-      <c r="B1253" s="3"/>
-      <c r="C1253" s="3"/>
-      <c r="D1253" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21446,106 +21408,106 @@
     <hyperlink ref="C213" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
     <hyperlink ref="C57" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C216" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C222" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C227" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C230" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C231" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C232" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C234" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C235" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C236" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C239" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C240" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C241" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C243" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C244" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C245" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C247" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C249" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C250" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C251" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C253" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C256" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C257" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C258" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C262" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C263" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C266" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C267" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C269" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C270" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C248" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C272" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C273" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C279" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C280" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C283" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C286" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C284" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C287" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C289" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C292" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C293" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C294" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C296" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C297" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C298" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C299" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C302" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C306" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C307" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C309" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C310" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C311" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C314" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C315" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C317" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C327" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C328" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C323" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C324" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C326" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C329" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C330" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C333" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C334" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C339" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C340" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C341" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C343" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C345" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C347" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C349" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C352" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C353" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C356" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C357" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C360" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C361" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C362" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C364" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C366" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C365" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C221" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C226" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C229" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C230" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C231" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C233" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C234" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C235" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C238" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C239" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C240" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C242" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C243" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C244" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C246" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C248" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C249" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C250" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C252" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C255" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C256" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C257" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C261" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C262" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C265" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C266" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C268" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C269" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C247" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C271" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C272" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C278" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C279" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C282" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C285" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C283" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C286" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C288" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C291" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C292" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C293" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C295" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C296" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C297" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C298" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C301" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C305" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C306" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C308" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C309" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C310" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C313" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C314" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C316" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C326" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C327" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C322" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C323" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C325" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C328" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C329" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C332" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C333" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C338" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C339" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C340" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C342" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C344" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C346" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C348" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C351" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C352" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C355" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C356" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C359" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C360" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C361" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C363" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C365" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C364" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C8" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C367" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C368" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C369" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C370" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C371" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C372" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C373" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C374" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C376" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C378" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C380" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C382" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C384" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C385" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C386" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C387" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C366" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C367" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C368" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C369" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C370" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C371" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C372" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C373" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C375" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C377" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C379" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C381" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C383" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C384" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C385" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C386" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="C167" r:id="rId230" xr:uid="{98DDE684-CC21-7C49-B22B-C4F92C88FD93}"/>
-    <hyperlink ref="C225" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
-    <hyperlink ref="C259" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
+    <hyperlink ref="C224" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
+    <hyperlink ref="C258" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
     <hyperlink ref="C133" r:id="rId233" xr:uid="{6B2056CE-BB4C-D74B-A597-EA3A8C5C2030}"/>
     <hyperlink ref="C6" r:id="rId234" xr:uid="{D36410A9-1671-0F4D-A4CE-1789BA83AD03}"/>
     <hyperlink ref="C24" r:id="rId235" xr:uid="{8BADE627-88AB-8344-8C39-BDD2E908CD68}"/>
@@ -21565,22 +21527,21 @@
     <hyperlink ref="C196" r:id="rId249" xr:uid="{B4AAB667-FFFA-F64C-BC79-708CC2119E9B}"/>
     <hyperlink ref="C202" r:id="rId250" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
     <hyperlink ref="C220" r:id="rId251" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
-    <hyperlink ref="C224" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
-    <hyperlink ref="C276" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
-    <hyperlink ref="C282" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
-    <hyperlink ref="C305" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
-    <hyperlink ref="C308" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
-    <hyperlink ref="C316" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C381" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C389" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C223" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
+    <hyperlink ref="C275" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
+    <hyperlink ref="C281" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
+    <hyperlink ref="C304" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
+    <hyperlink ref="C307" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
+    <hyperlink ref="C315" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
+    <hyperlink ref="C380" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C388" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C188" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
     <hyperlink ref="C215" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
-    <hyperlink ref="C221" r:id="rId262" xr:uid="{8D2B8DC1-9F59-E049-A731-DAB4A3C99261}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId263"/>
+    <tablePart r:id="rId262"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97960E61-00F9-3D48-943D-507125F71680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633ED5FA-E166-644F-A8FB-4E6351A4B0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="1051">
   <si>
     <t>Name</t>
   </si>
@@ -2619,9 +2619,6 @@
     <t>https://www.geonames.org/3077895/cesky-dub.html</t>
   </si>
   <si>
-    <t>Boehmisch-Aicha</t>
-  </si>
-  <si>
     <t>Brüssel</t>
   </si>
   <si>
@@ -3172,6 +3169,18 @@
   </si>
   <si>
     <t>Beirut</t>
+  </si>
+  <si>
+    <t>BoehmischAicha</t>
+  </si>
+  <si>
+    <t>Neuhaus</t>
+  </si>
+  <si>
+    <t>Jindřichův Hradec</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/3074149/jindrichuv-hradec.html</t>
   </si>
 </sst>
 </file>
@@ -3765,9 +3774,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D388" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D388">
-    <sortCondition ref="D388"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D389" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D389">
+    <sortCondition ref="D389"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -3977,7 +3986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Y1252"/>
+  <dimension ref="A2:Y1253"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -4024,14 +4033,14 @@
     </row>
     <row r="3" spans="1:25" ht="16">
       <c r="A3" s="78" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B3" s="78"/>
       <c r="C3" s="78" t="s">
+        <v>930</v>
+      </c>
+      <c r="D3" s="79" t="s">
         <v>931</v>
-      </c>
-      <c r="D3" s="79" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="4" spans="1:25">
@@ -4207,14 +4216,14 @@
     </row>
     <row r="9" spans="1:25" ht="16">
       <c r="A9" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -4240,16 +4249,16 @@
     </row>
     <row r="10" spans="1:25" ht="16">
       <c r="A10" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>1031</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>1032</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>1033</v>
-      </c>
       <c r="D10" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -4374,16 +4383,16 @@
     </row>
     <row r="14" spans="1:25" ht="16">
       <c r="A14" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>1034</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>1036</v>
-      </c>
       <c r="D14" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
@@ -4945,14 +4954,14 @@
     </row>
     <row r="31" spans="1:25">
       <c r="A31" s="9" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B31" s="9"/>
       <c r="C31" s="11" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>1046</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>1047</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -5011,14 +5020,14 @@
     </row>
     <row r="33" spans="1:25" ht="16">
       <c r="A33" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="3" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -5248,16 +5257,16 @@
     </row>
     <row r="40" spans="1:25" ht="16">
       <c r="A40" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>933</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>934</v>
       </c>
-      <c r="C40" s="3" t="s">
-        <v>935</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
@@ -5283,14 +5292,14 @@
     </row>
     <row r="41" spans="1:25" ht="16">
       <c r="A41" s="3" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B41" s="3"/>
       <c r="C41" s="3" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
@@ -5351,14 +5360,14 @@
     </row>
     <row r="43" spans="1:25" ht="16">
       <c r="A43" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>937</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>938</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -5393,7 +5402,7 @@
         <v>862</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>863</v>
+        <v>1047</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -5788,16 +5797,16 @@
     </row>
     <row r="56" spans="1:25" ht="16">
       <c r="A56" s="55" t="s">
+        <v>863</v>
+      </c>
+      <c r="B56" s="55" t="s">
+        <v>863</v>
+      </c>
+      <c r="C56" s="56" t="s">
         <v>864</v>
       </c>
-      <c r="B56" s="55" t="s">
-        <v>864</v>
-      </c>
-      <c r="C56" s="56" t="s">
+      <c r="D56" s="55" t="s">
         <v>865</v>
-      </c>
-      <c r="D56" s="55" t="s">
-        <v>866</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
@@ -5961,16 +5970,16 @@
     </row>
     <row r="61" spans="1:25" ht="16">
       <c r="A61" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>939</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>940</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>941</v>
-      </c>
       <c r="D61" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
@@ -6029,16 +6038,16 @@
     </row>
     <row r="63" spans="1:25" ht="16">
       <c r="A63" s="57" t="s">
+        <v>866</v>
+      </c>
+      <c r="B63" s="58" t="s">
+        <v>866</v>
+      </c>
+      <c r="C63" s="59" t="s">
         <v>867</v>
       </c>
-      <c r="B63" s="58" t="s">
-        <v>867</v>
-      </c>
-      <c r="C63" s="59" t="s">
-        <v>868</v>
-      </c>
       <c r="D63" s="57" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
@@ -6064,14 +6073,14 @@
     </row>
     <row r="64" spans="1:25" ht="16">
       <c r="A64" s="3" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B64" s="3"/>
       <c r="C64" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -6299,16 +6308,16 @@
     </row>
     <row r="71" spans="1:25" ht="16">
       <c r="A71" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>943</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>944</v>
-      </c>
       <c r="D71" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -6404,16 +6413,16 @@
     </row>
     <row r="74" spans="1:25" ht="16">
       <c r="A74" s="61" t="s">
+        <v>868</v>
+      </c>
+      <c r="B74" s="61" t="s">
         <v>869</v>
       </c>
-      <c r="B74" s="61" t="s">
+      <c r="C74" s="62" t="s">
         <v>870</v>
       </c>
-      <c r="C74" s="62" t="s">
-        <v>871</v>
-      </c>
       <c r="D74" s="61" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
@@ -6439,16 +6448,16 @@
     </row>
     <row r="75" spans="1:25" ht="16">
       <c r="A75" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>945</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>947</v>
-      </c>
       <c r="D75" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
@@ -6474,16 +6483,16 @@
     </row>
     <row r="76" spans="1:25" ht="16">
       <c r="A76" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="B76" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="B76" s="7" t="s">
+      <c r="C76" s="80" t="s">
         <v>873</v>
       </c>
-      <c r="C76" s="80" t="s">
-        <v>874</v>
-      </c>
       <c r="D76" s="7" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
@@ -7494,16 +7503,16 @@
     </row>
     <row r="106" spans="1:25" ht="15.75" customHeight="1">
       <c r="A106" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="B106" s="3" t="s">
         <v>948</v>
       </c>
-      <c r="B106" s="3" t="s">
+      <c r="C106" s="3" t="s">
         <v>949</v>
       </c>
-      <c r="C106" s="3" t="s">
-        <v>950</v>
-      </c>
       <c r="D106" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" s="2"/>
@@ -7665,16 +7674,16 @@
     </row>
     <row r="111" spans="1:25" ht="18.75" customHeight="1">
       <c r="A111" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="B111" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="C111" s="3" t="s">
+      <c r="D111" s="1" t="s">
         <v>953</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>954</v>
       </c>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -8238,14 +8247,14 @@
     </row>
     <row r="128" spans="1:25" ht="15.75" customHeight="1">
       <c r="A128" s="7" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B128" s="7"/>
       <c r="C128" s="53" t="s">
+        <v>875</v>
+      </c>
+      <c r="D128" s="7" t="s">
         <v>876</v>
-      </c>
-      <c r="D128" s="7" t="s">
-        <v>877</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -8271,16 +8280,16 @@
     </row>
     <row r="129" spans="1:25" ht="15.75" customHeight="1">
       <c r="A129" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="B129" s="3" t="s">
         <v>955</v>
       </c>
-      <c r="B129" s="3" t="s">
+      <c r="C129" s="3" t="s">
         <v>956</v>
       </c>
-      <c r="C129" s="3" t="s">
-        <v>957</v>
-      </c>
       <c r="D129" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -8541,16 +8550,16 @@
     </row>
     <row r="137" spans="1:25" ht="15.75" customHeight="1">
       <c r="A137" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="B137" s="7" t="s">
         <v>878</v>
       </c>
-      <c r="B137" s="7" t="s">
+      <c r="C137" s="53" t="s">
         <v>879</v>
       </c>
-      <c r="C137" s="53" t="s">
-        <v>880</v>
-      </c>
       <c r="D137" s="7" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -8611,14 +8620,14 @@
     </row>
     <row r="139" spans="1:25" ht="15.75" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -8644,16 +8653,16 @@
     </row>
     <row r="140" spans="1:25" ht="15.75" customHeight="1">
       <c r="A140" s="3" t="s">
+        <v>959</v>
+      </c>
+      <c r="B140" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="B140" s="3" t="s">
+      <c r="C140" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="C140" s="3" t="s">
-        <v>962</v>
-      </c>
       <c r="D140" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" s="2"/>
@@ -8679,14 +8688,14 @@
     </row>
     <row r="141" spans="1:25" ht="15.75" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -8879,16 +8888,16 @@
     </row>
     <row r="147" spans="1:25" ht="15.75" customHeight="1">
       <c r="A147" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="B147" s="7" t="s">
         <v>881</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="C147" s="64" t="s">
         <v>882</v>
       </c>
-      <c r="C147" s="64" t="s">
+      <c r="D147" s="7" t="s">
         <v>883</v>
-      </c>
-      <c r="D147" s="7" t="s">
-        <v>884</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -8982,16 +8991,16 @@
     </row>
     <row r="151" spans="1:25" ht="15.75" customHeight="1">
       <c r="A151" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="B151" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="B151" s="7" t="s">
+      <c r="C151" s="64" t="s">
         <v>886</v>
       </c>
-      <c r="C151" s="64" t="s">
-        <v>887</v>
-      </c>
       <c r="D151" s="7" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -9118,16 +9127,16 @@
     </row>
     <row r="155" spans="1:25" ht="15.75" customHeight="1">
       <c r="A155" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="B155" s="7" t="s">
         <v>888</v>
       </c>
-      <c r="B155" s="7" t="s">
+      <c r="C155" s="53" t="s">
         <v>889</v>
       </c>
-      <c r="C155" s="53" t="s">
+      <c r="D155" s="7" t="s">
         <v>890</v>
-      </c>
-      <c r="D155" s="7" t="s">
-        <v>891</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -9256,16 +9265,16 @@
     </row>
     <row r="159" spans="1:25" ht="15.75" customHeight="1">
       <c r="A159" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="B159" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="B159" s="3" t="s">
+      <c r="C159" s="3" t="s">
         <v>964</v>
       </c>
-      <c r="C159" s="3" t="s">
-        <v>965</v>
-      </c>
       <c r="D159" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -9291,16 +9300,16 @@
     </row>
     <row r="160" spans="1:25" ht="15.75" customHeight="1">
       <c r="A160" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B160" s="3" t="s">
         <v>966</v>
       </c>
-      <c r="B160" s="3" t="s">
+      <c r="C160" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="C160" s="3" t="s">
-        <v>968</v>
-      </c>
       <c r="D160" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -9670,16 +9679,16 @@
     </row>
     <row r="171" spans="1:25" ht="15.75" customHeight="1">
       <c r="A171" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="B171" s="3" t="s">
         <v>969</v>
       </c>
-      <c r="B171" s="3" t="s">
+      <c r="C171" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="C171" s="3" t="s">
-        <v>971</v>
-      </c>
       <c r="D171" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -9705,16 +9714,16 @@
     </row>
     <row r="172" spans="1:25" ht="15.75" customHeight="1">
       <c r="A172" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="B172" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="B172" s="3" t="s">
+      <c r="C172" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="C172" s="3" t="s">
-        <v>974</v>
-      </c>
       <c r="D172" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -10086,7 +10095,7 @@
         <v>367</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D183" s="1" t="s">
         <v>366</v>
@@ -10148,16 +10157,16 @@
     </row>
     <row r="185" spans="1:25" ht="15.75" customHeight="1">
       <c r="A185" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="B185" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="B185" s="3" t="s">
+      <c r="C185" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="C185" s="3" t="s">
-        <v>978</v>
-      </c>
       <c r="D185" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="E185" s="1"/>
       <c r="F185" s="1"/>
@@ -10183,16 +10192,16 @@
     </row>
     <row r="186" spans="1:25" ht="15.75" customHeight="1">
       <c r="A186" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="B186" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="B186" s="3" t="s">
+      <c r="C186" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="C186" s="3" t="s">
-        <v>981</v>
-      </c>
       <c r="D186" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -10391,16 +10400,16 @@
     </row>
     <row r="192" spans="1:25" ht="15.75" customHeight="1">
       <c r="A192" s="65" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B192" s="65" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C192" s="66" t="s">
         <v>729</v>
       </c>
       <c r="D192" s="65" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1"/>
@@ -10426,16 +10435,16 @@
     </row>
     <row r="193" spans="1:25" ht="15.75" customHeight="1">
       <c r="A193" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="B193" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="B193" s="3" t="s">
+      <c r="C193" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="C193" s="3" t="s">
-        <v>984</v>
-      </c>
       <c r="D193" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1"/>
@@ -10527,16 +10536,16 @@
     </row>
     <row r="196" spans="1:25" ht="15.75" customHeight="1">
       <c r="A196" s="65" t="s">
+        <v>894</v>
+      </c>
+      <c r="B196" s="65" t="s">
         <v>895</v>
       </c>
-      <c r="B196" s="65" t="s">
+      <c r="C196" s="66" t="s">
         <v>896</v>
       </c>
-      <c r="C196" s="66" t="s">
-        <v>897</v>
-      </c>
       <c r="D196" s="65" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
@@ -10698,16 +10707,16 @@
     </row>
     <row r="201" spans="1:25" ht="15.75" customHeight="1">
       <c r="A201" s="65" t="s">
+        <v>892</v>
+      </c>
+      <c r="B201" s="65" t="s">
+        <v>892</v>
+      </c>
+      <c r="C201" s="66" t="s">
         <v>893</v>
       </c>
-      <c r="B201" s="65" t="s">
-        <v>893</v>
-      </c>
-      <c r="C201" s="66" t="s">
-        <v>894</v>
-      </c>
       <c r="D201" s="65" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E201" s="1"/>
       <c r="F201" s="1"/>
@@ -10733,14 +10742,14 @@
     </row>
     <row r="202" spans="1:25" ht="15.75" customHeight="1">
       <c r="A202" s="65" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B202" s="65"/>
       <c r="C202" s="66" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D202" s="65" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1"/>
@@ -10801,14 +10810,14 @@
     </row>
     <row r="204" spans="1:25" ht="15.75" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="B204" s="3"/>
       <c r="C204" s="3" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1"/>
@@ -10968,14 +10977,14 @@
     </row>
     <row r="209" spans="1:25" ht="15.75" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B209" s="3"/>
       <c r="C209" s="3" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E209" s="1"/>
       <c r="F209" s="1"/>
@@ -11269,14 +11278,14 @@
     </row>
     <row r="218" spans="1:25" ht="15.75" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="B218" s="3"/>
       <c r="C218" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E218" s="1"/>
       <c r="F218" s="1"/>
@@ -11335,16 +11344,16 @@
     </row>
     <row r="220" spans="1:25" ht="15.75" customHeight="1">
       <c r="A220" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="B220" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="B220" s="7" t="s">
+      <c r="C220" s="53" t="s">
         <v>901</v>
       </c>
-      <c r="C220" s="53" t="s">
-        <v>902</v>
-      </c>
       <c r="D220" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E220" s="1"/>
       <c r="F220" s="1"/>
@@ -11369,17 +11378,17 @@
       <c r="Y220" s="1"/>
     </row>
     <row r="221" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A221" s="9" t="s">
-        <v>442</v>
-      </c>
-      <c r="B221" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="C221" s="11" t="s">
-        <v>444</v>
-      </c>
-      <c r="D221" s="9" t="s">
-        <v>442</v>
+      <c r="A221" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C221" s="53" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>1048</v>
       </c>
       <c r="E221" s="1"/>
       <c r="F221" s="1"/>
@@ -11405,16 +11414,16 @@
     </row>
     <row r="222" spans="1:25" ht="15.75" customHeight="1">
       <c r="A222" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B222" s="9" t="s">
-        <v>446</v>
-      </c>
-      <c r="C222" s="10" t="s">
-        <v>447</v>
+        <v>443</v>
+      </c>
+      <c r="C222" s="11" t="s">
+        <v>444</v>
       </c>
       <c r="D222" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E222" s="1"/>
       <c r="F222" s="1"/>
@@ -11439,52 +11448,52 @@
       <c r="Y222" s="1"/>
     </row>
     <row r="223" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A223" s="7" t="s">
+      <c r="A223" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="C223" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1"/>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1"/>
+      <c r="I223" s="1"/>
+      <c r="J223" s="1"/>
+      <c r="K223" s="1"/>
+      <c r="L223" s="1"/>
+      <c r="M223" s="1"/>
+      <c r="N223" s="1"/>
+      <c r="O223" s="1"/>
+      <c r="P223" s="1"/>
+      <c r="Q223" s="1"/>
+      <c r="R223" s="1"/>
+      <c r="S223" s="1"/>
+      <c r="T223" s="1"/>
+      <c r="U223" s="1"/>
+      <c r="V223" s="1"/>
+      <c r="W223" s="1"/>
+      <c r="X223" s="1"/>
+      <c r="Y223" s="1"/>
+    </row>
+    <row r="224" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A224" s="7" t="s">
+        <v>902</v>
+      </c>
+      <c r="B224" s="7" t="s">
         <v>903</v>
       </c>
-      <c r="B223" s="7" t="s">
+      <c r="C224" s="53" t="s">
         <v>904</v>
       </c>
-      <c r="C223" s="53" t="s">
-        <v>905</v>
-      </c>
-      <c r="D223" s="7" t="s">
-        <v>903</v>
-      </c>
-      <c r="E223" s="2"/>
-      <c r="F223" s="2"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="2"/>
-      <c r="K223" s="2"/>
-      <c r="L223" s="2"/>
-      <c r="M223" s="2"/>
-      <c r="N223" s="2"/>
-      <c r="O223" s="2"/>
-      <c r="P223" s="2"/>
-      <c r="Q223" s="2"/>
-      <c r="R223" s="2"/>
-      <c r="S223" s="2"/>
-      <c r="T223" s="2"/>
-      <c r="U223" s="2"/>
-      <c r="V223" s="2"/>
-      <c r="W223" s="2"/>
-      <c r="X223" s="2"/>
-      <c r="Y223" s="2"/>
-    </row>
-    <row r="224" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A224" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="C224" s="50" t="s">
-        <v>841</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>450</v>
+      <c r="D224" s="7" t="s">
+        <v>902</v>
       </c>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
@@ -11510,49 +11519,51 @@
     </row>
     <row r="225" spans="1:25" ht="15.75" customHeight="1">
       <c r="A225" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C225" s="50" t="s">
+        <v>841</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
+      <c r="J225" s="2"/>
+      <c r="K225" s="2"/>
+      <c r="L225" s="2"/>
+      <c r="M225" s="2"/>
+      <c r="N225" s="2"/>
+      <c r="O225" s="2"/>
+      <c r="P225" s="2"/>
+      <c r="Q225" s="2"/>
+      <c r="R225" s="2"/>
+      <c r="S225" s="2"/>
+      <c r="T225" s="2"/>
+      <c r="U225" s="2"/>
+      <c r="V225" s="2"/>
+      <c r="W225" s="2"/>
+      <c r="X225" s="2"/>
+      <c r="Y225" s="2"/>
+    </row>
+    <row r="226" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A226" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="B226" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="B225" s="3" t="s">
+      <c r="C226" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="C225" s="3" t="s">
+      <c r="D226" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>997</v>
-      </c>
-      <c r="E225" s="1"/>
-      <c r="F225" s="1"/>
-      <c r="G225" s="1"/>
-      <c r="H225" s="1"/>
-      <c r="I225" s="1"/>
-      <c r="J225" s="1"/>
-      <c r="K225" s="1"/>
-      <c r="L225" s="1"/>
-      <c r="M225" s="1"/>
-      <c r="N225" s="1"/>
-      <c r="O225" s="1"/>
-      <c r="P225" s="1"/>
-      <c r="Q225" s="1"/>
-      <c r="R225" s="1"/>
-      <c r="S225" s="1"/>
-      <c r="T225" s="1"/>
-      <c r="U225" s="1"/>
-      <c r="V225" s="1"/>
-      <c r="W225" s="1"/>
-      <c r="X225" s="1"/>
-      <c r="Y225" s="1"/>
-    </row>
-    <row r="226" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A226" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="B226" s="9"/>
-      <c r="C226" s="33" t="s">
-        <v>452</v>
-      </c>
-      <c r="D226" s="34" t="s">
-        <v>453</v>
       </c>
       <c r="E226" s="1"/>
       <c r="F226" s="1"/>
@@ -11577,15 +11588,15 @@
       <c r="Y226" s="1"/>
     </row>
     <row r="227" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A227" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="B227" s="3"/>
-      <c r="C227" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>456</v>
+      <c r="A227" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="B227" s="9"/>
+      <c r="C227" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="D227" s="34" t="s">
+        <v>453</v>
       </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1"/>
@@ -11610,120 +11621,118 @@
       <c r="Y227" s="1"/>
     </row>
     <row r="228" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A228" s="9" t="s">
+      <c r="A228" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E228" s="1"/>
+      <c r="F228" s="1"/>
+      <c r="G228" s="1"/>
+      <c r="H228" s="1"/>
+      <c r="I228" s="1"/>
+      <c r="J228" s="1"/>
+      <c r="K228" s="1"/>
+      <c r="L228" s="1"/>
+      <c r="M228" s="1"/>
+      <c r="N228" s="1"/>
+      <c r="O228" s="1"/>
+      <c r="P228" s="1"/>
+      <c r="Q228" s="1"/>
+      <c r="R228" s="1"/>
+      <c r="S228" s="1"/>
+      <c r="T228" s="1"/>
+      <c r="U228" s="1"/>
+      <c r="V228" s="1"/>
+      <c r="W228" s="1"/>
+      <c r="X228" s="1"/>
+      <c r="Y228" s="1"/>
+    </row>
+    <row r="229" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A229" s="9" t="s">
         <v>457</v>
       </c>
-      <c r="B228" s="9"/>
-      <c r="C228" s="10" t="s">
+      <c r="B229" s="9"/>
+      <c r="C229" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="D228" s="9" t="s">
+      <c r="D229" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="E228" s="2"/>
-      <c r="F228" s="2"/>
-      <c r="G228" s="2"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
-      <c r="J228" s="2"/>
-      <c r="K228" s="2"/>
-      <c r="L228" s="2"/>
-      <c r="M228" s="2"/>
-      <c r="N228" s="2"/>
-      <c r="O228" s="2"/>
-      <c r="P228" s="2"/>
-      <c r="Q228" s="2"/>
-      <c r="R228" s="2"/>
-      <c r="S228" s="2"/>
-      <c r="T228" s="2"/>
-      <c r="U228" s="2"/>
-      <c r="V228" s="2"/>
-      <c r="W228" s="2"/>
-      <c r="X228" s="2"/>
-      <c r="Y228" s="2"/>
-    </row>
-    <row r="229" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A229" s="7" t="s">
+      <c r="E229" s="2"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+      <c r="J229" s="2"/>
+      <c r="K229" s="2"/>
+      <c r="L229" s="2"/>
+      <c r="M229" s="2"/>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
+      <c r="P229" s="2"/>
+      <c r="Q229" s="2"/>
+      <c r="R229" s="2"/>
+      <c r="S229" s="2"/>
+      <c r="T229" s="2"/>
+      <c r="U229" s="2"/>
+      <c r="V229" s="2"/>
+      <c r="W229" s="2"/>
+      <c r="X229" s="2"/>
+      <c r="Y229" s="2"/>
+    </row>
+    <row r="230" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A230" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B230" s="7" t="s">
         <v>461</v>
       </c>
-      <c r="C229" s="29" t="s">
+      <c r="C230" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="D229" s="7" t="s">
+      <c r="D230" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="E229" s="1"/>
-      <c r="F229" s="1"/>
-      <c r="G229" s="1"/>
-      <c r="H229" s="1"/>
-      <c r="I229" s="1"/>
-      <c r="J229" s="1"/>
-      <c r="K229" s="1"/>
-      <c r="L229" s="1"/>
-      <c r="M229" s="1"/>
-      <c r="N229" s="1"/>
-      <c r="O229" s="1"/>
-      <c r="P229" s="1"/>
-      <c r="Q229" s="1"/>
-      <c r="R229" s="1"/>
-      <c r="S229" s="1"/>
-      <c r="T229" s="1"/>
-      <c r="U229" s="1"/>
-      <c r="V229" s="1"/>
-      <c r="W229" s="1"/>
-      <c r="X229" s="1"/>
-      <c r="Y229" s="1"/>
-    </row>
-    <row r="230" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A230" s="5" t="s">
+      <c r="E230" s="1"/>
+      <c r="F230" s="1"/>
+      <c r="G230" s="1"/>
+      <c r="H230" s="1"/>
+      <c r="I230" s="1"/>
+      <c r="J230" s="1"/>
+      <c r="K230" s="1"/>
+      <c r="L230" s="1"/>
+      <c r="M230" s="1"/>
+      <c r="N230" s="1"/>
+      <c r="O230" s="1"/>
+      <c r="P230" s="1"/>
+      <c r="Q230" s="1"/>
+      <c r="R230" s="1"/>
+      <c r="S230" s="1"/>
+      <c r="T230" s="1"/>
+      <c r="U230" s="1"/>
+      <c r="V230" s="1"/>
+      <c r="W230" s="1"/>
+      <c r="X230" s="1"/>
+      <c r="Y230" s="1"/>
+    </row>
+    <row r="231" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A231" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B230" s="5" t="s">
+      <c r="B231" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="C230" s="6" t="s">
+      <c r="C231" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D231" s="5" t="s">
         <v>463</v>
-      </c>
-      <c r="E230" s="2"/>
-      <c r="F230" s="2"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-      <c r="J230" s="2"/>
-      <c r="K230" s="2"/>
-      <c r="L230" s="2"/>
-      <c r="M230" s="2"/>
-      <c r="N230" s="2"/>
-      <c r="O230" s="2"/>
-      <c r="P230" s="2"/>
-      <c r="Q230" s="2"/>
-      <c r="R230" s="2"/>
-      <c r="S230" s="2"/>
-      <c r="T230" s="2"/>
-      <c r="U230" s="2"/>
-      <c r="V230" s="2"/>
-      <c r="W230" s="2"/>
-      <c r="X230" s="2"/>
-      <c r="Y230" s="2"/>
-    </row>
-    <row r="231" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A231" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="B231" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="C231" s="29" t="s">
-        <v>467</v>
-      </c>
-      <c r="D231" s="7" t="s">
-        <v>466</v>
       </c>
       <c r="E231" s="2"/>
       <c r="F231" s="2"/>
@@ -11748,15 +11757,17 @@
       <c r="Y231" s="2"/>
     </row>
     <row r="232" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A232" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="B232" s="3"/>
-      <c r="C232" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>468</v>
+      <c r="A232" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C232" s="29" t="s">
+        <v>467</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>466</v>
       </c>
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
@@ -11781,15 +11792,15 @@
       <c r="Y232" s="2"/>
     </row>
     <row r="233" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A233" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="B233" s="7"/>
-      <c r="C233" s="8" t="s">
-        <v>471</v>
-      </c>
-      <c r="D233" s="7" t="s">
-        <v>470</v>
+      <c r="A233" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="E233" s="2"/>
       <c r="F233" s="2"/>
@@ -11814,81 +11825,81 @@
       <c r="Y233" s="2"/>
     </row>
     <row r="234" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A234" s="3" t="s">
+      <c r="A234" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B234" s="7"/>
+      <c r="C234" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="2"/>
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
+      <c r="J234" s="2"/>
+      <c r="K234" s="2"/>
+      <c r="L234" s="2"/>
+      <c r="M234" s="2"/>
+      <c r="N234" s="2"/>
+      <c r="O234" s="2"/>
+      <c r="P234" s="2"/>
+      <c r="Q234" s="2"/>
+      <c r="R234" s="2"/>
+      <c r="S234" s="2"/>
+      <c r="T234" s="2"/>
+      <c r="U234" s="2"/>
+      <c r="V234" s="2"/>
+      <c r="W234" s="2"/>
+      <c r="X234" s="2"/>
+      <c r="Y234" s="2"/>
+    </row>
+    <row r="235" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A235" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B234" s="3"/>
-      <c r="C234" s="4" t="s">
+      <c r="B235" s="3"/>
+      <c r="C235" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="D234" s="3" t="s">
+      <c r="D235" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="E234" s="1"/>
-      <c r="F234" s="1"/>
-      <c r="G234" s="1"/>
-      <c r="H234" s="1"/>
-      <c r="I234" s="1"/>
-      <c r="J234" s="1"/>
-      <c r="K234" s="1"/>
-      <c r="L234" s="1"/>
-      <c r="M234" s="1"/>
-      <c r="N234" s="1"/>
-      <c r="O234" s="1"/>
-      <c r="P234" s="1"/>
-      <c r="Q234" s="1"/>
-      <c r="R234" s="1"/>
-      <c r="S234" s="1"/>
-      <c r="T234" s="1"/>
-      <c r="U234" s="1"/>
-      <c r="V234" s="1"/>
-      <c r="W234" s="1"/>
-      <c r="X234" s="1"/>
-      <c r="Y234" s="1"/>
-    </row>
-    <row r="235" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A235" s="7" t="s">
+      <c r="E235" s="1"/>
+      <c r="F235" s="1"/>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1"/>
+      <c r="I235" s="1"/>
+      <c r="J235" s="1"/>
+      <c r="K235" s="1"/>
+      <c r="L235" s="1"/>
+      <c r="M235" s="1"/>
+      <c r="N235" s="1"/>
+      <c r="O235" s="1"/>
+      <c r="P235" s="1"/>
+      <c r="Q235" s="1"/>
+      <c r="R235" s="1"/>
+      <c r="S235" s="1"/>
+      <c r="T235" s="1"/>
+      <c r="U235" s="1"/>
+      <c r="V235" s="1"/>
+      <c r="W235" s="1"/>
+      <c r="X235" s="1"/>
+      <c r="Y235" s="1"/>
+    </row>
+    <row r="236" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A236" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="B235" s="7"/>
-      <c r="C235" s="8" t="s">
+      <c r="B236" s="7"/>
+      <c r="C236" s="8" t="s">
         <v>476</v>
       </c>
-      <c r="D235" s="7" t="s">
+      <c r="D236" s="7" t="s">
         <v>477</v>
-      </c>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
-      <c r="I235" s="2"/>
-      <c r="J235" s="2"/>
-      <c r="K235" s="2"/>
-      <c r="L235" s="2"/>
-      <c r="M235" s="2"/>
-      <c r="N235" s="2"/>
-      <c r="O235" s="2"/>
-      <c r="P235" s="2"/>
-      <c r="Q235" s="2"/>
-      <c r="R235" s="2"/>
-      <c r="S235" s="2"/>
-      <c r="T235" s="2"/>
-      <c r="U235" s="2"/>
-      <c r="V235" s="2"/>
-      <c r="W235" s="2"/>
-      <c r="X235" s="2"/>
-      <c r="Y235" s="2"/>
-    </row>
-    <row r="236" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A236" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B236" s="3"/>
-      <c r="C236" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="E236" s="2"/>
       <c r="F236" s="2"/>
@@ -11913,120 +11924,118 @@
       <c r="Y236" s="2"/>
     </row>
     <row r="237" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A237" s="35" t="s">
+      <c r="A237" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="2"/>
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+      <c r="J237" s="2"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2"/>
+      <c r="M237" s="2"/>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2"/>
+      <c r="P237" s="2"/>
+      <c r="Q237" s="2"/>
+      <c r="R237" s="2"/>
+      <c r="S237" s="2"/>
+      <c r="T237" s="2"/>
+      <c r="U237" s="2"/>
+      <c r="V237" s="2"/>
+      <c r="W237" s="2"/>
+      <c r="X237" s="2"/>
+      <c r="Y237" s="2"/>
+    </row>
+    <row r="238" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A238" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="B237" s="35" t="s">
+      <c r="B238" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="C237" s="36" t="s">
+      <c r="C238" s="36" t="s">
         <v>485</v>
       </c>
-      <c r="D237" s="35" t="s">
+      <c r="D238" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="E237" s="1"/>
-      <c r="F237" s="1"/>
-      <c r="G237" s="1"/>
-      <c r="H237" s="1"/>
-      <c r="I237" s="1"/>
-      <c r="J237" s="1"/>
-      <c r="K237" s="1"/>
-      <c r="L237" s="1"/>
-      <c r="M237" s="1"/>
-      <c r="N237" s="1"/>
-      <c r="O237" s="1"/>
-      <c r="P237" s="1"/>
-      <c r="Q237" s="1"/>
-      <c r="R237" s="1"/>
-      <c r="S237" s="1"/>
-      <c r="T237" s="1"/>
-      <c r="U237" s="1"/>
-      <c r="V237" s="1"/>
-      <c r="W237" s="1"/>
-      <c r="X237" s="1"/>
-      <c r="Y237" s="1"/>
-    </row>
-    <row r="238" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A238" s="7" t="s">
+      <c r="E238" s="1"/>
+      <c r="F238" s="1"/>
+      <c r="G238" s="1"/>
+      <c r="H238" s="1"/>
+      <c r="I238" s="1"/>
+      <c r="J238" s="1"/>
+      <c r="K238" s="1"/>
+      <c r="L238" s="1"/>
+      <c r="M238" s="1"/>
+      <c r="N238" s="1"/>
+      <c r="O238" s="1"/>
+      <c r="P238" s="1"/>
+      <c r="Q238" s="1"/>
+      <c r="R238" s="1"/>
+      <c r="S238" s="1"/>
+      <c r="T238" s="1"/>
+      <c r="U238" s="1"/>
+      <c r="V238" s="1"/>
+      <c r="W238" s="1"/>
+      <c r="X238" s="1"/>
+      <c r="Y238" s="1"/>
+    </row>
+    <row r="239" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A239" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="B238" s="7"/>
-      <c r="C238" s="8" t="s">
+      <c r="B239" s="7"/>
+      <c r="C239" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="D238" s="7" t="s">
+      <c r="D239" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
-      <c r="K238" s="2"/>
-      <c r="L238" s="2"/>
-      <c r="M238" s="2"/>
-      <c r="N238" s="2"/>
-      <c r="O238" s="2"/>
-      <c r="P238" s="2"/>
-      <c r="Q238" s="2"/>
-      <c r="R238" s="2"/>
-      <c r="S238" s="2"/>
-      <c r="T238" s="2"/>
-      <c r="U238" s="2"/>
-      <c r="V238" s="2"/>
-      <c r="W238" s="2"/>
-      <c r="X238" s="2"/>
-      <c r="Y238" s="2"/>
-    </row>
-    <row r="239" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A239" s="35" t="s">
-        <v>486</v>
-      </c>
-      <c r="B239" s="35" t="s">
-        <v>487</v>
-      </c>
-      <c r="C239" s="37" t="s">
-        <v>488</v>
-      </c>
-      <c r="D239" s="35" t="s">
-        <v>489</v>
-      </c>
-      <c r="E239" s="1"/>
-      <c r="F239" s="1"/>
-      <c r="G239" s="1"/>
-      <c r="H239" s="1"/>
-      <c r="I239" s="1"/>
-      <c r="J239" s="1"/>
-      <c r="K239" s="1"/>
-      <c r="L239" s="1"/>
-      <c r="M239" s="1"/>
-      <c r="N239" s="1"/>
-      <c r="O239" s="1"/>
-      <c r="P239" s="1"/>
-      <c r="Q239" s="1"/>
-      <c r="R239" s="1"/>
-      <c r="S239" s="1"/>
-      <c r="T239" s="1"/>
-      <c r="U239" s="1"/>
-      <c r="V239" s="1"/>
-      <c r="W239" s="1"/>
-      <c r="X239" s="1"/>
-      <c r="Y239" s="1"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+      <c r="P239" s="2"/>
+      <c r="Q239" s="2"/>
+      <c r="R239" s="2"/>
+      <c r="S239" s="2"/>
+      <c r="T239" s="2"/>
+      <c r="U239" s="2"/>
+      <c r="V239" s="2"/>
+      <c r="W239" s="2"/>
+      <c r="X239" s="2"/>
+      <c r="Y239" s="2"/>
     </row>
     <row r="240" spans="1:25" ht="15.75" customHeight="1">
       <c r="A240" s="35" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B240" s="35" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C240" s="37" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D240" s="35" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -12051,15 +12060,17 @@
       <c r="Y240" s="1"/>
     </row>
     <row r="241" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A241" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B241" s="3"/>
-      <c r="C241" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>509</v>
+      <c r="A241" s="35" t="s">
+        <v>490</v>
+      </c>
+      <c r="B241" s="35" t="s">
+        <v>491</v>
+      </c>
+      <c r="C241" s="37" t="s">
+        <v>492</v>
+      </c>
+      <c r="D241" s="35" t="s">
+        <v>490</v>
       </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1"/>
@@ -12085,16 +12096,14 @@
     </row>
     <row r="242" spans="1:25" ht="15.75" customHeight="1">
       <c r="A242" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C242" s="12" t="s">
-        <v>495</v>
+        <v>507</v>
+      </c>
+      <c r="B242" s="3"/>
+      <c r="C242" s="3" t="s">
+        <v>508</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
       <c r="E242" s="1"/>
       <c r="F242" s="1"/>
@@ -12119,15 +12128,17 @@
       <c r="Y242" s="1"/>
     </row>
     <row r="243" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A243" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="B243" s="7"/>
-      <c r="C243" s="8" t="s">
-        <v>497</v>
-      </c>
-      <c r="D243" s="7" t="s">
-        <v>496</v>
+      <c r="A243" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C243" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>493</v>
       </c>
       <c r="E243" s="1"/>
       <c r="F243" s="1"/>
@@ -12152,17 +12163,15 @@
       <c r="Y243" s="1"/>
     </row>
     <row r="244" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A244" s="5" t="s">
-        <v>498</v>
-      </c>
-      <c r="B244" s="5" t="s">
-        <v>499</v>
-      </c>
-      <c r="C244" s="6" t="s">
-        <v>500</v>
-      </c>
-      <c r="D244" s="5" t="s">
-        <v>501</v>
+      <c r="A244" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="B244" s="7"/>
+      <c r="C244" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>496</v>
       </c>
       <c r="E244" s="1"/>
       <c r="F244" s="1"/>
@@ -12187,17 +12196,17 @@
       <c r="Y244" s="1"/>
     </row>
     <row r="245" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A245" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C245" s="50" t="s">
-        <v>847</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>504</v>
+      <c r="A245" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="D245" s="5" t="s">
+        <v>501</v>
       </c>
       <c r="E245" s="1"/>
       <c r="F245" s="1"/>
@@ -12222,15 +12231,17 @@
       <c r="Y245" s="1"/>
     </row>
     <row r="246" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A246" s="5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B246" s="5"/>
-      <c r="C246" s="30" t="s">
-        <v>506</v>
-      </c>
-      <c r="D246" s="5" t="s">
-        <v>505</v>
+      <c r="A246" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C246" s="50" t="s">
+        <v>847</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>504</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1"/>
@@ -12255,17 +12266,15 @@
       <c r="Y246" s="1"/>
     </row>
     <row r="247" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A247" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="B247" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="C247" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>560</v>
+      <c r="A247" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B247" s="5"/>
+      <c r="C247" s="30" t="s">
+        <v>506</v>
+      </c>
+      <c r="D247" s="5" t="s">
+        <v>505</v>
       </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1"/>
@@ -12291,14 +12300,16 @@
     </row>
     <row r="248" spans="1:25" ht="15.75" customHeight="1">
       <c r="A248" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="B248" s="3"/>
+        <v>559</v>
+      </c>
+      <c r="B248" s="3" t="s">
+        <v>560</v>
+      </c>
       <c r="C248" s="4" t="s">
-        <v>511</v>
+        <v>561</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>510</v>
+        <v>560</v>
       </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1"/>
@@ -12323,15 +12334,15 @@
       <c r="Y248" s="1"/>
     </row>
     <row r="249" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A249" s="9" t="s">
-        <v>512</v>
-      </c>
-      <c r="B249" s="38"/>
-      <c r="C249" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="D249" s="34" t="s">
-        <v>512</v>
+      <c r="A249" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B249" s="3"/>
+      <c r="C249" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>510</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -12356,15 +12367,15 @@
       <c r="Y249" s="1"/>
     </row>
     <row r="250" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A250" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="B250" s="5"/>
-      <c r="C250" s="6" t="s">
-        <v>515</v>
-      </c>
-      <c r="D250" s="5" t="s">
-        <v>514</v>
+      <c r="A250" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="B250" s="38"/>
+      <c r="C250" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="D250" s="34" t="s">
+        <v>512</v>
       </c>
       <c r="E250" s="1"/>
       <c r="F250" s="1"/>
@@ -12389,15 +12400,15 @@
       <c r="Y250" s="1"/>
     </row>
     <row r="251" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A251" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="B251" s="3"/>
-      <c r="C251" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>516</v>
+      <c r="A251" s="5" t="s">
+        <v>514</v>
+      </c>
+      <c r="B251" s="5"/>
+      <c r="C251" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>514</v>
       </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1"/>
@@ -12422,15 +12433,15 @@
       <c r="Y251" s="1"/>
     </row>
     <row r="252" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A252" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="B252" s="7"/>
-      <c r="C252" s="29" t="s">
-        <v>519</v>
-      </c>
-      <c r="D252" s="7" t="s">
-        <v>518</v>
+      <c r="A252" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="B252" s="3"/>
+      <c r="C252" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="E252" s="1"/>
       <c r="F252" s="1"/>
@@ -12456,49 +12467,47 @@
     </row>
     <row r="253" spans="1:25" ht="15.75" customHeight="1">
       <c r="A253" s="7" t="s">
-        <v>849</v>
+        <v>518</v>
       </c>
       <c r="B253" s="7"/>
       <c r="C253" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="E253" s="1"/>
+      <c r="F253" s="1"/>
+      <c r="G253" s="1"/>
+      <c r="H253" s="1"/>
+      <c r="I253" s="1"/>
+      <c r="J253" s="1"/>
+      <c r="K253" s="1"/>
+      <c r="L253" s="1"/>
+      <c r="M253" s="1"/>
+      <c r="N253" s="1"/>
+      <c r="O253" s="1"/>
+      <c r="P253" s="1"/>
+      <c r="Q253" s="1"/>
+      <c r="R253" s="1"/>
+      <c r="S253" s="1"/>
+      <c r="T253" s="1"/>
+      <c r="U253" s="1"/>
+      <c r="V253" s="1"/>
+      <c r="W253" s="1"/>
+      <c r="X253" s="1"/>
+      <c r="Y253" s="1"/>
+    </row>
+    <row r="254" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A254" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="B254" s="7"/>
+      <c r="C254" s="29" t="s">
         <v>850</v>
       </c>
-      <c r="D253" s="7" t="s">
+      <c r="D254" s="7" t="s">
         <v>849</v>
-      </c>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
-      <c r="J253" s="2"/>
-      <c r="K253" s="2"/>
-      <c r="L253" s="2"/>
-      <c r="M253" s="2"/>
-      <c r="N253" s="2"/>
-      <c r="O253" s="2"/>
-      <c r="P253" s="2"/>
-      <c r="Q253" s="2"/>
-      <c r="R253" s="2"/>
-      <c r="S253" s="2"/>
-      <c r="T253" s="2"/>
-      <c r="U253" s="2"/>
-      <c r="V253" s="2"/>
-      <c r="W253" s="2"/>
-      <c r="X253" s="2"/>
-      <c r="Y253" s="2"/>
-    </row>
-    <row r="254" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A254" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="B254" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="C254" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>520</v>
       </c>
       <c r="E254" s="2"/>
       <c r="F254" s="2"/>
@@ -12523,15 +12532,17 @@
       <c r="Y254" s="2"/>
     </row>
     <row r="255" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A255" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="B255" s="7"/>
-      <c r="C255" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D255" s="7" t="s">
-        <v>523</v>
+      <c r="A255" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="B255" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C255" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>520</v>
       </c>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
@@ -12556,52 +12567,50 @@
       <c r="Y255" s="2"/>
     </row>
     <row r="256" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A256" s="5" t="s">
+      <c r="A256" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="B256" s="7"/>
+      <c r="C256" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="2"/>
+      <c r="H256" s="2"/>
+      <c r="I256" s="2"/>
+      <c r="J256" s="2"/>
+      <c r="K256" s="2"/>
+      <c r="L256" s="2"/>
+      <c r="M256" s="2"/>
+      <c r="N256" s="2"/>
+      <c r="O256" s="2"/>
+      <c r="P256" s="2"/>
+      <c r="Q256" s="2"/>
+      <c r="R256" s="2"/>
+      <c r="S256" s="2"/>
+      <c r="T256" s="2"/>
+      <c r="U256" s="2"/>
+      <c r="V256" s="2"/>
+      <c r="W256" s="2"/>
+      <c r="X256" s="2"/>
+      <c r="Y256" s="2"/>
+    </row>
+    <row r="257" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A257" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="B256" s="5" t="s">
+      <c r="B257" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="C256" s="6" t="s">
+      <c r="C257" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="D256" s="5" t="s">
+      <c r="D257" s="5" t="s">
         <v>525</v>
-      </c>
-      <c r="E256" s="1"/>
-      <c r="F256" s="1"/>
-      <c r="G256" s="1"/>
-      <c r="H256" s="1"/>
-      <c r="I256" s="1"/>
-      <c r="J256" s="1"/>
-      <c r="K256" s="1"/>
-      <c r="L256" s="1"/>
-      <c r="M256" s="1"/>
-      <c r="N256" s="1"/>
-      <c r="O256" s="1"/>
-      <c r="P256" s="1"/>
-      <c r="Q256" s="1"/>
-      <c r="R256" s="1"/>
-      <c r="S256" s="1"/>
-      <c r="T256" s="1"/>
-      <c r="U256" s="1"/>
-      <c r="V256" s="1"/>
-      <c r="W256" s="1"/>
-      <c r="X256" s="1"/>
-      <c r="Y256" s="1"/>
-    </row>
-    <row r="257" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A257" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="B257" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="C257" s="12" t="s">
-        <v>530</v>
-      </c>
-      <c r="D257" s="3" t="s">
-        <v>528</v>
       </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1"/>
@@ -12626,50 +12635,52 @@
       <c r="Y257" s="1"/>
     </row>
     <row r="258" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A258" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="B258" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="C258" s="52" t="s">
-        <v>848</v>
-      </c>
-      <c r="D258" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="E258" s="2"/>
-      <c r="F258" s="2"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
-      <c r="J258" s="2"/>
-      <c r="K258" s="2"/>
-      <c r="L258" s="2"/>
-      <c r="M258" s="2"/>
-      <c r="N258" s="2"/>
-      <c r="O258" s="2"/>
-      <c r="P258" s="2"/>
-      <c r="Q258" s="2"/>
-      <c r="R258" s="2"/>
-      <c r="S258" s="2"/>
-      <c r="T258" s="2"/>
-      <c r="U258" s="2"/>
-      <c r="V258" s="2"/>
-      <c r="W258" s="2"/>
-      <c r="X258" s="2"/>
-      <c r="Y258" s="2"/>
+      <c r="A258" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="B258" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E258" s="1"/>
+      <c r="F258" s="1"/>
+      <c r="G258" s="1"/>
+      <c r="H258" s="1"/>
+      <c r="I258" s="1"/>
+      <c r="J258" s="1"/>
+      <c r="K258" s="1"/>
+      <c r="L258" s="1"/>
+      <c r="M258" s="1"/>
+      <c r="N258" s="1"/>
+      <c r="O258" s="1"/>
+      <c r="P258" s="1"/>
+      <c r="Q258" s="1"/>
+      <c r="R258" s="1"/>
+      <c r="S258" s="1"/>
+      <c r="T258" s="1"/>
+      <c r="U258" s="1"/>
+      <c r="V258" s="1"/>
+      <c r="W258" s="1"/>
+      <c r="X258" s="1"/>
+      <c r="Y258" s="1"/>
     </row>
     <row r="259" spans="1:25" ht="15.75" customHeight="1">
       <c r="A259" s="9" t="s">
-        <v>533</v>
-      </c>
-      <c r="B259" s="9"/>
-      <c r="C259" s="10" t="s">
-        <v>534</v>
+        <v>531</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C259" s="52" t="s">
+        <v>848</v>
       </c>
       <c r="D259" s="9" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
@@ -12694,17 +12705,15 @@
       <c r="Y259" s="2"/>
     </row>
     <row r="260" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A260" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="B260" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="C260" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>535</v>
+      <c r="A260" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B260" s="9"/>
+      <c r="C260" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="D260" s="9" t="s">
+        <v>533</v>
       </c>
       <c r="E260" s="2"/>
       <c r="F260" s="2"/>
@@ -12729,15 +12738,17 @@
       <c r="Y260" s="2"/>
     </row>
     <row r="261" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A261" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="B261" s="5"/>
-      <c r="C261" s="6" t="s">
-        <v>539</v>
-      </c>
-      <c r="D261" s="5" t="s">
-        <v>538</v>
+      <c r="A261" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B261" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C261" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>535</v>
       </c>
       <c r="E261" s="2"/>
       <c r="F261" s="2"/>
@@ -12762,52 +12773,50 @@
       <c r="Y261" s="2"/>
     </row>
     <row r="262" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A262" s="7" t="s">
+      <c r="A262" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="B262" s="5"/>
+      <c r="C262" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="2"/>
+      <c r="H262" s="2"/>
+      <c r="I262" s="2"/>
+      <c r="J262" s="2"/>
+      <c r="K262" s="2"/>
+      <c r="L262" s="2"/>
+      <c r="M262" s="2"/>
+      <c r="N262" s="2"/>
+      <c r="O262" s="2"/>
+      <c r="P262" s="2"/>
+      <c r="Q262" s="2"/>
+      <c r="R262" s="2"/>
+      <c r="S262" s="2"/>
+      <c r="T262" s="2"/>
+      <c r="U262" s="2"/>
+      <c r="V262" s="2"/>
+      <c r="W262" s="2"/>
+      <c r="X262" s="2"/>
+      <c r="Y262" s="2"/>
+    </row>
+    <row r="263" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A263" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="B262" s="7" t="s">
+      <c r="B263" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="C262" s="8" t="s">
+      <c r="C263" s="8" t="s">
         <v>542</v>
       </c>
-      <c r="D262" s="7" t="s">
+      <c r="D263" s="7" t="s">
         <v>540</v>
-      </c>
-      <c r="E262" s="1"/>
-      <c r="F262" s="1"/>
-      <c r="G262" s="1"/>
-      <c r="H262" s="1"/>
-      <c r="I262" s="1"/>
-      <c r="J262" s="1"/>
-      <c r="K262" s="1"/>
-      <c r="L262" s="1"/>
-      <c r="M262" s="1"/>
-      <c r="N262" s="1"/>
-      <c r="O262" s="1"/>
-      <c r="P262" s="1"/>
-      <c r="Q262" s="1"/>
-      <c r="R262" s="1"/>
-      <c r="S262" s="1"/>
-      <c r="T262" s="1"/>
-      <c r="U262" s="1"/>
-      <c r="V262" s="1"/>
-      <c r="W262" s="1"/>
-      <c r="X262" s="1"/>
-      <c r="Y262" s="1"/>
-    </row>
-    <row r="263" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A263" s="9" t="s">
-        <v>543</v>
-      </c>
-      <c r="B263" s="9" t="s">
-        <v>544</v>
-      </c>
-      <c r="C263" s="10" t="s">
-        <v>545</v>
-      </c>
-      <c r="D263" s="9" t="s">
-        <v>546</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1"/>
@@ -12832,52 +12841,52 @@
       <c r="Y263" s="1"/>
     </row>
     <row r="264" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A264" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="B264" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="C264" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>998</v>
-      </c>
-      <c r="E264" s="2"/>
-      <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="2"/>
-      <c r="I264" s="2"/>
-      <c r="J264" s="2"/>
-      <c r="K264" s="2"/>
-      <c r="L264" s="2"/>
-      <c r="M264" s="2"/>
-      <c r="N264" s="2"/>
-      <c r="O264" s="2"/>
-      <c r="P264" s="2"/>
-      <c r="Q264" s="2"/>
-      <c r="R264" s="2"/>
-      <c r="S264" s="2"/>
-      <c r="T264" s="2"/>
-      <c r="U264" s="2"/>
-      <c r="V264" s="2"/>
-      <c r="W264" s="2"/>
-      <c r="X264" s="2"/>
-      <c r="Y264" s="2"/>
+      <c r="A264" s="9" t="s">
+        <v>543</v>
+      </c>
+      <c r="B264" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C264" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="D264" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="E264" s="1"/>
+      <c r="F264" s="1"/>
+      <c r="G264" s="1"/>
+      <c r="H264" s="1"/>
+      <c r="I264" s="1"/>
+      <c r="J264" s="1"/>
+      <c r="K264" s="1"/>
+      <c r="L264" s="1"/>
+      <c r="M264" s="1"/>
+      <c r="N264" s="1"/>
+      <c r="O264" s="1"/>
+      <c r="P264" s="1"/>
+      <c r="Q264" s="1"/>
+      <c r="R264" s="1"/>
+      <c r="S264" s="1"/>
+      <c r="T264" s="1"/>
+      <c r="U264" s="1"/>
+      <c r="V264" s="1"/>
+      <c r="W264" s="1"/>
+      <c r="X264" s="1"/>
+      <c r="Y264" s="1"/>
     </row>
     <row r="265" spans="1:25" ht="15.75" customHeight="1">
       <c r="A265" s="3" t="s">
-        <v>547</v>
+        <v>997</v>
       </c>
       <c r="B265" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="C265" s="12" t="s">
-        <v>549</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>547</v>
+        <v>998</v>
+      </c>
+      <c r="C265" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>997</v>
       </c>
       <c r="E265" s="2"/>
       <c r="F265" s="2"/>
@@ -12902,17 +12911,17 @@
       <c r="Y265" s="2"/>
     </row>
     <row r="266" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A266" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B266" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C266" s="33" t="s">
-        <v>552</v>
-      </c>
-      <c r="D266" s="34" t="s">
-        <v>550</v>
+      <c r="A266" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B266" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>549</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>547</v>
       </c>
       <c r="E266" s="2"/>
       <c r="F266" s="2"/>
@@ -12938,12 +12947,16 @@
     </row>
     <row r="267" spans="1:25" ht="15.75" customHeight="1">
       <c r="A267" s="9" t="s">
-        <v>906</v>
-      </c>
-      <c r="B267" s="9"/>
-      <c r="C267" s="33"/>
+        <v>550</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C267" s="33" t="s">
+        <v>552</v>
+      </c>
       <c r="D267" s="34" t="s">
-        <v>906</v>
+        <v>550</v>
       </c>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
@@ -12968,15 +12981,13 @@
       <c r="Y267" s="2"/>
     </row>
     <row r="268" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A268" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="B268" s="13"/>
-      <c r="C268" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="D268" s="41" t="s">
-        <v>555</v>
+      <c r="A268" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="B268" s="9"/>
+      <c r="C268" s="33"/>
+      <c r="D268" s="34" t="s">
+        <v>905</v>
       </c>
       <c r="E268" s="2"/>
       <c r="F268" s="2"/>
@@ -13001,17 +13012,15 @@
       <c r="Y268" s="2"/>
     </row>
     <row r="269" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A269" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="B269" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="C269" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="D269" s="34" t="s">
-        <v>556</v>
+      <c r="A269" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B269" s="13"/>
+      <c r="C269" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="D269" s="41" t="s">
+        <v>555</v>
       </c>
       <c r="E269" s="2"/>
       <c r="F269" s="2"/>
@@ -13037,14 +13046,16 @@
     </row>
     <row r="270" spans="1:25" ht="15.75" customHeight="1">
       <c r="A270" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="B270" s="9"/>
-      <c r="C270" s="34" t="s">
-        <v>563</v>
-      </c>
-      <c r="D270" s="9" t="s">
-        <v>564</v>
+        <v>556</v>
+      </c>
+      <c r="B270" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C270" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="D270" s="34" t="s">
+        <v>556</v>
       </c>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
@@ -13070,16 +13081,14 @@
     </row>
     <row r="271" spans="1:25" ht="15.75" customHeight="1">
       <c r="A271" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B271" s="9" t="s">
-        <v>566</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="B271" s="9"/>
       <c r="C271" s="34" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D271" s="9" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E271" s="2"/>
       <c r="F271" s="2"/>
@@ -13104,17 +13113,17 @@
       <c r="Y271" s="2"/>
     </row>
     <row r="272" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A272" s="43" t="s">
-        <v>569</v>
-      </c>
-      <c r="B272" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="C272" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="D272" s="43" t="s">
-        <v>569</v>
+      <c r="A272" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="B272" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C272" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="D272" s="9" t="s">
+        <v>568</v>
       </c>
       <c r="E272" s="2"/>
       <c r="F272" s="2"/>
@@ -13139,15 +13148,17 @@
       <c r="Y272" s="2"/>
     </row>
     <row r="273" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A273" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="B273" s="3"/>
-      <c r="C273" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>1001</v>
+      <c r="A273" s="43" t="s">
+        <v>569</v>
+      </c>
+      <c r="B273" s="43" t="s">
+        <v>333</v>
+      </c>
+      <c r="C273" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D273" s="43" t="s">
+        <v>569</v>
       </c>
       <c r="E273" s="2"/>
       <c r="F273" s="2"/>
@@ -13172,17 +13183,15 @@
       <c r="Y273" s="2"/>
     </row>
     <row r="274" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A274" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="B274" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C274" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="D274" s="9" t="s">
-        <v>570</v>
+      <c r="A274" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B274" s="3"/>
+      <c r="C274" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>1000</v>
       </c>
       <c r="E274" s="2"/>
       <c r="F274" s="2"/>
@@ -13207,17 +13216,17 @@
       <c r="Y274" s="2"/>
     </row>
     <row r="275" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A275" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="B275" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="C275" s="53" t="s">
-        <v>909</v>
-      </c>
-      <c r="D275" s="7" t="s">
-        <v>907</v>
+      <c r="A275" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C275" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="E275" s="2"/>
       <c r="F275" s="2"/>
@@ -13242,17 +13251,17 @@
       <c r="Y275" s="2"/>
     </row>
     <row r="276" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A276" s="3" t="s">
+      <c r="A276" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="B276" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="B276" s="3" t="s">
+      <c r="C276" s="53" t="s">
         <v>908</v>
       </c>
-      <c r="C276" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>907</v>
+      <c r="D276" s="7" t="s">
+        <v>906</v>
       </c>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
@@ -13278,16 +13287,16 @@
     </row>
     <row r="277" spans="1:25" ht="15.75" customHeight="1">
       <c r="A277" s="3" t="s">
-        <v>573</v>
+        <v>906</v>
       </c>
       <c r="B277" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="C277" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>574</v>
+        <v>907</v>
+      </c>
+      <c r="C277" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>906</v>
       </c>
       <c r="E277" s="2"/>
       <c r="F277" s="2"/>
@@ -13312,50 +13321,50 @@
       <c r="Y277" s="2"/>
     </row>
     <row r="278" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A278" s="7" t="s">
+      <c r="A278" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B278" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C278" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E278" s="2"/>
+      <c r="F278" s="2"/>
+      <c r="G278" s="2"/>
+      <c r="H278" s="2"/>
+      <c r="I278" s="2"/>
+      <c r="J278" s="2"/>
+      <c r="K278" s="2"/>
+      <c r="L278" s="2"/>
+      <c r="M278" s="2"/>
+      <c r="N278" s="2"/>
+      <c r="O278" s="2"/>
+      <c r="P278" s="2"/>
+      <c r="Q278" s="2"/>
+      <c r="R278" s="2"/>
+      <c r="S278" s="2"/>
+      <c r="T278" s="2"/>
+      <c r="U278" s="2"/>
+      <c r="V278" s="2"/>
+      <c r="W278" s="2"/>
+      <c r="X278" s="2"/>
+      <c r="Y278" s="2"/>
+    </row>
+    <row r="279" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A279" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="B278" s="7"/>
-      <c r="C278" s="8" t="s">
+      <c r="B279" s="7"/>
+      <c r="C279" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="D278" s="7" t="s">
+      <c r="D279" s="7" t="s">
         <v>577</v>
-      </c>
-      <c r="E278" s="1"/>
-      <c r="F278" s="1"/>
-      <c r="G278" s="1"/>
-      <c r="H278" s="1"/>
-      <c r="I278" s="1"/>
-      <c r="J278" s="1"/>
-      <c r="K278" s="1"/>
-      <c r="L278" s="1"/>
-      <c r="M278" s="1"/>
-      <c r="N278" s="1"/>
-      <c r="O278" s="1"/>
-      <c r="P278" s="1"/>
-      <c r="Q278" s="1"/>
-      <c r="R278" s="1"/>
-      <c r="S278" s="1"/>
-      <c r="T278" s="1"/>
-      <c r="U278" s="1"/>
-      <c r="V278" s="1"/>
-      <c r="W278" s="1"/>
-      <c r="X278" s="1"/>
-      <c r="Y278" s="1"/>
-    </row>
-    <row r="279" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A279" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="B279" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C279" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="D279" s="5" t="s">
-        <v>578</v>
       </c>
       <c r="E279" s="1"/>
       <c r="F279" s="1"/>
@@ -13380,17 +13389,17 @@
       <c r="Y279" s="1"/>
     </row>
     <row r="280" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A280" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="B280" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C280" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>581</v>
+      <c r="A280" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>578</v>
       </c>
       <c r="E280" s="1"/>
       <c r="F280" s="1"/>
@@ -13415,15 +13424,17 @@
       <c r="Y280" s="1"/>
     </row>
     <row r="281" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A281" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="B281" s="7"/>
-      <c r="C281" s="53" t="s">
-        <v>911</v>
-      </c>
-      <c r="D281" s="7" t="s">
-        <v>910</v>
+      <c r="A281" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B281" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C281" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="E281" s="1"/>
       <c r="F281" s="1"/>
@@ -13449,49 +13460,47 @@
     </row>
     <row r="282" spans="1:25" ht="15.75" customHeight="1">
       <c r="A282" s="7" t="s">
-        <v>584</v>
+        <v>909</v>
       </c>
       <c r="B282" s="7"/>
-      <c r="C282" s="29" t="s">
-        <v>585</v>
+      <c r="C282" s="53" t="s">
+        <v>910</v>
       </c>
       <c r="D282" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
-      <c r="G282" s="2"/>
-      <c r="H282" s="2"/>
-      <c r="I282" s="2"/>
-      <c r="J282" s="2"/>
-      <c r="K282" s="2"/>
-      <c r="L282" s="2"/>
-      <c r="M282" s="2"/>
-      <c r="N282" s="2"/>
-      <c r="O282" s="2"/>
-      <c r="P282" s="2"/>
-      <c r="Q282" s="2"/>
-      <c r="R282" s="2"/>
-      <c r="S282" s="2"/>
-      <c r="T282" s="2"/>
-      <c r="U282" s="2"/>
-      <c r="V282" s="2"/>
-      <c r="W282" s="2"/>
-      <c r="X282" s="2"/>
-      <c r="Y282" s="2"/>
+        <v>909</v>
+      </c>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+      <c r="J282" s="1"/>
+      <c r="K282" s="1"/>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+      <c r="N282" s="1"/>
+      <c r="O282" s="1"/>
+      <c r="P282" s="1"/>
+      <c r="Q282" s="1"/>
+      <c r="R282" s="1"/>
+      <c r="S282" s="1"/>
+      <c r="T282" s="1"/>
+      <c r="U282" s="1"/>
+      <c r="V282" s="1"/>
+      <c r="W282" s="1"/>
+      <c r="X282" s="1"/>
+      <c r="Y282" s="1"/>
     </row>
     <row r="283" spans="1:25" ht="15.75" customHeight="1">
       <c r="A283" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B283" s="7" t="s">
-        <v>590</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="B283" s="7"/>
       <c r="C283" s="29" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E283" s="2"/>
       <c r="F283" s="2"/>
@@ -13516,17 +13525,17 @@
       <c r="Y283" s="2"/>
     </row>
     <row r="284" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A284" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B284" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="C284" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>1004</v>
+      <c r="A284" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C284" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
@@ -13551,17 +13560,17 @@
       <c r="Y284" s="2"/>
     </row>
     <row r="285" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A285" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B285" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="D285" s="5" t="s">
-        <v>586</v>
+      <c r="A285" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B285" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C285" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>1003</v>
       </c>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
@@ -13587,14 +13596,16 @@
     </row>
     <row r="286" spans="1:25" ht="15.75" customHeight="1">
       <c r="A286" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B286" s="5"/>
+        <v>586</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>587</v>
+      </c>
       <c r="C286" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E286" s="2"/>
       <c r="F286" s="2"/>
@@ -13619,15 +13630,15 @@
       <c r="Y286" s="2"/>
     </row>
     <row r="287" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A287" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="B287" s="3"/>
-      <c r="C287" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>595</v>
+      <c r="A287" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="B287" s="5"/>
+      <c r="C287" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D287" s="5" t="s">
+        <v>593</v>
       </c>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
@@ -13652,17 +13663,15 @@
       <c r="Y287" s="2"/>
     </row>
     <row r="288" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A288" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="B288" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="C288" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="D288" s="5" t="s">
-        <v>600</v>
+      <c r="A288" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B288" s="3"/>
+      <c r="C288" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E288" s="2"/>
       <c r="F288" s="2"/>
@@ -13687,15 +13696,17 @@
       <c r="Y288" s="2"/>
     </row>
     <row r="289" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A289" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B289" s="3"/>
-      <c r="C289" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>601</v>
+      <c r="A289" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C289" s="30" t="s">
+        <v>599</v>
+      </c>
+      <c r="D289" s="5" t="s">
+        <v>600</v>
       </c>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
@@ -13721,16 +13732,14 @@
     </row>
     <row r="290" spans="1:25" ht="15.75" customHeight="1">
       <c r="A290" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B290" s="3" t="s">
-        <v>604</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="B290" s="3"/>
       <c r="C290" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="E290" s="2"/>
       <c r="F290" s="2"/>
@@ -13755,17 +13764,17 @@
       <c r="Y290" s="2"/>
     </row>
     <row r="291" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A291" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="B291" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="C291" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="D291" s="9" t="s">
-        <v>607</v>
+      <c r="A291" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C291" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>606</v>
       </c>
       <c r="E291" s="2"/>
       <c r="F291" s="2"/>
@@ -13791,14 +13800,16 @@
     </row>
     <row r="292" spans="1:25" ht="15.75" customHeight="1">
       <c r="A292" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B292" s="9"/>
+        <v>607</v>
+      </c>
+      <c r="B292" s="9" t="s">
+        <v>608</v>
+      </c>
       <c r="C292" s="10" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D292" s="9" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E292" s="2"/>
       <c r="F292" s="2"/>
@@ -13824,14 +13835,14 @@
     </row>
     <row r="293" spans="1:25" ht="15.75" customHeight="1">
       <c r="A293" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B293" s="9"/>
-      <c r="C293" s="11" t="s">
-        <v>613</v>
+      <c r="C293" s="10" t="s">
+        <v>611</v>
       </c>
       <c r="D293" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E293" s="2"/>
       <c r="F293" s="2"/>
@@ -13856,52 +13867,50 @@
       <c r="Y293" s="2"/>
     </row>
     <row r="294" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A294" s="3" t="s">
+      <c r="A294" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B294" s="9"/>
+      <c r="C294" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="D294" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="E294" s="2"/>
+      <c r="F294" s="2"/>
+      <c r="G294" s="2"/>
+      <c r="H294" s="2"/>
+      <c r="I294" s="2"/>
+      <c r="J294" s="2"/>
+      <c r="K294" s="2"/>
+      <c r="L294" s="2"/>
+      <c r="M294" s="2"/>
+      <c r="N294" s="2"/>
+      <c r="O294" s="2"/>
+      <c r="P294" s="2"/>
+      <c r="Q294" s="2"/>
+      <c r="R294" s="2"/>
+      <c r="S294" s="2"/>
+      <c r="T294" s="2"/>
+      <c r="U294" s="2"/>
+      <c r="V294" s="2"/>
+      <c r="W294" s="2"/>
+      <c r="X294" s="2"/>
+      <c r="Y294" s="2"/>
+    </row>
+    <row r="295" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A295" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B294" s="3" t="s">
+      <c r="B295" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="C294" s="3" t="s">
+      <c r="C295" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="D294" s="3" t="s">
+      <c r="D295" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
-      <c r="K294" s="1"/>
-      <c r="L294" s="1"/>
-      <c r="M294" s="1"/>
-      <c r="N294" s="1"/>
-      <c r="O294" s="1"/>
-      <c r="P294" s="1"/>
-      <c r="Q294" s="1"/>
-      <c r="R294" s="1"/>
-      <c r="S294" s="1"/>
-      <c r="T294" s="1"/>
-      <c r="U294" s="1"/>
-      <c r="V294" s="1"/>
-      <c r="W294" s="1"/>
-      <c r="X294" s="1"/>
-      <c r="Y294" s="1"/>
-    </row>
-    <row r="295" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A295" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B295" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="C295" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="D295" s="7" t="s">
-        <v>620</v>
       </c>
       <c r="E295" s="1"/>
       <c r="F295" s="1"/>
@@ -13926,17 +13935,17 @@
       <c r="Y295" s="1"/>
     </row>
     <row r="296" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A296" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="B296" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C296" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="D296" s="34" t="s">
-        <v>624</v>
+      <c r="A296" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C296" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>620</v>
       </c>
       <c r="E296" s="1"/>
       <c r="F296" s="1"/>
@@ -13961,17 +13970,17 @@
       <c r="Y296" s="1"/>
     </row>
     <row r="297" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A297" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="B297" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="C297" s="41" t="s">
-        <v>626</v>
-      </c>
-      <c r="D297" s="13" t="s">
-        <v>625</v>
+      <c r="A297" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B297" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C297" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="D297" s="34" t="s">
+        <v>624</v>
       </c>
       <c r="E297" s="1"/>
       <c r="F297" s="1"/>
@@ -13997,14 +14006,16 @@
     </row>
     <row r="298" spans="1:25" ht="15.75" customHeight="1">
       <c r="A298" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B298" s="13"/>
+        <v>625</v>
+      </c>
+      <c r="B298" s="13" t="s">
+        <v>625</v>
+      </c>
       <c r="C298" s="41" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D298" s="13" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E298" s="1"/>
       <c r="F298" s="1"/>
@@ -14029,83 +14040,83 @@
       <c r="Y298" s="1"/>
     </row>
     <row r="299" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A299" s="9" t="s">
+      <c r="A299" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="B299" s="13"/>
+      <c r="C299" s="41" t="s">
+        <v>628</v>
+      </c>
+      <c r="D299" s="13" t="s">
+        <v>627</v>
+      </c>
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1"/>
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+      <c r="J299" s="1"/>
+      <c r="K299" s="1"/>
+      <c r="L299" s="1"/>
+      <c r="M299" s="1"/>
+      <c r="N299" s="1"/>
+      <c r="O299" s="1"/>
+      <c r="P299" s="1"/>
+      <c r="Q299" s="1"/>
+      <c r="R299" s="1"/>
+      <c r="S299" s="1"/>
+      <c r="T299" s="1"/>
+      <c r="U299" s="1"/>
+      <c r="V299" s="1"/>
+      <c r="W299" s="1"/>
+      <c r="X299" s="1"/>
+      <c r="Y299" s="1"/>
+    </row>
+    <row r="300" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A300" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="B299" s="9"/>
-      <c r="C299" s="34" t="s">
+      <c r="B300" s="9"/>
+      <c r="C300" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="D299" s="9" t="s">
+      <c r="D300" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="E299" s="2"/>
-      <c r="F299" s="2"/>
-      <c r="G299" s="2"/>
-      <c r="H299" s="2"/>
-      <c r="I299" s="2"/>
-      <c r="J299" s="2"/>
-      <c r="K299" s="2"/>
-      <c r="L299" s="2"/>
-      <c r="M299" s="2"/>
-      <c r="N299" s="2"/>
-      <c r="O299" s="2"/>
-      <c r="P299" s="2"/>
-      <c r="Q299" s="2"/>
-      <c r="R299" s="2"/>
-      <c r="S299" s="2"/>
-      <c r="T299" s="2"/>
-      <c r="U299" s="2"/>
-      <c r="V299" s="2"/>
-      <c r="W299" s="2"/>
-      <c r="X299" s="2"/>
-      <c r="Y299" s="2"/>
-    </row>
-    <row r="300" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A300" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B300" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C300" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="E300" s="1"/>
-      <c r="F300" s="1"/>
-      <c r="G300" s="1"/>
-      <c r="H300" s="1"/>
-      <c r="I300" s="1"/>
-      <c r="J300" s="1"/>
-      <c r="K300" s="1"/>
-      <c r="L300" s="1"/>
-      <c r="M300" s="1"/>
-      <c r="N300" s="1"/>
-      <c r="O300" s="1"/>
-      <c r="P300" s="1"/>
-      <c r="Q300" s="1"/>
-      <c r="R300" s="1"/>
-      <c r="S300" s="1"/>
-      <c r="T300" s="1"/>
-      <c r="U300" s="1"/>
-      <c r="V300" s="1"/>
-      <c r="W300" s="1"/>
-      <c r="X300" s="1"/>
-      <c r="Y300" s="1"/>
+      <c r="E300" s="2"/>
+      <c r="F300" s="2"/>
+      <c r="G300" s="2"/>
+      <c r="H300" s="2"/>
+      <c r="I300" s="2"/>
+      <c r="J300" s="2"/>
+      <c r="K300" s="2"/>
+      <c r="L300" s="2"/>
+      <c r="M300" s="2"/>
+      <c r="N300" s="2"/>
+      <c r="O300" s="2"/>
+      <c r="P300" s="2"/>
+      <c r="Q300" s="2"/>
+      <c r="R300" s="2"/>
+      <c r="S300" s="2"/>
+      <c r="T300" s="2"/>
+      <c r="U300" s="2"/>
+      <c r="V300" s="2"/>
+      <c r="W300" s="2"/>
+      <c r="X300" s="2"/>
+      <c r="Y300" s="2"/>
     </row>
     <row r="301" spans="1:25" ht="15.75" customHeight="1">
       <c r="A301" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="B301" s="3"/>
-      <c r="C301" s="18" t="s">
-        <v>635</v>
+        <v>631</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C301" s="3" t="s">
+        <v>633</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E301" s="1"/>
       <c r="F301" s="1"/>
@@ -14131,14 +14142,14 @@
     </row>
     <row r="302" spans="1:25" ht="15.75" customHeight="1">
       <c r="A302" s="3" t="s">
-        <v>1043</v>
+        <v>634</v>
       </c>
       <c r="B302" s="3"/>
-      <c r="C302" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>1045</v>
+      <c r="C302" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="E302" s="1"/>
       <c r="F302" s="1"/>
@@ -14163,48 +14174,46 @@
       <c r="Y302" s="1"/>
     </row>
     <row r="303" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A303" s="9" t="s">
+      <c r="A303" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B303" s="3"/>
+      <c r="C303" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D303" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E303" s="1"/>
+      <c r="F303" s="1"/>
+      <c r="G303" s="1"/>
+      <c r="H303" s="1"/>
+      <c r="I303" s="1"/>
+      <c r="J303" s="1"/>
+      <c r="K303" s="1"/>
+      <c r="L303" s="1"/>
+      <c r="M303" s="1"/>
+      <c r="N303" s="1"/>
+      <c r="O303" s="1"/>
+      <c r="P303" s="1"/>
+      <c r="Q303" s="1"/>
+      <c r="R303" s="1"/>
+      <c r="S303" s="1"/>
+      <c r="T303" s="1"/>
+      <c r="U303" s="1"/>
+      <c r="V303" s="1"/>
+      <c r="W303" s="1"/>
+      <c r="X303" s="1"/>
+      <c r="Y303" s="1"/>
+    </row>
+    <row r="304" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A304" s="9" t="s">
+        <v>911</v>
+      </c>
+      <c r="B304" s="9"/>
+      <c r="C304" s="10"/>
+      <c r="D304" s="9" t="s">
         <v>912</v>
-      </c>
-      <c r="B303" s="9"/>
-      <c r="C303" s="10"/>
-      <c r="D303" s="9" t="s">
-        <v>913</v>
-      </c>
-      <c r="E303" s="2"/>
-      <c r="F303" s="2"/>
-      <c r="G303" s="2"/>
-      <c r="H303" s="2"/>
-      <c r="I303" s="2"/>
-      <c r="J303" s="2"/>
-      <c r="K303" s="2"/>
-      <c r="L303" s="2"/>
-      <c r="M303" s="2"/>
-      <c r="N303" s="2"/>
-      <c r="O303" s="2"/>
-      <c r="P303" s="2"/>
-      <c r="Q303" s="2"/>
-      <c r="R303" s="2"/>
-      <c r="S303" s="2"/>
-      <c r="T303" s="2"/>
-      <c r="U303" s="2"/>
-      <c r="V303" s="2"/>
-      <c r="W303" s="2"/>
-      <c r="X303" s="2"/>
-      <c r="Y303" s="2"/>
-    </row>
-    <row r="304" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A304" s="13" t="s">
-        <v>914</v>
-      </c>
-      <c r="B304" s="13" t="s">
-        <v>915</v>
-      </c>
-      <c r="C304" s="68" t="s">
-        <v>916</v>
-      </c>
-      <c r="D304" s="13" t="s">
-        <v>917</v>
       </c>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
@@ -14229,50 +14238,52 @@
       <c r="Y304" s="2"/>
     </row>
     <row r="305" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A305" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="B305" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C305" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="D305" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="E305" s="1"/>
-      <c r="F305" s="1"/>
-      <c r="G305" s="1"/>
-      <c r="H305" s="1"/>
-      <c r="I305" s="1"/>
-      <c r="J305" s="1"/>
-      <c r="K305" s="1"/>
-      <c r="L305" s="1"/>
-      <c r="M305" s="1"/>
-      <c r="N305" s="1"/>
-      <c r="O305" s="1"/>
-      <c r="P305" s="1"/>
-      <c r="Q305" s="1"/>
-      <c r="R305" s="1"/>
-      <c r="S305" s="1"/>
-      <c r="T305" s="1"/>
-      <c r="U305" s="1"/>
-      <c r="V305" s="1"/>
-      <c r="W305" s="1"/>
-      <c r="X305" s="1"/>
-      <c r="Y305" s="1"/>
+      <c r="A305" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="B305" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="C305" s="68" t="s">
+        <v>915</v>
+      </c>
+      <c r="D305" s="13" t="s">
+        <v>916</v>
+      </c>
+      <c r="E305" s="2"/>
+      <c r="F305" s="2"/>
+      <c r="G305" s="2"/>
+      <c r="H305" s="2"/>
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="2"/>
+      <c r="M305" s="2"/>
+      <c r="N305" s="2"/>
+      <c r="O305" s="2"/>
+      <c r="P305" s="2"/>
+      <c r="Q305" s="2"/>
+      <c r="R305" s="2"/>
+      <c r="S305" s="2"/>
+      <c r="T305" s="2"/>
+      <c r="U305" s="2"/>
+      <c r="V305" s="2"/>
+      <c r="W305" s="2"/>
+      <c r="X305" s="2"/>
+      <c r="Y305" s="2"/>
     </row>
     <row r="306" spans="1:25" ht="15.75" customHeight="1">
       <c r="A306" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="B306" s="9"/>
-      <c r="C306" s="10" t="s">
-        <v>642</v>
+        <v>637</v>
+      </c>
+      <c r="B306" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C306" s="11" t="s">
+        <v>639</v>
       </c>
       <c r="D306" s="9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E306" s="1"/>
       <c r="F306" s="1"/>
@@ -14297,17 +14308,15 @@
       <c r="Y306" s="1"/>
     </row>
     <row r="307" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A307" s="13" t="s">
-        <v>918</v>
-      </c>
-      <c r="B307" s="13" t="s">
-        <v>919</v>
-      </c>
-      <c r="C307" s="68" t="s">
-        <v>920</v>
-      </c>
-      <c r="D307" s="13" t="s">
-        <v>918</v>
+      <c r="A307" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="B307" s="9"/>
+      <c r="C307" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="D307" s="9" t="s">
+        <v>643</v>
       </c>
       <c r="E307" s="1"/>
       <c r="F307" s="1"/>
@@ -14333,16 +14342,16 @@
     </row>
     <row r="308" spans="1:25" ht="15.75" customHeight="1">
       <c r="A308" s="13" t="s">
-        <v>644</v>
+        <v>917</v>
       </c>
       <c r="B308" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="C308" s="14" t="s">
-        <v>646</v>
+        <v>918</v>
+      </c>
+      <c r="C308" s="68" t="s">
+        <v>919</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>644</v>
+        <v>917</v>
       </c>
       <c r="E308" s="1"/>
       <c r="F308" s="1"/>
@@ -14367,15 +14376,17 @@
       <c r="Y308" s="1"/>
     </row>
     <row r="309" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A309" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="B309" s="9"/>
-      <c r="C309" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="D309" s="9" t="s">
-        <v>647</v>
+      <c r="A309" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="B309" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="C309" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="D309" s="13" t="s">
+        <v>644</v>
       </c>
       <c r="E309" s="1"/>
       <c r="F309" s="1"/>
@@ -14401,14 +14412,14 @@
     </row>
     <row r="310" spans="1:25" ht="15.75" customHeight="1">
       <c r="A310" s="9" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B310" s="9"/>
-      <c r="C310" s="11" t="s">
-        <v>650</v>
+      <c r="C310" s="10" t="s">
+        <v>648</v>
       </c>
       <c r="D310" s="9" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E310" s="1"/>
       <c r="F310" s="1"/>
@@ -14434,14 +14445,14 @@
     </row>
     <row r="311" spans="1:25" ht="15.75" customHeight="1">
       <c r="A311" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B311" s="9"/>
-      <c r="C311" s="10" t="s">
-        <v>652</v>
+      <c r="C311" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="D311" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E311" s="1"/>
       <c r="F311" s="1"/>
@@ -14467,14 +14478,14 @@
     </row>
     <row r="312" spans="1:25" ht="15.75" customHeight="1">
       <c r="A312" s="9" t="s">
-        <v>851</v>
+        <v>651</v>
       </c>
       <c r="B312" s="9"/>
       <c r="C312" s="10" t="s">
-        <v>852</v>
+        <v>652</v>
       </c>
       <c r="D312" s="9" t="s">
-        <v>851</v>
+        <v>651</v>
       </c>
       <c r="E312" s="1"/>
       <c r="F312" s="1"/>
@@ -14500,16 +14511,14 @@
     </row>
     <row r="313" spans="1:25" ht="15.75" customHeight="1">
       <c r="A313" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="B313" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="C313" s="11" t="s">
-        <v>655</v>
+        <v>851</v>
+      </c>
+      <c r="B313" s="9"/>
+      <c r="C313" s="10" t="s">
+        <v>852</v>
       </c>
       <c r="D313" s="9" t="s">
-        <v>653</v>
+        <v>851</v>
       </c>
       <c r="E313" s="1"/>
       <c r="F313" s="1"/>
@@ -14535,14 +14544,16 @@
     </row>
     <row r="314" spans="1:25" ht="15.75" customHeight="1">
       <c r="A314" s="9" t="s">
-        <v>656</v>
-      </c>
-      <c r="B314" s="9"/>
-      <c r="C314" s="16" t="s">
-        <v>657</v>
+        <v>653</v>
+      </c>
+      <c r="B314" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="C314" s="11" t="s">
+        <v>655</v>
       </c>
       <c r="D314" s="9" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="E314" s="1"/>
       <c r="F314" s="1"/>
@@ -14567,17 +14578,15 @@
       <c r="Y314" s="1"/>
     </row>
     <row r="315" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A315" s="13" t="s">
-        <v>921</v>
-      </c>
-      <c r="B315" s="13" t="s">
-        <v>922</v>
-      </c>
-      <c r="C315" s="68" t="s">
-        <v>923</v>
-      </c>
-      <c r="D315" s="13" t="s">
-        <v>921</v>
+      <c r="A315" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B315" s="9"/>
+      <c r="C315" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="D315" s="9" t="s">
+        <v>656</v>
       </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
@@ -14602,17 +14611,17 @@
       <c r="Y315" s="1"/>
     </row>
     <row r="316" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A316" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="B316" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="C316" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="D316" s="5" t="s">
-        <v>660</v>
+      <c r="A316" s="13" t="s">
+        <v>920</v>
+      </c>
+      <c r="B316" s="13" t="s">
+        <v>921</v>
+      </c>
+      <c r="C316" s="68" t="s">
+        <v>922</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>920</v>
       </c>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
@@ -14637,50 +14646,50 @@
       <c r="Y316" s="1"/>
     </row>
     <row r="317" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A317" s="9" t="s">
+      <c r="A317" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C317" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="D317" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="E317" s="1"/>
+      <c r="F317" s="1"/>
+      <c r="G317" s="1"/>
+      <c r="H317" s="1"/>
+      <c r="I317" s="1"/>
+      <c r="J317" s="1"/>
+      <c r="K317" s="1"/>
+      <c r="L317" s="1"/>
+      <c r="M317" s="1"/>
+      <c r="N317" s="1"/>
+      <c r="O317" s="1"/>
+      <c r="P317" s="1"/>
+      <c r="Q317" s="1"/>
+      <c r="R317" s="1"/>
+      <c r="S317" s="1"/>
+      <c r="T317" s="1"/>
+      <c r="U317" s="1"/>
+      <c r="V317" s="1"/>
+      <c r="W317" s="1"/>
+      <c r="X317" s="1"/>
+      <c r="Y317" s="1"/>
+    </row>
+    <row r="318" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A318" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="B317" s="9"/>
-      <c r="C317" s="10" t="s">
+      <c r="B318" s="9"/>
+      <c r="C318" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="D317" s="9" t="s">
+      <c r="D318" s="9" t="s">
         <v>658</v>
-      </c>
-      <c r="E317" s="2"/>
-      <c r="F317" s="2"/>
-      <c r="G317" s="2"/>
-      <c r="H317" s="2"/>
-      <c r="I317" s="2"/>
-      <c r="J317" s="2"/>
-      <c r="K317" s="2"/>
-      <c r="L317" s="2"/>
-      <c r="M317" s="2"/>
-      <c r="N317" s="2"/>
-      <c r="O317" s="2"/>
-      <c r="P317" s="2"/>
-      <c r="Q317" s="2"/>
-      <c r="R317" s="2"/>
-      <c r="S317" s="2"/>
-      <c r="T317" s="2"/>
-      <c r="U317" s="2"/>
-      <c r="V317" s="2"/>
-      <c r="W317" s="2"/>
-      <c r="X317" s="2"/>
-      <c r="Y317" s="2"/>
-    </row>
-    <row r="318" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A318" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="B318" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="C318" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>985</v>
       </c>
       <c r="E318" s="2"/>
       <c r="F318" s="2"/>
@@ -14706,14 +14715,16 @@
     </row>
     <row r="319" spans="1:25" ht="15.75" customHeight="1">
       <c r="A319" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B319" s="3"/>
+        <v>984</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>985</v>
+      </c>
       <c r="C319" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D319" s="3" t="s">
-        <v>665</v>
+        <v>986</v>
+      </c>
+      <c r="D319" s="1" t="s">
+        <v>984</v>
       </c>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
@@ -14739,49 +14750,49 @@
     </row>
     <row r="320" spans="1:25" ht="15.75" customHeight="1">
       <c r="A320" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>1008</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="B320" s="3"/>
       <c r="C320" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>1007</v>
-      </c>
-      <c r="E320" s="1"/>
-      <c r="F320" s="1"/>
-      <c r="G320" s="1"/>
-      <c r="H320" s="1"/>
-      <c r="I320" s="1"/>
-      <c r="J320" s="1"/>
-      <c r="K320" s="1"/>
-      <c r="L320" s="1"/>
-      <c r="M320" s="1"/>
-      <c r="N320" s="1"/>
-      <c r="O320" s="1"/>
-      <c r="P320" s="1"/>
-      <c r="Q320" s="1"/>
-      <c r="R320" s="1"/>
-      <c r="S320" s="1"/>
-      <c r="T320" s="1"/>
-      <c r="U320" s="1"/>
-      <c r="V320" s="1"/>
-      <c r="W320" s="1"/>
-      <c r="X320" s="1"/>
-      <c r="Y320" s="1"/>
+        <v>664</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E320" s="2"/>
+      <c r="F320" s="2"/>
+      <c r="G320" s="2"/>
+      <c r="H320" s="2"/>
+      <c r="I320" s="2"/>
+      <c r="J320" s="2"/>
+      <c r="K320" s="2"/>
+      <c r="L320" s="2"/>
+      <c r="M320" s="2"/>
+      <c r="N320" s="2"/>
+      <c r="O320" s="2"/>
+      <c r="P320" s="2"/>
+      <c r="Q320" s="2"/>
+      <c r="R320" s="2"/>
+      <c r="S320" s="2"/>
+      <c r="T320" s="2"/>
+      <c r="U320" s="2"/>
+      <c r="V320" s="2"/>
+      <c r="W320" s="2"/>
+      <c r="X320" s="2"/>
+      <c r="Y320" s="2"/>
     </row>
     <row r="321" spans="1:25" ht="15.75" customHeight="1">
       <c r="A321" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B321" s="3"/>
+        <v>1006</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="C321" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>666</v>
+        <v>1008</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>1006</v>
       </c>
       <c r="E321" s="1"/>
       <c r="F321" s="1"/>
@@ -14806,17 +14817,15 @@
       <c r="Y321" s="1"/>
     </row>
     <row r="322" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A322" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B322" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="C322" s="45" t="s">
-        <v>675</v>
-      </c>
-      <c r="D322" s="9" t="s">
-        <v>676</v>
+      <c r="A322" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B322" s="3"/>
+      <c r="C322" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="E322" s="1"/>
       <c r="F322" s="1"/>
@@ -14841,17 +14850,17 @@
       <c r="Y322" s="1"/>
     </row>
     <row r="323" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A323" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="B323" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="C323" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="D323" s="13" t="s">
-        <v>680</v>
+      <c r="A323" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="C323" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="D323" s="9" t="s">
+        <v>676</v>
       </c>
       <c r="E323" s="1"/>
       <c r="F323" s="1"/>
@@ -14876,17 +14885,17 @@
       <c r="Y323" s="1"/>
     </row>
     <row r="324" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A324" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="B324" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="C324" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="D324" s="9" t="s">
-        <v>684</v>
+      <c r="A324" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B324" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="C324" s="46" t="s">
+        <v>679</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>680</v>
       </c>
       <c r="E324" s="1"/>
       <c r="F324" s="1"/>
@@ -14911,15 +14920,17 @@
       <c r="Y324" s="1"/>
     </row>
     <row r="325" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A325" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B325" s="13"/>
-      <c r="C325" s="14" t="s">
-        <v>686</v>
-      </c>
-      <c r="D325" s="13" t="s">
-        <v>687</v>
+      <c r="A325" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="C325" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D325" s="9" t="s">
+        <v>684</v>
       </c>
       <c r="E325" s="1"/>
       <c r="F325" s="1"/>
@@ -14944,17 +14955,15 @@
       <c r="Y325" s="1"/>
     </row>
     <row r="326" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A326" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B326" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C326" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D326" s="7" t="s">
-        <v>668</v>
+      <c r="A326" s="13" t="s">
+        <v>685</v>
+      </c>
+      <c r="B326" s="13"/>
+      <c r="C326" s="14" t="s">
+        <v>686</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>687</v>
       </c>
       <c r="E326" s="1"/>
       <c r="F326" s="1"/>
@@ -14979,15 +14988,17 @@
       <c r="Y326" s="1"/>
     </row>
     <row r="327" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A327" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="B327" s="9"/>
-      <c r="C327" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="D327" s="9" t="s">
-        <v>671</v>
+      <c r="A327" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B327" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C327" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D327" s="7" t="s">
+        <v>668</v>
       </c>
       <c r="E327" s="1"/>
       <c r="F327" s="1"/>
@@ -15013,14 +15024,14 @@
     </row>
     <row r="328" spans="1:25" ht="15.75" customHeight="1">
       <c r="A328" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="B328" s="9"/>
-      <c r="C328" s="10" t="s">
-        <v>689</v>
+      <c r="C328" s="11" t="s">
+        <v>672</v>
       </c>
       <c r="D328" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="E328" s="1"/>
       <c r="F328" s="1"/>
@@ -15046,16 +15057,14 @@
     </row>
     <row r="329" spans="1:25" ht="15.75" customHeight="1">
       <c r="A329" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B329" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C329" s="11" t="s">
-        <v>692</v>
+        <v>688</v>
+      </c>
+      <c r="B329" s="9"/>
+      <c r="C329" s="10" t="s">
+        <v>689</v>
       </c>
       <c r="D329" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E329" s="1"/>
       <c r="F329" s="1"/>
@@ -15081,14 +15090,16 @@
     </row>
     <row r="330" spans="1:25" ht="15.75" customHeight="1">
       <c r="A330" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B330" s="9"/>
-      <c r="C330" s="10" t="s">
-        <v>844</v>
+        <v>690</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C330" s="11" t="s">
+        <v>692</v>
       </c>
       <c r="D330" s="9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E330" s="1"/>
       <c r="F330" s="1"/>
@@ -15113,17 +15124,15 @@
       <c r="Y330" s="1"/>
     </row>
     <row r="331" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A331" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="B331" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C331" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>1010</v>
+      <c r="A331" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B331" s="9"/>
+      <c r="C331" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="D331" s="9" t="s">
+        <v>695</v>
       </c>
       <c r="E331" s="1"/>
       <c r="F331" s="1"/>
@@ -15148,15 +15157,17 @@
       <c r="Y331" s="1"/>
     </row>
     <row r="332" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A332" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B332" s="13"/>
-      <c r="C332" s="22" t="s">
-        <v>697</v>
-      </c>
-      <c r="D332" s="13" t="s">
-        <v>696</v>
+      <c r="A332" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C332" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D332" s="1" t="s">
+        <v>1009</v>
       </c>
       <c r="E332" s="1"/>
       <c r="F332" s="1"/>
@@ -15182,51 +15193,49 @@
     </row>
     <row r="333" spans="1:25" ht="15.75" customHeight="1">
       <c r="A333" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="B333" s="13"/>
+      <c r="C333" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D333" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="E333" s="1"/>
+      <c r="F333" s="1"/>
+      <c r="G333" s="1"/>
+      <c r="H333" s="1"/>
+      <c r="I333" s="1"/>
+      <c r="J333" s="1"/>
+      <c r="K333" s="1"/>
+      <c r="L333" s="1"/>
+      <c r="M333" s="1"/>
+      <c r="N333" s="1"/>
+      <c r="O333" s="1"/>
+      <c r="P333" s="1"/>
+      <c r="Q333" s="1"/>
+      <c r="R333" s="1"/>
+      <c r="S333" s="1"/>
+      <c r="T333" s="1"/>
+      <c r="U333" s="1"/>
+      <c r="V333" s="1"/>
+      <c r="W333" s="1"/>
+      <c r="X333" s="1"/>
+      <c r="Y333" s="1"/>
+    </row>
+    <row r="334" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A334" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="B333" s="13" t="s">
+      <c r="B334" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="C333" s="14" t="s">
+      <c r="C334" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="D333" s="13" t="s">
+      <c r="D334" s="13" t="s">
         <v>698</v>
-      </c>
-      <c r="E333" s="2"/>
-      <c r="F333" s="2"/>
-      <c r="G333" s="2"/>
-      <c r="H333" s="2"/>
-      <c r="I333" s="2"/>
-      <c r="J333" s="2"/>
-      <c r="K333" s="2"/>
-      <c r="L333" s="2"/>
-      <c r="M333" s="2"/>
-      <c r="N333" s="2"/>
-      <c r="O333" s="2"/>
-      <c r="P333" s="2"/>
-      <c r="Q333" s="2"/>
-      <c r="R333" s="2"/>
-      <c r="S333" s="2"/>
-      <c r="T333" s="2"/>
-      <c r="U333" s="2"/>
-      <c r="V333" s="2"/>
-      <c r="W333" s="2"/>
-      <c r="X333" s="2"/>
-      <c r="Y333" s="2"/>
-    </row>
-    <row r="334" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A334" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B334" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="C334" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D334" s="9" t="s">
-        <v>701</v>
       </c>
       <c r="E334" s="2"/>
       <c r="F334" s="2"/>
@@ -15251,52 +15260,52 @@
       <c r="Y334" s="2"/>
     </row>
     <row r="335" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A335" s="3" t="s">
+      <c r="A335" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B335" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C335" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D335" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="E335" s="2"/>
+      <c r="F335" s="2"/>
+      <c r="G335" s="2"/>
+      <c r="H335" s="2"/>
+      <c r="I335" s="2"/>
+      <c r="J335" s="2"/>
+      <c r="K335" s="2"/>
+      <c r="L335" s="2"/>
+      <c r="M335" s="2"/>
+      <c r="N335" s="2"/>
+      <c r="O335" s="2"/>
+      <c r="P335" s="2"/>
+      <c r="Q335" s="2"/>
+      <c r="R335" s="2"/>
+      <c r="S335" s="2"/>
+      <c r="T335" s="2"/>
+      <c r="U335" s="2"/>
+      <c r="V335" s="2"/>
+      <c r="W335" s="2"/>
+      <c r="X335" s="2"/>
+      <c r="Y335" s="2"/>
+    </row>
+    <row r="336" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A336" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B336" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="B335" s="3" t="s">
+      <c r="C336" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="C335" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D335" s="1" t="s">
-        <v>1013</v>
-      </c>
-      <c r="E335" s="1"/>
-      <c r="F335" s="1"/>
-      <c r="G335" s="1"/>
-      <c r="H335" s="1"/>
-      <c r="I335" s="1"/>
-      <c r="J335" s="1"/>
-      <c r="K335" s="1"/>
-      <c r="L335" s="1"/>
-      <c r="M335" s="1"/>
-      <c r="N335" s="1"/>
-      <c r="O335" s="1"/>
-      <c r="P335" s="1"/>
-      <c r="Q335" s="1"/>
-      <c r="R335" s="1"/>
-      <c r="S335" s="1"/>
-      <c r="T335" s="1"/>
-      <c r="U335" s="1"/>
-      <c r="V335" s="1"/>
-      <c r="W335" s="1"/>
-      <c r="X335" s="1"/>
-      <c r="Y335" s="1"/>
-    </row>
-    <row r="336" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A336" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="B336" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="C336" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D336" s="9" t="s">
-        <v>704</v>
+      <c r="D336" s="1" t="s">
+        <v>1012</v>
       </c>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
@@ -15321,87 +15330,87 @@
       <c r="Y336" s="1"/>
     </row>
     <row r="337" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A337" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="B337" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C337" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="D337" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E337" s="2"/>
-      <c r="F337" s="2"/>
-      <c r="G337" s="2"/>
-      <c r="H337" s="2"/>
-      <c r="I337" s="2"/>
-      <c r="J337" s="2"/>
-      <c r="K337" s="2"/>
-      <c r="L337" s="2"/>
-      <c r="M337" s="2"/>
-      <c r="N337" s="2"/>
-      <c r="O337" s="2"/>
-      <c r="P337" s="2"/>
-      <c r="Q337" s="2"/>
-      <c r="R337" s="2"/>
-      <c r="S337" s="2"/>
-      <c r="T337" s="2"/>
-      <c r="U337" s="2"/>
-      <c r="V337" s="2"/>
-      <c r="W337" s="2"/>
-      <c r="X337" s="2"/>
-      <c r="Y337" s="2"/>
+      <c r="A337" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B337" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="C337" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="D337" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="E337" s="1"/>
+      <c r="F337" s="1"/>
+      <c r="G337" s="1"/>
+      <c r="H337" s="1"/>
+      <c r="I337" s="1"/>
+      <c r="J337" s="1"/>
+      <c r="K337" s="1"/>
+      <c r="L337" s="1"/>
+      <c r="M337" s="1"/>
+      <c r="N337" s="1"/>
+      <c r="O337" s="1"/>
+      <c r="P337" s="1"/>
+      <c r="Q337" s="1"/>
+      <c r="R337" s="1"/>
+      <c r="S337" s="1"/>
+      <c r="T337" s="1"/>
+      <c r="U337" s="1"/>
+      <c r="V337" s="1"/>
+      <c r="W337" s="1"/>
+      <c r="X337" s="1"/>
+      <c r="Y337" s="1"/>
     </row>
     <row r="338" spans="1:25" ht="15.75" customHeight="1">
       <c r="A338" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="C338" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="D338" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="E338" s="2"/>
+      <c r="F338" s="2"/>
+      <c r="G338" s="2"/>
+      <c r="H338" s="2"/>
+      <c r="I338" s="2"/>
+      <c r="J338" s="2"/>
+      <c r="K338" s="2"/>
+      <c r="L338" s="2"/>
+      <c r="M338" s="2"/>
+      <c r="N338" s="2"/>
+      <c r="O338" s="2"/>
+      <c r="P338" s="2"/>
+      <c r="Q338" s="2"/>
+      <c r="R338" s="2"/>
+      <c r="S338" s="2"/>
+      <c r="T338" s="2"/>
+      <c r="U338" s="2"/>
+      <c r="V338" s="2"/>
+      <c r="W338" s="2"/>
+      <c r="X338" s="2"/>
+      <c r="Y338" s="2"/>
+    </row>
+    <row r="339" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A339" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B338" s="3" t="s">
+      <c r="B339" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C338" s="4" t="s">
+      <c r="C339" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D338" s="3" t="s">
+      <c r="D339" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="E338" s="1"/>
-      <c r="F338" s="1"/>
-      <c r="G338" s="1"/>
-      <c r="H338" s="1"/>
-      <c r="I338" s="1"/>
-      <c r="J338" s="1"/>
-      <c r="K338" s="1"/>
-      <c r="L338" s="1"/>
-      <c r="M338" s="1"/>
-      <c r="N338" s="1"/>
-      <c r="O338" s="1"/>
-      <c r="P338" s="1"/>
-      <c r="Q338" s="1"/>
-      <c r="R338" s="1"/>
-      <c r="S338" s="1"/>
-      <c r="T338" s="1"/>
-      <c r="U338" s="1"/>
-      <c r="V338" s="1"/>
-      <c r="W338" s="1"/>
-      <c r="X338" s="1"/>
-      <c r="Y338" s="1"/>
-    </row>
-    <row r="339" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A339" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="B339" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="C339" s="47" t="s">
-        <v>715</v>
-      </c>
-      <c r="D339" s="5" t="s">
-        <v>716</v>
       </c>
       <c r="E339" s="1"/>
       <c r="F339" s="1"/>
@@ -15427,14 +15436,16 @@
     </row>
     <row r="340" spans="1:25" ht="15.75" customHeight="1">
       <c r="A340" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="B340" s="5"/>
-      <c r="C340" s="6" t="s">
-        <v>718</v>
+        <v>713</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C340" s="47" t="s">
+        <v>715</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
@@ -15459,642 +15470,669 @@
       <c r="Y340" s="1"/>
     </row>
     <row r="341" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A341" s="3" t="s">
+      <c r="A341" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B341" s="5"/>
+      <c r="C341" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="D341" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E341" s="1"/>
+      <c r="F341" s="1"/>
+      <c r="G341" s="1"/>
+      <c r="H341" s="1"/>
+      <c r="I341" s="1"/>
+      <c r="J341" s="1"/>
+      <c r="K341" s="1"/>
+      <c r="L341" s="1"/>
+      <c r="M341" s="1"/>
+      <c r="N341" s="1"/>
+      <c r="O341" s="1"/>
+      <c r="P341" s="1"/>
+      <c r="Q341" s="1"/>
+      <c r="R341" s="1"/>
+      <c r="S341" s="1"/>
+      <c r="T341" s="1"/>
+      <c r="U341" s="1"/>
+      <c r="V341" s="1"/>
+      <c r="W341" s="1"/>
+      <c r="X341" s="1"/>
+      <c r="Y341" s="1"/>
+    </row>
+    <row r="342" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A342" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="B341" s="3" t="s">
+      <c r="B342" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="C341" s="3" t="s">
+      <c r="C342" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="D341" s="3" t="s">
+      <c r="D342" s="3" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="342" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A342" s="9" t="s">
+    <row r="343" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A343" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="B342" s="9" t="s">
+      <c r="B343" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="C342" s="11" t="s">
+      <c r="C343" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="D342" s="9" t="s">
+      <c r="D343" s="9" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="343" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A343" s="3" t="s">
+    <row r="344" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A344" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B343" s="3" t="s">
+      <c r="B344" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C343" s="4" t="s">
+      <c r="C344" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="D343" s="3" t="s">
+      <c r="D344" s="3" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="344" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A344" s="5" t="s">
+    <row r="345" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A345" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="B344" s="5"/>
-      <c r="C344" s="47" t="s">
+      <c r="B345" s="5"/>
+      <c r="C345" s="47" t="s">
         <v>729</v>
       </c>
-      <c r="D344" s="5" t="s">
+      <c r="D345" s="5" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="345" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A345" s="3" t="s">
+    <row r="346" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A346" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B345" s="3"/>
-      <c r="C345" s="3" t="s">
+      <c r="B346" s="3"/>
+      <c r="C346" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="D345" s="3" t="s">
+      <c r="D346" s="3" t="s">
         <v>730</v>
-      </c>
-    </row>
-    <row r="346" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A346" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="B346" s="9"/>
-      <c r="C346" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="D346" s="9" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="347" spans="1:25" ht="15.75" customHeight="1">
       <c r="A347" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B347" s="9"/>
+      <c r="C347" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="D347" s="9" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="348" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A348" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="B347" s="9" t="s">
+      <c r="B348" s="9" t="s">
         <v>735</v>
       </c>
-      <c r="C347" s="10" t="s">
+      <c r="C348" s="10" t="s">
         <v>736</v>
       </c>
-      <c r="D347" s="9" t="s">
+      <c r="D348" s="9" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="348" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A348" s="5" t="s">
+    <row r="349" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A349" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B348" s="5" t="s">
+      <c r="B349" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C348" s="47" t="s">
+      <c r="C349" s="47" t="s">
         <v>739</v>
       </c>
-      <c r="D348" s="5" t="s">
+      <c r="D349" s="5" t="s">
         <v>737</v>
-      </c>
-    </row>
-    <row r="349" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A349" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="B349" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C349" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D349" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="350" spans="1:25" ht="15.75" customHeight="1">
       <c r="A350" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C350" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D350" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="351" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A351" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B350" s="3" t="s">
+      <c r="B351" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="C350" s="3" t="s">
+      <c r="C351" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="D350" s="3" t="s">
+      <c r="D351" s="3" t="s">
         <v>743</v>
-      </c>
-    </row>
-    <row r="351" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A351" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="B351" s="5"/>
-      <c r="C351" s="6" t="s">
-        <v>746</v>
-      </c>
-      <c r="D351" s="5" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="352" spans="1:25" ht="15.75" customHeight="1">
       <c r="A352" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B352" s="5"/>
+      <c r="C352" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A353" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B352" s="5" t="s">
+      <c r="B353" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C352" s="30" t="s">
+      <c r="C353" s="30" t="s">
         <v>750</v>
       </c>
-      <c r="D352" s="5" t="s">
+      <c r="D353" s="5" t="s">
         <v>748</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A353" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C353" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D353" s="3" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1">
       <c r="A354" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>752</v>
+      </c>
+      <c r="C354" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="D354" s="3" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A355" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="B354" s="3" t="s">
+      <c r="B355" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="C354" s="3" t="s">
+      <c r="C355" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="D354" s="3" t="s">
+      <c r="D355" s="3" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="355" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A355" s="5" t="s">
+    <row r="356" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A356" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B355" s="5" t="s">
+      <c r="B356" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="C355" s="6" t="s">
+      <c r="C356" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="D355" s="5" t="s">
+      <c r="D356" s="5" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="356" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A356" s="7" t="s">
+    <row r="357" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A357" s="7" t="s">
         <v>760</v>
       </c>
-      <c r="B356" s="7"/>
-      <c r="C356" s="31" t="s">
+      <c r="B357" s="7"/>
+      <c r="C357" s="31" t="s">
         <v>761</v>
       </c>
-      <c r="D356" s="7" t="s">
+      <c r="D357" s="7" t="s">
         <v>762</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A357" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B357" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C357" s="3" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1">
       <c r="A358" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C358" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A359" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B358" s="3" t="s">
+      <c r="B359" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C358" s="3" t="s">
+      <c r="C359" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="D358" s="3" t="s">
+      <c r="D359" s="3" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="359" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A359" s="5" t="s">
+    <row r="360" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A360" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B359" s="5" t="s">
+      <c r="B360" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="C359" s="6" t="s">
+      <c r="C360" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D359" s="5" t="s">
+      <c r="D360" s="5" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="360" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A360" s="3" t="s">
+    <row r="361" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A361" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B360" s="3" t="s">
+      <c r="B361" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="C360" s="4" t="s">
+      <c r="C361" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="D360" s="3" t="s">
+      <c r="D361" s="3" t="s">
         <v>770</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A361" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="B361" s="9"/>
-      <c r="C361" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="D361" s="9" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1">
       <c r="A362" s="9" t="s">
-        <v>775</v>
-      </c>
-      <c r="B362" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="C362" s="10" t="s">
-        <v>777</v>
+        <v>773</v>
+      </c>
+      <c r="B362" s="9"/>
+      <c r="C362" s="11" t="s">
+        <v>774</v>
       </c>
       <c r="D362" s="9" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1">
       <c r="A363" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B363" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="C363" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="D363" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A364" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="B363" s="9"/>
-      <c r="C363" s="11" t="s">
+      <c r="B364" s="9"/>
+      <c r="C364" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="D363" s="9" t="s">
+      <c r="D364" s="9" t="s">
         <v>780</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A364" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="B364" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C364" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D364" s="7" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1">
       <c r="A365" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B365" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C365" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D365" s="7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A366" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="B365" s="7"/>
-      <c r="C365" s="8" t="s">
+      <c r="B366" s="7"/>
+      <c r="C366" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="D365" s="7" t="s">
+      <c r="D366" s="7" t="s">
         <v>781</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A366" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="B366" s="5"/>
-      <c r="C366" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="D366" s="5" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1">
       <c r="A367" s="5" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B367" s="5"/>
       <c r="C367" s="6" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1">
       <c r="A368" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B368" s="5"/>
       <c r="C368" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1">
       <c r="A369" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B369" s="5"/>
       <c r="C369" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1">
       <c r="A370" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B370" s="5" t="s">
-        <v>801</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="B370" s="5"/>
       <c r="C370" s="6" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1">
       <c r="A371" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="D371" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A372" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B371" s="5"/>
-      <c r="C371" s="6" t="s">
+      <c r="B372" s="5"/>
+      <c r="C372" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="D371" s="5" t="s">
+      <c r="D372" s="5" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="372" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A372" s="7" t="s">
+    <row r="373" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A373" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B372" s="7"/>
-      <c r="C372" s="8" t="s">
+      <c r="B373" s="7"/>
+      <c r="C373" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="D372" s="7" t="s">
+      <c r="D373" s="7" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="373" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A373" s="5" t="s">
+    <row r="374" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A374" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B373" s="5"/>
-      <c r="C373" s="6" t="s">
+      <c r="B374" s="5"/>
+      <c r="C374" s="6" t="s">
         <v>810</v>
       </c>
-      <c r="D373" s="5" t="s">
+      <c r="D374" s="5" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="374" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A374" s="3" t="s">
+    <row r="375" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A375" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B375" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="B374" s="3" t="s">
+      <c r="C375" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="C374" s="3" t="s">
+      <c r="D375" s="1" t="s">
         <v>1021</v>
       </c>
-      <c r="D374" s="1" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A375" s="5" t="s">
+    </row>
+    <row r="376" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A376" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="B375" s="5" t="s">
+      <c r="B376" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="C375" s="6" t="s">
+      <c r="C376" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="D375" s="5" t="s">
+      <c r="D376" s="5" t="s">
         <v>811</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A376" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C376" s="3" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1">
       <c r="A377" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C377" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A378" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B377" s="3"/>
-      <c r="C377" s="50" t="s">
+      <c r="B378" s="3"/>
+      <c r="C378" s="50" t="s">
         <v>815</v>
       </c>
-      <c r="D377" s="3" t="s">
+      <c r="D378" s="3" t="s">
         <v>814</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A378" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="B378" s="9"/>
-      <c r="C378" s="10" t="s">
-        <v>817</v>
-      </c>
-      <c r="D378" s="9" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1">
       <c r="A379" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="B379" s="9"/>
+      <c r="C379" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="D379" s="9" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A380" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="B379" s="9" t="s">
+      <c r="B380" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="C379" s="11" t="s">
+      <c r="C380" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="D379" s="9" t="s">
+      <c r="D380" s="9" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="380" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A380" s="7" t="s">
+    <row r="381" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A381" s="7" t="s">
+        <v>923</v>
+      </c>
+      <c r="B381" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="B380" s="7" t="s">
+      <c r="C381" s="53" t="s">
         <v>925</v>
       </c>
-      <c r="C380" s="53" t="s">
+      <c r="D381" s="7" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A382" s="3" t="s">
+        <v>822</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="C382" s="50" t="s">
+        <v>824</v>
+      </c>
+      <c r="D382" s="3" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A383" s="9" t="s">
+        <v>825</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="D383" s="9" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A384" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="B384" s="3"/>
+      <c r="C384" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="D384" s="3" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A385" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="B385" s="5"/>
+      <c r="C385" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="D385" s="48" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A386" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C386" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A387" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="B387" s="5"/>
+      <c r="C387" s="6" t="s">
+        <v>836</v>
+      </c>
+      <c r="D387" s="49" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A388" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C388" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D388" s="1" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A389" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="D380" s="7" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A381" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="B381" s="3" t="s">
-        <v>823</v>
-      </c>
-      <c r="C381" s="4" t="s">
-        <v>824</v>
-      </c>
-      <c r="D381" s="3" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A382" s="9" t="s">
-        <v>825</v>
-      </c>
-      <c r="B382" s="9" t="s">
-        <v>826</v>
-      </c>
-      <c r="C382" s="10" t="s">
-        <v>827</v>
-      </c>
-      <c r="D382" s="9" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A383" s="3" t="s">
-        <v>828</v>
-      </c>
-      <c r="B383" s="3"/>
-      <c r="C383" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>828</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A384" s="5" t="s">
-        <v>830</v>
-      </c>
-      <c r="B384" s="5"/>
-      <c r="C384" s="6" t="s">
-        <v>831</v>
-      </c>
-      <c r="D384" s="48" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A385" s="3" t="s">
-        <v>832</v>
-      </c>
-      <c r="B385" s="3" t="s">
-        <v>833</v>
-      </c>
-      <c r="C385" s="12" t="s">
-        <v>834</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A386" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="B386" s="5"/>
-      <c r="C386" s="6" t="s">
-        <v>836</v>
-      </c>
-      <c r="D386" s="49" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A387" s="3" t="s">
-        <v>1026</v>
-      </c>
-      <c r="B387" s="3" t="s">
-        <v>1027</v>
-      </c>
-      <c r="C387" s="3" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D387" s="1" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A388" s="7" t="s">
+      <c r="B389" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="B388" s="7" t="s">
+      <c r="C389" s="69" t="s">
         <v>928</v>
       </c>
-      <c r="C388" s="69" t="s">
-        <v>929</v>
-      </c>
-      <c r="D388" s="70" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A389" s="3"/>
-      <c r="B389" s="3"/>
-      <c r="C389" s="3"/>
-      <c r="D389" s="1"/>
+      <c r="D389" s="70" t="s">
+        <v>926</v>
+      </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1">
       <c r="A390" s="3"/>
@@ -21273,6 +21311,12 @@
       <c r="B1252" s="3"/>
       <c r="C1252" s="3"/>
       <c r="D1252" s="1"/>
+    </row>
+    <row r="1253" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1253" s="3"/>
+      <c r="B1253" s="3"/>
+      <c r="C1253" s="3"/>
+      <c r="D1253" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -21408,106 +21452,106 @@
     <hyperlink ref="C213" r:id="rId130" xr:uid="{00000000-0004-0000-0000-000083000000}"/>
     <hyperlink ref="C57" r:id="rId131" xr:uid="{00000000-0004-0000-0000-000084000000}"/>
     <hyperlink ref="C216" r:id="rId132" xr:uid="{00000000-0004-0000-0000-000085000000}"/>
-    <hyperlink ref="C221" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
-    <hyperlink ref="C226" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
-    <hyperlink ref="C229" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
-    <hyperlink ref="C230" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
-    <hyperlink ref="C231" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
-    <hyperlink ref="C233" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
-    <hyperlink ref="C234" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
-    <hyperlink ref="C235" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
-    <hyperlink ref="C238" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
-    <hyperlink ref="C239" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
-    <hyperlink ref="C240" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
-    <hyperlink ref="C242" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
-    <hyperlink ref="C243" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
-    <hyperlink ref="C244" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
-    <hyperlink ref="C246" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
-    <hyperlink ref="C248" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
-    <hyperlink ref="C249" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
-    <hyperlink ref="C250" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
-    <hyperlink ref="C252" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
-    <hyperlink ref="C255" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
-    <hyperlink ref="C256" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
-    <hyperlink ref="C257" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
-    <hyperlink ref="C261" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
-    <hyperlink ref="C262" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
-    <hyperlink ref="C265" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C266" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C268" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C269" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
-    <hyperlink ref="C247" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C271" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C272" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C278" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C279" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C282" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C285" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C283" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C286" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C288" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C291" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C292" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C293" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C295" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C296" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C297" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C298" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C301" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C305" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C306" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C308" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C309" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C310" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C313" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C314" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C316" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C326" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C327" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C322" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C323" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C325" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C328" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C329" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C332" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C333" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C338" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C339" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C340" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C342" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C344" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C346" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C348" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C351" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C352" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C355" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C356" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C359" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C360" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C361" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C363" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C365" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C364" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C222" r:id="rId133" xr:uid="{00000000-0004-0000-0000-000087000000}"/>
+    <hyperlink ref="C227" r:id="rId134" xr:uid="{00000000-0004-0000-0000-000089000000}"/>
+    <hyperlink ref="C230" r:id="rId135" xr:uid="{00000000-0004-0000-0000-00008A000000}"/>
+    <hyperlink ref="C231" r:id="rId136" xr:uid="{00000000-0004-0000-0000-00008B000000}"/>
+    <hyperlink ref="C232" r:id="rId137" xr:uid="{00000000-0004-0000-0000-00008C000000}"/>
+    <hyperlink ref="C234" r:id="rId138" xr:uid="{00000000-0004-0000-0000-00008D000000}"/>
+    <hyperlink ref="C235" r:id="rId139" xr:uid="{00000000-0004-0000-0000-00008E000000}"/>
+    <hyperlink ref="C236" r:id="rId140" xr:uid="{00000000-0004-0000-0000-00008F000000}"/>
+    <hyperlink ref="C239" r:id="rId141" xr:uid="{00000000-0004-0000-0000-000090000000}"/>
+    <hyperlink ref="C240" r:id="rId142" xr:uid="{00000000-0004-0000-0000-000091000000}"/>
+    <hyperlink ref="C241" r:id="rId143" xr:uid="{00000000-0004-0000-0000-000092000000}"/>
+    <hyperlink ref="C243" r:id="rId144" xr:uid="{00000000-0004-0000-0000-000093000000}"/>
+    <hyperlink ref="C244" r:id="rId145" xr:uid="{00000000-0004-0000-0000-000094000000}"/>
+    <hyperlink ref="C245" r:id="rId146" xr:uid="{00000000-0004-0000-0000-000095000000}"/>
+    <hyperlink ref="C247" r:id="rId147" xr:uid="{00000000-0004-0000-0000-000096000000}"/>
+    <hyperlink ref="C249" r:id="rId148" xr:uid="{00000000-0004-0000-0000-000097000000}"/>
+    <hyperlink ref="C250" r:id="rId149" xr:uid="{00000000-0004-0000-0000-000098000000}"/>
+    <hyperlink ref="C251" r:id="rId150" xr:uid="{00000000-0004-0000-0000-000099000000}"/>
+    <hyperlink ref="C253" r:id="rId151" xr:uid="{00000000-0004-0000-0000-00009A000000}"/>
+    <hyperlink ref="C256" r:id="rId152" xr:uid="{00000000-0004-0000-0000-00009B000000}"/>
+    <hyperlink ref="C257" r:id="rId153" xr:uid="{00000000-0004-0000-0000-00009C000000}"/>
+    <hyperlink ref="C258" r:id="rId154" xr:uid="{00000000-0004-0000-0000-00009D000000}"/>
+    <hyperlink ref="C262" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
+    <hyperlink ref="C263" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
+    <hyperlink ref="C266" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
+    <hyperlink ref="C267" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C269" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C270" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C248" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
+    <hyperlink ref="C272" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C273" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C279" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C280" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C283" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C286" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C284" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C287" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C289" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C292" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C293" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C294" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C296" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C297" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C298" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C299" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C302" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C306" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C307" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C309" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C310" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C311" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C314" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C315" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C317" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C327" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C328" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C323" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C324" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C326" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C329" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C330" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C333" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C334" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C339" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C340" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C341" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C343" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C345" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C347" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C349" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C352" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C353" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C356" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C357" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C360" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C361" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C362" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C364" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C366" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C365" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C8" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C366" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C367" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C368" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C369" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C370" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C371" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C372" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C373" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C375" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C377" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C379" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C381" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C383" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C384" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C385" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C386" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C367" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C368" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C369" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C370" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C371" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C372" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C373" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C374" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C376" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C378" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C380" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C382" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C384" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C385" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C386" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C387" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="C167" r:id="rId230" xr:uid="{98DDE684-CC21-7C49-B22B-C4F92C88FD93}"/>
-    <hyperlink ref="C224" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
-    <hyperlink ref="C258" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
+    <hyperlink ref="C225" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
+    <hyperlink ref="C259" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
     <hyperlink ref="C133" r:id="rId233" xr:uid="{6B2056CE-BB4C-D74B-A597-EA3A8C5C2030}"/>
     <hyperlink ref="C6" r:id="rId234" xr:uid="{D36410A9-1671-0F4D-A4CE-1789BA83AD03}"/>
     <hyperlink ref="C24" r:id="rId235" xr:uid="{8BADE627-88AB-8344-8C39-BDD2E908CD68}"/>
@@ -21527,14 +21571,14 @@
     <hyperlink ref="C196" r:id="rId249" xr:uid="{B4AAB667-FFFA-F64C-BC79-708CC2119E9B}"/>
     <hyperlink ref="C202" r:id="rId250" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
     <hyperlink ref="C220" r:id="rId251" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
-    <hyperlink ref="C223" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
-    <hyperlink ref="C275" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
-    <hyperlink ref="C281" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
-    <hyperlink ref="C304" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
-    <hyperlink ref="C307" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
-    <hyperlink ref="C315" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C380" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C388" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C224" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
+    <hyperlink ref="C276" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
+    <hyperlink ref="C282" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
+    <hyperlink ref="C305" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
+    <hyperlink ref="C308" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
+    <hyperlink ref="C316" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
+    <hyperlink ref="C381" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C389" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C188" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
     <hyperlink ref="C215" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
   </hyperlinks>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633ED5FA-E166-644F-A8FB-4E6351A4B0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2CC3F8-92A2-AD41-A3F2-A677D2EC5673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -12099,7 +12099,7 @@
         <v>507</v>
       </c>
       <c r="B242" s="3"/>
-      <c r="C242" s="3" t="s">
+      <c r="C242" s="50" t="s">
         <v>508</v>
       </c>
       <c r="D242" s="3" t="s">
@@ -21581,11 +21581,12 @@
     <hyperlink ref="C389" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C188" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
     <hyperlink ref="C215" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
+    <hyperlink ref="C242" r:id="rId262" xr:uid="{20FF35A0-9072-C349-94BD-F07C44AE26C4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId262"/>
+    <tablePart r:id="rId263"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8732C83-ADF7-854F-9F06-7EAC4B0BE8B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985F91BC-B6BE-0D47-9371-6B63A431C740}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3976,7 +3976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4188,10 +4188,6 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -4526,16 +4522,16 @@
       </c>
     </row>
     <row r="4" spans="1:25" ht="16">
-      <c r="A4" s="81" t="s">
+      <c r="A4" s="3" t="s">
         <v>1051</v>
       </c>
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="3" t="s">
         <v>1052</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="3" t="s">
         <v>1053</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="1" t="s">
         <v>1051</v>
       </c>
     </row>
@@ -5684,7 +5680,7 @@
         <v>1036</v>
       </c>
       <c r="B39" s="3"/>
-      <c r="C39" s="3" t="s">
+      <c r="C39" s="50" t="s">
         <v>1037</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -6092,7 +6088,7 @@
         <v>935</v>
       </c>
       <c r="B51" s="3"/>
-      <c r="C51" s="3" t="s">
+      <c r="C51" s="50" t="s">
         <v>936</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -10026,13 +10022,13 @@
       <c r="Y166" s="1"/>
     </row>
     <row r="167" spans="1:25" ht="15" customHeight="1">
-      <c r="A167" s="83" t="s">
+      <c r="A167" s="81" t="s">
         <v>1096</v>
       </c>
       <c r="C167" t="s">
         <v>1097</v>
       </c>
-      <c r="D167" s="83" t="s">
+      <c r="D167" s="81" t="s">
         <v>1096</v>
       </c>
     </row>
@@ -10696,7 +10692,7 @@
       <c r="B187" s="5" t="s">
         <v>1103</v>
       </c>
-      <c r="C187" s="84" t="s">
+      <c r="C187" s="82" t="s">
         <v>1104</v>
       </c>
       <c r="D187" s="5" t="s">
@@ -10731,7 +10727,7 @@
       <c r="B188" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="C188" s="84" t="s">
+      <c r="C188" s="82" t="s">
         <v>1106</v>
       </c>
       <c r="D188" s="5" t="s">
@@ -13513,7 +13509,7 @@
       <c r="Y269" s="2"/>
     </row>
     <row r="270" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A270" s="85" t="s">
+      <c r="A270" s="83" t="s">
         <v>1128</v>
       </c>
       <c r="B270" s="7"/>
@@ -16066,7 +16062,7 @@
       <c r="Y344" s="1"/>
     </row>
     <row r="345" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A345" s="83" t="s">
+      <c r="A345" s="81" t="s">
         <v>1140</v>
       </c>
       <c r="B345" s="13" t="s">
@@ -16101,16 +16097,16 @@
       <c r="Y345" s="1"/>
     </row>
     <row r="346" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A346" s="86" t="s">
+      <c r="A346" s="84" t="s">
         <v>1143</v>
       </c>
-      <c r="B346" s="87" t="s">
+      <c r="B346" s="85" t="s">
         <v>1142</v>
       </c>
-      <c r="C346" s="88" t="s">
+      <c r="C346" s="86" t="s">
         <v>1144</v>
       </c>
-      <c r="D346" s="87" t="s">
+      <c r="D346" s="85" t="s">
         <v>1143</v>
       </c>
       <c r="E346" s="1"/>
@@ -23664,11 +23660,13 @@
     <hyperlink ref="C187" r:id="rId263" xr:uid="{3DD3F81F-9B00-6C41-B9BD-0B246E4511FC}"/>
     <hyperlink ref="C246" r:id="rId264" xr:uid="{2653430D-3B53-3342-82F4-5C182DA7B834}"/>
     <hyperlink ref="C143" r:id="rId265" xr:uid="{A86712C1-CF60-EC43-ACC0-2F9F008D6A13}"/>
+    <hyperlink ref="C39" r:id="rId266" xr:uid="{DEDBA11F-1236-FB46-9BF5-3341C3B4F82F}"/>
+    <hyperlink ref="C51" r:id="rId267" xr:uid="{A2CD9817-DB83-EB44-B2B9-3529BB5D6BE5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId266"/>
+    <tablePart r:id="rId268"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445854C3-4917-F44C-812E-DF991697CF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EA9C40-2B38-EC4E-A372-7E2BC4100B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3997,7 +3997,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4221,6 +4221,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -4561,7 +4567,7 @@
         <v>1193</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="50" t="s">
         <v>1194</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -7483,7 +7489,7 @@
         <v>1195</v>
       </c>
       <c r="B92" s="7"/>
-      <c r="C92" s="8" t="s">
+      <c r="C92" s="80" t="s">
         <v>1196</v>
       </c>
       <c r="D92" s="7" t="s">
@@ -8023,7 +8029,7 @@
         <v>1197</v>
       </c>
       <c r="B108" s="5"/>
-      <c r="C108" s="20" t="s">
+      <c r="C108" s="87" t="s">
         <v>1077</v>
       </c>
       <c r="D108" s="5" t="s">
@@ -10551,7 +10557,7 @@
       <c r="A183" s="7" t="s">
         <v>1101</v>
       </c>
-      <c r="C183" s="8" t="s">
+      <c r="C183" s="80" t="s">
         <v>1100</v>
       </c>
       <c r="D183" s="7" t="s">
@@ -15797,7 +15803,7 @@
       <c r="B337" s="13" t="s">
         <v>1199</v>
       </c>
-      <c r="C337" s="41" t="s">
+      <c r="C337" s="88" t="s">
         <v>1200</v>
       </c>
       <c r="D337" s="13" t="s">
@@ -23764,11 +23770,16 @@
     <hyperlink ref="C145" r:id="rId265" xr:uid="{A86712C1-CF60-EC43-ACC0-2F9F008D6A13}"/>
     <hyperlink ref="C40" r:id="rId266" xr:uid="{DEDBA11F-1236-FB46-9BF5-3341C3B4F82F}"/>
     <hyperlink ref="C52" r:id="rId267" xr:uid="{A2CD9817-DB83-EB44-B2B9-3529BB5D6BE5}"/>
+    <hyperlink ref="C5" r:id="rId268" xr:uid="{7D5C79DD-2090-AE42-8950-23F80385F704}"/>
+    <hyperlink ref="C92" r:id="rId269" xr:uid="{6FC99DC1-4D16-F748-9C57-B02E3B5B7ACB}"/>
+    <hyperlink ref="C108" r:id="rId270" xr:uid="{ED9FF9E1-0C2B-0E44-A3EF-F61085E02321}"/>
+    <hyperlink ref="C183" r:id="rId271" xr:uid="{525BDD05-8A3F-424A-B398-414EBECB8EF0}"/>
+    <hyperlink ref="C337" r:id="rId272" xr:uid="{220744C9-5318-7F48-8555-FABFF8F9D26F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId268"/>
+    <tablePart r:id="rId273"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7EA9C40-2B38-EC4E-A372-7E2BC4100B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DC3306-8604-0142-870E-30D385E51F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="1201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1203">
   <si>
     <t>Name</t>
   </si>
@@ -3631,6 +3631,12 @@
   </si>
   <si>
     <t>https://www.geonames.org/1027190/save.html</t>
+  </si>
+  <si>
+    <t>Prebilovci</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/3192571/prebilovci.html</t>
   </si>
 </sst>
 </file>
@@ -4279,9 +4285,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D447" headerRowCount="0">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D447">
-    <sortCondition ref="D447"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A3:D448" headerRowCount="0">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:D448">
+    <sortCondition ref="D448"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
@@ -4491,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:Y1311"/>
+  <dimension ref="A2:Y1312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
@@ -14536,17 +14542,15 @@
       <c r="Y299" s="2"/>
     </row>
     <row r="300" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A300" s="9" t="s">
-        <v>550</v>
-      </c>
-      <c r="B300" s="9" t="s">
-        <v>551</v>
-      </c>
-      <c r="C300" s="33" t="s">
-        <v>552</v>
-      </c>
-      <c r="D300" s="34" t="s">
-        <v>550</v>
+      <c r="A300" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B300" s="3"/>
+      <c r="C300" s="12" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>1201</v>
       </c>
       <c r="E300" s="2"/>
       <c r="F300" s="2"/>
@@ -14572,12 +14576,16 @@
     </row>
     <row r="301" spans="1:25" ht="15.75" customHeight="1">
       <c r="A301" s="9" t="s">
-        <v>905</v>
-      </c>
-      <c r="B301" s="9"/>
-      <c r="C301" s="33"/>
+        <v>550</v>
+      </c>
+      <c r="B301" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="C301" s="33" t="s">
+        <v>552</v>
+      </c>
       <c r="D301" s="34" t="s">
-        <v>905</v>
+        <v>550</v>
       </c>
       <c r="E301" s="2"/>
       <c r="F301" s="2"/>
@@ -14603,14 +14611,12 @@
     </row>
     <row r="302" spans="1:25" ht="15.75" customHeight="1">
       <c r="A302" s="9" t="s">
-        <v>1129</v>
+        <v>905</v>
       </c>
       <c r="B302" s="9"/>
-      <c r="C302" s="33" t="s">
-        <v>1128</v>
-      </c>
+      <c r="C302" s="33"/>
       <c r="D302" s="34" t="s">
-        <v>1129</v>
+        <v>905</v>
       </c>
       <c r="E302" s="2"/>
       <c r="F302" s="2"/>
@@ -14635,15 +14641,15 @@
       <c r="Y302" s="2"/>
     </row>
     <row r="303" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A303" s="13" t="s">
-        <v>553</v>
-      </c>
-      <c r="B303" s="13"/>
-      <c r="C303" s="40" t="s">
-        <v>554</v>
-      </c>
-      <c r="D303" s="41" t="s">
-        <v>555</v>
+      <c r="A303" s="9" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B303" s="9"/>
+      <c r="C303" s="33" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D303" s="34" t="s">
+        <v>1129</v>
       </c>
       <c r="E303" s="2"/>
       <c r="F303" s="2"/>
@@ -14668,17 +14674,15 @@
       <c r="Y303" s="2"/>
     </row>
     <row r="304" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A304" s="9" t="s">
-        <v>556</v>
-      </c>
-      <c r="B304" s="9" t="s">
-        <v>557</v>
-      </c>
-      <c r="C304" s="42" t="s">
-        <v>558</v>
-      </c>
-      <c r="D304" s="34" t="s">
-        <v>556</v>
+      <c r="A304" s="13" t="s">
+        <v>553</v>
+      </c>
+      <c r="B304" s="13"/>
+      <c r="C304" s="40" t="s">
+        <v>554</v>
+      </c>
+      <c r="D304" s="41" t="s">
+        <v>555</v>
       </c>
       <c r="E304" s="2"/>
       <c r="F304" s="2"/>
@@ -14704,14 +14708,16 @@
     </row>
     <row r="305" spans="1:25" ht="15.75" customHeight="1">
       <c r="A305" s="9" t="s">
-        <v>562</v>
-      </c>
-      <c r="B305" s="9"/>
-      <c r="C305" s="34" t="s">
-        <v>563</v>
-      </c>
-      <c r="D305" s="9" t="s">
-        <v>564</v>
+        <v>556</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="C305" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="D305" s="34" t="s">
+        <v>556</v>
       </c>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
@@ -14737,16 +14743,14 @@
     </row>
     <row r="306" spans="1:25" ht="15.75" customHeight="1">
       <c r="A306" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="B306" s="9" t="s">
-        <v>566</v>
-      </c>
+        <v>562</v>
+      </c>
+      <c r="B306" s="9"/>
       <c r="C306" s="34" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="D306" s="9" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="E306" s="2"/>
       <c r="F306" s="2"/>
@@ -14771,17 +14775,17 @@
       <c r="Y306" s="2"/>
     </row>
     <row r="307" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A307" s="43" t="s">
-        <v>569</v>
-      </c>
-      <c r="B307" s="43" t="s">
-        <v>333</v>
-      </c>
-      <c r="C307" s="44" t="s">
-        <v>334</v>
-      </c>
-      <c r="D307" s="43" t="s">
-        <v>569</v>
+      <c r="A307" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="B307" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C307" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="D307" s="9" t="s">
+        <v>568</v>
       </c>
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
@@ -14807,14 +14811,16 @@
     </row>
     <row r="308" spans="1:25" ht="15.75" customHeight="1">
       <c r="A308" s="43" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B308" s="43"/>
+        <v>569</v>
+      </c>
+      <c r="B308" s="43" t="s">
+        <v>333</v>
+      </c>
       <c r="C308" s="44" t="s">
-        <v>1131</v>
+        <v>334</v>
       </c>
       <c r="D308" s="43" t="s">
-        <v>1130</v>
+        <v>569</v>
       </c>
       <c r="E308" s="2"/>
       <c r="F308" s="2"/>
@@ -14839,15 +14845,15 @@
       <c r="Y308" s="2"/>
     </row>
     <row r="309" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A309" s="3" t="s">
-        <v>1000</v>
-      </c>
-      <c r="B309" s="3"/>
-      <c r="C309" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>1000</v>
+      <c r="A309" s="43" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B309" s="43"/>
+      <c r="C309" s="44" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D309" s="43" t="s">
+        <v>1130</v>
       </c>
       <c r="E309" s="2"/>
       <c r="F309" s="2"/>
@@ -14872,17 +14878,15 @@
       <c r="Y309" s="2"/>
     </row>
     <row r="310" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A310" s="9" t="s">
-        <v>570</v>
-      </c>
-      <c r="B310" s="9" t="s">
-        <v>571</v>
-      </c>
-      <c r="C310" s="34" t="s">
-        <v>572</v>
-      </c>
-      <c r="D310" s="9" t="s">
-        <v>570</v>
+      <c r="A310" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B310" s="3"/>
+      <c r="C310" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D310" s="1" t="s">
+        <v>1000</v>
       </c>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
@@ -14907,17 +14911,17 @@
       <c r="Y310" s="2"/>
     </row>
     <row r="311" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A311" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="B311" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="C311" s="53" t="s">
-        <v>908</v>
-      </c>
-      <c r="D311" s="7" t="s">
-        <v>906</v>
+      <c r="A311" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="B311" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="C311" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="D311" s="9" t="s">
+        <v>570</v>
       </c>
       <c r="E311" s="2"/>
       <c r="F311" s="2"/>
@@ -14942,16 +14946,16 @@
       <c r="Y311" s="2"/>
     </row>
     <row r="312" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A312" s="3" t="s">
+      <c r="A312" s="7" t="s">
         <v>906</v>
       </c>
-      <c r="B312" s="3" t="s">
+      <c r="B312" s="7" t="s">
         <v>907</v>
       </c>
-      <c r="C312" s="3" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D312" s="1" t="s">
+      <c r="C312" s="53" t="s">
+        <v>908</v>
+      </c>
+      <c r="D312" s="7" t="s">
         <v>906</v>
       </c>
       <c r="E312" s="2"/>
@@ -14978,16 +14982,16 @@
     </row>
     <row r="313" spans="1:25" ht="15.75" customHeight="1">
       <c r="A313" s="3" t="s">
-        <v>573</v>
+        <v>906</v>
       </c>
       <c r="B313" s="3" t="s">
-        <v>842</v>
-      </c>
-      <c r="C313" s="4" t="s">
-        <v>843</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>574</v>
+        <v>907</v>
+      </c>
+      <c r="C313" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D313" s="1" t="s">
+        <v>906</v>
       </c>
       <c r="E313" s="2"/>
       <c r="F313" s="2"/>
@@ -15012,50 +15016,50 @@
       <c r="Y313" s="2"/>
     </row>
     <row r="314" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A314" s="7" t="s">
+      <c r="A314" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="E314" s="2"/>
+      <c r="F314" s="2"/>
+      <c r="G314" s="2"/>
+      <c r="H314" s="2"/>
+      <c r="I314" s="2"/>
+      <c r="J314" s="2"/>
+      <c r="K314" s="2"/>
+      <c r="L314" s="2"/>
+      <c r="M314" s="2"/>
+      <c r="N314" s="2"/>
+      <c r="O314" s="2"/>
+      <c r="P314" s="2"/>
+      <c r="Q314" s="2"/>
+      <c r="R314" s="2"/>
+      <c r="S314" s="2"/>
+      <c r="T314" s="2"/>
+      <c r="U314" s="2"/>
+      <c r="V314" s="2"/>
+      <c r="W314" s="2"/>
+      <c r="X314" s="2"/>
+      <c r="Y314" s="2"/>
+    </row>
+    <row r="315" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A315" s="7" t="s">
         <v>575</v>
       </c>
-      <c r="B314" s="7"/>
-      <c r="C314" s="8" t="s">
+      <c r="B315" s="7"/>
+      <c r="C315" s="8" t="s">
         <v>576</v>
       </c>
-      <c r="D314" s="7" t="s">
+      <c r="D315" s="7" t="s">
         <v>577</v>
-      </c>
-      <c r="E314" s="1"/>
-      <c r="F314" s="1"/>
-      <c r="G314" s="1"/>
-      <c r="H314" s="1"/>
-      <c r="I314" s="1"/>
-      <c r="J314" s="1"/>
-      <c r="K314" s="1"/>
-      <c r="L314" s="1"/>
-      <c r="M314" s="1"/>
-      <c r="N314" s="1"/>
-      <c r="O314" s="1"/>
-      <c r="P314" s="1"/>
-      <c r="Q314" s="1"/>
-      <c r="R314" s="1"/>
-      <c r="S314" s="1"/>
-      <c r="T314" s="1"/>
-      <c r="U314" s="1"/>
-      <c r="V314" s="1"/>
-      <c r="W314" s="1"/>
-      <c r="X314" s="1"/>
-      <c r="Y314" s="1"/>
-    </row>
-    <row r="315" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A315" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="B315" s="5" t="s">
-        <v>579</v>
-      </c>
-      <c r="C315" s="6" t="s">
-        <v>580</v>
-      </c>
-      <c r="D315" s="5" t="s">
-        <v>578</v>
       </c>
       <c r="E315" s="1"/>
       <c r="F315" s="1"/>
@@ -15080,17 +15084,17 @@
       <c r="Y315" s="1"/>
     </row>
     <row r="316" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A316" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="B316" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="C316" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="D316" s="3" t="s">
-        <v>581</v>
+      <c r="A316" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>578</v>
       </c>
       <c r="E316" s="1"/>
       <c r="F316" s="1"/>
@@ -15115,15 +15119,17 @@
       <c r="Y316" s="1"/>
     </row>
     <row r="317" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A317" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="B317" s="7"/>
-      <c r="C317" s="53" t="s">
-        <v>910</v>
-      </c>
-      <c r="D317" s="7" t="s">
-        <v>909</v>
+      <c r="A317" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="C317" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>581</v>
       </c>
       <c r="E317" s="1"/>
       <c r="F317" s="1"/>
@@ -15149,49 +15155,47 @@
     </row>
     <row r="318" spans="1:25" ht="15.75" customHeight="1">
       <c r="A318" s="7" t="s">
-        <v>584</v>
+        <v>909</v>
       </c>
       <c r="B318" s="7"/>
-      <c r="C318" s="29" t="s">
-        <v>585</v>
+      <c r="C318" s="53" t="s">
+        <v>910</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>584</v>
-      </c>
-      <c r="E318" s="2"/>
-      <c r="F318" s="2"/>
-      <c r="G318" s="2"/>
-      <c r="H318" s="2"/>
-      <c r="I318" s="2"/>
-      <c r="J318" s="2"/>
-      <c r="K318" s="2"/>
-      <c r="L318" s="2"/>
-      <c r="M318" s="2"/>
-      <c r="N318" s="2"/>
-      <c r="O318" s="2"/>
-      <c r="P318" s="2"/>
-      <c r="Q318" s="2"/>
-      <c r="R318" s="2"/>
-      <c r="S318" s="2"/>
-      <c r="T318" s="2"/>
-      <c r="U318" s="2"/>
-      <c r="V318" s="2"/>
-      <c r="W318" s="2"/>
-      <c r="X318" s="2"/>
-      <c r="Y318" s="2"/>
+        <v>909</v>
+      </c>
+      <c r="E318" s="1"/>
+      <c r="F318" s="1"/>
+      <c r="G318" s="1"/>
+      <c r="H318" s="1"/>
+      <c r="I318" s="1"/>
+      <c r="J318" s="1"/>
+      <c r="K318" s="1"/>
+      <c r="L318" s="1"/>
+      <c r="M318" s="1"/>
+      <c r="N318" s="1"/>
+      <c r="O318" s="1"/>
+      <c r="P318" s="1"/>
+      <c r="Q318" s="1"/>
+      <c r="R318" s="1"/>
+      <c r="S318" s="1"/>
+      <c r="T318" s="1"/>
+      <c r="U318" s="1"/>
+      <c r="V318" s="1"/>
+      <c r="W318" s="1"/>
+      <c r="X318" s="1"/>
+      <c r="Y318" s="1"/>
     </row>
     <row r="319" spans="1:25" ht="15.75" customHeight="1">
       <c r="A319" s="7" t="s">
-        <v>589</v>
-      </c>
-      <c r="B319" s="7" t="s">
-        <v>590</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="B319" s="7"/>
       <c r="C319" s="29" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="E319" s="2"/>
       <c r="F319" s="2"/>
@@ -15216,17 +15220,17 @@
       <c r="Y319" s="2"/>
     </row>
     <row r="320" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A320" s="3" t="s">
-        <v>1003</v>
-      </c>
-      <c r="B320" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C320" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>1003</v>
+      <c r="A320" s="7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C320" s="29" t="s">
+        <v>591</v>
+      </c>
+      <c r="D320" s="7" t="s">
+        <v>592</v>
       </c>
       <c r="E320" s="2"/>
       <c r="F320" s="2"/>
@@ -15251,17 +15255,17 @@
       <c r="Y320" s="2"/>
     </row>
     <row r="321" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A321" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B321" s="5" t="s">
-        <v>587</v>
-      </c>
-      <c r="C321" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="D321" s="5" t="s">
-        <v>586</v>
+      <c r="A321" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C321" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D321" s="1" t="s">
+        <v>1003</v>
       </c>
       <c r="E321" s="2"/>
       <c r="F321" s="2"/>
@@ -15287,14 +15291,16 @@
     </row>
     <row r="322" spans="1:25" ht="15.75" customHeight="1">
       <c r="A322" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B322" s="5"/>
+        <v>586</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>587</v>
+      </c>
       <c r="C322" s="6" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="E322" s="2"/>
       <c r="F322" s="2"/>
@@ -15319,15 +15325,15 @@
       <c r="Y322" s="2"/>
     </row>
     <row r="323" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A323" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="B323" s="3"/>
-      <c r="C323" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>595</v>
+      <c r="A323" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="B323" s="5"/>
+      <c r="C323" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D323" s="5" t="s">
+        <v>593</v>
       </c>
       <c r="E323" s="2"/>
       <c r="F323" s="2"/>
@@ -15352,17 +15358,15 @@
       <c r="Y323" s="2"/>
     </row>
     <row r="324" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A324" s="5" t="s">
-        <v>597</v>
-      </c>
-      <c r="B324" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="C324" s="30" t="s">
-        <v>599</v>
-      </c>
-      <c r="D324" s="5" t="s">
-        <v>600</v>
+      <c r="A324" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="B324" s="3"/>
+      <c r="C324" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>595</v>
       </c>
       <c r="E324" s="2"/>
       <c r="F324" s="2"/>
@@ -15388,14 +15392,16 @@
     </row>
     <row r="325" spans="1:25" ht="15.75" customHeight="1">
       <c r="A325" s="5" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B325" s="5"/>
+        <v>597</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>598</v>
+      </c>
       <c r="C325" s="30" t="s">
-        <v>1133</v>
+        <v>599</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>1134</v>
+        <v>600</v>
       </c>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
@@ -15420,15 +15426,15 @@
       <c r="Y325" s="2"/>
     </row>
     <row r="326" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A326" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B326" s="3"/>
-      <c r="C326" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>601</v>
+      <c r="A326" s="5" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B326" s="5"/>
+      <c r="C326" s="30" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>1134</v>
       </c>
       <c r="E326" s="2"/>
       <c r="F326" s="2"/>
@@ -15454,16 +15460,14 @@
     </row>
     <row r="327" spans="1:25" ht="15.75" customHeight="1">
       <c r="A327" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="B327" s="3" t="s">
-        <v>604</v>
-      </c>
+        <v>601</v>
+      </c>
+      <c r="B327" s="3"/>
       <c r="C327" s="3" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>606</v>
+        <v>601</v>
       </c>
       <c r="E327" s="2"/>
       <c r="F327" s="2"/>
@@ -15489,16 +15493,16 @@
     </row>
     <row r="328" spans="1:25" ht="15.75" customHeight="1">
       <c r="A328" s="3" t="s">
-        <v>1136</v>
+        <v>603</v>
       </c>
       <c r="B328" s="3" t="s">
-        <v>1135</v>
+        <v>604</v>
       </c>
       <c r="C328" s="3" t="s">
-        <v>1137</v>
+        <v>605</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>1136</v>
+        <v>606</v>
       </c>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
@@ -15523,17 +15527,17 @@
       <c r="Y328" s="2"/>
     </row>
     <row r="329" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A329" s="9" t="s">
-        <v>607</v>
-      </c>
-      <c r="B329" s="9" t="s">
-        <v>608</v>
-      </c>
-      <c r="C329" s="10" t="s">
-        <v>609</v>
-      </c>
-      <c r="D329" s="9" t="s">
-        <v>607</v>
+      <c r="A329" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C329" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>1136</v>
       </c>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
@@ -15559,14 +15563,16 @@
     </row>
     <row r="330" spans="1:25" ht="15.75" customHeight="1">
       <c r="A330" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="B330" s="9"/>
+        <v>607</v>
+      </c>
+      <c r="B330" s="9" t="s">
+        <v>608</v>
+      </c>
       <c r="C330" s="10" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D330" s="9" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E330" s="2"/>
       <c r="F330" s="2"/>
@@ -15592,14 +15598,14 @@
     </row>
     <row r="331" spans="1:25" ht="15.75" customHeight="1">
       <c r="A331" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B331" s="9"/>
-      <c r="C331" s="11" t="s">
-        <v>613</v>
+      <c r="C331" s="10" t="s">
+        <v>611</v>
       </c>
       <c r="D331" s="9" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E331" s="2"/>
       <c r="F331" s="2"/>
@@ -15624,52 +15630,50 @@
       <c r="Y331" s="2"/>
     </row>
     <row r="332" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A332" s="3" t="s">
+      <c r="A332" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="B332" s="9"/>
+      <c r="C332" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="D332" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="E332" s="2"/>
+      <c r="F332" s="2"/>
+      <c r="G332" s="2"/>
+      <c r="H332" s="2"/>
+      <c r="I332" s="2"/>
+      <c r="J332" s="2"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="2"/>
+      <c r="M332" s="2"/>
+      <c r="N332" s="2"/>
+      <c r="O332" s="2"/>
+      <c r="P332" s="2"/>
+      <c r="Q332" s="2"/>
+      <c r="R332" s="2"/>
+      <c r="S332" s="2"/>
+      <c r="T332" s="2"/>
+      <c r="U332" s="2"/>
+      <c r="V332" s="2"/>
+      <c r="W332" s="2"/>
+      <c r="X332" s="2"/>
+      <c r="Y332" s="2"/>
+    </row>
+    <row r="333" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A333" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B332" s="3" t="s">
+      <c r="B333" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="C332" s="3" t="s">
+      <c r="C333" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="D332" s="3" t="s">
+      <c r="D333" s="3" t="s">
         <v>614</v>
-      </c>
-      <c r="E332" s="1"/>
-      <c r="F332" s="1"/>
-      <c r="G332" s="1"/>
-      <c r="H332" s="1"/>
-      <c r="I332" s="1"/>
-      <c r="J332" s="1"/>
-      <c r="K332" s="1"/>
-      <c r="L332" s="1"/>
-      <c r="M332" s="1"/>
-      <c r="N332" s="1"/>
-      <c r="O332" s="1"/>
-      <c r="P332" s="1"/>
-      <c r="Q332" s="1"/>
-      <c r="R332" s="1"/>
-      <c r="S332" s="1"/>
-      <c r="T332" s="1"/>
-      <c r="U332" s="1"/>
-      <c r="V332" s="1"/>
-      <c r="W332" s="1"/>
-      <c r="X332" s="1"/>
-      <c r="Y332" s="1"/>
-    </row>
-    <row r="333" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A333" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="B333" s="7" t="s">
-        <v>618</v>
-      </c>
-      <c r="C333" s="29" t="s">
-        <v>619</v>
-      </c>
-      <c r="D333" s="7" t="s">
-        <v>620</v>
       </c>
       <c r="E333" s="1"/>
       <c r="F333" s="1"/>
@@ -15694,17 +15698,17 @@
       <c r="Y333" s="1"/>
     </row>
     <row r="334" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A334" s="9" t="s">
-        <v>621</v>
-      </c>
-      <c r="B334" s="9" t="s">
-        <v>622</v>
-      </c>
-      <c r="C334" s="16" t="s">
-        <v>623</v>
-      </c>
-      <c r="D334" s="34" t="s">
-        <v>624</v>
+      <c r="A334" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="B334" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="C334" s="29" t="s">
+        <v>619</v>
+      </c>
+      <c r="D334" s="7" t="s">
+        <v>620</v>
       </c>
       <c r="E334" s="1"/>
       <c r="F334" s="1"/>
@@ -15729,17 +15733,17 @@
       <c r="Y334" s="1"/>
     </row>
     <row r="335" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A335" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="B335" s="13" t="s">
-        <v>625</v>
-      </c>
-      <c r="C335" s="41" t="s">
-        <v>626</v>
-      </c>
-      <c r="D335" s="13" t="s">
-        <v>625</v>
+      <c r="A335" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="B335" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="C335" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="D335" s="34" t="s">
+        <v>624</v>
       </c>
       <c r="E335" s="1"/>
       <c r="F335" s="1"/>
@@ -15765,14 +15769,16 @@
     </row>
     <row r="336" spans="1:25" ht="15.75" customHeight="1">
       <c r="A336" s="13" t="s">
-        <v>627</v>
-      </c>
-      <c r="B336" s="13"/>
+        <v>625</v>
+      </c>
+      <c r="B336" s="13" t="s">
+        <v>625</v>
+      </c>
       <c r="C336" s="41" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D336" s="13" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E336" s="1"/>
       <c r="F336" s="1"/>
@@ -15798,16 +15804,14 @@
     </row>
     <row r="337" spans="1:25" ht="15.75" customHeight="1">
       <c r="A337" s="13" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B337" s="13" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C337" s="88" t="s">
-        <v>1200</v>
+        <v>627</v>
+      </c>
+      <c r="B337" s="13"/>
+      <c r="C337" s="41" t="s">
+        <v>628</v>
       </c>
       <c r="D337" s="13" t="s">
-        <v>1199</v>
+        <v>627</v>
       </c>
       <c r="E337" s="1"/>
       <c r="F337" s="1"/>
@@ -15832,83 +15836,85 @@
       <c r="Y337" s="1"/>
     </row>
     <row r="338" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A338" s="9" t="s">
+      <c r="A338" s="13" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B338" s="13" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C338" s="88" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D338" s="13" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E338" s="1"/>
+      <c r="F338" s="1"/>
+      <c r="G338" s="1"/>
+      <c r="H338" s="1"/>
+      <c r="I338" s="1"/>
+      <c r="J338" s="1"/>
+      <c r="K338" s="1"/>
+      <c r="L338" s="1"/>
+      <c r="M338" s="1"/>
+      <c r="N338" s="1"/>
+      <c r="O338" s="1"/>
+      <c r="P338" s="1"/>
+      <c r="Q338" s="1"/>
+      <c r="R338" s="1"/>
+      <c r="S338" s="1"/>
+      <c r="T338" s="1"/>
+      <c r="U338" s="1"/>
+      <c r="V338" s="1"/>
+      <c r="W338" s="1"/>
+      <c r="X338" s="1"/>
+      <c r="Y338" s="1"/>
+    </row>
+    <row r="339" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A339" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="B338" s="9"/>
-      <c r="C338" s="34" t="s">
+      <c r="B339" s="9"/>
+      <c r="C339" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="D338" s="9" t="s">
+      <c r="D339" s="9" t="s">
         <v>629</v>
       </c>
-      <c r="E338" s="2"/>
-      <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-      <c r="H338" s="2"/>
-      <c r="I338" s="2"/>
-      <c r="J338" s="2"/>
-      <c r="K338" s="2"/>
-      <c r="L338" s="2"/>
-      <c r="M338" s="2"/>
-      <c r="N338" s="2"/>
-      <c r="O338" s="2"/>
-      <c r="P338" s="2"/>
-      <c r="Q338" s="2"/>
-      <c r="R338" s="2"/>
-      <c r="S338" s="2"/>
-      <c r="T338" s="2"/>
-      <c r="U338" s="2"/>
-      <c r="V338" s="2"/>
-      <c r="W338" s="2"/>
-      <c r="X338" s="2"/>
-      <c r="Y338" s="2"/>
-    </row>
-    <row r="339" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A339" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B339" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="C339" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="D339" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="E339" s="1"/>
-      <c r="F339" s="1"/>
-      <c r="G339" s="1"/>
-      <c r="H339" s="1"/>
-      <c r="I339" s="1"/>
-      <c r="J339" s="1"/>
-      <c r="K339" s="1"/>
-      <c r="L339" s="1"/>
-      <c r="M339" s="1"/>
-      <c r="N339" s="1"/>
-      <c r="O339" s="1"/>
-      <c r="P339" s="1"/>
-      <c r="Q339" s="1"/>
-      <c r="R339" s="1"/>
-      <c r="S339" s="1"/>
-      <c r="T339" s="1"/>
-      <c r="U339" s="1"/>
-      <c r="V339" s="1"/>
-      <c r="W339" s="1"/>
-      <c r="X339" s="1"/>
-      <c r="Y339" s="1"/>
+      <c r="E339" s="2"/>
+      <c r="F339" s="2"/>
+      <c r="G339" s="2"/>
+      <c r="H339" s="2"/>
+      <c r="I339" s="2"/>
+      <c r="J339" s="2"/>
+      <c r="K339" s="2"/>
+      <c r="L339" s="2"/>
+      <c r="M339" s="2"/>
+      <c r="N339" s="2"/>
+      <c r="O339" s="2"/>
+      <c r="P339" s="2"/>
+      <c r="Q339" s="2"/>
+      <c r="R339" s="2"/>
+      <c r="S339" s="2"/>
+      <c r="T339" s="2"/>
+      <c r="U339" s="2"/>
+      <c r="V339" s="2"/>
+      <c r="W339" s="2"/>
+      <c r="X339" s="2"/>
+      <c r="Y339" s="2"/>
     </row>
     <row r="340" spans="1:25" ht="15.75" customHeight="1">
       <c r="A340" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="B340" s="3"/>
-      <c r="C340" s="18" t="s">
-        <v>635</v>
+        <v>631</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="C340" s="3" t="s">
+        <v>633</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="E340" s="1"/>
       <c r="F340" s="1"/>
@@ -15934,14 +15940,14 @@
     </row>
     <row r="341" spans="1:25" ht="15.75" customHeight="1">
       <c r="A341" s="3" t="s">
-        <v>1042</v>
+        <v>634</v>
       </c>
       <c r="B341" s="3"/>
-      <c r="C341" s="3" t="s">
-        <v>1043</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>1044</v>
+      <c r="C341" s="18" t="s">
+        <v>635</v>
+      </c>
+      <c r="D341" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="E341" s="1"/>
       <c r="F341" s="1"/>
@@ -15966,48 +15972,46 @@
       <c r="Y341" s="1"/>
     </row>
     <row r="342" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A342" s="9" t="s">
+      <c r="A342" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B342" s="3"/>
+      <c r="C342" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E342" s="1"/>
+      <c r="F342" s="1"/>
+      <c r="G342" s="1"/>
+      <c r="H342" s="1"/>
+      <c r="I342" s="1"/>
+      <c r="J342" s="1"/>
+      <c r="K342" s="1"/>
+      <c r="L342" s="1"/>
+      <c r="M342" s="1"/>
+      <c r="N342" s="1"/>
+      <c r="O342" s="1"/>
+      <c r="P342" s="1"/>
+      <c r="Q342" s="1"/>
+      <c r="R342" s="1"/>
+      <c r="S342" s="1"/>
+      <c r="T342" s="1"/>
+      <c r="U342" s="1"/>
+      <c r="V342" s="1"/>
+      <c r="W342" s="1"/>
+      <c r="X342" s="1"/>
+      <c r="Y342" s="1"/>
+    </row>
+    <row r="343" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A343" s="9" t="s">
         <v>911</v>
       </c>
-      <c r="B342" s="9"/>
-      <c r="C342" s="10"/>
-      <c r="D342" s="9" t="s">
+      <c r="B343" s="9"/>
+      <c r="C343" s="10"/>
+      <c r="D343" s="9" t="s">
         <v>912</v>
-      </c>
-      <c r="E342" s="2"/>
-      <c r="F342" s="2"/>
-      <c r="G342" s="2"/>
-      <c r="H342" s="2"/>
-      <c r="I342" s="2"/>
-      <c r="J342" s="2"/>
-      <c r="K342" s="2"/>
-      <c r="L342" s="2"/>
-      <c r="M342" s="2"/>
-      <c r="N342" s="2"/>
-      <c r="O342" s="2"/>
-      <c r="P342" s="2"/>
-      <c r="Q342" s="2"/>
-      <c r="R342" s="2"/>
-      <c r="S342" s="2"/>
-      <c r="T342" s="2"/>
-      <c r="U342" s="2"/>
-      <c r="V342" s="2"/>
-      <c r="W342" s="2"/>
-      <c r="X342" s="2"/>
-      <c r="Y342" s="2"/>
-    </row>
-    <row r="343" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A343" s="13" t="s">
-        <v>913</v>
-      </c>
-      <c r="B343" s="13" t="s">
-        <v>914</v>
-      </c>
-      <c r="C343" s="68" t="s">
-        <v>915</v>
-      </c>
-      <c r="D343" s="13" t="s">
-        <v>916</v>
       </c>
       <c r="E343" s="2"/>
       <c r="F343" s="2"/>
@@ -16032,50 +16036,52 @@
       <c r="Y343" s="2"/>
     </row>
     <row r="344" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A344" s="9" t="s">
-        <v>637</v>
-      </c>
-      <c r="B344" s="9" t="s">
-        <v>638</v>
-      </c>
-      <c r="C344" s="11" t="s">
-        <v>639</v>
-      </c>
-      <c r="D344" s="9" t="s">
-        <v>640</v>
-      </c>
-      <c r="E344" s="1"/>
-      <c r="F344" s="1"/>
-      <c r="G344" s="1"/>
-      <c r="H344" s="1"/>
-      <c r="I344" s="1"/>
-      <c r="J344" s="1"/>
-      <c r="K344" s="1"/>
-      <c r="L344" s="1"/>
-      <c r="M344" s="1"/>
-      <c r="N344" s="1"/>
-      <c r="O344" s="1"/>
-      <c r="P344" s="1"/>
-      <c r="Q344" s="1"/>
-      <c r="R344" s="1"/>
-      <c r="S344" s="1"/>
-      <c r="T344" s="1"/>
-      <c r="U344" s="1"/>
-      <c r="V344" s="1"/>
-      <c r="W344" s="1"/>
-      <c r="X344" s="1"/>
-      <c r="Y344" s="1"/>
+      <c r="A344" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="B344" s="13" t="s">
+        <v>914</v>
+      </c>
+      <c r="C344" s="68" t="s">
+        <v>915</v>
+      </c>
+      <c r="D344" s="13" t="s">
+        <v>916</v>
+      </c>
+      <c r="E344" s="2"/>
+      <c r="F344" s="2"/>
+      <c r="G344" s="2"/>
+      <c r="H344" s="2"/>
+      <c r="I344" s="2"/>
+      <c r="J344" s="2"/>
+      <c r="K344" s="2"/>
+      <c r="L344" s="2"/>
+      <c r="M344" s="2"/>
+      <c r="N344" s="2"/>
+      <c r="O344" s="2"/>
+      <c r="P344" s="2"/>
+      <c r="Q344" s="2"/>
+      <c r="R344" s="2"/>
+      <c r="S344" s="2"/>
+      <c r="T344" s="2"/>
+      <c r="U344" s="2"/>
+      <c r="V344" s="2"/>
+      <c r="W344" s="2"/>
+      <c r="X344" s="2"/>
+      <c r="Y344" s="2"/>
     </row>
     <row r="345" spans="1:25" ht="15.75" customHeight="1">
       <c r="A345" s="9" t="s">
-        <v>641</v>
-      </c>
-      <c r="B345" s="9"/>
-      <c r="C345" s="10" t="s">
-        <v>642</v>
+        <v>637</v>
+      </c>
+      <c r="B345" s="9" t="s">
+        <v>638</v>
+      </c>
+      <c r="C345" s="11" t="s">
+        <v>639</v>
       </c>
       <c r="D345" s="9" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E345" s="1"/>
       <c r="F345" s="1"/>
@@ -16100,17 +16106,15 @@
       <c r="Y345" s="1"/>
     </row>
     <row r="346" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A346" s="13" t="s">
-        <v>917</v>
-      </c>
-      <c r="B346" s="13" t="s">
-        <v>918</v>
-      </c>
-      <c r="C346" s="68" t="s">
-        <v>919</v>
-      </c>
-      <c r="D346" s="13" t="s">
-        <v>917</v>
+      <c r="A346" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="B346" s="9"/>
+      <c r="C346" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="D346" s="9" t="s">
+        <v>643</v>
       </c>
       <c r="E346" s="1"/>
       <c r="F346" s="1"/>
@@ -16136,16 +16140,16 @@
     </row>
     <row r="347" spans="1:25" ht="15.75" customHeight="1">
       <c r="A347" s="13" t="s">
-        <v>644</v>
+        <v>917</v>
       </c>
       <c r="B347" s="13" t="s">
-        <v>645</v>
-      </c>
-      <c r="C347" s="14" t="s">
-        <v>646</v>
+        <v>918</v>
+      </c>
+      <c r="C347" s="68" t="s">
+        <v>919</v>
       </c>
       <c r="D347" s="13" t="s">
-        <v>644</v>
+        <v>917</v>
       </c>
       <c r="E347" s="1"/>
       <c r="F347" s="1"/>
@@ -16170,17 +16174,17 @@
       <c r="Y347" s="1"/>
     </row>
     <row r="348" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A348" s="81" t="s">
-        <v>1139</v>
+      <c r="A348" s="13" t="s">
+        <v>644</v>
       </c>
       <c r="B348" s="13" t="s">
-        <v>1138</v>
+        <v>645</v>
       </c>
       <c r="C348" s="14" t="s">
-        <v>1140</v>
+        <v>646</v>
       </c>
       <c r="D348" s="13" t="s">
-        <v>1139</v>
+        <v>644</v>
       </c>
       <c r="E348" s="1"/>
       <c r="F348" s="1"/>
@@ -16205,17 +16209,17 @@
       <c r="Y348" s="1"/>
     </row>
     <row r="349" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A349" s="84" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B349" s="85" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C349" s="86" t="s">
-        <v>1143</v>
-      </c>
-      <c r="D349" s="85" t="s">
-        <v>1142</v>
+      <c r="A349" s="81" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B349" s="13" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C349" s="14" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D349" s="13" t="s">
+        <v>1139</v>
       </c>
       <c r="E349" s="1"/>
       <c r="F349" s="1"/>
@@ -16240,15 +16244,17 @@
       <c r="Y349" s="1"/>
     </row>
     <row r="350" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A350" s="9" t="s">
-        <v>647</v>
-      </c>
-      <c r="B350" s="9"/>
-      <c r="C350" s="10" t="s">
-        <v>648</v>
-      </c>
-      <c r="D350" s="9" t="s">
-        <v>647</v>
+      <c r="A350" s="84" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B350" s="85" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C350" s="86" t="s">
+        <v>1143</v>
+      </c>
+      <c r="D350" s="85" t="s">
+        <v>1142</v>
       </c>
       <c r="E350" s="1"/>
       <c r="F350" s="1"/>
@@ -16274,14 +16280,14 @@
     </row>
     <row r="351" spans="1:25" ht="15.75" customHeight="1">
       <c r="A351" s="9" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B351" s="9"/>
-      <c r="C351" s="11" t="s">
-        <v>650</v>
+      <c r="C351" s="10" t="s">
+        <v>648</v>
       </c>
       <c r="D351" s="9" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E351" s="1"/>
       <c r="F351" s="1"/>
@@ -16307,14 +16313,14 @@
     </row>
     <row r="352" spans="1:25" ht="15.75" customHeight="1">
       <c r="A352" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B352" s="9"/>
-      <c r="C352" s="10" t="s">
-        <v>652</v>
+      <c r="C352" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="D352" s="9" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E352" s="1"/>
       <c r="F352" s="1"/>
@@ -16340,14 +16346,14 @@
     </row>
     <row r="353" spans="1:25" ht="15.75" customHeight="1">
       <c r="A353" s="9" t="s">
-        <v>851</v>
+        <v>651</v>
       </c>
       <c r="B353" s="9"/>
       <c r="C353" s="10" t="s">
-        <v>852</v>
+        <v>652</v>
       </c>
       <c r="D353" s="9" t="s">
-        <v>851</v>
+        <v>651</v>
       </c>
       <c r="E353" s="1"/>
       <c r="F353" s="1"/>
@@ -16373,16 +16379,14 @@
     </row>
     <row r="354" spans="1:25" ht="15.75" customHeight="1">
       <c r="A354" s="9" t="s">
-        <v>653</v>
-      </c>
-      <c r="B354" s="9" t="s">
-        <v>654</v>
-      </c>
-      <c r="C354" s="11" t="s">
-        <v>655</v>
+        <v>851</v>
+      </c>
+      <c r="B354" s="9"/>
+      <c r="C354" s="10" t="s">
+        <v>852</v>
       </c>
       <c r="D354" s="9" t="s">
-        <v>653</v>
+        <v>851</v>
       </c>
       <c r="E354" s="1"/>
       <c r="F354" s="1"/>
@@ -16408,14 +16412,16 @@
     </row>
     <row r="355" spans="1:25" ht="15.75" customHeight="1">
       <c r="A355" s="9" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B355" s="9"/>
+        <v>653</v>
+      </c>
+      <c r="B355" s="9" t="s">
+        <v>654</v>
+      </c>
       <c r="C355" s="11" t="s">
-        <v>1145</v>
+        <v>655</v>
       </c>
       <c r="D355" s="9" t="s">
-        <v>1144</v>
+        <v>653</v>
       </c>
       <c r="E355" s="1"/>
       <c r="F355" s="1"/>
@@ -16441,14 +16447,14 @@
     </row>
     <row r="356" spans="1:25" ht="15.75" customHeight="1">
       <c r="A356" s="9" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="B356" s="9"/>
       <c r="C356" s="11" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="D356" s="9" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="E356" s="1"/>
       <c r="F356" s="1"/>
@@ -16474,14 +16480,14 @@
     </row>
     <row r="357" spans="1:25" ht="15.75" customHeight="1">
       <c r="A357" s="9" t="s">
-        <v>656</v>
+        <v>1146</v>
       </c>
       <c r="B357" s="9"/>
-      <c r="C357" s="16" t="s">
-        <v>657</v>
+      <c r="C357" s="11" t="s">
+        <v>1147</v>
       </c>
       <c r="D357" s="9" t="s">
-        <v>656</v>
+        <v>1146</v>
       </c>
       <c r="E357" s="1"/>
       <c r="F357" s="1"/>
@@ -16506,17 +16512,15 @@
       <c r="Y357" s="1"/>
     </row>
     <row r="358" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A358" s="13" t="s">
-        <v>920</v>
-      </c>
-      <c r="B358" s="13" t="s">
-        <v>921</v>
-      </c>
-      <c r="C358" s="68" t="s">
-        <v>922</v>
-      </c>
-      <c r="D358" s="13" t="s">
-        <v>920</v>
+      <c r="A358" s="9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B358" s="9"/>
+      <c r="C358" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="D358" s="9" t="s">
+        <v>656</v>
       </c>
       <c r="E358" s="1"/>
       <c r="F358" s="1"/>
@@ -16542,14 +16546,16 @@
     </row>
     <row r="359" spans="1:25" ht="15.75" customHeight="1">
       <c r="A359" s="13" t="s">
-        <v>1148</v>
-      </c>
-      <c r="B359" s="13"/>
+        <v>920</v>
+      </c>
+      <c r="B359" s="13" t="s">
+        <v>921</v>
+      </c>
       <c r="C359" s="68" t="s">
-        <v>1149</v>
+        <v>922</v>
       </c>
       <c r="D359" s="13" t="s">
-        <v>1148</v>
+        <v>920</v>
       </c>
       <c r="E359" s="1"/>
       <c r="F359" s="1"/>
@@ -16574,17 +16580,15 @@
       <c r="Y359" s="1"/>
     </row>
     <row r="360" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A360" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="B360" s="5" t="s">
-        <v>661</v>
-      </c>
-      <c r="C360" s="30" t="s">
-        <v>662</v>
-      </c>
-      <c r="D360" s="5" t="s">
-        <v>660</v>
+      <c r="A360" s="13" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B360" s="13"/>
+      <c r="C360" s="68" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D360" s="13" t="s">
+        <v>1148</v>
       </c>
       <c r="E360" s="1"/>
       <c r="F360" s="1"/>
@@ -16609,50 +16613,50 @@
       <c r="Y360" s="1"/>
     </row>
     <row r="361" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A361" s="9" t="s">
+      <c r="A361" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="C361" s="30" t="s">
+        <v>662</v>
+      </c>
+      <c r="D361" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="E361" s="1"/>
+      <c r="F361" s="1"/>
+      <c r="G361" s="1"/>
+      <c r="H361" s="1"/>
+      <c r="I361" s="1"/>
+      <c r="J361" s="1"/>
+      <c r="K361" s="1"/>
+      <c r="L361" s="1"/>
+      <c r="M361" s="1"/>
+      <c r="N361" s="1"/>
+      <c r="O361" s="1"/>
+      <c r="P361" s="1"/>
+      <c r="Q361" s="1"/>
+      <c r="R361" s="1"/>
+      <c r="S361" s="1"/>
+      <c r="T361" s="1"/>
+      <c r="U361" s="1"/>
+      <c r="V361" s="1"/>
+      <c r="W361" s="1"/>
+      <c r="X361" s="1"/>
+      <c r="Y361" s="1"/>
+    </row>
+    <row r="362" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A362" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="B361" s="9"/>
-      <c r="C361" s="10" t="s">
+      <c r="B362" s="9"/>
+      <c r="C362" s="10" t="s">
         <v>659</v>
       </c>
-      <c r="D361" s="9" t="s">
+      <c r="D362" s="9" t="s">
         <v>658</v>
-      </c>
-      <c r="E361" s="2"/>
-      <c r="F361" s="2"/>
-      <c r="G361" s="2"/>
-      <c r="H361" s="2"/>
-      <c r="I361" s="2"/>
-      <c r="J361" s="2"/>
-      <c r="K361" s="2"/>
-      <c r="L361" s="2"/>
-      <c r="M361" s="2"/>
-      <c r="N361" s="2"/>
-      <c r="O361" s="2"/>
-      <c r="P361" s="2"/>
-      <c r="Q361" s="2"/>
-      <c r="R361" s="2"/>
-      <c r="S361" s="2"/>
-      <c r="T361" s="2"/>
-      <c r="U361" s="2"/>
-      <c r="V361" s="2"/>
-      <c r="W361" s="2"/>
-      <c r="X361" s="2"/>
-      <c r="Y361" s="2"/>
-    </row>
-    <row r="362" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A362" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="B362" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="C362" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="D362" s="1" t="s">
-        <v>984</v>
       </c>
       <c r="E362" s="2"/>
       <c r="F362" s="2"/>
@@ -16678,16 +16682,16 @@
     </row>
     <row r="363" spans="1:25" ht="15.75" customHeight="1">
       <c r="A363" s="3" t="s">
-        <v>1084</v>
+        <v>984</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>1085</v>
+        <v>985</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>1086</v>
+        <v>986</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>1084</v>
+        <v>984</v>
       </c>
       <c r="E363" s="2"/>
       <c r="F363" s="2"/>
@@ -16713,14 +16717,16 @@
     </row>
     <row r="364" spans="1:25" ht="15.75" customHeight="1">
       <c r="A364" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B364" s="3"/>
+        <v>1084</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>1085</v>
+      </c>
       <c r="C364" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="D364" s="3" t="s">
-        <v>665</v>
+        <v>1086</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>1084</v>
       </c>
       <c r="E364" s="2"/>
       <c r="F364" s="2"/>
@@ -16746,49 +16752,49 @@
     </row>
     <row r="365" spans="1:25" ht="15.75" customHeight="1">
       <c r="A365" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B365" s="3" t="s">
-        <v>1007</v>
-      </c>
+        <v>663</v>
+      </c>
+      <c r="B365" s="3"/>
       <c r="C365" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D365" s="1" t="s">
-        <v>1006</v>
-      </c>
-      <c r="E365" s="1"/>
-      <c r="F365" s="1"/>
-      <c r="G365" s="1"/>
-      <c r="H365" s="1"/>
-      <c r="I365" s="1"/>
-      <c r="J365" s="1"/>
-      <c r="K365" s="1"/>
-      <c r="L365" s="1"/>
-      <c r="M365" s="1"/>
-      <c r="N365" s="1"/>
-      <c r="O365" s="1"/>
-      <c r="P365" s="1"/>
-      <c r="Q365" s="1"/>
-      <c r="R365" s="1"/>
-      <c r="S365" s="1"/>
-      <c r="T365" s="1"/>
-      <c r="U365" s="1"/>
-      <c r="V365" s="1"/>
-      <c r="W365" s="1"/>
-      <c r="X365" s="1"/>
-      <c r="Y365" s="1"/>
+        <v>664</v>
+      </c>
+      <c r="D365" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="E365" s="2"/>
+      <c r="F365" s="2"/>
+      <c r="G365" s="2"/>
+      <c r="H365" s="2"/>
+      <c r="I365" s="2"/>
+      <c r="J365" s="2"/>
+      <c r="K365" s="2"/>
+      <c r="L365" s="2"/>
+      <c r="M365" s="2"/>
+      <c r="N365" s="2"/>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2"/>
+      <c r="Q365" s="2"/>
+      <c r="R365" s="2"/>
+      <c r="S365" s="2"/>
+      <c r="T365" s="2"/>
+      <c r="U365" s="2"/>
+      <c r="V365" s="2"/>
+      <c r="W365" s="2"/>
+      <c r="X365" s="2"/>
+      <c r="Y365" s="2"/>
     </row>
     <row r="366" spans="1:25" ht="15.75" customHeight="1">
       <c r="A366" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="B366" s="3"/>
+        <v>1006</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>1007</v>
+      </c>
       <c r="C366" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="D366" s="3" t="s">
-        <v>666</v>
+        <v>1008</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>1006</v>
       </c>
       <c r="E366" s="1"/>
       <c r="F366" s="1"/>
@@ -16813,17 +16819,15 @@
       <c r="Y366" s="1"/>
     </row>
     <row r="367" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A367" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="B367" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="C367" s="45" t="s">
-        <v>675</v>
-      </c>
-      <c r="D367" s="9" t="s">
-        <v>676</v>
+      <c r="A367" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B367" s="3"/>
+      <c r="C367" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="D367" s="3" t="s">
+        <v>666</v>
       </c>
       <c r="E367" s="1"/>
       <c r="F367" s="1"/>
@@ -16848,17 +16852,17 @@
       <c r="Y367" s="1"/>
     </row>
     <row r="368" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A368" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="B368" s="13" t="s">
-        <v>678</v>
-      </c>
-      <c r="C368" s="46" t="s">
-        <v>679</v>
-      </c>
-      <c r="D368" s="13" t="s">
-        <v>680</v>
+      <c r="A368" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B368" s="9" t="s">
+        <v>674</v>
+      </c>
+      <c r="C368" s="45" t="s">
+        <v>675</v>
+      </c>
+      <c r="D368" s="9" t="s">
+        <v>676</v>
       </c>
       <c r="E368" s="1"/>
       <c r="F368" s="1"/>
@@ -16883,17 +16887,17 @@
       <c r="Y368" s="1"/>
     </row>
     <row r="369" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A369" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="B369" s="9" t="s">
-        <v>682</v>
-      </c>
-      <c r="C369" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="D369" s="9" t="s">
-        <v>684</v>
+      <c r="A369" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B369" s="13" t="s">
+        <v>678</v>
+      </c>
+      <c r="C369" s="46" t="s">
+        <v>679</v>
+      </c>
+      <c r="D369" s="13" t="s">
+        <v>680</v>
       </c>
       <c r="E369" s="1"/>
       <c r="F369" s="1"/>
@@ -16918,15 +16922,17 @@
       <c r="Y369" s="1"/>
     </row>
     <row r="370" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A370" s="13" t="s">
-        <v>685</v>
-      </c>
-      <c r="B370" s="13"/>
-      <c r="C370" s="14" t="s">
-        <v>686</v>
-      </c>
-      <c r="D370" s="13" t="s">
-        <v>687</v>
+      <c r="A370" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B370" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="C370" s="10" t="s">
+        <v>683</v>
+      </c>
+      <c r="D370" s="9" t="s">
+        <v>684</v>
       </c>
       <c r="E370" s="1"/>
       <c r="F370" s="1"/>
@@ -16952,14 +16958,14 @@
     </row>
     <row r="371" spans="1:25" ht="15.75" customHeight="1">
       <c r="A371" s="13" t="s">
-        <v>1150</v>
+        <v>685</v>
       </c>
       <c r="B371" s="13"/>
       <c r="C371" s="14" t="s">
-        <v>1151</v>
+        <v>686</v>
       </c>
       <c r="D371" s="13" t="s">
-        <v>1152</v>
+        <v>687</v>
       </c>
       <c r="E371" s="1"/>
       <c r="F371" s="1"/>
@@ -16984,17 +16990,15 @@
       <c r="Y371" s="1"/>
     </row>
     <row r="372" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A372" s="7" t="s">
-        <v>668</v>
-      </c>
-      <c r="B372" s="7" t="s">
-        <v>669</v>
-      </c>
-      <c r="C372" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="D372" s="7" t="s">
-        <v>668</v>
+      <c r="A372" s="13" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B372" s="13"/>
+      <c r="C372" s="14" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D372" s="13" t="s">
+        <v>1152</v>
       </c>
       <c r="E372" s="1"/>
       <c r="F372" s="1"/>
@@ -17019,15 +17023,17 @@
       <c r="Y372" s="1"/>
     </row>
     <row r="373" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A373" s="9" t="s">
-        <v>671</v>
-      </c>
-      <c r="B373" s="9"/>
-      <c r="C373" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="D373" s="9" t="s">
-        <v>671</v>
+      <c r="A373" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="B373" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="C373" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>668</v>
       </c>
       <c r="E373" s="1"/>
       <c r="F373" s="1"/>
@@ -17053,14 +17059,14 @@
     </row>
     <row r="374" spans="1:25" ht="15.75" customHeight="1">
       <c r="A374" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="B374" s="9"/>
-      <c r="C374" s="10" t="s">
-        <v>689</v>
+      <c r="C374" s="11" t="s">
+        <v>672</v>
       </c>
       <c r="D374" s="9" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="E374" s="1"/>
       <c r="F374" s="1"/>
@@ -17086,16 +17092,14 @@
     </row>
     <row r="375" spans="1:25" ht="15.75" customHeight="1">
       <c r="A375" s="9" t="s">
-        <v>690</v>
-      </c>
-      <c r="B375" s="9" t="s">
-        <v>691</v>
-      </c>
-      <c r="C375" s="11" t="s">
-        <v>692</v>
+        <v>688</v>
+      </c>
+      <c r="B375" s="9"/>
+      <c r="C375" s="10" t="s">
+        <v>689</v>
       </c>
       <c r="D375" s="9" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="E375" s="1"/>
       <c r="F375" s="1"/>
@@ -17121,14 +17125,16 @@
     </row>
     <row r="376" spans="1:25" ht="15.75" customHeight="1">
       <c r="A376" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="B376" s="9"/>
-      <c r="C376" s="10" t="s">
-        <v>844</v>
+        <v>690</v>
+      </c>
+      <c r="B376" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="C376" s="11" t="s">
+        <v>692</v>
       </c>
       <c r="D376" s="9" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E376" s="1"/>
       <c r="F376" s="1"/>
@@ -17153,17 +17159,15 @@
       <c r="Y376" s="1"/>
     </row>
     <row r="377" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A377" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="B377" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C377" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>1009</v>
+      <c r="A377" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="B377" s="9"/>
+      <c r="C377" s="10" t="s">
+        <v>844</v>
+      </c>
+      <c r="D377" s="9" t="s">
+        <v>695</v>
       </c>
       <c r="E377" s="1"/>
       <c r="F377" s="1"/>
@@ -17188,15 +17192,17 @@
       <c r="Y377" s="1"/>
     </row>
     <row r="378" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A378" s="13" t="s">
-        <v>696</v>
-      </c>
-      <c r="B378" s="13"/>
-      <c r="C378" s="22" t="s">
-        <v>697</v>
-      </c>
-      <c r="D378" s="13" t="s">
-        <v>696</v>
+      <c r="A378" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C378" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>1009</v>
       </c>
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
@@ -17222,51 +17228,49 @@
     </row>
     <row r="379" spans="1:25" ht="15.75" customHeight="1">
       <c r="A379" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="B379" s="13"/>
+      <c r="C379" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="D379" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="E379" s="1"/>
+      <c r="F379" s="1"/>
+      <c r="G379" s="1"/>
+      <c r="H379" s="1"/>
+      <c r="I379" s="1"/>
+      <c r="J379" s="1"/>
+      <c r="K379" s="1"/>
+      <c r="L379" s="1"/>
+      <c r="M379" s="1"/>
+      <c r="N379" s="1"/>
+      <c r="O379" s="1"/>
+      <c r="P379" s="1"/>
+      <c r="Q379" s="1"/>
+      <c r="R379" s="1"/>
+      <c r="S379" s="1"/>
+      <c r="T379" s="1"/>
+      <c r="U379" s="1"/>
+      <c r="V379" s="1"/>
+      <c r="W379" s="1"/>
+      <c r="X379" s="1"/>
+      <c r="Y379" s="1"/>
+    </row>
+    <row r="380" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A380" s="13" t="s">
         <v>698</v>
       </c>
-      <c r="B379" s="13" t="s">
+      <c r="B380" s="13" t="s">
         <v>699</v>
       </c>
-      <c r="C379" s="14" t="s">
+      <c r="C380" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="D379" s="13" t="s">
+      <c r="D380" s="13" t="s">
         <v>698</v>
-      </c>
-      <c r="E379" s="2"/>
-      <c r="F379" s="2"/>
-      <c r="G379" s="2"/>
-      <c r="H379" s="2"/>
-      <c r="I379" s="2"/>
-      <c r="J379" s="2"/>
-      <c r="K379" s="2"/>
-      <c r="L379" s="2"/>
-      <c r="M379" s="2"/>
-      <c r="N379" s="2"/>
-      <c r="O379" s="2"/>
-      <c r="P379" s="2"/>
-      <c r="Q379" s="2"/>
-      <c r="R379" s="2"/>
-      <c r="S379" s="2"/>
-      <c r="T379" s="2"/>
-      <c r="U379" s="2"/>
-      <c r="V379" s="2"/>
-      <c r="W379" s="2"/>
-      <c r="X379" s="2"/>
-      <c r="Y379" s="2"/>
-    </row>
-    <row r="380" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A380" s="9" t="s">
-        <v>701</v>
-      </c>
-      <c r="B380" s="9" t="s">
-        <v>702</v>
-      </c>
-      <c r="C380" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D380" s="9" t="s">
-        <v>701</v>
       </c>
       <c r="E380" s="2"/>
       <c r="F380" s="2"/>
@@ -17291,52 +17295,52 @@
       <c r="Y380" s="2"/>
     </row>
     <row r="381" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A381" s="3" t="s">
+      <c r="A381" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="B381" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C381" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D381" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="E381" s="2"/>
+      <c r="F381" s="2"/>
+      <c r="G381" s="2"/>
+      <c r="H381" s="2"/>
+      <c r="I381" s="2"/>
+      <c r="J381" s="2"/>
+      <c r="K381" s="2"/>
+      <c r="L381" s="2"/>
+      <c r="M381" s="2"/>
+      <c r="N381" s="2"/>
+      <c r="O381" s="2"/>
+      <c r="P381" s="2"/>
+      <c r="Q381" s="2"/>
+      <c r="R381" s="2"/>
+      <c r="S381" s="2"/>
+      <c r="T381" s="2"/>
+      <c r="U381" s="2"/>
+      <c r="V381" s="2"/>
+      <c r="W381" s="2"/>
+      <c r="X381" s="2"/>
+      <c r="Y381" s="2"/>
+    </row>
+    <row r="382" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A382" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="B381" s="3" t="s">
+      <c r="B382" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="C381" s="3" t="s">
+      <c r="C382" s="3" t="s">
         <v>1014</v>
       </c>
-      <c r="D381" s="1" t="s">
+      <c r="D382" s="1" t="s">
         <v>1012</v>
-      </c>
-      <c r="E381" s="1"/>
-      <c r="F381" s="1"/>
-      <c r="G381" s="1"/>
-      <c r="H381" s="1"/>
-      <c r="I381" s="1"/>
-      <c r="J381" s="1"/>
-      <c r="K381" s="1"/>
-      <c r="L381" s="1"/>
-      <c r="M381" s="1"/>
-      <c r="N381" s="1"/>
-      <c r="O381" s="1"/>
-      <c r="P381" s="1"/>
-      <c r="Q381" s="1"/>
-      <c r="R381" s="1"/>
-      <c r="S381" s="1"/>
-      <c r="T381" s="1"/>
-      <c r="U381" s="1"/>
-      <c r="V381" s="1"/>
-      <c r="W381" s="1"/>
-      <c r="X381" s="1"/>
-      <c r="Y381" s="1"/>
-    </row>
-    <row r="382" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A382" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="B382" s="9" t="s">
-        <v>705</v>
-      </c>
-      <c r="C382" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="D382" s="9" t="s">
-        <v>704</v>
       </c>
       <c r="E382" s="1"/>
       <c r="F382" s="1"/>
@@ -17361,52 +17365,52 @@
       <c r="Y382" s="1"/>
     </row>
     <row r="383" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A383" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="B383" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="C383" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="D383" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="E383" s="2"/>
-      <c r="F383" s="2"/>
-      <c r="G383" s="2"/>
-      <c r="H383" s="2"/>
-      <c r="I383" s="2"/>
-      <c r="J383" s="2"/>
-      <c r="K383" s="2"/>
-      <c r="L383" s="2"/>
-      <c r="M383" s="2"/>
-      <c r="N383" s="2"/>
-      <c r="O383" s="2"/>
-      <c r="P383" s="2"/>
-      <c r="Q383" s="2"/>
-      <c r="R383" s="2"/>
-      <c r="S383" s="2"/>
-      <c r="T383" s="2"/>
-      <c r="U383" s="2"/>
-      <c r="V383" s="2"/>
-      <c r="W383" s="2"/>
-      <c r="X383" s="2"/>
-      <c r="Y383" s="2"/>
+      <c r="A383" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="C383" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="D383" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="E383" s="1"/>
+      <c r="F383" s="1"/>
+      <c r="G383" s="1"/>
+      <c r="H383" s="1"/>
+      <c r="I383" s="1"/>
+      <c r="J383" s="1"/>
+      <c r="K383" s="1"/>
+      <c r="L383" s="1"/>
+      <c r="M383" s="1"/>
+      <c r="N383" s="1"/>
+      <c r="O383" s="1"/>
+      <c r="P383" s="1"/>
+      <c r="Q383" s="1"/>
+      <c r="R383" s="1"/>
+      <c r="S383" s="1"/>
+      <c r="T383" s="1"/>
+      <c r="U383" s="1"/>
+      <c r="V383" s="1"/>
+      <c r="W383" s="1"/>
+      <c r="X383" s="1"/>
+      <c r="Y383" s="1"/>
     </row>
     <row r="384" spans="1:25" ht="15.75" customHeight="1">
       <c r="A384" s="3" t="s">
-        <v>1153</v>
+        <v>707</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>1154</v>
+        <v>708</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>1155</v>
+        <v>709</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1153</v>
+        <v>707</v>
       </c>
       <c r="E384" s="2"/>
       <c r="F384" s="2"/>
@@ -17432,51 +17436,51 @@
     </row>
     <row r="385" spans="1:25" ht="15.75" customHeight="1">
       <c r="A385" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C385" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="D385" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E385" s="2"/>
+      <c r="F385" s="2"/>
+      <c r="G385" s="2"/>
+      <c r="H385" s="2"/>
+      <c r="I385" s="2"/>
+      <c r="J385" s="2"/>
+      <c r="K385" s="2"/>
+      <c r="L385" s="2"/>
+      <c r="M385" s="2"/>
+      <c r="N385" s="2"/>
+      <c r="O385" s="2"/>
+      <c r="P385" s="2"/>
+      <c r="Q385" s="2"/>
+      <c r="R385" s="2"/>
+      <c r="S385" s="2"/>
+      <c r="T385" s="2"/>
+      <c r="U385" s="2"/>
+      <c r="V385" s="2"/>
+      <c r="W385" s="2"/>
+      <c r="X385" s="2"/>
+      <c r="Y385" s="2"/>
+    </row>
+    <row r="386" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A386" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="B385" s="3" t="s">
+      <c r="B386" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="C385" s="4" t="s">
+      <c r="C386" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="D385" s="3" t="s">
+      <c r="D386" s="3" t="s">
         <v>710</v>
-      </c>
-      <c r="E385" s="1"/>
-      <c r="F385" s="1"/>
-      <c r="G385" s="1"/>
-      <c r="H385" s="1"/>
-      <c r="I385" s="1"/>
-      <c r="J385" s="1"/>
-      <c r="K385" s="1"/>
-      <c r="L385" s="1"/>
-      <c r="M385" s="1"/>
-      <c r="N385" s="1"/>
-      <c r="O385" s="1"/>
-      <c r="P385" s="1"/>
-      <c r="Q385" s="1"/>
-      <c r="R385" s="1"/>
-      <c r="S385" s="1"/>
-      <c r="T385" s="1"/>
-      <c r="U385" s="1"/>
-      <c r="V385" s="1"/>
-      <c r="W385" s="1"/>
-      <c r="X385" s="1"/>
-      <c r="Y385" s="1"/>
-    </row>
-    <row r="386" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A386" s="5" t="s">
-        <v>713</v>
-      </c>
-      <c r="B386" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="C386" s="47" t="s">
-        <v>715</v>
-      </c>
-      <c r="D386" s="5" t="s">
-        <v>716</v>
       </c>
       <c r="E386" s="1"/>
       <c r="F386" s="1"/>
@@ -17502,14 +17506,16 @@
     </row>
     <row r="387" spans="1:25" ht="15.75" customHeight="1">
       <c r="A387" s="5" t="s">
-        <v>717</v>
-      </c>
-      <c r="B387" s="5"/>
-      <c r="C387" s="6" t="s">
-        <v>718</v>
+        <v>713</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="C387" s="47" t="s">
+        <v>715</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E387" s="1"/>
       <c r="F387" s="1"/>
@@ -17534,794 +17540,821 @@
       <c r="Y387" s="1"/>
     </row>
     <row r="388" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A388" s="3" t="s">
+      <c r="A388" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="B388" s="5"/>
+      <c r="C388" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="E388" s="1"/>
+      <c r="F388" s="1"/>
+      <c r="G388" s="1"/>
+      <c r="H388" s="1"/>
+      <c r="I388" s="1"/>
+      <c r="J388" s="1"/>
+      <c r="K388" s="1"/>
+      <c r="L388" s="1"/>
+      <c r="M388" s="1"/>
+      <c r="N388" s="1"/>
+      <c r="O388" s="1"/>
+      <c r="P388" s="1"/>
+      <c r="Q388" s="1"/>
+      <c r="R388" s="1"/>
+      <c r="S388" s="1"/>
+      <c r="T388" s="1"/>
+      <c r="U388" s="1"/>
+      <c r="V388" s="1"/>
+      <c r="W388" s="1"/>
+      <c r="X388" s="1"/>
+      <c r="Y388" s="1"/>
+    </row>
+    <row r="389" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A389" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="B388" s="3" t="s">
+      <c r="B389" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="C388" s="3" t="s">
+      <c r="C389" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="D388" s="3" t="s">
+      <c r="D389" s="3" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="389" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A389" s="9" t="s">
+    <row r="390" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A390" s="9" t="s">
         <v>722</v>
       </c>
-      <c r="B389" s="9" t="s">
+      <c r="B390" s="9" t="s">
         <v>723</v>
       </c>
-      <c r="C389" s="11" t="s">
+      <c r="C390" s="11" t="s">
         <v>724</v>
       </c>
-      <c r="D389" s="9" t="s">
+      <c r="D390" s="9" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="390" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A390" s="3" t="s">
+    <row r="391" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A391" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="B390" s="3" t="s">
+      <c r="B391" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="C390" s="4" t="s">
+      <c r="C391" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="D390" s="3" t="s">
+      <c r="D391" s="3" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="391" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A391" s="5" t="s">
+    <row r="392" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A392" s="5" t="s">
         <v>728</v>
       </c>
-      <c r="B391" s="5"/>
-      <c r="C391" s="47" t="s">
+      <c r="B392" s="5"/>
+      <c r="C392" s="47" t="s">
         <v>729</v>
       </c>
-      <c r="D391" s="5" t="s">
+      <c r="D392" s="5" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="392" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A392" s="3" t="s">
+    <row r="393" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A393" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="B392" s="3"/>
-      <c r="C392" s="3" t="s">
+      <c r="B393" s="3"/>
+      <c r="C393" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="D392" s="3" t="s">
+      <c r="D393" s="3" t="s">
         <v>730</v>
-      </c>
-    </row>
-    <row r="393" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A393" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="B393" s="9"/>
-      <c r="C393" s="10" t="s">
-        <v>733</v>
-      </c>
-      <c r="D393" s="9" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="394" spans="1:25" ht="15.75" customHeight="1">
       <c r="A394" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="B394" s="9" t="s">
-        <v>735</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="B394" s="9"/>
       <c r="C394" s="10" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D394" s="9" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
     </row>
     <row r="395" spans="1:25" ht="15.75" customHeight="1">
       <c r="A395" s="9" t="s">
-        <v>1156</v>
-      </c>
-      <c r="B395" s="9"/>
+        <v>734</v>
+      </c>
+      <c r="B395" s="9" t="s">
+        <v>735</v>
+      </c>
       <c r="C395" s="10" t="s">
-        <v>1157</v>
+        <v>736</v>
       </c>
       <c r="D395" s="9" t="s">
-        <v>1158</v>
+        <v>734</v>
       </c>
     </row>
     <row r="396" spans="1:25" ht="15.75" customHeight="1">
       <c r="A396" s="9" t="s">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="B396" s="9"/>
       <c r="C396" s="10" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D396" s="9" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="397" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A397" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B397" s="9"/>
+      <c r="C397" s="10" t="s">
         <v>1161</v>
       </c>
-      <c r="D396" s="9" t="s">
+      <c r="D397" s="9" t="s">
         <v>1160</v>
       </c>
     </row>
-    <row r="397" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A397" s="5" t="s">
+    <row r="398" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A398" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B397" s="5" t="s">
+      <c r="B398" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="C397" s="47" t="s">
+      <c r="C398" s="47" t="s">
         <v>739</v>
       </c>
-      <c r="D397" s="5" t="s">
+      <c r="D398" s="5" t="s">
         <v>737</v>
-      </c>
-    </row>
-    <row r="398" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A398" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="B398" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C398" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="D398" s="3" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="399" spans="1:25" ht="15.75" customHeight="1">
       <c r="A399" s="3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="C399" s="3" t="s">
+        <v>742</v>
+      </c>
+      <c r="D399" s="3" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="400" spans="1:25" ht="15.75" customHeight="1">
+      <c r="A400" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B399" s="3" t="s">
+      <c r="B400" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="C399" s="3" t="s">
+      <c r="C400" s="3" t="s">
         <v>744</v>
       </c>
-      <c r="D399" s="3" t="s">
+      <c r="D400" s="3" t="s">
         <v>743</v>
-      </c>
-    </row>
-    <row r="400" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A400" s="5" t="s">
-        <v>745</v>
-      </c>
-      <c r="B400" s="5"/>
-      <c r="C400" s="6" t="s">
-        <v>746</v>
-      </c>
-      <c r="D400" s="5" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1">
       <c r="A401" s="5" t="s">
+        <v>745</v>
+      </c>
+      <c r="B401" s="5"/>
+      <c r="C401" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="D401" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A402" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B401" s="5" t="s">
+      <c r="B402" s="5" t="s">
         <v>749</v>
       </c>
-      <c r="C401" s="30" t="s">
+      <c r="C402" s="30" t="s">
         <v>750</v>
       </c>
-      <c r="D401" s="5" t="s">
+      <c r="D402" s="5" t="s">
         <v>748</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A402" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B402" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="D402" s="3" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1">
       <c r="A403" s="3" t="s">
-        <v>1162</v>
-      </c>
-      <c r="B403" s="3"/>
+        <v>751</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>752</v>
+      </c>
       <c r="C403" s="3" t="s">
-        <v>1163</v>
+        <v>753</v>
       </c>
       <c r="D403" s="3" t="s">
-        <v>1162</v>
+        <v>751</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1">
       <c r="A404" s="3" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B404" s="3"/>
       <c r="C404" s="3" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="D404" s="3" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1">
       <c r="A405" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B405" s="3"/>
+      <c r="C405" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D405" s="3" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A406" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="B405" s="3" t="s">
+      <c r="B406" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="C405" s="3" t="s">
+      <c r="C406" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="D405" s="3" t="s">
+      <c r="D406" s="3" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="406" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A406" s="5" t="s">
+    <row r="407" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A407" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B406" s="5" t="s">
+      <c r="B407" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="C406" s="6" t="s">
+      <c r="C407" s="6" t="s">
         <v>759</v>
       </c>
-      <c r="D406" s="5" t="s">
+      <c r="D407" s="5" t="s">
         <v>757</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A407" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="B407" s="7"/>
-      <c r="C407" s="31" t="s">
-        <v>761</v>
-      </c>
-      <c r="D407" s="7" t="s">
-        <v>762</v>
       </c>
     </row>
     <row r="408" spans="1:4" ht="15.75" customHeight="1">
       <c r="A408" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="B408" s="7"/>
+      <c r="C408" s="31" t="s">
+        <v>761</v>
+      </c>
+      <c r="D408" s="7" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A409" s="7" t="s">
         <v>1167</v>
       </c>
-      <c r="B408" s="7" t="s">
+      <c r="B409" s="7" t="s">
         <v>1168</v>
       </c>
-      <c r="C408" s="31" t="s">
+      <c r="C409" s="31" t="s">
         <v>1169</v>
       </c>
-      <c r="D408" s="7" t="s">
+      <c r="D409" s="7" t="s">
         <v>1167</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A409" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="B409" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D409" s="1" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="410" spans="1:4" ht="15.75" customHeight="1">
       <c r="A410" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C410" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D410" s="1" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A411" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="B410" s="3" t="s">
+      <c r="B411" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C410" s="3" t="s">
+      <c r="C411" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="D410" s="3" t="s">
+      <c r="D411" s="3" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="411" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A411" s="5" t="s">
+    <row r="412" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A412" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="B411" s="5" t="s">
+      <c r="B412" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="C411" s="6" t="s">
+      <c r="C412" s="6" t="s">
         <v>768</v>
       </c>
-      <c r="D411" s="5" t="s">
+      <c r="D412" s="5" t="s">
         <v>769</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A412" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B412" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="C412" s="4" t="s">
-        <v>772</v>
-      </c>
-      <c r="D412" s="3" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="413" spans="1:4" ht="15.75" customHeight="1">
       <c r="A413" s="3" t="s">
-        <v>1170</v>
+        <v>770</v>
       </c>
       <c r="B413" s="3" t="s">
-        <v>1171</v>
+        <v>771</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1172</v>
+        <v>772</v>
       </c>
       <c r="D413" s="3" t="s">
-        <v>1173</v>
+        <v>770</v>
       </c>
     </row>
     <row r="414" spans="1:4" ht="15.75" customHeight="1">
       <c r="A414" s="3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B414" s="3"/>
+        <v>1170</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>1171</v>
+      </c>
       <c r="C414" s="4" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1177</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="415" spans="1:4" ht="15.75" customHeight="1">
       <c r="A415" s="3" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B415" s="3"/>
       <c r="C415" s="4" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D415" s="3" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A416" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B416" s="3"/>
+      <c r="C416" s="4" t="s">
         <v>1180</v>
       </c>
-      <c r="D415" s="3" t="s">
+      <c r="D416" s="3" t="s">
         <v>1181</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A416" s="9" t="s">
-        <v>773</v>
-      </c>
-      <c r="B416" s="9"/>
-      <c r="C416" s="11" t="s">
-        <v>774</v>
-      </c>
-      <c r="D416" s="9" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="417" spans="1:4" ht="15.75" customHeight="1">
       <c r="A417" s="9" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B417" s="9" t="s">
-        <v>1183</v>
-      </c>
+        <v>773</v>
+      </c>
+      <c r="B417" s="9"/>
       <c r="C417" s="11" t="s">
-        <v>1184</v>
+        <v>774</v>
       </c>
       <c r="D417" s="9" t="s">
-        <v>1183</v>
+        <v>773</v>
       </c>
     </row>
     <row r="418" spans="1:4" ht="15.75" customHeight="1">
       <c r="A418" s="9" t="s">
-        <v>775</v>
+        <v>1182</v>
       </c>
       <c r="B418" s="9" t="s">
-        <v>776</v>
-      </c>
-      <c r="C418" s="10" t="s">
-        <v>777</v>
+        <v>1183</v>
+      </c>
+      <c r="C418" s="11" t="s">
+        <v>1184</v>
       </c>
       <c r="D418" s="9" t="s">
-        <v>775</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="419" spans="1:4" ht="15.75" customHeight="1">
       <c r="A419" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="B419" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="C419" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="D419" s="9" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A420" s="9" t="s">
         <v>778</v>
       </c>
-      <c r="B419" s="9"/>
-      <c r="C419" s="11" t="s">
+      <c r="B420" s="9"/>
+      <c r="C420" s="11" t="s">
         <v>779</v>
       </c>
-      <c r="D419" s="9" t="s">
+      <c r="D420" s="9" t="s">
         <v>780</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A420" s="7" t="s">
-        <v>783</v>
-      </c>
-      <c r="B420" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C420" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="D420" s="7" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="421" spans="1:4" ht="15.75" customHeight="1">
       <c r="A421" s="7" t="s">
+        <v>783</v>
+      </c>
+      <c r="B421" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="C421" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="D421" s="7" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A422" s="7" t="s">
         <v>781</v>
       </c>
-      <c r="B421" s="7"/>
-      <c r="C421" s="8" t="s">
+      <c r="B422" s="7"/>
+      <c r="C422" s="8" t="s">
         <v>782</v>
       </c>
-      <c r="D421" s="7" t="s">
+      <c r="D422" s="7" t="s">
         <v>781</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A422" s="5" t="s">
-        <v>790</v>
-      </c>
-      <c r="B422" s="5"/>
-      <c r="C422" s="6" t="s">
-        <v>791</v>
-      </c>
-      <c r="D422" s="5" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="423" spans="1:4" ht="15.75" customHeight="1">
       <c r="A423" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B423" s="5" t="s">
-        <v>1186</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="B423" s="5"/>
       <c r="C423" s="6" t="s">
-        <v>1185</v>
+        <v>791</v>
       </c>
       <c r="D423" s="5" t="s">
-        <v>1188</v>
+        <v>790</v>
       </c>
     </row>
     <row r="424" spans="1:4" ht="15.75" customHeight="1">
       <c r="A424" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="B424" s="5"/>
+        <v>1187</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>1186</v>
+      </c>
       <c r="C424" s="6" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="425" spans="1:4" ht="15.75" customHeight="1">
       <c r="A425" s="5" t="s">
-        <v>792</v>
+        <v>1189</v>
       </c>
       <c r="B425" s="5"/>
       <c r="C425" s="6" t="s">
-        <v>793</v>
+        <v>1190</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>794</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="426" spans="1:4" ht="15.75" customHeight="1">
       <c r="A426" s="5" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="B426" s="5"/>
       <c r="C426" s="6" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="427" spans="1:4" ht="15.75" customHeight="1">
       <c r="A427" s="5" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="B427" s="5"/>
       <c r="C427" s="6" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
     </row>
     <row r="428" spans="1:4" ht="15.75" customHeight="1">
       <c r="A428" s="5" t="s">
-        <v>1191</v>
+        <v>797</v>
       </c>
       <c r="B428" s="5"/>
       <c r="C428" s="6" t="s">
-        <v>1192</v>
+        <v>798</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>1191</v>
+        <v>799</v>
       </c>
     </row>
     <row r="429" spans="1:4" ht="15.75" customHeight="1">
       <c r="A429" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="B429" s="5" t="s">
-        <v>801</v>
-      </c>
+        <v>1191</v>
+      </c>
+      <c r="B429" s="5"/>
       <c r="C429" s="6" t="s">
-        <v>802</v>
+        <v>1192</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>803</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="430" spans="1:4" ht="15.75" customHeight="1">
       <c r="A430" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="C430" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="D430" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A431" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B430" s="5"/>
-      <c r="C430" s="6" t="s">
+      <c r="B431" s="5"/>
+      <c r="C431" s="6" t="s">
         <v>805</v>
       </c>
-      <c r="D430" s="5" t="s">
+      <c r="D431" s="5" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="431" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A431" s="7" t="s">
+    <row r="432" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A432" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="B431" s="7"/>
-      <c r="C431" s="8" t="s">
+      <c r="B432" s="7"/>
+      <c r="C432" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="D431" s="7" t="s">
+      <c r="D432" s="7" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="432" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A432" s="5" t="s">
+    <row r="433" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A433" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B432" s="5"/>
-      <c r="C432" s="6" t="s">
+      <c r="B433" s="5"/>
+      <c r="C433" s="6" t="s">
         <v>810</v>
       </c>
-      <c r="D432" s="5" t="s">
+      <c r="D433" s="5" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="433" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A433" s="3" t="s">
+    <row r="434" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A434" s="3" t="s">
         <v>1018</v>
       </c>
-      <c r="B433" s="3" t="s">
+      <c r="B434" s="3" t="s">
         <v>1019</v>
       </c>
-      <c r="C433" s="3" t="s">
+      <c r="C434" s="3" t="s">
         <v>1020</v>
       </c>
-      <c r="D433" s="1" t="s">
+      <c r="D434" s="1" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="434" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A434" s="5" t="s">
+    <row r="435" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A435" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="B434" s="5" t="s">
+      <c r="B435" s="5" t="s">
         <v>812</v>
       </c>
-      <c r="C434" s="6" t="s">
+      <c r="C435" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="D434" s="5" t="s">
+      <c r="D435" s="5" t="s">
         <v>811</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A435" s="3" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B435" s="3" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>1024</v>
-      </c>
-      <c r="D435" s="1" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="436" spans="1:4" ht="15.75" customHeight="1">
       <c r="A436" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B436" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C436" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D436" s="1" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A437" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B436" s="3"/>
-      <c r="C436" s="50" t="s">
+      <c r="B437" s="3"/>
+      <c r="C437" s="50" t="s">
         <v>815</v>
       </c>
-      <c r="D436" s="3" t="s">
+      <c r="D437" s="3" t="s">
         <v>814</v>
-      </c>
-    </row>
-    <row r="437" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A437" s="9" t="s">
-        <v>816</v>
-      </c>
-      <c r="B437" s="9"/>
-      <c r="C437" s="10" t="s">
-        <v>817</v>
-      </c>
-      <c r="D437" s="9" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="438" spans="1:4" ht="15.75" customHeight="1">
       <c r="A438" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="B438" s="9"/>
+      <c r="C438" s="10" t="s">
+        <v>817</v>
+      </c>
+      <c r="D438" s="9" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A439" s="9" t="s">
         <v>819</v>
       </c>
-      <c r="B438" s="9" t="s">
+      <c r="B439" s="9" t="s">
         <v>820</v>
       </c>
-      <c r="C438" s="11" t="s">
+      <c r="C439" s="11" t="s">
         <v>821</v>
       </c>
-      <c r="D438" s="9" t="s">
+      <c r="D439" s="9" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="439" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A439" s="7" t="s">
+    <row r="440" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A440" s="7" t="s">
         <v>923</v>
       </c>
-      <c r="B439" s="7" t="s">
+      <c r="B440" s="7" t="s">
         <v>924</v>
       </c>
-      <c r="C439" s="53" t="s">
+      <c r="C440" s="53" t="s">
         <v>925</v>
       </c>
-      <c r="D439" s="7" t="s">
+      <c r="D440" s="7" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="440" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A440" s="3" t="s">
+    <row r="441" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A441" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="B440" s="3" t="s">
+      <c r="B441" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="C440" s="50" t="s">
+      <c r="C441" s="50" t="s">
         <v>824</v>
       </c>
-      <c r="D440" s="3" t="s">
+      <c r="D441" s="3" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A441" s="9" t="s">
+    <row r="442" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A442" s="9" t="s">
         <v>825</v>
       </c>
-      <c r="B441" s="9" t="s">
+      <c r="B442" s="9" t="s">
         <v>826</v>
       </c>
-      <c r="C441" s="10" t="s">
+      <c r="C442" s="10" t="s">
         <v>827</v>
       </c>
-      <c r="D441" s="9" t="s">
+      <c r="D442" s="9" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="442" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A442" s="3" t="s">
+    <row r="443" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A443" s="3" t="s">
         <v>828</v>
       </c>
-      <c r="B442" s="3"/>
-      <c r="C442" s="4" t="s">
+      <c r="B443" s="3"/>
+      <c r="C443" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="D442" s="3" t="s">
+      <c r="D443" s="3" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="443" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A443" s="5" t="s">
+    <row r="444" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A444" s="5" t="s">
         <v>830</v>
       </c>
-      <c r="B443" s="5"/>
-      <c r="C443" s="6" t="s">
+      <c r="B444" s="5"/>
+      <c r="C444" s="6" t="s">
         <v>831</v>
       </c>
-      <c r="D443" s="48" t="s">
+      <c r="D444" s="48" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A444" s="3" t="s">
+    <row r="445" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A445" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="B444" s="3" t="s">
+      <c r="B445" s="3" t="s">
         <v>833</v>
       </c>
-      <c r="C444" s="12" t="s">
+      <c r="C445" s="12" t="s">
         <v>834</v>
       </c>
-      <c r="D444" s="1" t="s">
+      <c r="D445" s="1" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="445" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A445" s="5" t="s">
+    <row r="446" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A446" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="B445" s="5"/>
-      <c r="C445" s="6" t="s">
+      <c r="B446" s="5"/>
+      <c r="C446" s="6" t="s">
         <v>836</v>
       </c>
-      <c r="D445" s="49" t="s">
+      <c r="D446" s="49" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="446" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A446" s="3" t="s">
+    <row r="447" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A447" s="3" t="s">
         <v>1025</v>
       </c>
-      <c r="B446" s="3" t="s">
+      <c r="B447" s="3" t="s">
         <v>1026</v>
       </c>
-      <c r="C446" s="3" t="s">
+      <c r="C447" s="3" t="s">
         <v>1027</v>
       </c>
-      <c r="D446" s="1" t="s">
+      <c r="D447" s="1" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="447" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A447" s="7" t="s">
+    <row r="448" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A448" s="7" t="s">
         <v>926</v>
       </c>
-      <c r="B447" s="7" t="s">
+      <c r="B448" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="C447" s="69" t="s">
+      <c r="C448" s="69" t="s">
         <v>928</v>
       </c>
-      <c r="D447" s="70" t="s">
+      <c r="D448" s="70" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="448" spans="1:4" ht="15.75" customHeight="1">
-      <c r="A448" s="3"/>
-      <c r="B448" s="3"/>
-      <c r="C448" s="3"/>
-      <c r="D448" s="1"/>
     </row>
     <row r="449" spans="1:4" ht="15.75" customHeight="1">
       <c r="A449" s="3"/>
@@ -23500,6 +23533,12 @@
       <c r="B1311" s="3"/>
       <c r="C1311" s="3"/>
       <c r="D1311" s="1"/>
+    </row>
+    <row r="1312" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A1312" s="3"/>
+      <c r="B1312" s="3"/>
+      <c r="C1312" s="3"/>
+      <c r="D1312" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -23660,78 +23699,78 @@
     <hyperlink ref="C295" r:id="rId155" xr:uid="{00000000-0004-0000-0000-00009E000000}"/>
     <hyperlink ref="C296" r:id="rId156" xr:uid="{00000000-0004-0000-0000-00009F000000}"/>
     <hyperlink ref="C299" r:id="rId157" xr:uid="{00000000-0004-0000-0000-0000A0000000}"/>
-    <hyperlink ref="C300" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
-    <hyperlink ref="C303" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
-    <hyperlink ref="C304" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
+    <hyperlink ref="C301" r:id="rId158" xr:uid="{00000000-0004-0000-0000-0000A1000000}"/>
+    <hyperlink ref="C304" r:id="rId159" xr:uid="{00000000-0004-0000-0000-0000A2000000}"/>
+    <hyperlink ref="C305" r:id="rId160" xr:uid="{00000000-0004-0000-0000-0000A3000000}"/>
     <hyperlink ref="C281" r:id="rId161" xr:uid="{00000000-0004-0000-0000-0000A4000000}"/>
-    <hyperlink ref="C306" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
-    <hyperlink ref="C307" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
-    <hyperlink ref="C314" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
-    <hyperlink ref="C315" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
-    <hyperlink ref="C318" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
-    <hyperlink ref="C321" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
-    <hyperlink ref="C319" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
-    <hyperlink ref="C322" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
-    <hyperlink ref="C324" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
-    <hyperlink ref="C329" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
-    <hyperlink ref="C330" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
-    <hyperlink ref="C331" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
-    <hyperlink ref="C333" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
-    <hyperlink ref="C334" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
-    <hyperlink ref="C335" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
-    <hyperlink ref="C336" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
-    <hyperlink ref="C340" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
-    <hyperlink ref="C344" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
-    <hyperlink ref="C345" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
-    <hyperlink ref="C347" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
-    <hyperlink ref="C350" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
-    <hyperlink ref="C351" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
-    <hyperlink ref="C354" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
-    <hyperlink ref="C357" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
-    <hyperlink ref="C360" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
-    <hyperlink ref="C372" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
-    <hyperlink ref="C373" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
-    <hyperlink ref="C367" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
-    <hyperlink ref="C368" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
-    <hyperlink ref="C370" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
-    <hyperlink ref="C374" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
-    <hyperlink ref="C375" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
-    <hyperlink ref="C378" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
-    <hyperlink ref="C379" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
-    <hyperlink ref="C385" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
-    <hyperlink ref="C386" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
-    <hyperlink ref="C387" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
-    <hyperlink ref="C389" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
-    <hyperlink ref="C391" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
-    <hyperlink ref="C393" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
-    <hyperlink ref="C397" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
-    <hyperlink ref="C400" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
-    <hyperlink ref="C401" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
-    <hyperlink ref="C406" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
-    <hyperlink ref="C407" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
-    <hyperlink ref="C411" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
-    <hyperlink ref="C412" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
-    <hyperlink ref="C416" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
-    <hyperlink ref="C419" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
-    <hyperlink ref="C421" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
-    <hyperlink ref="C420" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
+    <hyperlink ref="C307" r:id="rId162" xr:uid="{00000000-0004-0000-0000-0000A5000000}"/>
+    <hyperlink ref="C308" r:id="rId163" xr:uid="{00000000-0004-0000-0000-0000A6000000}"/>
+    <hyperlink ref="C315" r:id="rId164" xr:uid="{00000000-0004-0000-0000-0000A8000000}"/>
+    <hyperlink ref="C316" r:id="rId165" xr:uid="{00000000-0004-0000-0000-0000A9000000}"/>
+    <hyperlink ref="C319" r:id="rId166" xr:uid="{00000000-0004-0000-0000-0000AA000000}"/>
+    <hyperlink ref="C322" r:id="rId167" xr:uid="{00000000-0004-0000-0000-0000AB000000}"/>
+    <hyperlink ref="C320" r:id="rId168" xr:uid="{00000000-0004-0000-0000-0000AC000000}"/>
+    <hyperlink ref="C323" r:id="rId169" xr:uid="{00000000-0004-0000-0000-0000AD000000}"/>
+    <hyperlink ref="C325" r:id="rId170" xr:uid="{00000000-0004-0000-0000-0000AE000000}"/>
+    <hyperlink ref="C330" r:id="rId171" xr:uid="{00000000-0004-0000-0000-0000AF000000}"/>
+    <hyperlink ref="C331" r:id="rId172" xr:uid="{00000000-0004-0000-0000-0000B0000000}"/>
+    <hyperlink ref="C332" r:id="rId173" xr:uid="{00000000-0004-0000-0000-0000B1000000}"/>
+    <hyperlink ref="C334" r:id="rId174" xr:uid="{00000000-0004-0000-0000-0000B2000000}"/>
+    <hyperlink ref="C335" r:id="rId175" xr:uid="{00000000-0004-0000-0000-0000B3000000}"/>
+    <hyperlink ref="C336" r:id="rId176" xr:uid="{00000000-0004-0000-0000-0000B4000000}"/>
+    <hyperlink ref="C337" r:id="rId177" xr:uid="{00000000-0004-0000-0000-0000B5000000}"/>
+    <hyperlink ref="C341" r:id="rId178" xr:uid="{00000000-0004-0000-0000-0000B6000000}"/>
+    <hyperlink ref="C345" r:id="rId179" xr:uid="{00000000-0004-0000-0000-0000B7000000}"/>
+    <hyperlink ref="C346" r:id="rId180" xr:uid="{00000000-0004-0000-0000-0000B8000000}"/>
+    <hyperlink ref="C348" r:id="rId181" xr:uid="{00000000-0004-0000-0000-0000B9000000}"/>
+    <hyperlink ref="C351" r:id="rId182" xr:uid="{00000000-0004-0000-0000-0000BA000000}"/>
+    <hyperlink ref="C352" r:id="rId183" xr:uid="{00000000-0004-0000-0000-0000BB000000}"/>
+    <hyperlink ref="C355" r:id="rId184" xr:uid="{00000000-0004-0000-0000-0000BC000000}"/>
+    <hyperlink ref="C358" r:id="rId185" xr:uid="{00000000-0004-0000-0000-0000BD000000}"/>
+    <hyperlink ref="C361" r:id="rId186" xr:uid="{00000000-0004-0000-0000-0000BE000000}"/>
+    <hyperlink ref="C373" r:id="rId187" xr:uid="{00000000-0004-0000-0000-0000BF000000}"/>
+    <hyperlink ref="C374" r:id="rId188" xr:uid="{00000000-0004-0000-0000-0000C0000000}"/>
+    <hyperlink ref="C368" r:id="rId189" xr:uid="{00000000-0004-0000-0000-0000C1000000}"/>
+    <hyperlink ref="C369" r:id="rId190" xr:uid="{00000000-0004-0000-0000-0000C2000000}"/>
+    <hyperlink ref="C371" r:id="rId191" xr:uid="{00000000-0004-0000-0000-0000C3000000}"/>
+    <hyperlink ref="C375" r:id="rId192" xr:uid="{00000000-0004-0000-0000-0000C4000000}"/>
+    <hyperlink ref="C376" r:id="rId193" xr:uid="{00000000-0004-0000-0000-0000C5000000}"/>
+    <hyperlink ref="C379" r:id="rId194" xr:uid="{00000000-0004-0000-0000-0000C6000000}"/>
+    <hyperlink ref="C380" r:id="rId195" xr:uid="{00000000-0004-0000-0000-0000C7000000}"/>
+    <hyperlink ref="C386" r:id="rId196" xr:uid="{00000000-0004-0000-0000-0000C8000000}"/>
+    <hyperlink ref="C387" r:id="rId197" xr:uid="{00000000-0004-0000-0000-0000C9000000}"/>
+    <hyperlink ref="C388" r:id="rId198" xr:uid="{00000000-0004-0000-0000-0000CA000000}"/>
+    <hyperlink ref="C390" r:id="rId199" xr:uid="{00000000-0004-0000-0000-0000CB000000}"/>
+    <hyperlink ref="C392" r:id="rId200" xr:uid="{00000000-0004-0000-0000-0000CD000000}"/>
+    <hyperlink ref="C394" r:id="rId201" xr:uid="{00000000-0004-0000-0000-0000CE000000}"/>
+    <hyperlink ref="C398" r:id="rId202" xr:uid="{00000000-0004-0000-0000-0000CF000000}"/>
+    <hyperlink ref="C401" r:id="rId203" xr:uid="{00000000-0004-0000-0000-0000D0000000}"/>
+    <hyperlink ref="C402" r:id="rId204" xr:uid="{00000000-0004-0000-0000-0000D1000000}"/>
+    <hyperlink ref="C407" r:id="rId205" xr:uid="{00000000-0004-0000-0000-0000D2000000}"/>
+    <hyperlink ref="C408" r:id="rId206" xr:uid="{00000000-0004-0000-0000-0000D3000000}"/>
+    <hyperlink ref="C412" r:id="rId207" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
+    <hyperlink ref="C413" r:id="rId208" xr:uid="{00000000-0004-0000-0000-0000D5000000}"/>
+    <hyperlink ref="C417" r:id="rId209" xr:uid="{00000000-0004-0000-0000-0000D6000000}"/>
+    <hyperlink ref="C420" r:id="rId210" xr:uid="{00000000-0004-0000-0000-0000D7000000}"/>
+    <hyperlink ref="C422" r:id="rId211" xr:uid="{00000000-0004-0000-0000-0000D8000000}"/>
+    <hyperlink ref="C421" r:id="rId212" xr:uid="{00000000-0004-0000-0000-0000D9000000}"/>
     <hyperlink ref="C11" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000DA000000}"/>
-    <hyperlink ref="C422" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
-    <hyperlink ref="C425" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
-    <hyperlink ref="C426" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
-    <hyperlink ref="C427" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
-    <hyperlink ref="C429" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
-    <hyperlink ref="C430" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
-    <hyperlink ref="C431" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
-    <hyperlink ref="C432" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
-    <hyperlink ref="C434" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
-    <hyperlink ref="C436" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
-    <hyperlink ref="C438" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
-    <hyperlink ref="C440" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
-    <hyperlink ref="C442" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
-    <hyperlink ref="C443" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
-    <hyperlink ref="C444" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
-    <hyperlink ref="C445" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
+    <hyperlink ref="C423" r:id="rId214" xr:uid="{00000000-0004-0000-0000-0000DB000000}"/>
+    <hyperlink ref="C426" r:id="rId215" xr:uid="{00000000-0004-0000-0000-0000DC000000}"/>
+    <hyperlink ref="C427" r:id="rId216" xr:uid="{00000000-0004-0000-0000-0000DD000000}"/>
+    <hyperlink ref="C428" r:id="rId217" xr:uid="{00000000-0004-0000-0000-0000DE000000}"/>
+    <hyperlink ref="C430" r:id="rId218" xr:uid="{00000000-0004-0000-0000-0000DF000000}"/>
+    <hyperlink ref="C431" r:id="rId219" xr:uid="{00000000-0004-0000-0000-0000E0000000}"/>
+    <hyperlink ref="C432" r:id="rId220" xr:uid="{00000000-0004-0000-0000-0000E1000000}"/>
+    <hyperlink ref="C433" r:id="rId221" xr:uid="{00000000-0004-0000-0000-0000E2000000}"/>
+    <hyperlink ref="C435" r:id="rId222" xr:uid="{00000000-0004-0000-0000-0000E3000000}"/>
+    <hyperlink ref="C437" r:id="rId223" xr:uid="{00000000-0004-0000-0000-0000E4000000}"/>
+    <hyperlink ref="C439" r:id="rId224" xr:uid="{00000000-0004-0000-0000-0000E5000000}"/>
+    <hyperlink ref="C441" r:id="rId225" xr:uid="{00000000-0004-0000-0000-0000E6000000}"/>
+    <hyperlink ref="C443" r:id="rId226" xr:uid="{00000000-0004-0000-0000-0000E7000000}"/>
+    <hyperlink ref="C444" r:id="rId227" xr:uid="{00000000-0004-0000-0000-0000E8000000}"/>
+    <hyperlink ref="C445" r:id="rId228" xr:uid="{00000000-0004-0000-0000-0000E9000000}"/>
+    <hyperlink ref="C446" r:id="rId229" xr:uid="{00000000-0004-0000-0000-0000EA000000}"/>
     <hyperlink ref="C191" r:id="rId230" xr:uid="{98DDE684-CC21-7C49-B22B-C4F92C88FD93}"/>
     <hyperlink ref="C255" r:id="rId231" xr:uid="{E941C717-9955-3748-A705-A152EB86702B}"/>
     <hyperlink ref="C292" r:id="rId232" xr:uid="{35AE7ED9-3884-6948-9153-E51142B0BF49}"/>
@@ -23755,13 +23794,13 @@
     <hyperlink ref="C229" r:id="rId250" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
     <hyperlink ref="C250" r:id="rId251" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
     <hyperlink ref="C254" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
-    <hyperlink ref="C311" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
-    <hyperlink ref="C317" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
-    <hyperlink ref="C343" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
-    <hyperlink ref="C346" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
-    <hyperlink ref="C358" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C439" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C447" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C312" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
+    <hyperlink ref="C318" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
+    <hyperlink ref="C344" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
+    <hyperlink ref="C347" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
+    <hyperlink ref="C359" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
+    <hyperlink ref="C440" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C448" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
     <hyperlink ref="C214" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
     <hyperlink ref="C244" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
     <hyperlink ref="C275" r:id="rId262" xr:uid="{20FF35A0-9072-C349-94BD-F07C44AE26C4}"/>
@@ -23774,7 +23813,7 @@
     <hyperlink ref="C92" r:id="rId269" xr:uid="{6FC99DC1-4D16-F748-9C57-B02E3B5B7ACB}"/>
     <hyperlink ref="C108" r:id="rId270" xr:uid="{ED9FF9E1-0C2B-0E44-A3EF-F61085E02321}"/>
     <hyperlink ref="C183" r:id="rId271" xr:uid="{525BDD05-8A3F-424A-B398-414EBECB8EF0}"/>
-    <hyperlink ref="C337" r:id="rId272" xr:uid="{220744C9-5318-7F48-8555-FABFF8F9D26F}"/>
+    <hyperlink ref="C338" r:id="rId272" xr:uid="{220744C9-5318-7F48-8555-FABFF8F9D26F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rh\github\dev-baernreither-data\data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C4B7A1-7629-374F-996C-335EE6FB10B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCB304-FC89-44AE-8A9C-4A985D3E4EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31095" yWindow="5685" windowWidth="12225" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="tRO03vBbdgxA9ML+L9HI+fAJAQe/m24vycmGrGZE2sg="/>
     </ext>
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1699" uniqueCount="1307">
   <si>
     <t>Name</t>
   </si>
@@ -3798,9 +3801,6 @@
     <t>Jungbunzlau</t>
   </si>
   <si>
-    <t>Junbunzlau</t>
-  </si>
-  <si>
     <t>Kastell Kapersburg</t>
   </si>
   <si>
@@ -3949,6 +3949,9 @@
   </si>
   <si>
     <t>https://www.geonames.org/3186573/zenica.html</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/3070543/okres-mlada-boleslav.html</t>
   </si>
 </sst>
 </file>
@@ -4817,13 +4820,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Y1350"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" customWidth="1"/>
-    <col min="3" max="3" width="74.33203125" customWidth="1"/>
-    <col min="4" max="4" width="23.1640625" customWidth="1"/>
-    <col min="5" max="25" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="74.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" customWidth="1"/>
+    <col min="5" max="25" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="15.75" customHeight="1">
@@ -4861,7 +4864,7 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:25" ht="16">
+    <row r="3" spans="1:25">
       <c r="A3" s="78" t="s">
         <v>929</v>
       </c>
@@ -4873,7 +4876,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="16">
+    <row r="4" spans="1:25">
       <c r="A4" s="3" t="s">
         <v>1051</v>
       </c>
@@ -4887,7 +4890,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="16">
+    <row r="5" spans="1:25">
       <c r="A5" s="3" t="s">
         <v>1193</v>
       </c>
@@ -4932,7 +4935,7 @@
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
-    <row r="7" spans="1:25" ht="16">
+    <row r="7" spans="1:25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -4967,7 +4970,7 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" spans="1:25" ht="16">
+    <row r="8" spans="1:25">
       <c r="A8" s="3" t="s">
         <v>1054</v>
       </c>
@@ -5000,7 +5003,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:25" ht="16">
+    <row r="9" spans="1:25">
       <c r="A9" s="7" t="s">
         <v>853</v>
       </c>
@@ -5033,7 +5036,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:25" ht="16">
+    <row r="10" spans="1:25">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -5068,7 +5071,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:25" ht="32">
+    <row r="11" spans="1:25" ht="30">
       <c r="A11" s="3" t="s">
         <v>786</v>
       </c>
@@ -5103,7 +5106,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="16">
+    <row r="12" spans="1:25">
       <c r="A12" s="3" t="s">
         <v>1028</v>
       </c>
@@ -5136,7 +5139,7 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
     </row>
-    <row r="13" spans="1:25" ht="16">
+    <row r="13" spans="1:25">
       <c r="A13" s="3" t="s">
         <v>1198</v>
       </c>
@@ -5171,7 +5174,7 @@
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
-    <row r="14" spans="1:25" ht="16">
+    <row r="14" spans="1:25">
       <c r="A14" s="3" t="s">
         <v>1030</v>
       </c>
@@ -5206,7 +5209,7 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
-    <row r="15" spans="1:25" ht="16">
+    <row r="15" spans="1:25">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -5305,7 +5308,7 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:25" ht="16">
+    <row r="18" spans="1:25">
       <c r="A18" s="3" t="s">
         <v>1033</v>
       </c>
@@ -5577,7 +5580,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25" ht="16">
+    <row r="26" spans="1:25">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -5612,7 +5615,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:25" ht="16">
+    <row r="27" spans="1:25">
       <c r="A27" s="5" t="s">
         <v>31</v>
       </c>
@@ -5645,7 +5648,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:25" ht="16">
+    <row r="28" spans="1:25">
       <c r="A28" s="5" t="s">
         <v>34</v>
       </c>
@@ -5678,7 +5681,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="16">
+    <row r="29" spans="1:25">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -5711,7 +5714,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="16">
+    <row r="30" spans="1:25">
       <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
@@ -5744,7 +5747,7 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="1:25" ht="16">
+    <row r="31" spans="1:25">
       <c r="A31" s="7" t="s">
         <v>855</v>
       </c>
@@ -5777,7 +5780,7 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
     </row>
-    <row r="32" spans="1:25" ht="16">
+    <row r="32" spans="1:25">
       <c r="A32" s="3" t="s">
         <v>42</v>
       </c>
@@ -5810,7 +5813,7 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
     </row>
-    <row r="33" spans="1:25" ht="16">
+    <row r="33" spans="1:25">
       <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
@@ -6144,7 +6147,7 @@
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
     </row>
-    <row r="43" spans="1:25" ht="16">
+    <row r="43" spans="1:25">
       <c r="A43" s="3" t="s">
         <v>56</v>
       </c>
@@ -6177,7 +6180,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25" ht="16">
+    <row r="44" spans="1:25">
       <c r="A44" s="3" t="s">
         <v>1036</v>
       </c>
@@ -6210,7 +6213,7 @@
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
     </row>
-    <row r="45" spans="1:25" ht="16">
+    <row r="45" spans="1:25">
       <c r="A45" s="7" t="s">
         <v>58</v>
       </c>
@@ -6243,7 +6246,7 @@
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="16">
+    <row r="46" spans="1:25">
       <c r="A46" s="3" t="s">
         <v>60</v>
       </c>
@@ -6309,7 +6312,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" spans="1:25" ht="16">
+    <row r="48" spans="1:25">
       <c r="A48" s="3" t="s">
         <v>64</v>
       </c>
@@ -6344,7 +6347,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25" ht="16">
+    <row r="49" spans="1:25">
       <c r="A49" s="3" t="s">
         <v>1064</v>
       </c>
@@ -6482,7 +6485,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" spans="1:25" ht="16">
+    <row r="53" spans="1:25">
       <c r="A53" s="3" t="s">
         <v>932</v>
       </c>
@@ -6517,7 +6520,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" spans="1:25" ht="16">
+    <row r="54" spans="1:25">
       <c r="A54" s="3" t="s">
         <v>1038</v>
       </c>
@@ -6550,7 +6553,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" spans="1:25" ht="16">
+    <row r="55" spans="1:25">
       <c r="A55" s="3" t="s">
         <v>72</v>
       </c>
@@ -6585,7 +6588,7 @@
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
     </row>
-    <row r="56" spans="1:25" ht="16">
+    <row r="56" spans="1:25">
       <c r="A56" s="3" t="s">
         <v>935</v>
       </c>
@@ -6618,7 +6621,7 @@
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
     </row>
-    <row r="57" spans="1:25" ht="16">
+    <row r="57" spans="1:25">
       <c r="A57" s="7" t="s">
         <v>860</v>
       </c>
@@ -6653,7 +6656,7 @@
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
     </row>
-    <row r="58" spans="1:25" ht="16">
+    <row r="58" spans="1:25">
       <c r="A58" s="7" t="s">
         <v>76</v>
       </c>
@@ -6686,7 +6689,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" spans="1:25" ht="16">
+    <row r="59" spans="1:25">
       <c r="A59" s="7" t="s">
         <v>1211</v>
       </c>
@@ -6721,7 +6724,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" spans="1:25" ht="16">
+    <row r="60" spans="1:25">
       <c r="A60" s="7" t="s">
         <v>78</v>
       </c>
@@ -6754,7 +6757,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="16">
+    <row r="61" spans="1:25">
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
@@ -6787,7 +6790,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" spans="1:25" ht="16">
+    <row r="62" spans="1:25">
       <c r="A62" s="7" t="s">
         <v>80</v>
       </c>
@@ -6820,7 +6823,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" spans="1:25" ht="16">
+    <row r="63" spans="1:25">
       <c r="A63" s="3" t="s">
         <v>82</v>
       </c>
@@ -6954,7 +6957,7 @@
       <c r="X66" s="2"/>
       <c r="Y66" s="2"/>
     </row>
-    <row r="67" spans="1:25" ht="16">
+    <row r="67" spans="1:25">
       <c r="A67" s="7" t="s">
         <v>94</v>
       </c>
@@ -6987,7 +6990,7 @@
       <c r="X67" s="60"/>
       <c r="Y67" s="60"/>
     </row>
-    <row r="68" spans="1:25" ht="16">
+    <row r="68" spans="1:25">
       <c r="A68" s="5" t="s">
         <v>96</v>
       </c>
@@ -7022,7 +7025,7 @@
       <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
-    <row r="69" spans="1:25" ht="16">
+    <row r="69" spans="1:25">
       <c r="A69" s="5" t="s">
         <v>1213</v>
       </c>
@@ -7057,7 +7060,7 @@
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
     </row>
-    <row r="70" spans="1:25" ht="16">
+    <row r="70" spans="1:25">
       <c r="A70" s="3" t="s">
         <v>100</v>
       </c>
@@ -7092,7 +7095,7 @@
       <c r="X70" s="2"/>
       <c r="Y70" s="2"/>
     </row>
-    <row r="71" spans="1:25" ht="16">
+    <row r="71" spans="1:25">
       <c r="A71" s="55" t="s">
         <v>863</v>
       </c>
@@ -7127,7 +7130,7 @@
       <c r="X71" s="2"/>
       <c r="Y71" s="2"/>
     </row>
-    <row r="72" spans="1:25" ht="16">
+    <row r="72" spans="1:25">
       <c r="A72" s="3" t="s">
         <v>428</v>
       </c>
@@ -7162,7 +7165,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" spans="1:25" ht="16">
+    <row r="73" spans="1:25">
       <c r="A73" s="3" t="s">
         <v>104</v>
       </c>
@@ -7195,7 +7198,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:25" ht="16">
+    <row r="74" spans="1:25">
       <c r="A74" s="3" t="s">
         <v>106</v>
       </c>
@@ -7230,7 +7233,7 @@
       <c r="X74" s="2"/>
       <c r="Y74" s="2"/>
     </row>
-    <row r="75" spans="1:25" ht="16">
+    <row r="75" spans="1:25">
       <c r="A75" s="3" t="s">
         <v>109</v>
       </c>
@@ -7265,7 +7268,7 @@
       <c r="X75" s="2"/>
       <c r="Y75" s="2"/>
     </row>
-    <row r="76" spans="1:25" ht="16">
+    <row r="76" spans="1:25">
       <c r="A76" s="3" t="s">
         <v>938</v>
       </c>
@@ -7333,7 +7336,7 @@
       <c r="X77" s="63"/>
       <c r="Y77" s="63"/>
     </row>
-    <row r="78" spans="1:25" ht="16">
+    <row r="78" spans="1:25">
       <c r="A78" s="57" t="s">
         <v>866</v>
       </c>
@@ -7368,7 +7371,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" spans="1:25" ht="16">
+    <row r="79" spans="1:25">
       <c r="A79" s="3" t="s">
         <v>866</v>
       </c>
@@ -7434,7 +7437,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" spans="1:25" ht="16">
+    <row r="81" spans="1:25">
       <c r="A81" s="9" t="s">
         <v>1217</v>
       </c>
@@ -7469,7 +7472,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" spans="1:25" ht="16">
+    <row r="82" spans="1:25">
       <c r="A82" s="9" t="s">
         <v>1220</v>
       </c>
@@ -7504,7 +7507,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" spans="1:25" ht="16">
+    <row r="83" spans="1:25" ht="30">
       <c r="A83" s="9" t="s">
         <v>115</v>
       </c>
@@ -7605,7 +7608,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" spans="1:25" ht="16">
+    <row r="86" spans="1:25">
       <c r="A86" s="3" t="s">
         <v>120</v>
       </c>
@@ -7640,7 +7643,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" spans="1:25" ht="16">
+    <row r="87" spans="1:25">
       <c r="A87" s="7" t="s">
         <v>123</v>
       </c>
@@ -7741,7 +7744,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" spans="1:25" ht="16">
+    <row r="90" spans="1:25">
       <c r="A90" s="3" t="s">
         <v>941</v>
       </c>
@@ -7811,7 +7814,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" spans="1:25" ht="16">
+    <row r="92" spans="1:25">
       <c r="A92" s="3" t="s">
         <v>130</v>
       </c>
@@ -7846,7 +7849,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" spans="1:25" ht="16">
+    <row r="93" spans="1:25">
       <c r="A93" s="61" t="s">
         <v>868</v>
       </c>
@@ -7881,7 +7884,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" spans="1:25" ht="16">
+    <row r="94" spans="1:25">
       <c r="A94" s="3" t="s">
         <v>944</v>
       </c>
@@ -7916,7 +7919,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25" ht="16">
+    <row r="95" spans="1:25">
       <c r="A95" s="7" t="s">
         <v>871</v>
       </c>
@@ -7951,7 +7954,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" spans="1:25" ht="16">
+    <row r="96" spans="1:25">
       <c r="A96" s="3" t="s">
         <v>133</v>
       </c>
@@ -7986,7 +7989,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" spans="1:25" ht="16">
+    <row r="97" spans="1:25">
       <c r="A97" s="5" t="s">
         <v>136</v>
       </c>
@@ -8021,7 +8024,7 @@
       <c r="X97" s="2"/>
       <c r="Y97" s="2"/>
     </row>
-    <row r="98" spans="1:25" ht="16">
+    <row r="98" spans="1:25">
       <c r="A98" s="5" t="s">
         <v>1073</v>
       </c>
@@ -8054,7 +8057,7 @@
       <c r="X98" s="2"/>
       <c r="Y98" s="2"/>
     </row>
-    <row r="99" spans="1:25" ht="16">
+    <row r="99" spans="1:25">
       <c r="A99" s="7" t="s">
         <v>138</v>
       </c>
@@ -8087,7 +8090,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" spans="1:25" ht="16">
+    <row r="100" spans="1:25">
       <c r="A100" s="7" t="s">
         <v>140</v>
       </c>
@@ -8120,7 +8123,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" spans="1:25" ht="16">
+    <row r="101" spans="1:25">
       <c r="A101" s="7" t="s">
         <v>1195</v>
       </c>
@@ -8153,7 +8156,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" spans="1:25" ht="16">
+    <row r="102" spans="1:25">
       <c r="A102" s="7" t="s">
         <v>1226</v>
       </c>
@@ -8186,7 +8189,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" spans="1:25" ht="16">
+    <row r="103" spans="1:25">
       <c r="A103" s="7" t="s">
         <v>1074</v>
       </c>
@@ -8221,7 +8224,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" spans="1:25" ht="16">
+    <row r="104" spans="1:25">
       <c r="A104" s="5" t="s">
         <v>142</v>
       </c>
@@ -8256,7 +8259,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" spans="1:25" ht="16">
+    <row r="105" spans="1:25">
       <c r="A105" s="5" t="s">
         <v>145</v>
       </c>
@@ -10740,9 +10743,11 @@
       <c r="B178" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="C178" s="3"/>
+      <c r="C178" s="50" t="s">
+        <v>1306</v>
+      </c>
       <c r="D178" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1"/>
@@ -11005,14 +11010,14 @@
     </row>
     <row r="186" spans="1:25" ht="15.75" customHeight="1">
       <c r="A186" s="7" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B186" s="7"/>
       <c r="C186" s="64" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D186" s="7" t="s">
         <v>1258</v>
-      </c>
-      <c r="D186" s="7" t="s">
-        <v>1259</v>
       </c>
       <c r="E186" s="1"/>
       <c r="F186" s="1"/>
@@ -11253,14 +11258,14 @@
     </row>
     <row r="194" spans="1:25" ht="15.75" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B194" s="3"/>
       <c r="C194" s="4" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1"/>
@@ -11701,16 +11706,16 @@
     </row>
     <row r="207" spans="1:25" ht="15.75" customHeight="1">
       <c r="A207" s="7" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B207" s="7" t="s">
         <v>1263</v>
       </c>
-      <c r="B207" s="7" t="s">
+      <c r="C207" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="C207" s="8" t="s">
-        <v>1265</v>
-      </c>
       <c r="D207" s="7" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="E207" s="67"/>
       <c r="F207" s="67"/>
@@ -12451,16 +12456,16 @@
     </row>
     <row r="229" spans="1:25" ht="15.75" customHeight="1">
       <c r="A229" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B229" s="89" t="s">
         <v>1266</v>
       </c>
-      <c r="B229" s="89" t="s">
+      <c r="C229" s="3" t="s">
         <v>1267</v>
       </c>
-      <c r="C229" s="3" t="s">
-        <v>1268</v>
-      </c>
       <c r="D229" s="3" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="E229" s="1"/>
       <c r="F229" s="1"/>
@@ -12832,14 +12837,14 @@
     </row>
     <row r="240" spans="1:25" ht="15.75" customHeight="1">
       <c r="A240" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B240" s="7"/>
       <c r="C240" s="29" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="D240" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1"/>
@@ -13137,16 +13142,16 @@
     </row>
     <row r="249" spans="1:25" ht="15.75" customHeight="1">
       <c r="A249" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C249" s="19" t="s">
         <v>1271</v>
       </c>
-      <c r="B249" s="5" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C249" s="19" t="s">
-        <v>1272</v>
-      </c>
       <c r="D249" s="5" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1"/>
@@ -13446,14 +13451,14 @@
     </row>
     <row r="258" spans="1:25" ht="15.75" customHeight="1">
       <c r="A258" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B258" s="3"/>
       <c r="C258" s="51" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="E258" s="1"/>
       <c r="F258" s="1"/>
@@ -13578,16 +13583,16 @@
     </row>
     <row r="262" spans="1:25" ht="15.75" customHeight="1">
       <c r="A262" s="13" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C262" s="32" t="s">
         <v>1276</v>
       </c>
-      <c r="B262" s="13" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C262" s="32" t="s">
-        <v>1277</v>
-      </c>
       <c r="D262" s="13" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="E262" s="1"/>
       <c r="F262" s="1"/>
@@ -16737,16 +16742,16 @@
     </row>
     <row r="355" spans="1:25" ht="15.75" customHeight="1">
       <c r="A355" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B355" s="3" t="s">
         <v>1279</v>
       </c>
-      <c r="B355" s="3" t="s">
+      <c r="C355" s="3" t="s">
         <v>1280</v>
       </c>
-      <c r="C355" s="3" t="s">
-        <v>1281</v>
-      </c>
       <c r="D355" s="3" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="E355" s="2"/>
       <c r="F355" s="2"/>
@@ -16943,16 +16948,16 @@
     </row>
     <row r="361" spans="1:25" ht="15.75" customHeight="1">
       <c r="A361" s="9" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B361" s="9" t="s">
         <v>1282</v>
       </c>
-      <c r="B361" s="9" t="s">
+      <c r="C361" s="11" t="s">
+        <v>1284</v>
+      </c>
+      <c r="D361" s="9" t="s">
         <v>1283</v>
-      </c>
-      <c r="C361" s="11" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D361" s="9" t="s">
-        <v>1284</v>
       </c>
       <c r="E361" s="2"/>
       <c r="F361" s="2"/>
@@ -17386,14 +17391,14 @@
     </row>
     <row r="374" spans="1:25" ht="15.75" customHeight="1">
       <c r="A374" s="13" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B374" s="13"/>
       <c r="C374" s="68" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D374" s="13" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="E374" s="2"/>
       <c r="F374" s="2"/>
@@ -17522,14 +17527,14 @@
     </row>
     <row r="378" spans="1:25" ht="15.75" customHeight="1">
       <c r="A378" s="13" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B378" s="13"/>
       <c r="C378" s="68" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D378" s="13" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="E378" s="1"/>
       <c r="F378" s="1"/>
@@ -18781,14 +18786,14 @@
     </row>
     <row r="415" spans="1:25" ht="15.75" customHeight="1">
       <c r="A415" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B415" s="9"/>
       <c r="C415" s="10" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D415" s="9" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="E415" s="1"/>
       <c r="F415" s="1"/>
@@ -18814,14 +18819,14 @@
     </row>
     <row r="416" spans="1:25" ht="15.75" customHeight="1">
       <c r="A416" s="9" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B416" s="9"/>
       <c r="C416" s="10" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D416" s="9" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="E416" s="1"/>
       <c r="F416" s="1"/>
@@ -19164,14 +19169,14 @@
     </row>
     <row r="433" spans="1:4" ht="15.75" customHeight="1">
       <c r="A433" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B433" s="3"/>
       <c r="C433" s="3" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D433" s="3" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="434" spans="1:4" ht="15.75" customHeight="1">
@@ -19644,16 +19649,16 @@
     </row>
     <row r="470" spans="1:4" ht="15.75" customHeight="1">
       <c r="A470" s="5" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B470" s="5" t="s">
         <v>1296</v>
       </c>
-      <c r="B470" s="5" t="s">
+      <c r="C470" s="6" t="s">
         <v>1297</v>
       </c>
-      <c r="C470" s="6" t="s">
-        <v>1298</v>
-      </c>
       <c r="D470" s="5" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="471" spans="1:4" ht="15.75" customHeight="1">
@@ -19696,14 +19701,14 @@
     </row>
     <row r="474" spans="1:4" ht="15.75" customHeight="1">
       <c r="A474" s="9" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B474" s="9"/>
       <c r="C474" s="10" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D474" s="9" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="475" spans="1:4" ht="15.75" customHeight="1">
@@ -19750,16 +19755,16 @@
     </row>
     <row r="478" spans="1:4" ht="15.75" customHeight="1">
       <c r="A478" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B478" s="3" t="s">
         <v>1301</v>
       </c>
-      <c r="B478" s="3" t="s">
+      <c r="C478" s="50" t="s">
         <v>1302</v>
       </c>
-      <c r="C478" s="50" t="s">
-        <v>1303</v>
-      </c>
       <c r="D478" s="3" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="479" spans="1:4" ht="15.75" customHeight="1">
@@ -19842,14 +19847,14 @@
     </row>
     <row r="485" spans="1:4" ht="15.75" customHeight="1">
       <c r="A485" s="3" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B485" s="3"/>
       <c r="C485" s="3" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="486" spans="1:4" ht="15.75" customHeight="1">
@@ -25328,11 +25333,12 @@
     <hyperlink ref="C115" r:id="rId274" xr:uid="{8CDF73E8-B690-9A45-811B-8EBDEC80D17B}"/>
     <hyperlink ref="C82" r:id="rId275" xr:uid="{2F7AE097-DEF5-4146-A716-E70F95AD9CF2}"/>
     <hyperlink ref="C259" r:id="rId276" xr:uid="{47C430DC-91D2-1440-9854-F4E2C65DA30F}"/>
+    <hyperlink ref="C178" r:id="rId277" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId277"/>
+    <tablePart r:id="rId278"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25340,9 +25346,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A21:A1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="10.6640625" customWidth="1"/>
+    <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -26334,9 +26340,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A21:A1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="10.6640625" customWidth="1"/>
+    <col min="1" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\rh\github\dev-baernreither-data\data\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBCB304-FC89-44AE-8A9C-4A985D3E4EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED26ED6-8A4C-5242-9F02-755D700E9FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31095" yWindow="5685" windowWidth="12225" windowHeight="10860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,6 @@
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="tRO03vBbdgxA9ML+L9HI+fAJAQe/m24vycmGrGZE2sg="/>
     </ext>
@@ -4820,13 +4817,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:Y1350"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="74.28515625" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" customWidth="1"/>
-    <col min="5" max="25" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="74.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" customWidth="1"/>
+    <col min="5" max="25" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="15.75" customHeight="1">
@@ -4864,7 +4861,7 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" ht="16">
       <c r="A3" s="78" t="s">
         <v>929</v>
       </c>
@@ -4876,7 +4873,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" ht="16">
       <c r="A4" s="3" t="s">
         <v>1051</v>
       </c>
@@ -4890,7 +4887,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="5" spans="1:25">
+    <row r="5" spans="1:25" ht="16">
       <c r="A5" s="3" t="s">
         <v>1193</v>
       </c>
@@ -4935,7 +4932,7 @@
       <c r="X6" s="2"/>
       <c r="Y6" s="2"/>
     </row>
-    <row r="7" spans="1:25">
+    <row r="7" spans="1:25" ht="16">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -4970,12 +4967,12 @@
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
     </row>
-    <row r="8" spans="1:25">
+    <row r="8" spans="1:25" ht="16">
       <c r="A8" s="3" t="s">
         <v>1054</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="50" t="s">
         <v>1055</v>
       </c>
       <c r="D8" s="3" t="s">
@@ -5003,7 +5000,7 @@
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
     </row>
-    <row r="9" spans="1:25">
+    <row r="9" spans="1:25" ht="16">
       <c r="A9" s="7" t="s">
         <v>853</v>
       </c>
@@ -5036,7 +5033,7 @@
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
     </row>
-    <row r="10" spans="1:25">
+    <row r="10" spans="1:25" ht="16">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -5071,7 +5068,7 @@
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
     </row>
-    <row r="11" spans="1:25" ht="30">
+    <row r="11" spans="1:25" ht="32">
       <c r="A11" s="3" t="s">
         <v>786</v>
       </c>
@@ -5106,7 +5103,7 @@
       <c r="X11" s="1"/>
       <c r="Y11" s="1"/>
     </row>
-    <row r="12" spans="1:25">
+    <row r="12" spans="1:25" ht="16">
       <c r="A12" s="3" t="s">
         <v>1028</v>
       </c>
@@ -5139,7 +5136,7 @@
       <c r="X12" s="2"/>
       <c r="Y12" s="2"/>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" ht="16">
       <c r="A13" s="3" t="s">
         <v>1198</v>
       </c>
@@ -5174,7 +5171,7 @@
       <c r="X13" s="2"/>
       <c r="Y13" s="2"/>
     </row>
-    <row r="14" spans="1:25">
+    <row r="14" spans="1:25" ht="16">
       <c r="A14" s="3" t="s">
         <v>1030</v>
       </c>
@@ -5209,7 +5206,7 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
-    <row r="15" spans="1:25">
+    <row r="15" spans="1:25" ht="16">
       <c r="A15" s="7" t="s">
         <v>12</v>
       </c>
@@ -5308,7 +5305,7 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" ht="16">
       <c r="A18" s="3" t="s">
         <v>1033</v>
       </c>
@@ -5580,7 +5577,7 @@
       <c r="X25" s="1"/>
       <c r="Y25" s="1"/>
     </row>
-    <row r="26" spans="1:25">
+    <row r="26" spans="1:25" ht="16">
       <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
@@ -5615,7 +5612,7 @@
       <c r="X26" s="1"/>
       <c r="Y26" s="1"/>
     </row>
-    <row r="27" spans="1:25">
+    <row r="27" spans="1:25" ht="16">
       <c r="A27" s="5" t="s">
         <v>31</v>
       </c>
@@ -5648,7 +5645,7 @@
       <c r="X27" s="1"/>
       <c r="Y27" s="1"/>
     </row>
-    <row r="28" spans="1:25">
+    <row r="28" spans="1:25" ht="16">
       <c r="A28" s="5" t="s">
         <v>34</v>
       </c>
@@ -5681,7 +5678,7 @@
       <c r="X28" s="1"/>
       <c r="Y28" s="1"/>
     </row>
-    <row r="29" spans="1:25">
+    <row r="29" spans="1:25" ht="16">
       <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
@@ -5714,7 +5711,7 @@
       <c r="X29" s="1"/>
       <c r="Y29" s="1"/>
     </row>
-    <row r="30" spans="1:25">
+    <row r="30" spans="1:25" ht="16">
       <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
@@ -5747,7 +5744,7 @@
       <c r="X30" s="2"/>
       <c r="Y30" s="2"/>
     </row>
-    <row r="31" spans="1:25">
+    <row r="31" spans="1:25" ht="16">
       <c r="A31" s="7" t="s">
         <v>855</v>
       </c>
@@ -5780,7 +5777,7 @@
       <c r="X31" s="2"/>
       <c r="Y31" s="2"/>
     </row>
-    <row r="32" spans="1:25">
+    <row r="32" spans="1:25" ht="16">
       <c r="A32" s="3" t="s">
         <v>42</v>
       </c>
@@ -5813,7 +5810,7 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
     </row>
-    <row r="33" spans="1:25">
+    <row r="33" spans="1:25" ht="16">
       <c r="A33" s="3" t="s">
         <v>45</v>
       </c>
@@ -6147,7 +6144,7 @@
       <c r="X42" s="2"/>
       <c r="Y42" s="2"/>
     </row>
-    <row r="43" spans="1:25">
+    <row r="43" spans="1:25" ht="16">
       <c r="A43" s="3" t="s">
         <v>56</v>
       </c>
@@ -6180,7 +6177,7 @@
       <c r="X43" s="1"/>
       <c r="Y43" s="1"/>
     </row>
-    <row r="44" spans="1:25">
+    <row r="44" spans="1:25" ht="16">
       <c r="A44" s="3" t="s">
         <v>1036</v>
       </c>
@@ -6213,7 +6210,7 @@
       <c r="X44" s="2"/>
       <c r="Y44" s="2"/>
     </row>
-    <row r="45" spans="1:25">
+    <row r="45" spans="1:25" ht="16">
       <c r="A45" s="7" t="s">
         <v>58</v>
       </c>
@@ -6246,7 +6243,7 @@
       <c r="X45" s="2"/>
       <c r="Y45" s="2"/>
     </row>
-    <row r="46" spans="1:25">
+    <row r="46" spans="1:25" ht="16">
       <c r="A46" s="3" t="s">
         <v>60</v>
       </c>
@@ -6312,7 +6309,7 @@
       <c r="X47" s="1"/>
       <c r="Y47" s="1"/>
     </row>
-    <row r="48" spans="1:25">
+    <row r="48" spans="1:25" ht="16">
       <c r="A48" s="3" t="s">
         <v>64</v>
       </c>
@@ -6347,7 +6344,7 @@
       <c r="X48" s="1"/>
       <c r="Y48" s="1"/>
     </row>
-    <row r="49" spans="1:25">
+    <row r="49" spans="1:25" ht="16">
       <c r="A49" s="3" t="s">
         <v>1064</v>
       </c>
@@ -6485,7 +6482,7 @@
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
     </row>
-    <row r="53" spans="1:25">
+    <row r="53" spans="1:25" ht="16">
       <c r="A53" s="3" t="s">
         <v>932</v>
       </c>
@@ -6520,7 +6517,7 @@
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
     </row>
-    <row r="54" spans="1:25">
+    <row r="54" spans="1:25" ht="16">
       <c r="A54" s="3" t="s">
         <v>1038</v>
       </c>
@@ -6553,7 +6550,7 @@
       <c r="X54" s="1"/>
       <c r="Y54" s="1"/>
     </row>
-    <row r="55" spans="1:25">
+    <row r="55" spans="1:25" ht="16">
       <c r="A55" s="3" t="s">
         <v>72</v>
       </c>
@@ -6588,7 +6585,7 @@
       <c r="X55" s="2"/>
       <c r="Y55" s="2"/>
     </row>
-    <row r="56" spans="1:25">
+    <row r="56" spans="1:25" ht="16">
       <c r="A56" s="3" t="s">
         <v>935</v>
       </c>
@@ -6621,7 +6618,7 @@
       <c r="X56" s="2"/>
       <c r="Y56" s="2"/>
     </row>
-    <row r="57" spans="1:25">
+    <row r="57" spans="1:25" ht="16">
       <c r="A57" s="7" t="s">
         <v>860</v>
       </c>
@@ -6656,7 +6653,7 @@
       <c r="X57" s="2"/>
       <c r="Y57" s="2"/>
     </row>
-    <row r="58" spans="1:25">
+    <row r="58" spans="1:25" ht="16">
       <c r="A58" s="7" t="s">
         <v>76</v>
       </c>
@@ -6689,7 +6686,7 @@
       <c r="X58" s="1"/>
       <c r="Y58" s="1"/>
     </row>
-    <row r="59" spans="1:25">
+    <row r="59" spans="1:25" ht="16">
       <c r="A59" s="7" t="s">
         <v>1211</v>
       </c>
@@ -6724,7 +6721,7 @@
       <c r="X59" s="1"/>
       <c r="Y59" s="1"/>
     </row>
-    <row r="60" spans="1:25">
+    <row r="60" spans="1:25" ht="16">
       <c r="A60" s="7" t="s">
         <v>78</v>
       </c>
@@ -6757,7 +6754,7 @@
       <c r="X60" s="1"/>
       <c r="Y60" s="1"/>
     </row>
-    <row r="61" spans="1:25">
+    <row r="61" spans="1:25" ht="16">
       <c r="A61" s="3" t="s">
         <v>85</v>
       </c>
@@ -6790,7 +6787,7 @@
       <c r="X61" s="1"/>
       <c r="Y61" s="1"/>
     </row>
-    <row r="62" spans="1:25">
+    <row r="62" spans="1:25" ht="16">
       <c r="A62" s="7" t="s">
         <v>80</v>
       </c>
@@ -6823,7 +6820,7 @@
       <c r="X62" s="1"/>
       <c r="Y62" s="1"/>
     </row>
-    <row r="63" spans="1:25">
+    <row r="63" spans="1:25" ht="16">
       <c r="A63" s="3" t="s">
         <v>82</v>
       </c>
@@ -6957,7 +6954,7 @@
       <c r="X66" s="2"/>
       <c r="Y66" s="2"/>
     </row>
-    <row r="67" spans="1:25">
+    <row r="67" spans="1:25" ht="16">
       <c r="A67" s="7" t="s">
         <v>94</v>
       </c>
@@ -6990,7 +6987,7 @@
       <c r="X67" s="60"/>
       <c r="Y67" s="60"/>
     </row>
-    <row r="68" spans="1:25">
+    <row r="68" spans="1:25" ht="16">
       <c r="A68" s="5" t="s">
         <v>96</v>
       </c>
@@ -7025,7 +7022,7 @@
       <c r="X68" s="2"/>
       <c r="Y68" s="2"/>
     </row>
-    <row r="69" spans="1:25">
+    <row r="69" spans="1:25" ht="16">
       <c r="A69" s="5" t="s">
         <v>1213</v>
       </c>
@@ -7060,7 +7057,7 @@
       <c r="X69" s="2"/>
       <c r="Y69" s="2"/>
     </row>
-    <row r="70" spans="1:25">
+    <row r="70" spans="1:25" ht="16">
       <c r="A70" s="3" t="s">
         <v>100</v>
       </c>
@@ -7095,7 +7092,7 @@
       <c r="X70" s="2"/>
       <c r="Y70" s="2"/>
     </row>
-    <row r="71" spans="1:25">
+    <row r="71" spans="1:25" ht="16">
       <c r="A71" s="55" t="s">
         <v>863</v>
       </c>
@@ -7130,7 +7127,7 @@
       <c r="X71" s="2"/>
       <c r="Y71" s="2"/>
     </row>
-    <row r="72" spans="1:25">
+    <row r="72" spans="1:25" ht="16">
       <c r="A72" s="3" t="s">
         <v>428</v>
       </c>
@@ -7165,7 +7162,7 @@
       <c r="X72" s="1"/>
       <c r="Y72" s="1"/>
     </row>
-    <row r="73" spans="1:25">
+    <row r="73" spans="1:25" ht="16">
       <c r="A73" s="3" t="s">
         <v>104</v>
       </c>
@@ -7198,7 +7195,7 @@
       <c r="X73" s="1"/>
       <c r="Y73" s="1"/>
     </row>
-    <row r="74" spans="1:25">
+    <row r="74" spans="1:25" ht="16">
       <c r="A74" s="3" t="s">
         <v>106</v>
       </c>
@@ -7233,7 +7230,7 @@
       <c r="X74" s="2"/>
       <c r="Y74" s="2"/>
     </row>
-    <row r="75" spans="1:25">
+    <row r="75" spans="1:25" ht="16">
       <c r="A75" s="3" t="s">
         <v>109</v>
       </c>
@@ -7268,7 +7265,7 @@
       <c r="X75" s="2"/>
       <c r="Y75" s="2"/>
     </row>
-    <row r="76" spans="1:25">
+    <row r="76" spans="1:25" ht="16">
       <c r="A76" s="3" t="s">
         <v>938</v>
       </c>
@@ -7336,7 +7333,7 @@
       <c r="X77" s="63"/>
       <c r="Y77" s="63"/>
     </row>
-    <row r="78" spans="1:25">
+    <row r="78" spans="1:25" ht="16">
       <c r="A78" s="57" t="s">
         <v>866</v>
       </c>
@@ -7371,7 +7368,7 @@
       <c r="X78" s="1"/>
       <c r="Y78" s="1"/>
     </row>
-    <row r="79" spans="1:25">
+    <row r="79" spans="1:25" ht="16">
       <c r="A79" s="3" t="s">
         <v>866</v>
       </c>
@@ -7437,7 +7434,7 @@
       <c r="X80" s="1"/>
       <c r="Y80" s="1"/>
     </row>
-    <row r="81" spans="1:25">
+    <row r="81" spans="1:25" ht="16">
       <c r="A81" s="9" t="s">
         <v>1217</v>
       </c>
@@ -7472,7 +7469,7 @@
       <c r="X81" s="1"/>
       <c r="Y81" s="1"/>
     </row>
-    <row r="82" spans="1:25">
+    <row r="82" spans="1:25" ht="16">
       <c r="A82" s="9" t="s">
         <v>1220</v>
       </c>
@@ -7507,7 +7504,7 @@
       <c r="X82" s="1"/>
       <c r="Y82" s="1"/>
     </row>
-    <row r="83" spans="1:25" ht="30">
+    <row r="83" spans="1:25" ht="16">
       <c r="A83" s="9" t="s">
         <v>115</v>
       </c>
@@ -7608,7 +7605,7 @@
       <c r="X85" s="1"/>
       <c r="Y85" s="1"/>
     </row>
-    <row r="86" spans="1:25">
+    <row r="86" spans="1:25" ht="16">
       <c r="A86" s="3" t="s">
         <v>120</v>
       </c>
@@ -7643,7 +7640,7 @@
       <c r="X86" s="1"/>
       <c r="Y86" s="1"/>
     </row>
-    <row r="87" spans="1:25">
+    <row r="87" spans="1:25" ht="16">
       <c r="A87" s="7" t="s">
         <v>123</v>
       </c>
@@ -7744,7 +7741,7 @@
       <c r="X89" s="1"/>
       <c r="Y89" s="1"/>
     </row>
-    <row r="90" spans="1:25">
+    <row r="90" spans="1:25" ht="16">
       <c r="A90" s="3" t="s">
         <v>941</v>
       </c>
@@ -7814,7 +7811,7 @@
       <c r="X91" s="1"/>
       <c r="Y91" s="1"/>
     </row>
-    <row r="92" spans="1:25">
+    <row r="92" spans="1:25" ht="16">
       <c r="A92" s="3" t="s">
         <v>130</v>
       </c>
@@ -7849,7 +7846,7 @@
       <c r="X92" s="1"/>
       <c r="Y92" s="1"/>
     </row>
-    <row r="93" spans="1:25">
+    <row r="93" spans="1:25" ht="16">
       <c r="A93" s="61" t="s">
         <v>868</v>
       </c>
@@ -7884,7 +7881,7 @@
       <c r="X93" s="1"/>
       <c r="Y93" s="1"/>
     </row>
-    <row r="94" spans="1:25">
+    <row r="94" spans="1:25" ht="16">
       <c r="A94" s="3" t="s">
         <v>944</v>
       </c>
@@ -7919,7 +7916,7 @@
       <c r="X94" s="1"/>
       <c r="Y94" s="1"/>
     </row>
-    <row r="95" spans="1:25">
+    <row r="95" spans="1:25" ht="16">
       <c r="A95" s="7" t="s">
         <v>871</v>
       </c>
@@ -7954,7 +7951,7 @@
       <c r="X95" s="1"/>
       <c r="Y95" s="1"/>
     </row>
-    <row r="96" spans="1:25">
+    <row r="96" spans="1:25" ht="16">
       <c r="A96" s="3" t="s">
         <v>133</v>
       </c>
@@ -7989,7 +7986,7 @@
       <c r="X96" s="1"/>
       <c r="Y96" s="1"/>
     </row>
-    <row r="97" spans="1:25">
+    <row r="97" spans="1:25" ht="16">
       <c r="A97" s="5" t="s">
         <v>136</v>
       </c>
@@ -8024,7 +8021,7 @@
       <c r="X97" s="2"/>
       <c r="Y97" s="2"/>
     </row>
-    <row r="98" spans="1:25">
+    <row r="98" spans="1:25" ht="16">
       <c r="A98" s="5" t="s">
         <v>1073</v>
       </c>
@@ -8057,7 +8054,7 @@
       <c r="X98" s="2"/>
       <c r="Y98" s="2"/>
     </row>
-    <row r="99" spans="1:25">
+    <row r="99" spans="1:25" ht="16">
       <c r="A99" s="7" t="s">
         <v>138</v>
       </c>
@@ -8090,7 +8087,7 @@
       <c r="X99" s="1"/>
       <c r="Y99" s="1"/>
     </row>
-    <row r="100" spans="1:25">
+    <row r="100" spans="1:25" ht="16">
       <c r="A100" s="7" t="s">
         <v>140</v>
       </c>
@@ -8123,7 +8120,7 @@
       <c r="X100" s="1"/>
       <c r="Y100" s="1"/>
     </row>
-    <row r="101" spans="1:25">
+    <row r="101" spans="1:25" ht="16">
       <c r="A101" s="7" t="s">
         <v>1195</v>
       </c>
@@ -8156,7 +8153,7 @@
       <c r="X101" s="1"/>
       <c r="Y101" s="1"/>
     </row>
-    <row r="102" spans="1:25">
+    <row r="102" spans="1:25" ht="16">
       <c r="A102" s="7" t="s">
         <v>1226</v>
       </c>
@@ -8189,7 +8186,7 @@
       <c r="X102" s="1"/>
       <c r="Y102" s="1"/>
     </row>
-    <row r="103" spans="1:25">
+    <row r="103" spans="1:25" ht="16">
       <c r="A103" s="7" t="s">
         <v>1074</v>
       </c>
@@ -8224,7 +8221,7 @@
       <c r="X103" s="1"/>
       <c r="Y103" s="1"/>
     </row>
-    <row r="104" spans="1:25">
+    <row r="104" spans="1:25" ht="16">
       <c r="A104" s="5" t="s">
         <v>142</v>
       </c>
@@ -8259,7 +8256,7 @@
       <c r="X104" s="1"/>
       <c r="Y104" s="1"/>
     </row>
-    <row r="105" spans="1:25">
+    <row r="105" spans="1:25" ht="16">
       <c r="A105" s="5" t="s">
         <v>145</v>
       </c>
@@ -25334,11 +25331,12 @@
     <hyperlink ref="C82" r:id="rId275" xr:uid="{2F7AE097-DEF5-4146-A716-E70F95AD9CF2}"/>
     <hyperlink ref="C259" r:id="rId276" xr:uid="{47C430DC-91D2-1440-9854-F4E2C65DA30F}"/>
     <hyperlink ref="C178" r:id="rId277" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
+    <hyperlink ref="C8" r:id="rId278" xr:uid="{B3656FCB-334A-C24F-B9FD-77A2E94511A7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId278"/>
+    <tablePart r:id="rId279"/>
   </tableParts>
 </worksheet>
 </file>
@@ -25346,9 +25344,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A21:A1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="10.7109375" customWidth="1"/>
+    <col min="1" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -26340,9 +26338,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A21:A1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="26" width="10.7109375" customWidth="1"/>
+    <col min="1" max="26" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D69C06-D230-D74A-B16F-D8D3361A7550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AD01A61-96B6-7348-BEB9-D46A5B60CC53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3976,7 +3976,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="44">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4262,14 +4262,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -4342,7 +4334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4506,9 +4498,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -4565,16 +4554,16 @@
     <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
@@ -4848,16 +4837,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A2" s="74" t="s">
+      <c r="A2" s="73" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="75" t="s">
+      <c r="C2" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="73" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1"/>
@@ -4883,14 +4872,14 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="16">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="77" t="s">
         <v>929</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="78" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="77" t="s">
         <v>930</v>
       </c>
-      <c r="D3" s="79" t="s">
+      <c r="D3" s="78" t="s">
         <v>931</v>
       </c>
     </row>
@@ -4921,14 +4910,14 @@
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="76" t="s">
+      <c r="A6" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="76"/>
-      <c r="C6" s="77" t="s">
+      <c r="B6" s="75"/>
+      <c r="C6" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="75" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="2"/>
@@ -6032,14 +6021,14 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" spans="1:25">
-      <c r="A39" s="72" t="s">
+      <c r="A39" s="71" t="s">
         <v>858</v>
       </c>
-      <c r="B39" s="72"/>
-      <c r="C39" s="73" t="s">
+      <c r="B39" s="71"/>
+      <c r="C39" s="72" t="s">
         <v>859</v>
       </c>
-      <c r="D39" s="72" t="s">
+      <c r="D39" s="71" t="s">
         <v>858</v>
       </c>
       <c r="E39" s="1"/>
@@ -6065,14 +6054,14 @@
       <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="1:25">
-      <c r="A40" s="72" t="s">
+      <c r="A40" s="71" t="s">
         <v>1062</v>
       </c>
-      <c r="B40" s="72"/>
-      <c r="C40" s="73" t="s">
+      <c r="B40" s="71"/>
+      <c r="C40" s="72" t="s">
         <v>1063</v>
       </c>
-      <c r="D40" s="72" t="s">
+      <c r="D40" s="71" t="s">
         <v>1062</v>
       </c>
       <c r="E40" s="1"/>
@@ -7019,27 +7008,27 @@
       <c r="D68" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E68" s="60"/>
-      <c r="F68" s="60"/>
-      <c r="G68" s="60"/>
-      <c r="H68" s="60"/>
-      <c r="I68" s="60"/>
-      <c r="J68" s="60"/>
-      <c r="K68" s="60"/>
-      <c r="L68" s="60"/>
-      <c r="M68" s="60"/>
-      <c r="N68" s="60"/>
-      <c r="O68" s="60"/>
-      <c r="P68" s="60"/>
-      <c r="Q68" s="60"/>
-      <c r="R68" s="60"/>
-      <c r="S68" s="60"/>
-      <c r="T68" s="60"/>
-      <c r="U68" s="60"/>
-      <c r="V68" s="60"/>
-      <c r="W68" s="60"/>
-      <c r="X68" s="60"/>
-      <c r="Y68" s="60"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="59"/>
+      <c r="J68" s="59"/>
+      <c r="K68" s="59"/>
+      <c r="L68" s="59"/>
+      <c r="M68" s="59"/>
+      <c r="N68" s="59"/>
+      <c r="O68" s="59"/>
+      <c r="P68" s="59"/>
+      <c r="Q68" s="59"/>
+      <c r="R68" s="59"/>
+      <c r="S68" s="59"/>
+      <c r="T68" s="59"/>
+      <c r="U68" s="59"/>
+      <c r="V68" s="59"/>
+      <c r="W68" s="59"/>
+      <c r="X68" s="59"/>
+      <c r="Y68" s="59"/>
     </row>
     <row r="69" spans="1:25" ht="16">
       <c r="A69" s="5" t="s">
@@ -7365,27 +7354,27 @@
       <c r="D78" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="E78" s="63"/>
-      <c r="F78" s="63"/>
-      <c r="G78" s="63"/>
-      <c r="H78" s="63"/>
-      <c r="I78" s="63"/>
-      <c r="J78" s="63"/>
-      <c r="K78" s="63"/>
-      <c r="L78" s="63"/>
-      <c r="M78" s="63"/>
-      <c r="N78" s="63"/>
-      <c r="O78" s="63"/>
-      <c r="P78" s="63"/>
-      <c r="Q78" s="63"/>
-      <c r="R78" s="63"/>
-      <c r="S78" s="63"/>
-      <c r="T78" s="63"/>
-      <c r="U78" s="63"/>
-      <c r="V78" s="63"/>
-      <c r="W78" s="63"/>
-      <c r="X78" s="63"/>
-      <c r="Y78" s="63"/>
+      <c r="E78" s="62"/>
+      <c r="F78" s="62"/>
+      <c r="G78" s="62"/>
+      <c r="H78" s="62"/>
+      <c r="I78" s="62"/>
+      <c r="J78" s="62"/>
+      <c r="K78" s="62"/>
+      <c r="L78" s="62"/>
+      <c r="M78" s="62"/>
+      <c r="N78" s="62"/>
+      <c r="O78" s="62"/>
+      <c r="P78" s="62"/>
+      <c r="Q78" s="62"/>
+      <c r="R78" s="62"/>
+      <c r="S78" s="62"/>
+      <c r="T78" s="62"/>
+      <c r="U78" s="62"/>
+      <c r="V78" s="62"/>
+      <c r="W78" s="62"/>
+      <c r="X78" s="62"/>
+      <c r="Y78" s="62"/>
     </row>
     <row r="79" spans="1:25" ht="16">
       <c r="A79" s="57" t="s">
@@ -7394,7 +7383,7 @@
       <c r="B79" s="58" t="s">
         <v>866</v>
       </c>
-      <c r="C79" s="59" t="s">
+      <c r="C79" s="88" t="s">
         <v>867</v>
       </c>
       <c r="D79" s="57" t="s">
@@ -7901,16 +7890,16 @@
       <c r="Y93" s="1"/>
     </row>
     <row r="94" spans="1:25" ht="16">
-      <c r="A94" s="61" t="s">
+      <c r="A94" s="60" t="s">
         <v>868</v>
       </c>
-      <c r="B94" s="61" t="s">
+      <c r="B94" s="60" t="s">
         <v>869</v>
       </c>
-      <c r="C94" s="62" t="s">
+      <c r="C94" s="61" t="s">
         <v>870</v>
       </c>
-      <c r="D94" s="61" t="s">
+      <c r="D94" s="60" t="s">
         <v>868</v>
       </c>
       <c r="E94" s="1"/>
@@ -7977,7 +7966,7 @@
       <c r="B96" s="7" t="s">
         <v>872</v>
       </c>
-      <c r="C96" s="80" t="s">
+      <c r="C96" s="79" t="s">
         <v>873</v>
       </c>
       <c r="D96" s="7" t="s">
@@ -8212,7 +8201,7 @@
         <v>1195</v>
       </c>
       <c r="B103" s="7"/>
-      <c r="C103" s="80" t="s">
+      <c r="C103" s="79" t="s">
         <v>1196</v>
       </c>
       <c r="D103" s="7" t="s">
@@ -8245,7 +8234,7 @@
         <v>1226</v>
       </c>
       <c r="B104" s="7"/>
-      <c r="C104" s="80" t="s">
+      <c r="C104" s="79" t="s">
         <v>1227</v>
       </c>
       <c r="D104" s="7" t="s">
@@ -8820,7 +8809,7 @@
         <v>1197</v>
       </c>
       <c r="B121" s="5"/>
-      <c r="C121" s="87" t="s">
+      <c r="C121" s="85" t="s">
         <v>1077</v>
       </c>
       <c r="D121" s="5" t="s">
@@ -10217,7 +10206,7 @@
         <v>1174</v>
       </c>
       <c r="B162" s="7"/>
-      <c r="C162" s="80" t="s">
+      <c r="C162" s="79" t="s">
         <v>1175</v>
       </c>
       <c r="D162" s="7" t="s">
@@ -11064,7 +11053,7 @@
       <c r="B187" s="7" t="s">
         <v>881</v>
       </c>
-      <c r="C187" s="64" t="s">
+      <c r="C187" s="63" t="s">
         <v>882</v>
       </c>
       <c r="D187" s="7" t="s">
@@ -11097,7 +11086,7 @@
         <v>1256</v>
       </c>
       <c r="B188" s="7"/>
-      <c r="C188" s="64" t="s">
+      <c r="C188" s="63" t="s">
         <v>1257</v>
       </c>
       <c r="D188" s="7" t="s">
@@ -11161,13 +11150,13 @@
       <c r="Y189" s="1"/>
     </row>
     <row r="190" spans="1:25" ht="15" customHeight="1">
-      <c r="A190" s="81" t="s">
+      <c r="A190" s="80" t="s">
         <v>1095</v>
       </c>
       <c r="C190" t="s">
         <v>1096</v>
       </c>
-      <c r="D190" s="81" t="s">
+      <c r="D190" s="80" t="s">
         <v>1095</v>
       </c>
     </row>
@@ -11211,7 +11200,7 @@
       <c r="B192" s="7" t="s">
         <v>885</v>
       </c>
-      <c r="C192" s="64" t="s">
+      <c r="C192" s="63" t="s">
         <v>886</v>
       </c>
       <c r="D192" s="7" t="s">
@@ -11655,7 +11644,7 @@
       <c r="A205" s="7" t="s">
         <v>1101</v>
       </c>
-      <c r="C205" s="80" t="s">
+      <c r="C205" s="79" t="s">
         <v>1100</v>
       </c>
       <c r="D205" s="7" t="s">
@@ -11766,27 +11755,27 @@
       <c r="D208" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="E208" s="67"/>
-      <c r="F208" s="67"/>
-      <c r="G208" s="67"/>
-      <c r="H208" s="67"/>
-      <c r="I208" s="67"/>
-      <c r="J208" s="67"/>
-      <c r="K208" s="67"/>
-      <c r="L208" s="67"/>
-      <c r="M208" s="67"/>
-      <c r="N208" s="67"/>
-      <c r="O208" s="67"/>
-      <c r="P208" s="67"/>
-      <c r="Q208" s="67"/>
-      <c r="R208" s="67"/>
-      <c r="S208" s="67"/>
-      <c r="T208" s="67"/>
-      <c r="U208" s="67"/>
-      <c r="V208" s="67"/>
-      <c r="W208" s="67"/>
-      <c r="X208" s="67"/>
-      <c r="Y208" s="67"/>
+      <c r="E208" s="66"/>
+      <c r="F208" s="66"/>
+      <c r="G208" s="66"/>
+      <c r="H208" s="66"/>
+      <c r="I208" s="66"/>
+      <c r="J208" s="66"/>
+      <c r="K208" s="66"/>
+      <c r="L208" s="66"/>
+      <c r="M208" s="66"/>
+      <c r="N208" s="66"/>
+      <c r="O208" s="66"/>
+      <c r="P208" s="66"/>
+      <c r="Q208" s="66"/>
+      <c r="R208" s="66"/>
+      <c r="S208" s="66"/>
+      <c r="T208" s="66"/>
+      <c r="U208" s="66"/>
+      <c r="V208" s="66"/>
+      <c r="W208" s="66"/>
+      <c r="X208" s="66"/>
+      <c r="Y208" s="66"/>
     </row>
     <row r="209" spans="1:25" ht="15.75" customHeight="1">
       <c r="A209" s="7" t="s">
@@ -11801,27 +11790,27 @@
       <c r="D209" s="7" t="s">
         <v>1262</v>
       </c>
-      <c r="E209" s="67"/>
-      <c r="F209" s="67"/>
-      <c r="G209" s="67"/>
-      <c r="H209" s="67"/>
-      <c r="I209" s="67"/>
-      <c r="J209" s="67"/>
-      <c r="K209" s="67"/>
-      <c r="L209" s="67"/>
-      <c r="M209" s="67"/>
-      <c r="N209" s="67"/>
-      <c r="O209" s="67"/>
-      <c r="P209" s="67"/>
-      <c r="Q209" s="67"/>
-      <c r="R209" s="67"/>
-      <c r="S209" s="67"/>
-      <c r="T209" s="67"/>
-      <c r="U209" s="67"/>
-      <c r="V209" s="67"/>
-      <c r="W209" s="67"/>
-      <c r="X209" s="67"/>
-      <c r="Y209" s="67"/>
+      <c r="E209" s="66"/>
+      <c r="F209" s="66"/>
+      <c r="G209" s="66"/>
+      <c r="H209" s="66"/>
+      <c r="I209" s="66"/>
+      <c r="J209" s="66"/>
+      <c r="K209" s="66"/>
+      <c r="L209" s="66"/>
+      <c r="M209" s="66"/>
+      <c r="N209" s="66"/>
+      <c r="O209" s="66"/>
+      <c r="P209" s="66"/>
+      <c r="Q209" s="66"/>
+      <c r="R209" s="66"/>
+      <c r="S209" s="66"/>
+      <c r="T209" s="66"/>
+      <c r="U209" s="66"/>
+      <c r="V209" s="66"/>
+      <c r="W209" s="66"/>
+      <c r="X209" s="66"/>
+      <c r="Y209" s="66"/>
     </row>
     <row r="210" spans="1:25" ht="15.75" customHeight="1">
       <c r="A210" s="3" t="s">
@@ -11836,27 +11825,27 @@
       <c r="D210" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E210" s="67"/>
-      <c r="F210" s="67"/>
-      <c r="G210" s="67"/>
-      <c r="H210" s="67"/>
-      <c r="I210" s="67"/>
-      <c r="J210" s="67"/>
-      <c r="K210" s="67"/>
-      <c r="L210" s="67"/>
-      <c r="M210" s="67"/>
-      <c r="N210" s="67"/>
-      <c r="O210" s="67"/>
-      <c r="P210" s="67"/>
-      <c r="Q210" s="67"/>
-      <c r="R210" s="67"/>
-      <c r="S210" s="67"/>
-      <c r="T210" s="67"/>
-      <c r="U210" s="67"/>
-      <c r="V210" s="67"/>
-      <c r="W210" s="67"/>
-      <c r="X210" s="67"/>
-      <c r="Y210" s="67"/>
+      <c r="E210" s="66"/>
+      <c r="F210" s="66"/>
+      <c r="G210" s="66"/>
+      <c r="H210" s="66"/>
+      <c r="I210" s="66"/>
+      <c r="J210" s="66"/>
+      <c r="K210" s="66"/>
+      <c r="L210" s="66"/>
+      <c r="M210" s="66"/>
+      <c r="N210" s="66"/>
+      <c r="O210" s="66"/>
+      <c r="P210" s="66"/>
+      <c r="Q210" s="66"/>
+      <c r="R210" s="66"/>
+      <c r="S210" s="66"/>
+      <c r="T210" s="66"/>
+      <c r="U210" s="66"/>
+      <c r="V210" s="66"/>
+      <c r="W210" s="66"/>
+      <c r="X210" s="66"/>
+      <c r="Y210" s="66"/>
     </row>
     <row r="211" spans="1:25" ht="15.75" customHeight="1">
       <c r="A211" s="5" t="s">
@@ -11898,7 +11887,7 @@
       <c r="B212" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="C212" s="82" t="s">
+      <c r="C212" s="81" t="s">
         <v>1103</v>
       </c>
       <c r="D212" s="5" t="s">
@@ -11933,7 +11922,7 @@
       <c r="B213" s="5" t="s">
         <v>1104</v>
       </c>
-      <c r="C213" s="82" t="s">
+      <c r="C213" s="81" t="s">
         <v>1105</v>
       </c>
       <c r="D213" s="5" t="s">
@@ -11966,7 +11955,7 @@
         <v>336</v>
       </c>
       <c r="B214" s="27"/>
-      <c r="C214" s="71" t="s">
+      <c r="C214" s="70" t="s">
         <v>840</v>
       </c>
       <c r="D214" s="3" t="s">
@@ -12542,7 +12531,7 @@
       <c r="A231" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="B231" s="89" t="s">
+      <c r="B231" s="87" t="s">
         <v>1266</v>
       </c>
       <c r="C231" s="3" t="s">
@@ -12988,16 +12977,16 @@
       <c r="Y243" s="1"/>
     </row>
     <row r="244" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A244" s="65" t="s">
+      <c r="A244" s="64" t="s">
         <v>891</v>
       </c>
-      <c r="B244" s="65" t="s">
+      <c r="B244" s="64" t="s">
         <v>891</v>
       </c>
-      <c r="C244" s="66" t="s">
+      <c r="C244" s="65" t="s">
         <v>729</v>
       </c>
-      <c r="D244" s="65" t="s">
+      <c r="D244" s="64" t="s">
         <v>891</v>
       </c>
       <c r="E244" s="1"/>
@@ -13124,16 +13113,16 @@
       <c r="Y247" s="1"/>
     </row>
     <row r="248" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A248" s="65" t="s">
+      <c r="A248" s="64" t="s">
         <v>894</v>
       </c>
-      <c r="B248" s="65" t="s">
+      <c r="B248" s="64" t="s">
         <v>895</v>
       </c>
-      <c r="C248" s="66" t="s">
+      <c r="C248" s="65" t="s">
         <v>896</v>
       </c>
-      <c r="D248" s="65" t="s">
+      <c r="D248" s="64" t="s">
         <v>894</v>
       </c>
       <c r="E248" s="2"/>
@@ -13330,16 +13319,16 @@
       <c r="Y253" s="1"/>
     </row>
     <row r="254" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A254" s="65" t="s">
+      <c r="A254" s="64" t="s">
         <v>892</v>
       </c>
-      <c r="B254" s="65" t="s">
+      <c r="B254" s="64" t="s">
         <v>892</v>
       </c>
-      <c r="C254" s="66" t="s">
+      <c r="C254" s="65" t="s">
         <v>893</v>
       </c>
-      <c r="D254" s="65" t="s">
+      <c r="D254" s="64" t="s">
         <v>892</v>
       </c>
       <c r="E254" s="1"/>
@@ -13365,16 +13354,16 @@
       <c r="Y254" s="1"/>
     </row>
     <row r="255" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A255" s="65" t="s">
+      <c r="A255" s="64" t="s">
         <v>1110</v>
       </c>
-      <c r="B255" s="65" t="s">
+      <c r="B255" s="64" t="s">
         <v>1111</v>
       </c>
-      <c r="C255" s="66" t="s">
+      <c r="C255" s="65" t="s">
         <v>1112</v>
       </c>
-      <c r="D255" s="65" t="s">
+      <c r="D255" s="64" t="s">
         <v>1113</v>
       </c>
       <c r="E255" s="1"/>
@@ -13400,14 +13389,14 @@
       <c r="Y255" s="1"/>
     </row>
     <row r="256" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A256" s="65" t="s">
+      <c r="A256" s="64" t="s">
         <v>897</v>
       </c>
-      <c r="B256" s="65"/>
-      <c r="C256" s="66" t="s">
+      <c r="B256" s="64"/>
+      <c r="C256" s="65" t="s">
         <v>898</v>
       </c>
-      <c r="D256" s="65" t="s">
+      <c r="D256" s="64" t="s">
         <v>897</v>
       </c>
       <c r="E256" s="1"/>
@@ -14921,7 +14910,7 @@
       <c r="Y300" s="2"/>
     </row>
     <row r="301" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A301" s="83" t="s">
+      <c r="A301" s="82" t="s">
         <v>1127</v>
       </c>
       <c r="B301" s="7"/>
@@ -16831,7 +16820,7 @@
         <v>601</v>
       </c>
       <c r="B357" s="3"/>
-      <c r="C357" s="3" t="s">
+      <c r="C357" s="50" t="s">
         <v>602</v>
       </c>
       <c r="D357" s="3" t="s">
@@ -17280,7 +17269,7 @@
       <c r="B370" s="13" t="s">
         <v>1199</v>
       </c>
-      <c r="C370" s="88" t="s">
+      <c r="C370" s="86" t="s">
         <v>1200</v>
       </c>
       <c r="D370" s="13" t="s">
@@ -17480,7 +17469,7 @@
       <c r="B376" s="13" t="s">
         <v>914</v>
       </c>
-      <c r="C376" s="68" t="s">
+      <c r="C376" s="67" t="s">
         <v>915</v>
       </c>
       <c r="D376" s="13" t="s">
@@ -17513,7 +17502,7 @@
         <v>1285</v>
       </c>
       <c r="B377" s="13"/>
-      <c r="C377" s="68" t="s">
+      <c r="C377" s="67" t="s">
         <v>1286</v>
       </c>
       <c r="D377" s="13" t="s">
@@ -17616,7 +17605,7 @@
       <c r="B380" s="13" t="s">
         <v>918</v>
       </c>
-      <c r="C380" s="68" t="s">
+      <c r="C380" s="67" t="s">
         <v>919</v>
       </c>
       <c r="D380" s="13" t="s">
@@ -17649,7 +17638,7 @@
         <v>1287</v>
       </c>
       <c r="B381" s="13"/>
-      <c r="C381" s="68" t="s">
+      <c r="C381" s="67" t="s">
         <v>1288</v>
       </c>
       <c r="D381" s="13" t="s">
@@ -17713,7 +17702,7 @@
       <c r="Y382" s="1"/>
     </row>
     <row r="383" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A383" s="81" t="s">
+      <c r="A383" s="80" t="s">
         <v>1139</v>
       </c>
       <c r="B383" s="13" t="s">
@@ -17748,16 +17737,16 @@
       <c r="Y383" s="1"/>
     </row>
     <row r="384" spans="1:25" ht="15.75" customHeight="1">
-      <c r="A384" s="84" t="s">
+      <c r="A384" s="83" t="s">
         <v>1142</v>
       </c>
-      <c r="B384" s="85" t="s">
+      <c r="B384" s="84" t="s">
         <v>1141</v>
       </c>
       <c r="C384" s="86" t="s">
         <v>1143</v>
       </c>
-      <c r="D384" s="85" t="s">
+      <c r="D384" s="84" t="s">
         <v>1142</v>
       </c>
       <c r="E384" s="1"/>
@@ -17820,7 +17809,7 @@
         <v>649</v>
       </c>
       <c r="B386" s="9"/>
-      <c r="C386" s="11" t="s">
+      <c r="C386" s="52" t="s">
         <v>650</v>
       </c>
       <c r="D386" s="9" t="s">
@@ -18055,7 +18044,7 @@
       <c r="B393" s="13" t="s">
         <v>921</v>
       </c>
-      <c r="C393" s="68" t="s">
+      <c r="C393" s="67" t="s">
         <v>922</v>
       </c>
       <c r="D393" s="13" t="s">
@@ -18088,7 +18077,7 @@
         <v>1148</v>
       </c>
       <c r="B394" s="13"/>
-      <c r="C394" s="68" t="s">
+      <c r="C394" s="67" t="s">
         <v>1149</v>
       </c>
       <c r="D394" s="13" t="s">
@@ -18498,7 +18487,7 @@
         <v>1150</v>
       </c>
       <c r="B406" s="13"/>
-      <c r="C406" s="14" t="s">
+      <c r="C406" s="86" t="s">
         <v>1151</v>
       </c>
       <c r="D406" s="13" t="s">
@@ -19239,7 +19228,7 @@
         <v>1156</v>
       </c>
       <c r="B432" s="9"/>
-      <c r="C432" s="10" t="s">
+      <c r="C432" s="52" t="s">
         <v>1157</v>
       </c>
       <c r="D432" s="9" t="s">
@@ -19983,10 +19972,10 @@
       <c r="B489" s="7" t="s">
         <v>927</v>
       </c>
-      <c r="C489" s="69" t="s">
+      <c r="C489" s="68" t="s">
         <v>928</v>
       </c>
-      <c r="D489" s="70" t="s">
+      <c r="D489" s="69" t="s">
         <v>926</v>
       </c>
     </row>
@@ -25455,11 +25444,15 @@
     <hyperlink ref="C180" r:id="rId277" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
     <hyperlink ref="C8" r:id="rId278" xr:uid="{B3656FCB-334A-C24F-B9FD-77A2E94511A7}"/>
     <hyperlink ref="C241" r:id="rId279" xr:uid="{8B707DBA-5046-0842-8A9D-B479BE7B3F26}"/>
+    <hyperlink ref="C432" r:id="rId280" xr:uid="{F0689FA1-BCC1-394B-AED5-B9A03C77A143}"/>
+    <hyperlink ref="C384" r:id="rId281" xr:uid="{6636B7ED-934A-D247-B837-6E7A652A0F48}"/>
+    <hyperlink ref="C357" r:id="rId282" xr:uid="{27DBBE71-CF56-034F-A814-92AB6B007119}"/>
+    <hyperlink ref="C406" r:id="rId283" xr:uid="{65BB9F36-0658-5746-8674-E771C17EC4A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId280"/>
+    <tablePart r:id="rId284"/>
   </tableParts>
 </worksheet>
 </file>

--- a/data/xlsx/Baernreither_Ortsregister_2023.xlsx
+++ b/data/xlsx/Baernreither_Ortsregister_2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/melaniedaubner/Documents/Ohne Titel/data/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christofaichner/Documents/GitHub/baernreither-data/data/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9670448B-1CC6-694C-AEBF-4F988AEA938D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6952E402-D6E4-944F-96BA-DF15BB47FA4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="12720" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="26860" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1890" uniqueCount="1453">
   <si>
     <t>Name</t>
   </si>
@@ -4384,6 +4384,9 @@
   </si>
   <si>
     <t>Zuerich</t>
+  </si>
+  <si>
+    <t>https://www.geonames.org/6697801/central-macedonia.html</t>
   </si>
 </sst>
 </file>
@@ -4760,7 +4763,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4995,11 +4998,12 @@
     </xf>
     <xf numFmtId="0" fontId="39" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="8" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="43" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5386,7 +5390,7 @@
       <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="50" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -5458,27 +5462,27 @@
       <c r="D9" s="90" t="s">
         <v>1314</v>
       </c>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="92"/>
-      <c r="I9" s="92"/>
-      <c r="J9" s="92"/>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
-      <c r="N9" s="92"/>
-      <c r="O9" s="92"/>
-      <c r="P9" s="92"/>
-      <c r="Q9" s="92"/>
-      <c r="R9" s="92"/>
-      <c r="S9" s="92"/>
-      <c r="T9" s="92"/>
-      <c r="U9" s="92"/>
-      <c r="V9" s="92"/>
-      <c r="W9" s="92"/>
-      <c r="X9" s="92"/>
-      <c r="Y9" s="92"/>
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="80"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="80"/>
+      <c r="L9" s="80"/>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="80"/>
+      <c r="T9" s="80"/>
+      <c r="U9" s="80"/>
+      <c r="V9" s="80"/>
+      <c r="W9" s="80"/>
+      <c r="X9" s="80"/>
+      <c r="Y9" s="80"/>
     </row>
     <row r="10" spans="1:25" ht="16">
       <c r="A10" s="7" t="s">
@@ -5491,27 +5495,27 @@
       <c r="D10" s="7" t="s">
         <v>853</v>
       </c>
-      <c r="E10" s="93"/>
-      <c r="F10" s="93"/>
-      <c r="G10" s="93"/>
-      <c r="H10" s="93"/>
-      <c r="I10" s="93"/>
-      <c r="J10" s="93"/>
-      <c r="K10" s="93"/>
-      <c r="L10" s="93"/>
-      <c r="M10" s="93"/>
-      <c r="N10" s="93"/>
-      <c r="O10" s="93"/>
-      <c r="P10" s="93"/>
-      <c r="Q10" s="93"/>
-      <c r="R10" s="93"/>
-      <c r="S10" s="93"/>
-      <c r="T10" s="93"/>
-      <c r="U10" s="93"/>
-      <c r="V10" s="93"/>
-      <c r="W10" s="93"/>
-      <c r="X10" s="93"/>
-      <c r="Y10" s="93"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="16">
       <c r="A11" s="5" t="s">
@@ -5526,27 +5530,27 @@
       <c r="D11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="93"/>
-      <c r="F11" s="93"/>
-      <c r="G11" s="93"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="93"/>
-      <c r="J11" s="93"/>
-      <c r="K11" s="93"/>
-      <c r="L11" s="93"/>
-      <c r="M11" s="93"/>
-      <c r="N11" s="93"/>
-      <c r="O11" s="93"/>
-      <c r="P11" s="93"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="93"/>
-      <c r="S11" s="93"/>
-      <c r="T11" s="93"/>
-      <c r="U11" s="93"/>
-      <c r="V11" s="93"/>
-      <c r="W11" s="93"/>
-      <c r="X11" s="93"/>
-      <c r="Y11" s="93"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+      <c r="V11" s="1"/>
+      <c r="W11" s="1"/>
+      <c r="X11" s="1"/>
+      <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:25" ht="32">
       <c r="A12" s="3" t="s">
@@ -5561,27 +5565,27 @@
       <c r="D12" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="E12" s="93"/>
-      <c r="F12" s="93"/>
-      <c r="G12" s="93"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="93"/>
-      <c r="J12" s="93"/>
-      <c r="K12" s="93"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="93"/>
-      <c r="N12" s="93"/>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="93"/>
-      <c r="R12" s="93"/>
-      <c r="S12" s="93"/>
-      <c r="T12" s="93"/>
-      <c r="U12" s="93"/>
-      <c r="V12" s="93"/>
-      <c r="W12" s="93"/>
-      <c r="X12" s="93"/>
-      <c r="Y12" s="93"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="16">
       <c r="A13" s="3" t="s">
@@ -6528,7 +6532,7 @@
         <v>858</v>
       </c>
       <c r="B41" s="71"/>
-      <c r="C41" s="72" t="s">
+      <c r="C41" s="94" t="s">
         <v>859</v>
       </c>
       <c r="D41" s="71" t="s">
@@ -9611,7 +9615,7 @@
         <v>169</v>
       </c>
       <c r="B132" s="3"/>
-      <c r="C132" s="12" t="s">
+      <c r="C132" s="50" t="s">
         <v>170</v>
       </c>
       <c r="D132" s="3" t="s">
@@ -14254,7 +14258,7 @@
         <v>891</v>
       </c>
       <c r="C269" s="65" t="s">
-        <v>729</v>
+        <v>1452</v>
       </c>
       <c r="D269" s="64" t="s">
         <v>891</v>
@@ -14865,7 +14869,7 @@
         <v>987</v>
       </c>
       <c r="B287" s="3"/>
-      <c r="C287" s="3" t="s">
+      <c r="C287" s="50" t="s">
         <v>988</v>
       </c>
       <c r="D287" s="1" t="s">
@@ -15880,7 +15884,7 @@
       <c r="C317" s="91" t="s">
         <v>1391</v>
       </c>
-      <c r="D317" s="94" t="s">
+      <c r="D317" s="92" t="s">
         <v>1390</v>
       </c>
       <c r="E317" s="2"/>
@@ -15948,7 +15952,7 @@
       <c r="C319" s="91" t="s">
         <v>1393</v>
       </c>
-      <c r="D319" s="94" t="s">
+      <c r="D319" s="92" t="s">
         <v>1394</v>
       </c>
       <c r="E319" s="1"/>
@@ -17807,7 +17811,7 @@
       <c r="C374" s="91" t="s">
         <v>1414</v>
       </c>
-      <c r="D374" s="94" t="s">
+      <c r="D374" s="92" t="s">
         <v>1412</v>
       </c>
       <c r="E374" s="2"/>
@@ -17840,7 +17844,7 @@
       <c r="C375" s="91" t="s">
         <v>1416</v>
       </c>
-      <c r="D375" s="94" t="s">
+      <c r="D375" s="92" t="s">
         <v>1415</v>
       </c>
       <c r="E375" s="2"/>
@@ -18105,7 +18109,7 @@
         <v>1419</v>
       </c>
       <c r="B383" s="43"/>
-      <c r="C383" s="95" t="s">
+      <c r="C383" s="93" t="s">
         <v>1131</v>
       </c>
       <c r="D383" s="43" t="s">
@@ -19267,7 +19271,7 @@
       <c r="B417" s="13" t="s">
         <v>625</v>
       </c>
-      <c r="C417" s="41" t="s">
+      <c r="C417" s="86" t="s">
         <v>626</v>
       </c>
       <c r="D417" s="13" t="s">
@@ -21643,7 +21647,7 @@
       <c r="B503" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="C503" s="3" t="s">
+      <c r="C503" s="50" t="s">
         <v>765</v>
       </c>
       <c r="D503" s="3" t="s">
@@ -27644,107 +27648,108 @@
     <hyperlink ref="C208" r:id="rId244" xr:uid="{A0B7F6C6-0B8F-8D4B-B4BC-AE7AECCC68C7}"/>
     <hyperlink ref="C214" r:id="rId245" xr:uid="{F699C5E6-56FF-4E4E-BCEA-D6C02CE4FE14}"/>
     <hyperlink ref="C220" r:id="rId246" xr:uid="{8A036D46-5D20-9D47-80F4-72C1BAA307D0}"/>
-    <hyperlink ref="C269" r:id="rId247" xr:uid="{F849399C-0F88-7D45-BEDA-B9D0BDE046F4}"/>
-    <hyperlink ref="C282" r:id="rId248" xr:uid="{4DF4BC3F-5FEC-5241-A415-BA4D9AB2E9C4}"/>
-    <hyperlink ref="C276" r:id="rId249" xr:uid="{B4AAB667-FFFA-F64C-BC79-708CC2119E9B}"/>
-    <hyperlink ref="C284" r:id="rId250" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
-    <hyperlink ref="C311" r:id="rId251" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
-    <hyperlink ref="C315" r:id="rId252" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
-    <hyperlink ref="C387" r:id="rId253" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
-    <hyperlink ref="C395" r:id="rId254" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
-    <hyperlink ref="C426" r:id="rId255" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
-    <hyperlink ref="C430" r:id="rId256" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
-    <hyperlink ref="C443" r:id="rId257" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
-    <hyperlink ref="C536" r:id="rId258" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
-    <hyperlink ref="C546" r:id="rId259" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
-    <hyperlink ref="C263" r:id="rId260" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
-    <hyperlink ref="C303" r:id="rId261" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
-    <hyperlink ref="C338" r:id="rId262" xr:uid="{20FF35A0-9072-C349-94BD-F07C44AE26C4}"/>
-    <hyperlink ref="C235" r:id="rId263" xr:uid="{3DD3F81F-9B00-6C41-B9BD-0B246E4511FC}"/>
-    <hyperlink ref="C309" r:id="rId264" xr:uid="{2653430D-3B53-3342-82F4-5C182DA7B834}"/>
-    <hyperlink ref="C181" r:id="rId265" xr:uid="{A86712C1-CF60-EC43-ACC0-2F9F008D6A13}"/>
-    <hyperlink ref="C47" r:id="rId266" xr:uid="{DEDBA11F-1236-FB46-9BF5-3341C3B4F82F}"/>
-    <hyperlink ref="C60" r:id="rId267" xr:uid="{A2CD9817-DB83-EB44-B2B9-3529BB5D6BE5}"/>
-    <hyperlink ref="C5" r:id="rId268" xr:uid="{7D5C79DD-2090-AE42-8950-23F80385F704}"/>
-    <hyperlink ref="C118" r:id="rId269" xr:uid="{6FC99DC1-4D16-F748-9C57-B02E3B5B7ACB}"/>
-    <hyperlink ref="C137" r:id="rId270" xr:uid="{ED9FF9E1-0C2B-0E44-A3EF-F61085E02321}"/>
-    <hyperlink ref="C228" r:id="rId271" xr:uid="{525BDD05-8A3F-424A-B398-414EBECB8EF0}"/>
-    <hyperlink ref="C419" r:id="rId272" xr:uid="{220744C9-5318-7F48-8555-FABFF8F9D26F}"/>
-    <hyperlink ref="C119" r:id="rId273" xr:uid="{B187C345-3CCA-7A42-A65B-9D24BD058186}"/>
-    <hyperlink ref="C133" r:id="rId274" xr:uid="{8CDF73E8-B690-9A45-811B-8EBDEC80D17B}"/>
-    <hyperlink ref="C92" r:id="rId275" xr:uid="{2F7AE097-DEF5-4146-A716-E70F95AD9CF2}"/>
-    <hyperlink ref="C291" r:id="rId276" xr:uid="{47C430DC-91D2-1440-9854-F4E2C65DA30F}"/>
-    <hyperlink ref="C199" r:id="rId277" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
-    <hyperlink ref="C8" r:id="rId278" xr:uid="{B3656FCB-334A-C24F-B9FD-77A2E94511A7}"/>
-    <hyperlink ref="C266" r:id="rId279" xr:uid="{8B707DBA-5046-0842-8A9D-B479BE7B3F26}"/>
-    <hyperlink ref="C485" r:id="rId280" xr:uid="{F0689FA1-BCC1-394B-AED5-B9A03C77A143}"/>
-    <hyperlink ref="C434" r:id="rId281" xr:uid="{6636B7ED-934A-D247-B837-6E7A652A0F48}"/>
-    <hyperlink ref="C404" r:id="rId282" xr:uid="{27DBBE71-CF56-034F-A814-92AB6B007119}"/>
-    <hyperlink ref="C456" r:id="rId283" xr:uid="{65BB9F36-0658-5746-8674-E771C17EC4A1}"/>
-    <hyperlink ref="C3" r:id="rId284" xr:uid="{B66C9298-F7DC-4B4E-AAB0-9EE8349C9F1C}"/>
-    <hyperlink ref="C9" r:id="rId285" xr:uid="{DC4D060D-57F7-0C44-9224-72CA0BA78162}"/>
-    <hyperlink ref="C28" r:id="rId286" xr:uid="{19CEABC1-E5BB-1049-854F-4E4315DD70A2}"/>
-    <hyperlink ref="C56" r:id="rId287" xr:uid="{1129F233-886E-0347-8B47-BDD996C35B44}"/>
-    <hyperlink ref="C65" r:id="rId288" xr:uid="{A96B7428-3D4A-414C-9995-8100BEECE458}"/>
-    <hyperlink ref="C67" r:id="rId289" xr:uid="{FECE0575-F73F-D746-A3CE-71DF7934B388}"/>
-    <hyperlink ref="C74" r:id="rId290" xr:uid="{657BD4C3-2D96-9B47-A471-B244239DD853}"/>
-    <hyperlink ref="C77" r:id="rId291" xr:uid="{58F906BD-AF47-1343-A640-FB8B8AFE6CB3}"/>
-    <hyperlink ref="C83" r:id="rId292" xr:uid="{9BFBE007-F7AC-6041-91AA-2E092C5889AE}"/>
-    <hyperlink ref="C89" r:id="rId293" xr:uid="{A30C4013-413B-8D42-BAC8-5F7B86D6217F}"/>
-    <hyperlink ref="C95" r:id="rId294" xr:uid="{58C88071-C557-9B4B-97B3-9F31936BD74C}"/>
-    <hyperlink ref="C100" r:id="rId295" xr:uid="{276EB430-6D90-704D-9856-7A6A61E5AB2C}"/>
-    <hyperlink ref="C102" r:id="rId296" xr:uid="{9C4D1BAB-C120-D14A-9FEC-20B44CEB0B0B}"/>
-    <hyperlink ref="C109" r:id="rId297" xr:uid="{AF5E2383-18ED-654D-9534-4295996FF71D}"/>
-    <hyperlink ref="C116" r:id="rId298" xr:uid="{164AC784-B3B0-9A42-801B-D575E4F153C6}"/>
-    <hyperlink ref="C124" r:id="rId299" xr:uid="{74727307-BEC7-714F-BE5C-D8A88C067061}"/>
-    <hyperlink ref="C138" r:id="rId300" xr:uid="{91E7416E-8FE1-1244-991D-5E7EA4523271}"/>
-    <hyperlink ref="C151" r:id="rId301" xr:uid="{F5855752-0067-434F-B581-AC509D84E5F7}"/>
-    <hyperlink ref="C168" r:id="rId302" xr:uid="{15F4585C-652B-4646-986A-D0C6B92DB0E6}"/>
-    <hyperlink ref="C202" r:id="rId303" xr:uid="{8487DBCA-37E8-1D46-8394-F590FF6C3BA2}"/>
-    <hyperlink ref="C203" r:id="rId304" xr:uid="{8B0E6A00-A4D8-9549-8787-9334D5B92213}"/>
-    <hyperlink ref="C211" r:id="rId305" xr:uid="{BB4B1121-4934-8741-B17D-48788F26E92E}"/>
-    <hyperlink ref="C225" r:id="rId306" xr:uid="{218C8E15-4075-DF49-BFC8-33F08FEC50F3}"/>
-    <hyperlink ref="C241" r:id="rId307" xr:uid="{4301457D-4E25-7542-93C5-027338F1D2B2}"/>
-    <hyperlink ref="C259" r:id="rId308" xr:uid="{680D9EEC-16E5-3B4A-B688-B33AF37A692D}"/>
-    <hyperlink ref="C270" r:id="rId309" xr:uid="{671017B4-77FF-3347-AC04-A4122C6916A4}"/>
-    <hyperlink ref="C271" r:id="rId310" xr:uid="{8590D42C-0863-0D49-A719-5A07EDA84FF0}"/>
-    <hyperlink ref="C273" r:id="rId311" xr:uid="{03DAECCF-1AE9-8F46-AEFA-C16A52E668ED}"/>
-    <hyperlink ref="C288" r:id="rId312" xr:uid="{FC0990AE-18E8-984C-8C4D-C6A8E1965611}"/>
-    <hyperlink ref="C301" r:id="rId313" xr:uid="{B5AFB92E-F996-7D41-9218-E7E3A4AD8026}"/>
-    <hyperlink ref="C304" r:id="rId314" xr:uid="{7226970B-3FF3-7047-84C7-81709CA5D489}"/>
-    <hyperlink ref="C307" r:id="rId315" xr:uid="{1B6F9686-012A-DD4E-BB4E-8E888DBAEAB0}"/>
-    <hyperlink ref="C317" r:id="rId316" xr:uid="{8752026B-80F6-4645-B379-B554AFF4328A}"/>
-    <hyperlink ref="C319" r:id="rId317" xr:uid="{25CF3685-CB6B-8748-897A-6BE39EB03C9D}"/>
-    <hyperlink ref="C343" r:id="rId318" xr:uid="{605B8DE6-6D4C-3C4D-B742-6BF43B11FEB3}"/>
-    <hyperlink ref="C344" r:id="rId319" xr:uid="{733769E8-B4F6-C247-BA2A-DD7C49538D58}"/>
-    <hyperlink ref="C346" r:id="rId320" xr:uid="{A89D9334-EE69-7D44-823B-40BF7BDE29AC}"/>
-    <hyperlink ref="C350" r:id="rId321" xr:uid="{E35B3813-B3FE-624F-B860-F3939A5E4714}"/>
-    <hyperlink ref="C356" r:id="rId322" xr:uid="{9ADD1583-C4E5-FC43-92A1-350F8D5AFB1F}"/>
-    <hyperlink ref="C357" r:id="rId323" xr:uid="{F0B0FADF-CD27-C941-9383-4A9E5B8133D4}"/>
-    <hyperlink ref="C362" r:id="rId324" xr:uid="{A122F189-FBA6-DE4D-A439-2BAF817DEFD3}"/>
-    <hyperlink ref="C367" r:id="rId325" xr:uid="{FD9C23FC-6B71-D94B-BBAE-558A4EA50101}"/>
-    <hyperlink ref="C374" r:id="rId326" xr:uid="{3F7A41CA-92AE-C141-8080-9502E89F1145}"/>
-    <hyperlink ref="C375" r:id="rId327" xr:uid="{EB1E8EA3-E33F-7F41-B7F5-01B680514140}"/>
-    <hyperlink ref="C370" r:id="rId328" xr:uid="{59C6307C-F420-8946-94EA-C799AD4B7627}"/>
-    <hyperlink ref="C383" r:id="rId329" xr:uid="{F69EAF41-04CE-664B-A51A-EE01024DD2F2}"/>
-    <hyperlink ref="C393" r:id="rId330" xr:uid="{F7157600-6177-404F-8A14-CBADD4935D45}"/>
-    <hyperlink ref="C394" r:id="rId331" xr:uid="{E97356A3-FEB0-5348-81D9-D01C6B319AA3}"/>
-    <hyperlink ref="C407" r:id="rId332" xr:uid="{6763A48D-7B18-E649-886C-08D461F9C515}"/>
-    <hyperlink ref="C409" r:id="rId333" xr:uid="{FDF960AD-ED15-2749-AA75-EA51A85C1D97}"/>
-    <hyperlink ref="C424" r:id="rId334" xr:uid="{86E669FB-1204-5549-9E6B-B0F1D2D62AF8}"/>
-    <hyperlink ref="C457" r:id="rId335" xr:uid="{3CEF2BDF-D127-3D4E-8E2B-EE75CD438AB1}"/>
-    <hyperlink ref="C461" r:id="rId336" xr:uid="{C7C34AC7-D6F1-4147-8650-1947BBC9693A}"/>
-    <hyperlink ref="C481" r:id="rId337" xr:uid="{119B456E-EC3C-F844-A9AD-61D4D0D2AFC3}"/>
-    <hyperlink ref="C487" r:id="rId338" xr:uid="{7E211C4E-5E81-EF40-84F3-839C934125D6}"/>
-    <hyperlink ref="C488" r:id="rId339" xr:uid="{8F44069E-D100-9645-8AB2-4DB0E187F4B3}"/>
-    <hyperlink ref="C526" r:id="rId340" xr:uid="{BF5A6084-E948-3645-A67B-5D86F56ECA88}"/>
-    <hyperlink ref="C530" r:id="rId341" xr:uid="{5AAAF9CF-4460-B54B-88C3-4A48BF9440D1}"/>
-    <hyperlink ref="C547" r:id="rId342" xr:uid="{7FBAFA5F-205B-2047-B22D-48C7875A450E}"/>
+    <hyperlink ref="C282" r:id="rId247" xr:uid="{4DF4BC3F-5FEC-5241-A415-BA4D9AB2E9C4}"/>
+    <hyperlink ref="C276" r:id="rId248" xr:uid="{B4AAB667-FFFA-F64C-BC79-708CC2119E9B}"/>
+    <hyperlink ref="C284" r:id="rId249" xr:uid="{43C29840-1AC5-BD48-966B-C22652F605F3}"/>
+    <hyperlink ref="C311" r:id="rId250" xr:uid="{F4707F58-E802-4447-8605-F892FDA7CCF3}"/>
+    <hyperlink ref="C315" r:id="rId251" xr:uid="{6F202B6D-51F3-3D40-ACFD-F320AD483051}"/>
+    <hyperlink ref="C387" r:id="rId252" xr:uid="{F7FBCB2E-4711-C544-9815-FD10E00005DB}"/>
+    <hyperlink ref="C395" r:id="rId253" xr:uid="{C7781A41-89E3-2541-A4FA-5BF087F3142E}"/>
+    <hyperlink ref="C426" r:id="rId254" xr:uid="{C212FA9C-10DC-2F42-8D5D-EB52A99491C5}"/>
+    <hyperlink ref="C430" r:id="rId255" xr:uid="{A0B32A55-6210-CE4A-BCA3-0D2A05DAFFBB}"/>
+    <hyperlink ref="C443" r:id="rId256" xr:uid="{BC3C3FDC-FCEA-6D4A-8DBA-4B5AE9B46289}"/>
+    <hyperlink ref="C536" r:id="rId257" xr:uid="{9A44993A-AC34-6E44-89CE-089783013815}"/>
+    <hyperlink ref="C546" r:id="rId258" xr:uid="{824EA9FD-498D-6C41-8984-11E42AF76234}"/>
+    <hyperlink ref="C263" r:id="rId259" xr:uid="{AC776A1A-36C9-6A4A-A870-243A0ADDFB79}"/>
+    <hyperlink ref="C303" r:id="rId260" xr:uid="{8DDCB9EB-E30B-B64F-BA5D-64D285B20953}"/>
+    <hyperlink ref="C235" r:id="rId261" xr:uid="{3DD3F81F-9B00-6C41-B9BD-0B246E4511FC}"/>
+    <hyperlink ref="C309" r:id="rId262" xr:uid="{2653430D-3B53-3342-82F4-5C182DA7B834}"/>
+    <hyperlink ref="C181" r:id="rId263" xr:uid="{A86712C1-CF60-EC43-ACC0-2F9F008D6A13}"/>
+    <hyperlink ref="C47" r:id="rId264" xr:uid="{DEDBA11F-1236-FB46-9BF5-3341C3B4F82F}"/>
+    <hyperlink ref="C60" r:id="rId265" xr:uid="{A2CD9817-DB83-EB44-B2B9-3529BB5D6BE5}"/>
+    <hyperlink ref="C5" r:id="rId266" xr:uid="{7D5C79DD-2090-AE42-8950-23F80385F704}"/>
+    <hyperlink ref="C118" r:id="rId267" xr:uid="{6FC99DC1-4D16-F748-9C57-B02E3B5B7ACB}"/>
+    <hyperlink ref="C137" r:id="rId268" xr:uid="{ED9FF9E1-0C2B-0E44-A3EF-F61085E02321}"/>
+    <hyperlink ref="C228" r:id="rId269" xr:uid="{525BDD05-8A3F-424A-B398-414EBECB8EF0}"/>
+    <hyperlink ref="C419" r:id="rId270" xr:uid="{220744C9-5318-7F48-8555-FABFF8F9D26F}"/>
+    <hyperlink ref="C119" r:id="rId271" xr:uid="{B187C345-3CCA-7A42-A65B-9D24BD058186}"/>
+    <hyperlink ref="C133" r:id="rId272" xr:uid="{8CDF73E8-B690-9A45-811B-8EBDEC80D17B}"/>
+    <hyperlink ref="C92" r:id="rId273" xr:uid="{2F7AE097-DEF5-4146-A716-E70F95AD9CF2}"/>
+    <hyperlink ref="C291" r:id="rId274" xr:uid="{47C430DC-91D2-1440-9854-F4E2C65DA30F}"/>
+    <hyperlink ref="C199" r:id="rId275" xr:uid="{DAC017FB-0466-4033-933D-263056845BE4}"/>
+    <hyperlink ref="C8" r:id="rId276" xr:uid="{B3656FCB-334A-C24F-B9FD-77A2E94511A7}"/>
+    <hyperlink ref="C266" r:id="rId277" xr:uid="{8B707DBA-5046-0842-8A9D-B479BE7B3F26}"/>
+    <hyperlink ref="C485" r:id="rId278" xr:uid="{F0689FA1-BCC1-394B-AED5-B9A03C77A143}"/>
+    <hyperlink ref="C434" r:id="rId279" xr:uid="{6636B7ED-934A-D247-B837-6E7A652A0F48}"/>
+    <hyperlink ref="C404" r:id="rId280" xr:uid="{27DBBE71-CF56-034F-A814-92AB6B007119}"/>
+    <hyperlink ref="C456" r:id="rId281" xr:uid="{65BB9F36-0658-5746-8674-E771C17EC4A1}"/>
+    <hyperlink ref="C3" r:id="rId282" xr:uid="{B66C9298-F7DC-4B4E-AAB0-9EE8349C9F1C}"/>
+    <hyperlink ref="C9" r:id="rId283" xr:uid="{DC4D060D-57F7-0C44-9224-72CA0BA78162}"/>
+    <hyperlink ref="C28" r:id="rId284" xr:uid="{19CEABC1-E5BB-1049-854F-4E4315DD70A2}"/>
+    <hyperlink ref="C56" r:id="rId285" xr:uid="{1129F233-886E-0347-8B47-BDD996C35B44}"/>
+    <hyperlink ref="C65" r:id="rId286" xr:uid="{A96B7428-3D4A-414C-9995-8100BEECE458}"/>
+    <hyperlink ref="C67" r:id="rId287" xr:uid="{FECE0575-F73F-D746-A3CE-71DF7934B388}"/>
+    <hyperlink ref="C74" r:id="rId288" xr:uid="{657BD4C3-2D96-9B47-A471-B244239DD853}"/>
+    <hyperlink ref="C77" r:id="rId289" xr:uid="{58F906BD-AF47-1343-A640-FB8B8AFE6CB3}"/>
+    <hyperlink ref="C83" r:id="rId290" xr:uid="{9BFBE007-F7AC-6041-91AA-2E092C5889AE}"/>
+    <hyperlink ref="C89" r:id="rId291" xr:uid="{A30C4013-413B-8D42-BAC8-5F7B86D6217F}"/>
+    <hyperlink ref="C95" r:id="rId292" xr:uid="{58C88071-C557-9B4B-97B3-9F31936BD74C}"/>
+    <hyperlink ref="C100" r:id="rId293" xr:uid="{276EB430-6D90-704D-9856-7A6A61E5AB2C}"/>
+    <hyperlink ref="C102" r:id="rId294" xr:uid="{9C4D1BAB-C120-D14A-9FEC-20B44CEB0B0B}"/>
+    <hyperlink ref="C109" r:id="rId295" xr:uid="{AF5E2383-18ED-654D-9534-4295996FF71D}"/>
+    <hyperlink ref="C116" r:id="rId296" xr:uid="{164AC784-B3B0-9A42-801B-D575E4F153C6}"/>
+    <hyperlink ref="C124" r:id="rId297" xr:uid="{74727307-BEC7-714F-BE5C-D8A88C067061}"/>
+    <hyperlink ref="C138" r:id="rId298" xr:uid="{91E7416E-8FE1-1244-991D-5E7EA4523271}"/>
+    <hyperlink ref="C151" r:id="rId299" xr:uid="{F5855752-0067-434F-B581-AC509D84E5F7}"/>
+    <hyperlink ref="C168" r:id="rId300" xr:uid="{15F4585C-652B-4646-986A-D0C6B92DB0E6}"/>
+    <hyperlink ref="C202" r:id="rId301" xr:uid="{8487DBCA-37E8-1D46-8394-F590FF6C3BA2}"/>
+    <hyperlink ref="C203" r:id="rId302" xr:uid="{8B0E6A00-A4D8-9549-8787-9334D5B92213}"/>
+    <hyperlink ref="C211" r:id="rId303" xr:uid="{BB4B1121-4934-8741-B17D-48788F26E92E}"/>
+    <hyperlink ref="C225" r:id="rId304" xr:uid="{218C8E15-4075-DF49-BFC8-33F08FEC50F3}"/>
+    <hyperlink ref="C241" r:id="rId305" xr:uid="{4301457D-4E25-7542-93C5-027338F1D2B2}"/>
+    <hyperlink ref="C259" r:id="rId306" xr:uid="{680D9EEC-16E5-3B4A-B688-B33AF37A692D}"/>
+    <hyperlink ref="C270" r:id="rId307" xr:uid="{671017B4-77FF-3347-AC04-A4122C6916A4}"/>
+    <hyperlink ref="C271" r:id="rId308" xr:uid="{8590D42C-0863-0D49-A719-5A07EDA84FF0}"/>
+    <hyperlink ref="C273" r:id="rId309" xr:uid="{03DAECCF-1AE9-8F46-AEFA-C16A52E668ED}"/>
+    <hyperlink ref="C288" r:id="rId310" xr:uid="{FC0990AE-18E8-984C-8C4D-C6A8E1965611}"/>
+    <hyperlink ref="C301" r:id="rId311" xr:uid="{B5AFB92E-F996-7D41-9218-E7E3A4AD8026}"/>
+    <hyperlink ref="C304" r:id="rId312" xr:uid="{7226970B-3FF3-7047-84C7-81709CA5D489}"/>
+    <hyperlink ref="C307" r:id="rId313" xr:uid="{1B6F9686-012A-DD4E-BB4E-8E888DBAEAB0}"/>
+    <hyperlink ref="C317" r:id="rId314" xr:uid="{8752026B-80F6-4645-B379-B554AFF4328A}"/>
+    <hyperlink ref="C319" r:id="rId315" xr:uid="{25CF3685-CB6B-8748-897A-6BE39EB03C9D}"/>
+    <hyperlink ref="C343" r:id="rId316" xr:uid="{605B8DE6-6D4C-3C4D-B742-6BF43B11FEB3}"/>
+    <hyperlink ref="C344" r:id="rId317" xr:uid="{733769E8-B4F6-C247-BA2A-DD7C49538D58}"/>
+    <hyperlink ref="C346" r:id="rId318" xr:uid="{A89D9334-EE69-7D44-823B-40BF7BDE29AC}"/>
+    <hyperlink ref="C350" r:id="rId319" xr:uid="{E35B3813-B3FE-624F-B860-F3939A5E4714}"/>
+    <hyperlink ref="C356" r:id="rId320" xr:uid="{9ADD1583-C4E5-FC43-92A1-350F8D5AFB1F}"/>
+    <hyperlink ref="C357" r:id="rId321" xr:uid="{F0B0FADF-CD27-C941-9383-4A9E5B8133D4}"/>
+    <hyperlink ref="C362" r:id="rId322" xr:uid="{A122F189-FBA6-DE4D-A439-2BAF817DEFD3}"/>
+    <hyperlink ref="C367" r:id="rId323" xr:uid="{FD9C23FC-6B71-D94B-BBAE-558A4EA50101}"/>
+    <hyperlink ref="C374" r:id="rId324" xr:uid="{3F7A41CA-92AE-C141-8080-9502E89F1145}"/>
+    <hyperlink ref="C375" r:id="rId325" xr:uid="{EB1E8EA3-E33F-7F41-B7F5-01B680514140}"/>
+    <hyperlink ref="C370" r:id="rId326" xr:uid="{59C6307C-F420-8946-94EA-C799AD4B7627}"/>
+    <hyperlink ref="C383" r:id="rId327" xr:uid="{F69EAF41-04CE-664B-A51A-EE01024DD2F2}"/>
+    <hyperlink ref="C393" r:id="rId328" xr:uid="{F7157600-6177-404F-8A14-CBADD4935D45}"/>
+    <hyperlink ref="C394" r:id="rId329" xr:uid="{E97356A3-FEB0-5348-81D9-D01C6B319AA3}"/>
+    <hyperlink ref="C407" r:id="rId330" xr:uid="{6763A48D-7B18-E649-886C-08D461F9C515}"/>
+    <hyperlink ref="C409" r:id="rId331" xr:uid="{FDF960AD-ED15-2749-AA75-EA51A85C1D97}"/>
+    <hyperlink ref="C424" r:id="rId332" xr:uid="{86E669FB-1204-5549-9E6B-B0F1D2D62AF8}"/>
+    <hyperlink ref="C457" r:id="rId333" xr:uid="{3CEF2BDF-D127-3D4E-8E2B-EE75CD438AB1}"/>
+    <hyperlink ref="C461" r:id="rId334" xr:uid="{C7C34AC7-D6F1-4147-8650-1947BBC9693A}"/>
+    <hyperlink ref="C481" r:id="rId335" xr:uid="{119B456E-EC3C-F844-A9AD-61D4D0D2AFC3}"/>
+    <hyperlink ref="C487" r:id="rId336" xr:uid="{7E211C4E-5E81-EF40-84F3-839C934125D6}"/>
+    <hyperlink ref="C488" r:id="rId337" xr:uid="{8F44069E-D100-9645-8AB2-4DB0E187F4B3}"/>
+    <hyperlink ref="C526" r:id="rId338" xr:uid="{BF5A6084-E948-3645-A67B-5D86F56ECA88}"/>
+    <hyperlink ref="C530" r:id="rId339" xr:uid="{5AAAF9CF-4460-B54B-88C3-4A48BF9440D1}"/>
+    <hyperlink ref="C547" r:id="rId340" xr:uid="{7FBAFA5F-205B-2047-B22D-48C7875A450E}"/>
+    <hyperlink ref="C338" r:id="rId341" xr:uid="{20FF35A0-9072-C349-94BD-F07C44AE26C4}"/>
+    <hyperlink ref="C503" r:id="rId342" xr:uid="{494AF78A-1E67-9744-B143-9F0F78B10E88}"/>
+    <hyperlink ref="C287" r:id="rId343" xr:uid="{C9BBF0C7-EF54-7043-A3FA-B4E339DB0706}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId343"/>
+    <tablePart r:id="rId344"/>
   </tableParts>
 </worksheet>
 </file>
